--- a/data/global/2026-05-week04/titles.xlsx
+++ b/data/global/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L216"/>
+  <dimension ref="A1:L199"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קובי צור - לאן קאבר</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-21</v>
+        <v>5 days ago</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410986&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-22</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קובי צור - לאן קאבר</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>צביקה חי - עטלף עיוור קאבר</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-21</v>
+        <v>5 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410985&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-22</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>צביקה חי - עטלף עיוור קאבר</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>עפרה &amp; עידן עינב - ירושלים של זהב קאבר</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-21</v>
+        <v>5 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410984&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-22</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>עפרה &amp; עידן עינב - ירושלים של זהב קאבר</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>עמיחי שרעבי - לב לבן קאבר</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-21</v>
+        <v>5 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410983&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-22</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>עמיחי שרעבי - לב לבן קאבר</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>נוריאל פיאמנטה - עיניים עצובות קאבר</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-05-21</v>
+        <v>5 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410982&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-22</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>נוריאל פיאמנטה - עיניים עצובות קאבר</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>מתנאל סבח - בית מזכוכית קאבר</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-05-21</v>
+        <v>5 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410981&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-22</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>מתנאל סבח - בית מזכוכית קאבר</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>מתן סממה - נווה הדרים קאבר</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-05-21</v>
+        <v>6 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410980&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-22</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>Evanescence</v>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>מתן סממה - נווה הדרים קאבר</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>מירב ארז - מונו קאבר</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-05-21</v>
+        <v>9 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410979&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-22</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>9 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I9" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>מירב ארז - מונו קאבר</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>מאי היגאני - עיניים עצובות קאבר</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-05-21</v>
+        <v>5 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410978&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-22</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I10" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>מאי היגאני - עיניים עצובות קאבר</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ליאור לוי - נדלקתי נערה קאבר</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-05-21</v>
+        <v>5 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410977&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-22</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I11" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>ליאור לוי - נדלקתי נערה קאבר</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>יוסף חיים - עיניים עצובות קאבר</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-05-21</v>
+        <v>6 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410976&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-22</v>
@@ -831,16 +831,16 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I12" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>יוסף חיים - עיניים עצובות קאבר</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>טל לוי &amp; ברטין - חלף הגעגוע קאבר</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-05-21</v>
+        <v>6 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410975&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-22</v>
@@ -869,16 +869,16 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>Carver Jones</v>
       </c>
       <c r="I13" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>טל לוי &amp; ברטין - חלף הגעגוע קאבר</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>חיים דדון - עיניים עצובות קאבר</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-05-21</v>
+        <v>6 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410974&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-22</v>
@@ -907,16 +907,16 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>Jazmin bean</v>
       </c>
       <c r="I14" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>חיים דדון - עיניים עצובות קאבר</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>דליה מזרחי - נפש תאומה קאבר</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-05-21</v>
+        <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410973&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-22</v>
@@ -945,16 +945,16 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>Baby Queen</v>
       </c>
       <c r="I15" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>דליה מזרחי - נפש תאומה קאבר</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>אליאור נונה - סיגליות קאבר</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-05-21</v>
+        <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410972&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-22</v>
@@ -983,16 +983,16 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>Switchfoot</v>
       </c>
       <c r="I16" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>אליאור נונה - סיגליות קאבר</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>אורית יצחק - חי קאבר</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-05-21</v>
+        <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410971&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-22</v>
@@ -1021,16 +1021,16 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>Grace Potter</v>
       </c>
       <c r="I17" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>אורית יצחק - חי קאבר</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>אורי ראובני - עוד ישמע קאבר</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-05-21</v>
+        <v>7 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410970&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-22</v>
@@ -1059,16 +1059,16 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>7 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I18" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>אורי ראובני - עוד ישמע קאבר</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-22</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B20" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-22</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-22</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-22</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B23" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-22</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-22</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-22</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Evanescence</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-22</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>VALÉ</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B27" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-22</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Armin van Buuren</v>
+        <v>Mackenzie Carpenter</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-22</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Madison Cunningham</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-22</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Johnny Orlando</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-22</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Carver Jones</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-22</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Jazmin bean</v>
+        <v>Becky G</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Becky G - EPA (Official Video) - Becky G</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-22</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Baby Queen</v>
+        <v>Daisy the Great</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-22</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Switchfoot</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-22</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Grace Potter</v>
+        <v>Madonna</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-22</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-22</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>The All-American Rejects</v>
+        <v>Bella White</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Bella White - Better - Official Music Video - Bella White</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-22</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Henry Moodie</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B38" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-22</v>
@@ -1825,7 +1825,7 @@
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Spacey Jane</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B39" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-22</v>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Megan Moroney</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B40" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-22</v>
@@ -1901,7 +1901,7 @@
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Matt Hansen</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B41" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
+        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-22</v>
@@ -1939,7 +1939,7 @@
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Matt Hansen</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Keith Urban - Steal Away (Visualizer)</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B42" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
+        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-22</v>
@@ -1977,7 +1977,7 @@
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Keith Urban</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>VALÉ - Mugshot (Official Video)</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B43" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
+        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-22</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>VALÉ</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio)</v>
+        <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B44" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
+        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-22</v>
@@ -2053,7 +2053,7 @@
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Mackenzie Carpenter</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
+        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
+        <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
+        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-22</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Towa Bird</v>
+        <v>LP</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
+        <v>LP - Shelly (Official Music Video) - LP</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
+        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-22</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Sabrina Sterling</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B47" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
+        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-22</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Little Big Town</v>
+        <v>Oasis</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Becky G - EPA (Official Video)</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
+        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-22</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Becky G</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Becky G - EPA (Official Video) - Becky G</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B49" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
+        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-22</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Daisy the Great</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Towa Bird - Dog (Official Music Video)</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
+        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-22</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Towa Bird</v>
+        <v>Linkin Park</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
+        <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
+        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-22</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Madonna</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
+        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video)</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
+        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-22</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Ally Salort</v>
+        <v>Eagles</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Bella White - Better - Official Music Video</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B53" t="str">
-        <v>7 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
+        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-22</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>7 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Bella White</v>
+        <v>Nora Fatehi</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Bella White - Better - Official Music Video - Bella White</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B54" t="str">
-        <v>7 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
+        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-22</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>7 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B55" t="str">
-        <v>7 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
+        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-22</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>7 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Towa Bird</v>
+        <v>Eurovision Song Contest and Alis</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer)</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B56" t="str">
-        <v>7 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
+        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-22</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>7 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Miranda Lambert</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
+        <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
+        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-22</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Lady Gaga</v>
+        <v>The Head And The Heart</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
+        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B58" t="str">
-        <v>7 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
+        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-22</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>7 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Gracie Abrams</v>
+        <v>Simply Red</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
+        <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>7 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
+        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-22</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>7 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Talking Heads</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
+        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
+        <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
+        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-22</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Martin Garrix</v>
+        <v>Ellise</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
+        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Jorja Smith - What's Done Is Done</v>
+        <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
+        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-22</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Jorja Smith</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
+        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>LP - Shelly (Official Music Video)</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B62" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
+        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-22</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>LP</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>LP - Shelly (Official Music Video) - LP</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B63" t="str">
-        <v>8 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
+        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-22</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>The Rolling Stones</v>
+        <v>Scorpions</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>8 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
+        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-22</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Oasis</v>
+        <v>Claire Leslie</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
+        <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>9 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
+        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-22</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>9 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Breaking Benjamin</v>
+        <v>Michael Schulte</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
+        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
+        <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
+        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-22</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>VictorBiliac</v>
+        <v>Caity Baser</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
+        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B67" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
+        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-22</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Linkin Park</v>
+        <v>Sam Fischer</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Harry Styles - Dance No More (Official Video)</v>
+        <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
+        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-22</v>
@@ -2965,7 +2965,7 @@
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Harry Styles</v>
+        <v>Porches</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
+        <v>Porches- HABIT (Official Video) - Porches</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
+        <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
+        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-22</v>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Eagles</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
+        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
+        <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B70" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
+        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-22</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Nora Fatehi</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
+        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
+        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-22</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Tigirlily Gold</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
+        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-22</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Eurovision Song Contest and Alis</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B73" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
+        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-22</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video)</v>
+        <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
+        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-22</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>The Head And The Heart</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
+        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
+        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-22</v>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Simply Red</v>
+        <v>bea miller</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video)</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B76" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
+        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-22</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Talking Heads</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Ellise - Liplock (Official Music Video)</v>
+        <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B77" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
+        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-22</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Ellise</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
+        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Tori Kelly - Dive (Official Music Video)</v>
+        <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B78" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
+        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-22</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
+        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
+        <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B79" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
+        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-22</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>David Gilmour</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
+        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B80" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
+        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-22</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Scorpions</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
+        <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B81" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
+        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-22</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Claire Leslie</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
+        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Michael Schulte - Lovesick (Official Video)</v>
+        <v>Ari Abdul - Ego (Visualizer)</v>
       </c>
       <c r="B82" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
+        <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-22</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Michael Schulte</v>
+        <v>Ari Abdul</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
+        <v>Ari Abdul - Ego (Visualizer) - Ari Abdul</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Caity Baser - Holiday Song (Official Video)</v>
+        <v>Quinn XCII - HOOPLA (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
+        <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-22</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Caity Baser</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
+        <v>Quinn XCII - HOOPLA (Official Music Video) - Quinn XCII</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
+        <v>Madison Beer - lovergirl (Official Music Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
+        <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-22</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Sam Fischer</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
+        <v>Madison Beer - lovergirl (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Porches- HABIT (Official Video)</v>
+        <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
+        <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-22</v>
@@ -3611,7 +3611,7 @@
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Porches</v>
+        <v>David J</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Porches- HABIT (Official Video) - Porches</v>
+        <v>David J - WHAT IF I'M IN LOVE (Official Video) - David J</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Charli xcx - Rock Music (Official Video)</v>
+        <v>The Last Dinner Party - Big Dog (On The Road)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
+        <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-22</v>
@@ -3649,7 +3649,7 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Charli xcx</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
+        <v>The Last Dinner Party - Big Dog (On The Road) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Jon Batiste - Alla Blues (Audio)</v>
+        <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
+        <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-22</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Jon Batiste</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
+        <v>OCEAN ALLEY - HOLD ON (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
+        <v>Dagny - Closet Disco Queen (Lyric Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
+        <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-22</v>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Tigirlily Gold</v>
+        <v>Dagny</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
+        <v>Dagny - Closet Disco Queen (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
+        <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
+        <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-22</v>
@@ -3763,7 +3763,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Purple Disco Machine - Disco Cherry (Official Video) - Purple Disco Machine</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
+        <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
+        <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-22</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Bruno Mars</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
+        <v>Paris Paloma - Stem the Flow [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Tori Kelly - Control (Official Visualizer)</v>
+        <v>Lucy Blue - Who you love (Visualiser)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
+        <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-22</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Tori Kelly</v>
+        <v>Lucy Blue</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
+        <v>Lucy Blue - Who you love (Visualiser) - Lucy Blue</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
+        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
+        <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-22</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>bea miller</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
+        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026) - Olivia Dean</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
+        <v>Aaron Frazer - It's A Shame (Official Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
+        <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-22</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>The Chainsmokers</v>
+        <v>Aaron Frazer</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
+        <v>Aaron Frazer - It's A Shame (Official Video) - Aaron Frazer</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Madison Beer - free (Official Audio)</v>
+        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
+        <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-22</v>
@@ -3953,7 +3953,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Madison Beer</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
+        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Tori Kelly - Dive (Official Audio)</v>
+        <v>DANNA - OUT OF MY BODY</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
+        <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-22</v>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Tori Kelly</v>
+        <v>Danna</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
+        <v>DANNA - OUT OF MY BODY - Danna</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio)</v>
+        <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
+        <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-22</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>JeremyCampMusic</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
+        <v>The Rolling Stones - In The Stars (Official Lyric Video) - The Rolling Stones</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
+        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
+        <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-22</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>The Chainsmokers</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
+        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Ashley Cooke - high school sweetheart</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
+        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-22</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Ashley Cooke</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Ari Abdul - Ego (Visualizer)</v>
+        <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
+        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-22</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Ari Abdul</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Ari Abdul - Ego (Visualizer) - Ari Abdul</v>
+        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Quinn XCII - HOOPLA (Official Music Video)</v>
+        <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
+        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-22</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Quinn XCII</v>
+        <v>Jessie J</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Quinn XCII - HOOPLA (Official Music Video) - Quinn XCII</v>
+        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Madison Beer - lovergirl (Official Music Video)</v>
+        <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
+        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-22</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Madison Beer</v>
+        <v>The Takes</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Madison Beer - lovergirl (Official Music Video) - Madison Beer</v>
+        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
+        <v>From Down Here</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
+        <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-22</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>From Down Here - Single</v>
       </c>
       <c r="G102" t="str">
-        <v/>
+        <v>4:01</v>
       </c>
       <c r="H102" t="str">
-        <v>David J</v>
+        <v>Lola Young</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/lola-young/452271760</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/from-down-here/6768357139</v>
       </c>
       <c r="L102" t="str">
-        <v>David J - WHAT IF I'M IN LOVE (Official Video) - David J</v>
+        <v>From Down Here - Lola Young</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>The Last Dinner Party - Big Dog (On The Road)</v>
+        <v>the cure</v>
       </c>
       <c r="B103" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
+        <v>https://music.apple.com/us/song/the-cure/1889992123</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-22</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>2 weeks ago</v>
+        <v>you seem pretty sad for a girl so in love</v>
       </c>
       <c r="G103" t="str">
-        <v/>
+        <v>4:57</v>
       </c>
       <c r="H103" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/the-cure/1889992111</v>
       </c>
       <c r="L103" t="str">
-        <v>The Last Dinner Party - Big Dog (On The Road) - The Last Dinner Party</v>
+        <v>the cure - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
+        <v>SS26</v>
       </c>
       <c r="B104" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
+        <v>https://music.apple.com/us/song/ss26/6771061782</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-22</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>2 weeks ago</v>
+        <v>SS26 - Single</v>
       </c>
       <c r="G104" t="str">
-        <v/>
+        <v>2:47</v>
       </c>
       <c r="H104" t="str">
-        <v>Ocean Alley</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/ss26/6771061771</v>
       </c>
       <c r="L104" t="str">
-        <v>OCEAN ALLEY - HOLD ON (Official Video) - Ocean Alley</v>
+        <v>SS26 - Charli xcx</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Dagny - Closet Disco Queen (Lyric Video)</v>
+        <v>White Flag</v>
       </c>
       <c r="B105" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
+        <v>https://music.apple.com/us/song/white-flag/1887627840</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-22</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>2 weeks ago</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G105" t="str">
-        <v/>
+        <v>2:34</v>
       </c>
       <c r="H105" t="str">
-        <v>Dagny</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/white-flag/1887627836</v>
       </c>
       <c r="L105" t="str">
-        <v>Dagny - Closet Disco Queen (Lyric Video) - Dagny</v>
+        <v>White Flag - Vince Staples</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
+        <v>Knew Better Part Two</v>
       </c>
       <c r="B106" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
+        <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-22</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>2 weeks ago</v>
+        <v>Dangerous Woman (Tenth Anniversary Edition)</v>
       </c>
       <c r="G106" t="str">
-        <v/>
+        <v>2:44</v>
       </c>
       <c r="H106" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/knew-better-part-two/6770600996</v>
       </c>
       <c r="L106" t="str">
-        <v>Purple Disco Machine - Disco Cherry (Official Video) - Purple Disco Machine</v>
+        <v>Knew Better Part Two - Ariana Grande</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
+        <v>Goals</v>
       </c>
       <c r="B107" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
+        <v>https://music.apple.com/us/song/goals/6769251838</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-22</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>2 weeks ago</v>
+        <v>Goals (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G107" t="str">
-        <v/>
+        <v>3:00</v>
       </c>
       <c r="H107" t="str">
-        <v>Paris Paloma</v>
+        <v>LISA</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/lisa/1583908668</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/goals/6769251829</v>
       </c>
       <c r="L107" t="str">
-        <v>Paris Paloma - Stem the Flow [Official Music Video] - Paris Paloma</v>
+        <v>Goals - LISA</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Lucy Blue - Who you love (Visualiser)</v>
+        <v>we should talk</v>
       </c>
       <c r="B108" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
+        <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-22</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>2 weeks ago</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G108" t="str">
-        <v/>
+        <v>3:04</v>
       </c>
       <c r="H108" t="str">
-        <v>Lucy Blue</v>
+        <v>Bleachers</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/we-should-talk/1872842313</v>
       </c>
       <c r="L108" t="str">
-        <v>Lucy Blue - Who you love (Visualiser) - Lucy Blue</v>
+        <v>we should talk - Bleachers</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
+        <v>Do What You Gotta Do</v>
       </c>
       <c r="B109" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
+        <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-22</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>2 weeks ago</v>
+        <v>NeverAlways (Vol. 2)</v>
       </c>
       <c r="G109" t="str">
-        <v/>
+        <v>3:26</v>
       </c>
       <c r="H109" t="str">
-        <v>Olivia Dean</v>
+        <v>The Band CAMINO</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/do-what-you-gotta-do/1887616173</v>
       </c>
       <c r="L109" t="str">
-        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026) - Olivia Dean</v>
+        <v>Do What You Gotta Do - The Band CAMINO</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Aaron Frazer - It's A Shame (Official Video)</v>
+        <v>Ego</v>
       </c>
       <c r="B110" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
+        <v>https://music.apple.com/us/song/ego/6769207667</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-22</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>2 weeks ago</v>
+        <v>Ego - Single</v>
       </c>
       <c r="G110" t="str">
-        <v/>
+        <v>2:53</v>
       </c>
       <c r="H110" t="str">
-        <v>Aaron Frazer</v>
+        <v>The Warning</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/ego/6769207665</v>
       </c>
       <c r="L110" t="str">
-        <v>Aaron Frazer - It's A Shame (Official Video) - Aaron Frazer</v>
+        <v>Ego - The Warning</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
+        <v>Light up (From the Netflix Documentary 'kylie')</v>
       </c>
       <c r="B111" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
+        <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-22</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>2 weeks ago</v>
+        <v>Light up (From the Netflix Documentary 'Kylie') - Single</v>
       </c>
       <c r="G111" t="str">
-        <v/>
+        <v>3:17</v>
       </c>
       <c r="H111" t="str">
-        <v>Holly Humberstone</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/kylie-minogue/465031</v>
       </c>
       <c r="K111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/light-up-from-the-netflix-documentary-kylie/6768013505</v>
       </c>
       <c r="L111" t="str">
-        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>Light up (From the Netflix Documentary 'kylie') - Kylie Minogue</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>DANNA - OUT OF MY BODY</v>
+        <v>All That Matters</v>
       </c>
       <c r="B112" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
+        <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-22</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>2 weeks ago</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G112" t="str">
-        <v/>
+        <v>3:43</v>
       </c>
       <c r="H112" t="str">
-        <v>Danna</v>
+        <v>6LACK</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/all-that-matters/1884792154</v>
       </c>
       <c r="L112" t="str">
-        <v>DANNA - OUT OF MY BODY - Danna</v>
+        <v>All That Matters - 6LACK</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
+        <v>Like A Virgin</v>
       </c>
       <c r="B113" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
+        <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-22</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>2 weeks ago</v>
+        <v>Terrified .</v>
       </c>
       <c r="G113" t="str">
-        <v/>
+        <v>2:34</v>
       </c>
       <c r="H113" t="str">
-        <v>The Rolling Stones</v>
+        <v>fakemink</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/like-a-virgin/6768157748</v>
       </c>
       <c r="L113" t="str">
-        <v>The Rolling Stones - In The Stars (Official Lyric Video) - The Rolling Stones</v>
+        <v>Like A Virgin - fakemink</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
+        <v>24 Hours</v>
       </c>
       <c r="B114" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
+        <v>https://music.apple.com/us/song/24-hours/6771060076</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-22</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>2 weeks ago</v>
+        <v>24 Hours - Single</v>
       </c>
       <c r="G114" t="str">
-        <v/>
+        <v>3:17</v>
       </c>
       <c r="H114" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Stormzy</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/stormzy/394865154</v>
       </c>
       <c r="K114" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/24-hours/6771060073</v>
       </c>
       <c r="L114" t="str">
-        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser) - Dermot Kennedy</v>
+        <v>24 Hours - Stormzy</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
+        <v>HOES (From Scary Movie)</v>
       </c>
       <c r="B115" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
+        <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-22</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>3 weeks ago</v>
+        <v>HOES (From Scary Movie) - Single</v>
       </c>
       <c r="G115" t="str">
-        <v/>
+        <v>2:09</v>
       </c>
       <c r="H115" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Lizzo</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K115" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/hoes-from-scary-movie/6770661290</v>
       </c>
       <c r="L115" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
+        <v>HOES (From Scary Movie) - Lizzo</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Rick Astley - Raindrops (Official Video)</v>
+        <v>Ms. Tundra</v>
       </c>
       <c r="B116" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
+        <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-22</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>2 weeks ago</v>
+        <v>Highway 79</v>
       </c>
       <c r="G116" t="str">
-        <v/>
+        <v>3:12</v>
       </c>
       <c r="H116" t="str">
-        <v>Rick Astley</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K116" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/ms-tundra/6770614875</v>
       </c>
       <c r="L116" t="str">
-        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
+        <v>Ms. Tundra - Ne-Yo</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video)</v>
+        <v>TARENTINO</v>
       </c>
       <c r="B117" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
+        <v>https://music.apple.com/us/song/tarentino/6769927265</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-22</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>2 weeks ago</v>
+        <v>TARENTINO - Single</v>
       </c>
       <c r="G117" t="str">
-        <v/>
+        <v>2:23</v>
       </c>
       <c r="H117" t="str">
-        <v>Jessie J</v>
+        <v>Labrinth</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K117" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/tarentino/6769927262</v>
       </c>
       <c r="L117" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
+        <v>TARENTINO - Labrinth</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>The Takes - Ain't Love (Lyric Video)</v>
+        <v>Daydreamin’</v>
       </c>
       <c r="B118" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
+        <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-22</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>2 weeks ago</v>
+        <v>KONNAKOL (Deluxe)</v>
       </c>
       <c r="G118" t="str">
-        <v/>
+        <v>2:58</v>
       </c>
       <c r="H118" t="str">
-        <v>The Takes</v>
+        <v>ZAYN</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K118" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/daydreamin/6769559345</v>
       </c>
       <c r="L118" t="str">
-        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
+        <v>Daydreamin’ - ZAYN</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>From Down Here</v>
+        <v>End of an Era</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
+        <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-22</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>From Down Here - Single</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G119" t="str">
-        <v>4:01</v>
+        <v>3:38</v>
       </c>
       <c r="H119" t="str">
-        <v>Lola Young</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/lola-young/452271760</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/from-down-here/6768357139</v>
+        <v>https://music.apple.com/us/album/end-of-an-era/1884418567</v>
       </c>
       <c r="L119" t="str">
-        <v>From Down Here - Lola Young</v>
+        <v>End of an Era - Niall Horan</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>the cure</v>
+        <v>Questions</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/the-cure/1889992123</v>
+        <v>https://music.apple.com/us/song/questions/1871502847</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-22</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>you seem pretty sad for a girl so in love</v>
+        <v>Florescence</v>
       </c>
       <c r="G120" t="str">
-        <v>4:57</v>
+        <v>3:07</v>
       </c>
       <c r="H120" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/the-cure/1889992111</v>
+        <v>https://music.apple.com/us/album/questions/1871502372</v>
       </c>
       <c r="L120" t="str">
-        <v>the cure - Olivia Rodrigo</v>
+        <v>Questions - Maisie Peters</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>SS26</v>
+        <v>Heart Has To Work So Hard</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/ss26/6771061782</v>
+        <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-22</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>SS26 - Single</v>
+        <v>Heart Has To Work So Hard - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:47</v>
+        <v>3:12</v>
       </c>
       <c r="H121" t="str">
-        <v>Charli xcx</v>
+        <v>Blondshell</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v>https://music.apple.com/us/artist/blondshell/1624592688</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/ss26/6771061771</v>
+        <v>https://music.apple.com/us/album/heart-has-to-work-so-hard/1895982147</v>
       </c>
       <c r="L121" t="str">
-        <v>SS26 - Charli xcx</v>
+        <v>Heart Has To Work So Hard - Blondshell</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>White Flag</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/white-flag/1887627840</v>
+        <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-22</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Cry Baby</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski) - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:34</v>
+        <v>3:44</v>
       </c>
       <c r="H122" t="str">
-        <v>Vince Staples</v>
+        <v>Kygo</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/white-flag/1887627836</v>
+        <v>https://music.apple.com/us/album/heaven-on-your-mind-feat-dan-tyminski/6769007431</v>
       </c>
       <c r="L122" t="str">
-        <v>White Flag - Vince Staples</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski) - Kygo</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Knew Better Part Two</v>
+        <v>PERDISTE EL EMMY.</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
+        <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-22</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Dangerous Woman (Tenth Anniversary Edition)</v>
+        <v>OMAKASE</v>
       </c>
       <c r="G123" t="str">
-        <v>2:44</v>
+        <v>4:03</v>
       </c>
       <c r="H123" t="str">
-        <v>Ariana Grande</v>
+        <v>Álvaro Díaz</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/knew-better-part-two/6770600996</v>
+        <v>https://music.apple.com/us/album/perdiste-el-emmy/6771082594</v>
       </c>
       <c r="L123" t="str">
-        <v>Knew Better Part Two - Ariana Grande</v>
+        <v>PERDISTE EL EMMY. - Álvaro Díaz</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Goals</v>
+        <v>Dosis</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/goals/6769251838</v>
+        <v>https://music.apple.com/us/song/dosis/6762929729</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-22</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Goals (FIFA World Cup 2026™) - Single</v>
+        <v>DOSIS</v>
       </c>
       <c r="G124" t="str">
         <v>3:00</v>
       </c>
       <c r="H124" t="str">
-        <v>LISA</v>
+        <v>Xavi</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/lisa/1583908668</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/goals/6769251829</v>
+        <v>https://music.apple.com/us/album/dosis/1895081885</v>
       </c>
       <c r="L124" t="str">
-        <v>Goals - LISA</v>
+        <v>Dosis - Xavi</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>we should talk</v>
+        <v>Would U Still Love Me</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
+        <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-22</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Whitcomb vs. Flores - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:04</v>
+        <v>2:36</v>
       </c>
       <c r="H125" t="str">
-        <v>Bleachers</v>
+        <v>Diplo</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/we-should-talk/1872842313</v>
+        <v>https://music.apple.com/us/album/would-u-still-love-me/6769907832</v>
       </c>
       <c r="L125" t="str">
-        <v>we should talk - Bleachers</v>
+        <v>Would U Still Love Me - Diplo</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Do What You Gotta Do</v>
+        <v>Saving This Bottle</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
+        <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-22</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>NeverAlways (Vol. 2)</v>
+        <v>Whitcomb vs. Flores - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:26</v>
+        <v>3:05</v>
       </c>
       <c r="H126" t="str">
-        <v>The Band CAMINO</v>
+        <v>Diplo</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
+        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/do-what-you-gotta-do/1887616173</v>
+        <v>https://music.apple.com/us/album/saving-this-bottle/6769907832</v>
       </c>
       <c r="L126" t="str">
-        <v>Do What You Gotta Do - The Band CAMINO</v>
+        <v>Saving This Bottle - Diplo</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Ego</v>
+        <v>The Climb</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/ego/6769207667</v>
+        <v>https://music.apple.com/us/song/the-climb/6769546149</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-22</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Ego - Single</v>
+        <v>The Climb - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:53</v>
+        <v>3:50</v>
       </c>
       <c r="H127" t="str">
-        <v>The Warning</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/ego/6769207665</v>
+        <v>https://music.apple.com/us/album/the-climb/6769546147</v>
       </c>
       <c r="L127" t="str">
-        <v>Ego - The Warning</v>
+        <v>The Climb - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Light up (From the Netflix Documentary 'kylie')</v>
+        <v>everything tatted</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
+        <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-22</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Light up (From the Netflix Documentary 'Kylie') - Single</v>
+        <v>everything tatted - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:17</v>
+        <v>3:25</v>
       </c>
       <c r="H128" t="str">
-        <v>Kylie Minogue</v>
+        <v>mgk</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/kylie-minogue/465031</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/light-up-from-the-netflix-documentary-kylie/6768013505</v>
+        <v>https://music.apple.com/us/album/everything-tatted/6770773606</v>
       </c>
       <c r="L128" t="str">
-        <v>Light up (From the Netflix Documentary 'kylie') - Kylie Minogue</v>
+        <v>everything tatted - mgk</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>All That Matters</v>
+        <v>BOOMPALA</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
+        <v>https://music.apple.com/us/song/boompala/1894802726</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-22</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>'PUREFLOW', Pt. 1</v>
       </c>
       <c r="G129" t="str">
-        <v>3:43</v>
+        <v>2:56</v>
       </c>
       <c r="H129" t="str">
-        <v>6LACK</v>
+        <v>LE SSERAFIM</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/all-that-matters/1884792154</v>
+        <v>https://music.apple.com/us/album/boompala/1894802719</v>
       </c>
       <c r="L129" t="str">
-        <v>All That Matters - 6LACK</v>
+        <v>BOOMPALA - LE SSERAFIM</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Like A Virgin</v>
+        <v>Let Me Be In Your Arms</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
+        <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-22</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Terrified .</v>
+        <v>can we do it all again?</v>
       </c>
       <c r="G130" t="str">
-        <v>2:34</v>
+        <v>3:13</v>
       </c>
       <c r="H130" t="str">
-        <v>fakemink</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/like-a-virgin/6768157748</v>
+        <v>https://music.apple.com/us/album/let-me-be-in-your-arms/1881610862</v>
       </c>
       <c r="L130" t="str">
-        <v>Like A Virgin - fakemink</v>
+        <v>Let Me Be In Your Arms - Sonny Fodera</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>24 Hours</v>
+        <v>Eat, Work, Pray</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/24-hours/6771060076</v>
+        <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-22</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>24 Hours - Single</v>
+        <v>Eat, Work, Pray - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:17</v>
+        <v>2:28</v>
       </c>
       <c r="H131" t="str">
-        <v>Stormzy</v>
+        <v>Sheff G</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/stormzy/394865154</v>
+        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/24-hours/6771060073</v>
+        <v>https://music.apple.com/us/album/eat-work-pray/6769134493</v>
       </c>
       <c r="L131" t="str">
-        <v>24 Hours - Stormzy</v>
+        <v>Eat, Work, Pray - Sheff G</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>HOES (From Scary Movie)</v>
+        <v>touch myself</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
+        <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-22</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>HOES (From Scary Movie) - Single</v>
+        <v>and all pride aside</v>
       </c>
       <c r="G132" t="str">
-        <v>2:09</v>
+        <v>4:09</v>
       </c>
       <c r="H132" t="str">
-        <v>Lizzo</v>
+        <v>kwn</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/hoes-from-scary-movie/6770661290</v>
+        <v>https://music.apple.com/us/album/touch-myself/6769880663</v>
       </c>
       <c r="L132" t="str">
-        <v>HOES (From Scary Movie) - Lizzo</v>
+        <v>touch myself - kwn</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Ms. Tundra</v>
+        <v>Comes and Goes</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
+        <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-22</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Highway 79</v>
+        <v>Comes and Goes - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:12</v>
+        <v>4:22</v>
       </c>
       <c r="H133" t="str">
-        <v>Ne-Yo</v>
+        <v>KETTAMA</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/kettama/1425703970</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/ms-tundra/6770614875</v>
+        <v>https://music.apple.com/us/album/comes-and-goes/6766618930</v>
       </c>
       <c r="L133" t="str">
-        <v>Ms. Tundra - Ne-Yo</v>
+        <v>Comes and Goes - KETTAMA</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>TARENTINO</v>
+        <v>Dear God</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/tarentino/6769927265</v>
+        <v>https://music.apple.com/us/song/dear-god/1878237813</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-22</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>TARENTINO - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G134" t="str">
-        <v>2:23</v>
+        <v>6:08</v>
       </c>
       <c r="H134" t="str">
-        <v>Labrinth</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/tarentino/6769927262</v>
+        <v>https://music.apple.com/us/album/dear-god/1878237662</v>
       </c>
       <c r="L134" t="str">
-        <v>TARENTINO - Labrinth</v>
+        <v>Dear God - The Pretty Reckless</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Daydreamin’</v>
+        <v>Hexagons</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
+        <v>https://music.apple.com/us/song/hexagons/1885607736</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-22</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>KONNAKOL (Deluxe)</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G135" t="str">
-        <v>2:58</v>
+        <v>5:26</v>
       </c>
       <c r="H135" t="str">
-        <v>ZAYN</v>
+        <v>Muse</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/daydreamin/6769559345</v>
+        <v>https://music.apple.com/us/album/hexagons/1885607338</v>
       </c>
       <c r="L135" t="str">
-        <v>Daydreamin’ - ZAYN</v>
+        <v>Hexagons - Muse</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>End of an Era</v>
+        <v>Facile-Batiste</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
+        <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-22</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Dinner Party</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G136" t="str">
-        <v>3:38</v>
+        <v>4:55</v>
       </c>
       <c r="H136" t="str">
-        <v>Niall Horan</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/end-of-an-era/1884418567</v>
+        <v>https://music.apple.com/us/album/facile-batiste/1895866355</v>
       </c>
       <c r="L136" t="str">
-        <v>End of an Era - Niall Horan</v>
+        <v>Facile-Batiste - Jon Batiste</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Questions</v>
+        <v>Pop Pop</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/questions/1871502847</v>
+        <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-22</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Florescence</v>
+        <v>Pop Pop - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:07</v>
+        <v>2:57</v>
       </c>
       <c r="H137" t="str">
-        <v>Maisie Peters</v>
+        <v>Channel Tres</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/questions/1871502372</v>
+        <v>https://music.apple.com/us/album/pop-pop/1896269430</v>
       </c>
       <c r="L137" t="str">
-        <v>Questions - Maisie Peters</v>
+        <v>Pop Pop - Channel Tres</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Heart Has To Work So Hard</v>
+        <v>One Of Us</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
+        <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-22</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Heart Has To Work So Hard - Single</v>
+        <v>One Of Us - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:12</v>
+        <v>3:35</v>
       </c>
       <c r="H138" t="str">
-        <v>Blondshell</v>
+        <v>Chris Young</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/blondshell/1624592688</v>
+        <v>https://music.apple.com/us/artist/chris-young/4779205</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/heart-has-to-work-so-hard/1895982147</v>
+        <v>https://music.apple.com/us/album/one-of-us/1895402922</v>
       </c>
       <c r="L138" t="str">
-        <v>Heart Has To Work So Hard - Blondshell</v>
+        <v>One Of Us - Chris Young</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski)</v>
+        <v>Sins of the Father</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
+        <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-22</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski) - Single</v>
+        <v>Is God Is (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G139" t="str">
-        <v>3:44</v>
+        <v>3:20</v>
       </c>
       <c r="H139" t="str">
-        <v>Kygo</v>
+        <v>Moses Sumney</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/moses-sumney/843536848</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-your-mind-feat-dan-tyminski/6769007431</v>
+        <v>https://music.apple.com/us/album/sins-of-the-father/6771012707</v>
       </c>
       <c r="L139" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski) - Kygo</v>
+        <v>Sins of the Father - Moses Sumney</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>PERDISTE EL EMMY.</v>
+        <v>Life On The Run</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
+        <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-22</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>OMAKASE</v>
+        <v>Life On The Run - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>4:03</v>
+        <v>3:49</v>
       </c>
       <c r="H140" t="str">
-        <v>Álvaro Díaz</v>
+        <v>Brandi Carlile</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
+        <v>https://music.apple.com/us/artist/brandi-carlile/64387579</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/perdiste-el-emmy/6771082594</v>
+        <v>https://music.apple.com/us/album/life-on-the-run/6766761019</v>
       </c>
       <c r="L140" t="str">
-        <v>PERDISTE EL EMMY. - Álvaro Díaz</v>
+        <v>Life On The Run - Brandi Carlile</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Dosis</v>
+        <v>New York Confident</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/dosis/6762929729</v>
+        <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-22</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>DOSIS</v>
+        <v>New York Confident - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:00</v>
+        <v>2:27</v>
       </c>
       <c r="H141" t="str">
-        <v>Xavi</v>
+        <v>Mark Ambor</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/mark-ambor/1459754985</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/dosis/1895081885</v>
+        <v>https://music.apple.com/us/album/new-york-confident/6765558036</v>
       </c>
       <c r="L141" t="str">
-        <v>Dosis - Xavi</v>
+        <v>New York Confident - Mark Ambor</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Would U Still Love Me</v>
+        <v>pequeñita!</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
+        <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-22</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Whitcomb vs. Flores - Single</v>
+        <v>pequeñita! - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:36</v>
+        <v>2:39</v>
       </c>
       <c r="H142" t="str">
-        <v>Diplo</v>
+        <v>Judeline</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
+        <v>https://music.apple.com/us/artist/judeline/1487503245</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/would-u-still-love-me/6769907832</v>
+        <v>https://music.apple.com/us/album/peque%C3%B1ita/6769827604</v>
       </c>
       <c r="L142" t="str">
-        <v>Would U Still Love Me - Diplo</v>
+        <v>pequeñita! - Judeline</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Saving This Bottle</v>
+        <v>Opaline</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
+        <v>https://music.apple.com/us/song/opaline/1886737060</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-22</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Whitcomb vs. Flores - Single</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G143" t="str">
-        <v>3:05</v>
+        <v>3:17</v>
       </c>
       <c r="H143" t="str">
-        <v>Diplo</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/saving-this-bottle/6769907832</v>
+        <v>https://music.apple.com/us/album/opaline/1886736650</v>
       </c>
       <c r="L143" t="str">
-        <v>Saving This Bottle - Diplo</v>
+        <v>Opaline - Stephan Moccio</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>The Climb</v>
+        <v>Pretty Little Things</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/the-climb/6769546149</v>
+        <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-22</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>The Climb - Single</v>
+        <v>Pretty Little Things - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:50</v>
+        <v>2:51</v>
       </c>
       <c r="H144" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Lauv</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/the-climb/6769546147</v>
+        <v>https://music.apple.com/us/album/pretty-little-things/6767353963</v>
       </c>
       <c r="L144" t="str">
-        <v>The Climb - Bailey Zimmerman</v>
+        <v>Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>everything tatted</v>
+        <v>COLORADO</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
+        <v>https://music.apple.com/us/song/colorado/6769065232</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-22</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>everything tatted - Single</v>
+        <v>COLORADO - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:25</v>
+        <v>1:54</v>
       </c>
       <c r="H145" t="str">
-        <v>mgk</v>
+        <v>Loud Luxury</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/everything-tatted/6770773606</v>
+        <v>https://music.apple.com/us/album/colorado/6769064981</v>
       </c>
       <c r="L145" t="str">
-        <v>everything tatted - mgk</v>
+        <v>COLORADO - Loud Luxury</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>BOOMPALA</v>
+        <v>Infidelidad</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/boompala/1894802726</v>
+        <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-22</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>'PUREFLOW', Pt. 1</v>
+        <v>El Disco de Salsa</v>
       </c>
       <c r="G146" t="str">
-        <v>2:56</v>
+        <v>3:29</v>
       </c>
       <c r="H146" t="str">
-        <v>LE SSERAFIM</v>
+        <v>Neutro Shorty</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
+        <v>https://music.apple.com/us/artist/neutro-shorty/1066850977</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/boompala/1894802719</v>
+        <v>https://music.apple.com/us/album/infidelidad/6768853655</v>
       </c>
       <c r="L146" t="str">
-        <v>BOOMPALA - LE SSERAFIM</v>
+        <v>Infidelidad - Neutro Shorty</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Let Me Be In Your Arms</v>
+        <v>Wrong Place, Wrong time</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
+        <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-22</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>can we do it all again?</v>
+        <v>Y'all Won</v>
       </c>
       <c r="G147" t="str">
-        <v>3:13</v>
+        <v>2:57</v>
       </c>
       <c r="H147" t="str">
-        <v>Sonny Fodera</v>
+        <v>Veeze</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/let-me-be-in-your-arms/1881610862</v>
+        <v>https://music.apple.com/us/album/wrong-place-wrong-time/6771553812</v>
       </c>
       <c r="L147" t="str">
-        <v>Let Me Be In Your Arms - Sonny Fodera</v>
+        <v>Wrong Place, Wrong time - Veeze</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Eat, Work, Pray</v>
+        <v>La Semana</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
+        <v>https://music.apple.com/us/song/la-semana/6769913466</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-22</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Eat, Work, Pray - Single</v>
+        <v>No Quiero Que Se Acabe Este Bendito Verano - EP</v>
       </c>
       <c r="G148" t="str">
-        <v>2:28</v>
+        <v>3:30</v>
       </c>
       <c r="H148" t="str">
-        <v>Sheff G</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/eat-work-pray/6769134493</v>
+        <v>https://music.apple.com/us/album/la-semana/6769913464</v>
       </c>
       <c r="L148" t="str">
-        <v>Eat, Work, Pray - Sheff G</v>
+        <v>La Semana - ELENA ROSE</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>touch myself</v>
+        <v>Una Mujer Como la Suya</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
+        <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-22</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>and all pride aside</v>
+        <v>Bandera Blanca</v>
       </c>
       <c r="G149" t="str">
-        <v>4:09</v>
+        <v>3:34</v>
       </c>
       <c r="H149" t="str">
-        <v>kwn</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/touch-myself/6769880663</v>
+        <v>https://music.apple.com/us/album/una-mujer-como-la-suya/1895154946</v>
       </c>
       <c r="L149" t="str">
-        <v>touch myself - kwn</v>
+        <v>Una Mujer Como la Suya - Christian Nodal</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Comes and Goes</v>
+        <v>Cold</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
+        <v>https://music.apple.com/us/song/cold/6763763802</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-22</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Comes and Goes - Single</v>
+        <v>Cold - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>4:22</v>
+        <v>2:52</v>
       </c>
       <c r="H150" t="str">
-        <v>KETTAMA</v>
+        <v>Majid Jordan</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/kettama/1425703970</v>
+        <v>https://music.apple.com/us/artist/majid-jordan/684530590</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/comes-and-goes/6766618930</v>
+        <v>https://music.apple.com/us/album/cold/1895478371</v>
       </c>
       <c r="L150" t="str">
-        <v>Comes and Goes - KETTAMA</v>
+        <v>Cold - Majid Jordan</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Dear God</v>
+        <v>VERTICAL WORLDS</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/dear-god/1878237813</v>
+        <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-22</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Dear God</v>
+        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
       </c>
       <c r="G151" t="str">
-        <v>6:08</v>
+        <v>3:15</v>
       </c>
       <c r="H151" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Ecca Vandal</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/dear-god/1878237662</v>
+        <v>https://music.apple.com/us/album/vertical-worlds/1886485694</v>
       </c>
       <c r="L151" t="str">
-        <v>Dear God - The Pretty Reckless</v>
+        <v>VERTICAL WORLDS - Ecca Vandal</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Hexagons</v>
+        <v>Child of Divorce</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/hexagons/1885607736</v>
+        <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-22</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>The Wow! Signal</v>
+        <v>soft pop</v>
       </c>
       <c r="G152" t="str">
-        <v>5:26</v>
+        <v>3:24</v>
       </c>
       <c r="H152" t="str">
-        <v>Muse</v>
+        <v>Amy Shark</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/hexagons/1885607338</v>
+        <v>https://music.apple.com/us/album/child-of-divorce/1880496743</v>
       </c>
       <c r="L152" t="str">
-        <v>Hexagons - Muse</v>
+        <v>Child of Divorce - Amy Shark</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Facile-Batiste</v>
+        <v>Taboo</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
+        <v>https://music.apple.com/us/song/taboo/6762838716</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-22</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Black Mozart</v>
+        <v>Taboo - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>4:55</v>
+        <v>3:38</v>
       </c>
       <c r="H153" t="str">
-        <v>Jon Batiste</v>
+        <v>Jensen McRae</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/jensen-mcrae/591974463</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/facile-batiste/1895866355</v>
+        <v>https://music.apple.com/us/album/taboo/1895036934</v>
       </c>
       <c r="L153" t="str">
-        <v>Facile-Batiste - Jon Batiste</v>
+        <v>Taboo - Jensen McRae</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Pop Pop</v>
+        <v>I'M OK</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
+        <v>https://music.apple.com/us/song/im-ok/1893392647</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-22</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Pop Pop - Single</v>
+        <v>A Rii Set</v>
       </c>
       <c r="G154" t="str">
-        <v>2:57</v>
+        <v>2:37</v>
       </c>
       <c r="H154" t="str">
-        <v>Channel Tres</v>
+        <v>Pheelz</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
+        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/pop-pop/1896269430</v>
+        <v>https://music.apple.com/us/album/im-ok/1893392643</v>
       </c>
       <c r="L154" t="str">
-        <v>Pop Pop - Channel Tres</v>
+        <v>I'M OK - Pheelz</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>One Of Us</v>
+        <v>Butterfly Feelings</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
+        <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-22</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>One Of Us - Single</v>
+        <v>Ritual</v>
       </c>
       <c r="G155" t="str">
-        <v>3:35</v>
+        <v>2:35</v>
       </c>
       <c r="H155" t="str">
-        <v>Chris Young</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/chris-young/4779205</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/one-of-us/1895402922</v>
+        <v>https://music.apple.com/us/album/butterfly-feelings/1892426976</v>
       </c>
       <c r="L155" t="str">
-        <v>One Of Us - Chris Young</v>
+        <v>Butterfly Feelings - Icona Pop</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Sins of the Father</v>
+        <v>F**k the DJ</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
+        <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-22</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Is God Is (Original Motion Picture Soundtrack)</v>
+        <v>Stage Girl (Not A Dream Anymore)</v>
       </c>
       <c r="G156" t="str">
-        <v>3:20</v>
+        <v>2:57</v>
       </c>
       <c r="H156" t="str">
-        <v>Moses Sumney</v>
+        <v>Eli</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/moses-sumney/843536848</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/sins-of-the-father/6771012707</v>
+        <v>https://music.apple.com/us/album/f-k-the-dj/6769903867</v>
       </c>
       <c r="L156" t="str">
-        <v>Sins of the Father - Moses Sumney</v>
+        <v>F**k the DJ - Eli</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Life On The Run</v>
+        <v>Grateful</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
+        <v>https://music.apple.com/us/song/grateful/1887166624</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-22</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Life On The Run - Single</v>
+        <v>24</v>
       </c>
       <c r="G157" t="str">
-        <v>3:49</v>
+        <v>2:18</v>
       </c>
       <c r="H157" t="str">
-        <v>Brandi Carlile</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/brandi-carlile/64387579</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/life-on-the-run/6766761019</v>
+        <v>https://music.apple.com/us/album/grateful/1887166427</v>
       </c>
       <c r="L157" t="str">
-        <v>Life On The Run - Brandi Carlile</v>
+        <v>Grateful - Alexis Ffrench</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>New York Confident</v>
+        <v>Second Chance</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
+        <v>https://music.apple.com/us/song/second-chance/6766778687</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-22</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>New York Confident - Single</v>
+        <v>Second Chance - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:27</v>
+        <v>3:06</v>
       </c>
       <c r="H158" t="str">
-        <v>Mark Ambor</v>
+        <v>Lukas Graham</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/mark-ambor/1459754985</v>
+        <v>https://music.apple.com/us/artist/lukas-graham/473219952</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/new-york-confident/6765558036</v>
+        <v>https://music.apple.com/us/album/second-chance/6766778682</v>
       </c>
       <c r="L158" t="str">
-        <v>New York Confident - Mark Ambor</v>
+        <v>Second Chance - Lukas Graham</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>pequeñita!</v>
+        <v>Stupid World (feat. Chad Tepper) [Bonus Track]</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
+        <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-22</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>pequeñita! - Single</v>
+        <v>Tommyland Rides Again</v>
       </c>
       <c r="G159" t="str">
-        <v>2:39</v>
+        <v>3:49</v>
       </c>
       <c r="H159" t="str">
-        <v>Judeline</v>
+        <v>Tommy Lee</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/judeline/1487503245</v>
+        <v>https://music.apple.com/us/artist/tommy-lee/68696</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/peque%C3%B1ita/6769827604</v>
+        <v>https://music.apple.com/us/album/stupid-world-feat-chad-tepper-bonus-track/1893473875</v>
       </c>
       <c r="L159" t="str">
-        <v>pequeñita! - Judeline</v>
+        <v>Stupid World (feat. Chad Tepper) [Bonus Track] - Tommy Lee</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Opaline</v>
+        <v>DOOM LOOP</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/opaline/1886737060</v>
+        <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-22</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>Blood Of Your Empire</v>
       </c>
       <c r="G160" t="str">
-        <v>3:17</v>
+        <v>4:00</v>
       </c>
       <c r="H160" t="str">
-        <v>Stephan Moccio</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/opaline/1886736650</v>
+        <v>https://music.apple.com/us/album/doom-loop/6769905842</v>
       </c>
       <c r="L160" t="str">
-        <v>Opaline - Stephan Moccio</v>
+        <v>DOOM LOOP - PRESIDENT</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Pretty Little Things</v>
+        <v>New York City</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
+        <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-22</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Pretty Little Things - Single</v>
+        <v>New York City - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:51</v>
+        <v>3:30</v>
       </c>
       <c r="H161" t="str">
-        <v>Lauv</v>
+        <v>Anthony Ramos</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/anthony-ramos/1313064678</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/pretty-little-things/6767353963</v>
+        <v>https://music.apple.com/us/album/new-york-city/6770624324</v>
       </c>
       <c r="L161" t="str">
-        <v>Pretty Little Things - Lauv</v>
+        <v>New York City - Anthony Ramos</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>COLORADO</v>
+        <v>I Found You</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/colorado/6769065232</v>
+        <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-22</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>COLORADO - Single</v>
+        <v>I Found You - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>1:54</v>
+        <v>3:18</v>
       </c>
       <c r="H162" t="str">
-        <v>Loud Luxury</v>
+        <v>TA Thomas</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
+        <v>https://music.apple.com/us/artist/ta-thomas/1232189106</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/colorado/6769064981</v>
+        <v>https://music.apple.com/us/album/i-found-you/1894024530</v>
       </c>
       <c r="L162" t="str">
-        <v>COLORADO - Loud Luxury</v>
+        <v>I Found You - TA Thomas</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Infidelidad</v>
+        <v>Just My Type</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
+        <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-22</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>El Disco de Salsa</v>
+        <v>Labor Of Love</v>
       </c>
       <c r="G163" t="str">
-        <v>3:29</v>
+        <v>2:40</v>
       </c>
       <c r="H163" t="str">
-        <v>Neutro Shorty</v>
+        <v>Blxst</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/neutro-shorty/1066850977</v>
+        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/infidelidad/6768853655</v>
+        <v>https://music.apple.com/us/album/just-my-type/1895199881</v>
       </c>
       <c r="L163" t="str">
-        <v>Infidelidad - Neutro Shorty</v>
+        <v>Just My Type - Blxst</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Wrong Place, Wrong time</v>
+        <v>teenage drama</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
+        <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-22</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Y'all Won</v>
+        <v>teenage drama - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:57</v>
+        <v>3:06</v>
       </c>
       <c r="H164" t="str">
-        <v>Veeze</v>
+        <v>paris jackson</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/wrong-place-wrong-time/6771553812</v>
+        <v>https://music.apple.com/us/album/teenage-drama/6768447515</v>
       </c>
       <c r="L164" t="str">
-        <v>Wrong Place, Wrong time - Veeze</v>
+        <v>teenage drama - paris jackson</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>La Semana</v>
+        <v>does it still mean something?</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/la-semana/6769913466</v>
+        <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-22</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>No Quiero Que Se Acabe Este Bendito Verano - EP</v>
+        <v>only if it matters</v>
       </c>
       <c r="G165" t="str">
-        <v>3:30</v>
+        <v>3:48</v>
       </c>
       <c r="H165" t="str">
-        <v>ELENA ROSE</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/la-semana/6769913464</v>
+        <v>https://music.apple.com/us/album/does-it-still-mean-something/6768446154</v>
       </c>
       <c r="L165" t="str">
-        <v>La Semana - ELENA ROSE</v>
+        <v>does it still mean something? - Kevian Kraemer</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Una Mujer Como la Suya</v>
+        <v>Debbie Don't Cry</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
+        <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-22</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Bandera Blanca</v>
+        <v>Debbie Don't Cry - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:34</v>
+        <v>3:00</v>
       </c>
       <c r="H166" t="str">
-        <v>Christian Nodal</v>
+        <v>Ruel</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/una-mujer-como-la-suya/1895154946</v>
+        <v>https://music.apple.com/us/album/debbie-dont-cry/6768206616</v>
       </c>
       <c r="L166" t="str">
-        <v>Una Mujer Como la Suya - Christian Nodal</v>
+        <v>Debbie Don't Cry - Ruel</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Cold</v>
+        <v>YEAH YEAH YEAH</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/cold/6763763802</v>
+        <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-22</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Cold - Single</v>
+        <v>YEAH YEAH YEAH - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:52</v>
+        <v>2:25</v>
       </c>
       <c r="H167" t="str">
-        <v>Majid Jordan</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/majid-jordan/684530590</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/cold/1895478371</v>
+        <v>https://music.apple.com/us/album/yeah-yeah-yeah/6767515610</v>
       </c>
       <c r="L167" t="str">
-        <v>Cold - Majid Jordan</v>
+        <v>YEAH YEAH YEAH - Cruz Beckham</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>VERTICAL WORLDS</v>
+        <v>Cotton Flower</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
+        <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-22</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G168" t="str">
-        <v>3:15</v>
+        <v>3:53</v>
       </c>
       <c r="H168" t="str">
-        <v>Ecca Vandal</v>
+        <v>Future Islands</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/vertical-worlds/1886485694</v>
+        <v>https://music.apple.com/us/album/cotton-flower/1883045480</v>
       </c>
       <c r="L168" t="str">
-        <v>VERTICAL WORLDS - Ecca Vandal</v>
+        <v>Cotton Flower - Future Islands</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Child of Divorce</v>
+        <v>WAHALA RIDDIM</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
+        <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-22</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>soft pop</v>
+        <v>WAHALA RIDDIM - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:24</v>
+        <v>3:22</v>
       </c>
       <c r="H169" t="str">
-        <v>Amy Shark</v>
+        <v>THEHONESTGUY</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
+        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/child-of-divorce/1880496743</v>
+        <v>https://music.apple.com/us/album/wahala-riddim/1895810537</v>
       </c>
       <c r="L169" t="str">
-        <v>Child of Divorce - Amy Shark</v>
+        <v>WAHALA RIDDIM - THEHONESTGUY</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Taboo</v>
+        <v>Comfort</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/taboo/6762838716</v>
+        <v>https://music.apple.com/us/song/comfort/1876521401</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-22</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Taboo - Single</v>
+        <v>So Help Me God</v>
       </c>
       <c r="G170" t="str">
-        <v>3:38</v>
+        <v>5:35</v>
       </c>
       <c r="H170" t="str">
-        <v>Jensen McRae</v>
+        <v>Kelsey Lu</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/jensen-mcrae/591974463</v>
+        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/taboo/1895036934</v>
+        <v>https://music.apple.com/us/album/comfort/1876521144</v>
       </c>
       <c r="L170" t="str">
-        <v>Taboo - Jensen McRae</v>
+        <v>Comfort - Kelsey Lu</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>I'M OK</v>
+        <v>Skin</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/im-ok/1893392647</v>
+        <v>https://music.apple.com/us/song/skin/6764651585</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-22</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>A Rii Set</v>
+        <v>Skin - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:37</v>
+        <v>3:00</v>
       </c>
       <c r="H171" t="str">
-        <v>Pheelz</v>
+        <v>Alessi Rose</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
+        <v>https://music.apple.com/us/artist/alessi-rose/1628689028</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/im-ok/1893392643</v>
+        <v>https://music.apple.com/us/album/skin/1895865252</v>
       </c>
       <c r="L171" t="str">
-        <v>I'M OK - Pheelz</v>
+        <v>Skin - Alessi Rose</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Butterfly Feelings</v>
+        <v>IDGAF</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
+        <v>https://music.apple.com/us/song/idgaf/6764422210</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-22</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Ritual</v>
+        <v>IDGAF - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:35</v>
+        <v>2:55</v>
       </c>
       <c r="H172" t="str">
-        <v>Icona Pop</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/butterfly-feelings/1892426976</v>
+        <v>https://music.apple.com/us/album/idgaf/1895773358</v>
       </c>
       <c r="L172" t="str">
-        <v>Butterfly Feelings - Icona Pop</v>
+        <v>IDGAF - Katelyn Tarver</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>F**k the DJ</v>
+        <v>Run Rabbit</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
+        <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-22</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Stage Girl (Not A Dream Anymore)</v>
+        <v>Run Rabbit - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:57</v>
+        <v>3:09</v>
       </c>
       <c r="H173" t="str">
-        <v>Eli</v>
+        <v>Mollie Elizabeth</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/mollie-elizabeth/1780515318</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/f-k-the-dj/6769903867</v>
+        <v>https://music.apple.com/us/album/run-rabbit/6767354664</v>
       </c>
       <c r="L173" t="str">
-        <v>F**k the DJ - Eli</v>
+        <v>Run Rabbit - Mollie Elizabeth</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Grateful</v>
+        <v>So Good (feat. Kuuda)</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/grateful/1887166624</v>
+        <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-22</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>24</v>
+        <v>So Good (feat. Kuuda) - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:18</v>
+        <v>3:03</v>
       </c>
       <c r="H174" t="str">
-        <v>Alexis Ffrench</v>
+        <v>CamelPhat</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/camelphat/385810888</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/grateful/1887166427</v>
+        <v>https://music.apple.com/us/album/so-good-feat-kuuda/6766655768</v>
       </c>
       <c r="L174" t="str">
-        <v>Grateful - Alexis Ffrench</v>
+        <v>So Good (feat. Kuuda) - CamelPhat</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Second Chance</v>
+        <v>Empty Theatre, Pretty Picture</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/second-chance/6766778687</v>
+        <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-22</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Second Chance - Single</v>
+        <v>Empty Theatre, Pretty Picture</v>
       </c>
       <c r="G175" t="str">
-        <v>3:06</v>
+        <v>5:01</v>
       </c>
       <c r="H175" t="str">
-        <v>Lukas Graham</v>
+        <v>Lane 8</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/lukas-graham/473219952</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/second-chance/6766778682</v>
+        <v>https://music.apple.com/us/album/empty-theatre-pretty-picture/1895395993</v>
       </c>
       <c r="L175" t="str">
-        <v>Second Chance - Lukas Graham</v>
+        <v>Empty Theatre, Pretty Picture - Lane 8</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Stupid World (feat. Chad Tepper) [Bonus Track]</v>
+        <v>regalametutiempo</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
+        <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-22</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Tommyland Rides Again</v>
+        <v>PROYECTANDO</v>
       </c>
       <c r="G176" t="str">
-        <v>3:49</v>
+        <v>3:01</v>
       </c>
       <c r="H176" t="str">
-        <v>Tommy Lee</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/tommy-lee/68696</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/stupid-world-feat-chad-tepper-bonus-track/1893473875</v>
+        <v>https://music.apple.com/us/album/regalametutiempo/6769922866</v>
       </c>
       <c r="L176" t="str">
-        <v>Stupid World (feat. Chad Tepper) [Bonus Track] - Tommy Lee</v>
+        <v>regalametutiempo - Julio Caesar</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>DOOM LOOP</v>
+        <v>On Sight</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
+        <v>https://music.apple.com/us/song/on-sight/6763971220</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-22</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Blood Of Your Empire</v>
+        <v>Left on RED</v>
       </c>
       <c r="G177" t="str">
-        <v>4:00</v>
+        <v>2:25</v>
       </c>
       <c r="H177" t="str">
-        <v>PRESIDENT</v>
+        <v>REMI</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/remi/1716510008</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/doom-loop/6769905842</v>
+        <v>https://music.apple.com/us/album/on-sight/1895580736</v>
       </c>
       <c r="L177" t="str">
-        <v>DOOM LOOP - PRESIDENT</v>
+        <v>On Sight - REMI</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>New York City</v>
+        <v>Masks Off</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
+        <v>https://music.apple.com/us/song/masks-off/6764077133</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-22</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>New York City - Single</v>
+        <v>Masks Off - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:30</v>
+        <v>3:24</v>
       </c>
       <c r="H178" t="str">
-        <v>Anthony Ramos</v>
+        <v>Jesse Welles</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/anthony-ramos/1313064678</v>
+        <v>https://music.apple.com/us/artist/jesse-welles/1737507146</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/new-york-city/6770624324</v>
+        <v>https://music.apple.com/us/album/masks-off/1895628310</v>
       </c>
       <c r="L178" t="str">
-        <v>New York City - Anthony Ramos</v>
+        <v>Masks Off - Jesse Welles</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>I Found You</v>
+        <v>I'm Just A Girl</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
+        <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-22</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>I Found You - Single</v>
+        <v>Di Hotel Malibu</v>
       </c>
       <c r="G179" t="str">
-        <v>3:18</v>
+        <v>2:49</v>
       </c>
       <c r="H179" t="str">
-        <v>TA Thomas</v>
+        <v>Thee Marloes</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/ta-thomas/1232189106</v>
+        <v>https://music.apple.com/us/artist/thee-marloes/1541376632</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/i-found-you/1894024530</v>
+        <v>https://music.apple.com/us/album/im-just-a-girl/1878399768</v>
       </c>
       <c r="L179" t="str">
-        <v>I Found You - TA Thomas</v>
+        <v>I'm Just A Girl - Thee Marloes</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Just My Type</v>
+        <v>Soleil (feat. Isabella Lovestory)</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
+        <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-22</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Labor Of Love</v>
+        <v>EXIT 2B</v>
       </c>
       <c r="G180" t="str">
-        <v>2:40</v>
+        <v>2:11</v>
       </c>
       <c r="H180" t="str">
-        <v>Blxst</v>
+        <v>B0YG1RL</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
+        <v>https://music.apple.com/us/artist/b0yg1rl/1847766665</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/just-my-type/1895199881</v>
+        <v>https://music.apple.com/us/album/soleil-feat-isabella-lovestory/6769526101</v>
       </c>
       <c r="L180" t="str">
-        <v>Just My Type - Blxst</v>
+        <v>Soleil (feat. Isabella Lovestory) - B0YG1RL</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>teenage drama</v>
+        <v>Money Tree</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
+        <v>https://music.apple.com/us/song/money-tree/6763211637</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-22</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>teenage drama - Single</v>
+        <v>Money Tree - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:06</v>
+        <v>2:39</v>
       </c>
       <c r="H181" t="str">
-        <v>paris jackson</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/teenage-drama/6768447515</v>
+        <v>https://music.apple.com/us/album/money-tree/1895216986</v>
       </c>
       <c r="L181" t="str">
-        <v>teenage drama - paris jackson</v>
+        <v>Money Tree - Olympia Vitalis</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>does it still mean something?</v>
+        <v>Homerunner</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
+        <v>https://music.apple.com/us/song/homerunner/6770682178</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-22</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>only if it matters</v>
+        <v>Homerunner - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:48</v>
+        <v>2:36</v>
       </c>
       <c r="H182" t="str">
-        <v>Kevian Kraemer</v>
+        <v>slayr</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/does-it-still-mean-something/6768446154</v>
+        <v>https://music.apple.com/us/album/homerunner/6770682177</v>
       </c>
       <c r="L182" t="str">
-        <v>does it still mean something? - Kevian Kraemer</v>
+        <v>Homerunner - slayr</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Debbie Don't Cry</v>
+        <v>Mail</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
+        <v>https://music.apple.com/us/song/mail/6769190635</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-22</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Debbie Don't Cry - Single</v>
+        <v>Mail - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:00</v>
+        <v>2:14</v>
       </c>
       <c r="H183" t="str">
-        <v>Ruel</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/debbie-dont-cry/6768206616</v>
+        <v>https://music.apple.com/us/album/mail/6769190634</v>
       </c>
       <c r="L183" t="str">
-        <v>Debbie Don't Cry - Ruel</v>
+        <v>Mail - MexikoDro</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>YEAH YEAH YEAH</v>
+        <v>Waste Your Heart</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
+        <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-22</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>YEAH YEAH YEAH - Single</v>
+        <v>Waste Your Heart - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:25</v>
+        <v>2:31</v>
       </c>
       <c r="H184" t="str">
-        <v>Cruz Beckham</v>
+        <v>Magnus Ferrell</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/yeah-yeah-yeah/6767515610</v>
+        <v>https://music.apple.com/us/album/waste-your-heart/6769241913</v>
       </c>
       <c r="L184" t="str">
-        <v>YEAH YEAH YEAH - Cruz Beckham</v>
+        <v>Waste Your Heart - Magnus Ferrell</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Cotton Flower</v>
+        <v>Sleeping Pills</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
+        <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-22</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>Sleeping Pills - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:53</v>
+        <v>3:03</v>
       </c>
       <c r="H185" t="str">
-        <v>Future Islands</v>
+        <v>Dolder</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/cotton-flower/1883045480</v>
+        <v>https://music.apple.com/us/album/sleeping-pills/1896452689</v>
       </c>
       <c r="L185" t="str">
-        <v>Cotton Flower - Future Islands</v>
+        <v>Sleeping Pills - Dolder</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>WAHALA RIDDIM</v>
+        <v>KODACHROMATIC</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
+        <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-22</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>WAHALA RIDDIM - Single</v>
+        <v>KODACHROMATIC - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:22</v>
+        <v>2:53</v>
       </c>
       <c r="H186" t="str">
-        <v>THEHONESTGUY</v>
+        <v>Tiger La Flor</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
+        <v>https://music.apple.com/us/artist/tiger-la-flor/1613113982</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/wahala-riddim/1895810537</v>
+        <v>https://music.apple.com/us/album/kodachromatic/6770724719</v>
       </c>
       <c r="L186" t="str">
-        <v>WAHALA RIDDIM - THEHONESTGUY</v>
+        <v>KODACHROMATIC - Tiger La Flor</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Comfort</v>
+        <v>FOMO</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/comfort/1876521401</v>
+        <v>https://music.apple.com/us/song/fomo/1890190631</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-22</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>So Help Me God</v>
+        <v>Map Of Her Shadow</v>
       </c>
       <c r="G187" t="str">
-        <v>5:35</v>
+        <v>3:01</v>
       </c>
       <c r="H187" t="str">
-        <v>Kelsey Lu</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/comfort/1876521144</v>
+        <v>https://music.apple.com/us/album/fomo/1890190623</v>
       </c>
       <c r="L187" t="str">
-        <v>Comfort - Kelsey Lu</v>
+        <v>FOMO - Anais Cardot</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Skin</v>
+        <v>Black Fire</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/skin/6764651585</v>
+        <v>https://music.apple.com/us/song/black-fire/6770696877</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-22</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Skin - Single</v>
+        <v>Sulfur Surfer</v>
       </c>
       <c r="G188" t="str">
-        <v>3:00</v>
+        <v>3:37</v>
       </c>
       <c r="H188" t="str">
-        <v>Alessi Rose</v>
+        <v>Bladee</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/alessi-rose/1628689028</v>
+        <v>https://music.apple.com/us/artist/bladee/861359576</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/skin/1895865252</v>
+        <v>https://music.apple.com/us/album/black-fire/6770696743</v>
       </c>
       <c r="L188" t="str">
-        <v>Skin - Alessi Rose</v>
+        <v>Black Fire - Bladee</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>IDGAF</v>
+        <v>As Seen in the Unseen</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/idgaf/6764422210</v>
+        <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-22</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>IDGAF - Single</v>
+        <v>Grand Serpent Rising</v>
       </c>
       <c r="G189" t="str">
-        <v>2:55</v>
+        <v>6:59</v>
       </c>
       <c r="H189" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Dimmu Borgir</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/idgaf/1895773358</v>
+        <v>https://music.apple.com/us/album/as-seen-in-the-unseen/1883121436</v>
       </c>
       <c r="L189" t="str">
-        <v>IDGAF - Katelyn Tarver</v>
+        <v>As Seen in the Unseen - Dimmu Borgir</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Run Rabbit</v>
+        <v>Every Man-Any Man</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
+        <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-22</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Run Rabbit - Single</v>
+        <v>Emotion Factory Reset</v>
       </c>
       <c r="G190" t="str">
-        <v>3:09</v>
+        <v>4:20</v>
       </c>
       <c r="H190" t="str">
-        <v>Mollie Elizabeth</v>
+        <v>Armored Saint</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/mollie-elizabeth/1780515318</v>
+        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/run-rabbit/6767354664</v>
+        <v>https://music.apple.com/us/album/every-man-any-man/1872193859</v>
       </c>
       <c r="L190" t="str">
-        <v>Run Rabbit - Mollie Elizabeth</v>
+        <v>Every Man-Any Man - Armored Saint</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>So Good (feat. Kuuda)</v>
+        <v>No Arms</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
+        <v>https://music.apple.com/us/song/no-arms/6765776563</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-22</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>So Good (feat. Kuuda) - Single</v>
+        <v>From A Distance</v>
       </c>
       <c r="G191" t="str">
-        <v>3:03</v>
+        <v>3:43</v>
       </c>
       <c r="H191" t="str">
-        <v>CamelPhat</v>
+        <v>156/Silence</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/camelphat/385810888</v>
+        <v>https://music.apple.com/us/artist/156-silence/1071395282</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/so-good-feat-kuuda/6766655768</v>
+        <v>https://music.apple.com/us/album/no-arms/1896069437</v>
       </c>
       <c r="L191" t="str">
-        <v>So Good (feat. Kuuda) - CamelPhat</v>
+        <v>No Arms - 156/Silence</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Empty Theatre, Pretty Picture</v>
+        <v>It's Neverending</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
+        <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-22</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Empty Theatre, Pretty Picture</v>
+        <v>Neverending</v>
       </c>
       <c r="G192" t="str">
-        <v>5:01</v>
+        <v>8:35</v>
       </c>
       <c r="H192" t="str">
-        <v>Lane 8</v>
+        <v>Monolord</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/empty-theatre-pretty-picture/1895395993</v>
+        <v>https://music.apple.com/us/album/its-neverending/1871211801</v>
       </c>
       <c r="L192" t="str">
-        <v>Empty Theatre, Pretty Picture - Lane 8</v>
+        <v>It's Neverending - Monolord</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>regalametutiempo</v>
+        <v>The Kids Will Kill Us</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
+        <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-22</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>PROYECTANDO</v>
+        <v>The Kids Will Kill Us - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:01</v>
+        <v>3:45</v>
       </c>
       <c r="H193" t="str">
-        <v>Julio Caesar</v>
+        <v>Witch Club Satan</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/witch-club-satan/1626477576</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/regalametutiempo/6769922866</v>
+        <v>https://music.apple.com/us/album/the-kids-will-kill-us/6766343272</v>
       </c>
       <c r="L193" t="str">
-        <v>regalametutiempo - Julio Caesar</v>
+        <v>The Kids Will Kill Us - Witch Club Satan</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>On Sight</v>
+        <v>Masters of the Universe (from "Masters of the Universe")</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/on-sight/6763971220</v>
+        <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-22</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Left on RED</v>
+        <v>Masters of the Universe (from "Masters of the Universe") - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>2:25</v>
+        <v>3:20</v>
       </c>
       <c r="H194" t="str">
-        <v>REMI</v>
+        <v>The Darkness</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/remi/1716510008</v>
+        <v>https://music.apple.com/us/artist/the-darkness/2417388</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/on-sight/1895580736</v>
+        <v>https://music.apple.com/us/album/masters-of-the-universe-from-masters-of-the-universe/6769065779</v>
       </c>
       <c r="L194" t="str">
-        <v>On Sight - REMI</v>
+        <v>Masters of the Universe (from "Masters of the Universe") - The Darkness</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Masks Off</v>
+        <v>All Day</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/masks-off/6764077133</v>
+        <v>https://music.apple.com/us/song/all-day/1880746584</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-22</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Masks Off - Single</v>
+        <v>Feet On Fire</v>
       </c>
       <c r="G195" t="str">
-        <v>3:24</v>
+        <v>2:29</v>
       </c>
       <c r="H195" t="str">
-        <v>Jesse Welles</v>
+        <v>Ben Chapman</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/jesse-welles/1737507146</v>
+        <v>https://music.apple.com/us/artist/ben-chapman/1581192612</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/masks-off/1895628310</v>
+        <v>https://music.apple.com/us/album/all-day/1880746349</v>
       </c>
       <c r="L195" t="str">
-        <v>Masks Off - Jesse Welles</v>
+        <v>All Day - Ben Chapman</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>I'm Just A Girl</v>
+        <v>Sigui</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
+        <v>https://music.apple.com/us/song/sigui/1890241955</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-22</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Di Hotel Malibu</v>
+        <v>Massa</v>
       </c>
       <c r="G196" t="str">
-        <v>2:49</v>
+        <v>3:17</v>
       </c>
       <c r="H196" t="str">
-        <v>Thee Marloes</v>
+        <v>Fatoumata Diawara</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/thee-marloes/1541376632</v>
+        <v>https://music.apple.com/us/artist/fatoumata-diawara/466213610</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/im-just-a-girl/1878399768</v>
+        <v>https://music.apple.com/us/album/sigui/1890241617</v>
       </c>
       <c r="L196" t="str">
-        <v>I'm Just A Girl - Thee Marloes</v>
+        <v>Sigui - Fatoumata Diawara</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Soleil (feat. Isabella Lovestory)</v>
+        <v>High Tail</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
+        <v>https://music.apple.com/us/song/high-tail/1870432994</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-22</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>EXIT 2B</v>
+        <v>Where the South Winds Wail</v>
       </c>
       <c r="G197" t="str">
-        <v>2:11</v>
+        <v>2:31</v>
       </c>
       <c r="H197" t="str">
-        <v>B0YG1RL</v>
+        <v>Gitkin</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/b0yg1rl/1847766665</v>
+        <v>https://music.apple.com/us/artist/gitkin/1345281815</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/soleil-feat-isabella-lovestory/6769526101</v>
+        <v>https://music.apple.com/us/album/high-tail/1870432670</v>
       </c>
       <c r="L197" t="str">
-        <v>Soleil (feat. Isabella Lovestory) - B0YG1RL</v>
+        <v>High Tail - Gitkin</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Money Tree</v>
+        <v>Mice Protection</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/money-tree/6763211637</v>
+        <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-22</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Money Tree - Single</v>
+        <v>Ugly Duckling Union</v>
       </c>
       <c r="G198" t="str">
-        <v>2:39</v>
+        <v>3:34</v>
       </c>
       <c r="H198" t="str">
-        <v>Olympia Vitalis</v>
+        <v>Lowertown</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/lowertown/1448207323</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/money-tree/1895216986</v>
+        <v>https://music.apple.com/us/album/mice-protection/1872171971</v>
       </c>
       <c r="L198" t="str">
-        <v>Money Tree - Olympia Vitalis</v>
+        <v>Mice Protection - Lowertown</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Homerunner</v>
+        <v>Tóxica</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/homerunner/6770682178</v>
+        <v>https://music.apple.com/us/song/t%C3%B3xica/6763056240</v>
       </c>
       <c r="D199" t="str">
         <v>2026-05-22</v>
@@ -7937,676 +7937,30 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Homerunner - Single</v>
+        <v>Caribenya</v>
       </c>
       <c r="G199" t="str">
-        <v>2:36</v>
+        <v>3:48</v>
       </c>
       <c r="H199" t="str">
-        <v>slayr</v>
+        <v>Lido Pimienta</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/lido-pimienta/389475023</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/homerunner/6770682177</v>
+        <v>https://music.apple.com/us/album/t%C3%B3xica/1895141218</v>
       </c>
       <c r="L199" t="str">
-        <v>Homerunner - slayr</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>Mail</v>
-      </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/mail/6769190635</v>
-      </c>
-      <c r="D200" t="str">
-        <v>2026-05-22</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
-        <v>Mail - Single</v>
-      </c>
-      <c r="G200" t="str">
-        <v>2:14</v>
-      </c>
-      <c r="H200" t="str">
-        <v>MexikoDro</v>
-      </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
-      </c>
-      <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/mail/6769190634</v>
-      </c>
-      <c r="L200" t="str">
-        <v>Mail - MexikoDro</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>Waste Your Heart</v>
-      </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
-      </c>
-      <c r="D201" t="str">
-        <v>2026-05-22</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
-        <v>Waste Your Heart - Single</v>
-      </c>
-      <c r="G201" t="str">
-        <v>2:31</v>
-      </c>
-      <c r="H201" t="str">
-        <v>Magnus Ferrell</v>
-      </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
-      </c>
-      <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/waste-your-heart/6769241913</v>
-      </c>
-      <c r="L201" t="str">
-        <v>Waste Your Heart - Magnus Ferrell</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>Sleeping Pills</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
-      </c>
-      <c r="D202" t="str">
-        <v>2026-05-22</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
-        <v>Sleeping Pills - Single</v>
-      </c>
-      <c r="G202" t="str">
-        <v>3:03</v>
-      </c>
-      <c r="H202" t="str">
-        <v>Dolder</v>
-      </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
-      </c>
-      <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/sleeping-pills/1896452689</v>
-      </c>
-      <c r="L202" t="str">
-        <v>Sleeping Pills - Dolder</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>KODACHROMATIC</v>
-      </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
-      </c>
-      <c r="D203" t="str">
-        <v>2026-05-22</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
-        <v>KODACHROMATIC - Single</v>
-      </c>
-      <c r="G203" t="str">
-        <v>2:53</v>
-      </c>
-      <c r="H203" t="str">
-        <v>Tiger La Flor</v>
-      </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/tiger-la-flor/1613113982</v>
-      </c>
-      <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/kodachromatic/6770724719</v>
-      </c>
-      <c r="L203" t="str">
-        <v>KODACHROMATIC - Tiger La Flor</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>FOMO</v>
-      </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/fomo/1890190631</v>
-      </c>
-      <c r="D204" t="str">
-        <v>2026-05-22</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
-        <v>Map Of Her Shadow</v>
-      </c>
-      <c r="G204" t="str">
-        <v>3:01</v>
-      </c>
-      <c r="H204" t="str">
-        <v>Anais Cardot</v>
-      </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
-      </c>
-      <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/fomo/1890190623</v>
-      </c>
-      <c r="L204" t="str">
-        <v>FOMO - Anais Cardot</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>Black Fire</v>
-      </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/black-fire/6770696877</v>
-      </c>
-      <c r="D205" t="str">
-        <v>2026-05-22</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
-        <v>Sulfur Surfer</v>
-      </c>
-      <c r="G205" t="str">
-        <v>3:37</v>
-      </c>
-      <c r="H205" t="str">
-        <v>Bladee</v>
-      </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/bladee/861359576</v>
-      </c>
-      <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/black-fire/6770696743</v>
-      </c>
-      <c r="L205" t="str">
-        <v>Black Fire - Bladee</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>As Seen in the Unseen</v>
-      </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
-      </c>
-      <c r="D206" t="str">
-        <v>2026-05-22</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
-        <v>Grand Serpent Rising</v>
-      </c>
-      <c r="G206" t="str">
-        <v>6:59</v>
-      </c>
-      <c r="H206" t="str">
-        <v>Dimmu Borgir</v>
-      </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
-      </c>
-      <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/as-seen-in-the-unseen/1883121436</v>
-      </c>
-      <c r="L206" t="str">
-        <v>As Seen in the Unseen - Dimmu Borgir</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>Every Man-Any Man</v>
-      </c>
-      <c r="B207" t="str">
-        <v/>
-      </c>
-      <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
-      </c>
-      <c r="D207" t="str">
-        <v>2026-05-22</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
-        <v>Emotion Factory Reset</v>
-      </c>
-      <c r="G207" t="str">
-        <v>4:20</v>
-      </c>
-      <c r="H207" t="str">
-        <v>Armored Saint</v>
-      </c>
-      <c r="I207" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
-      </c>
-      <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/every-man-any-man/1872193859</v>
-      </c>
-      <c r="L207" t="str">
-        <v>Every Man-Any Man - Armored Saint</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>No Arms</v>
-      </c>
-      <c r="B208" t="str">
-        <v/>
-      </c>
-      <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/no-arms/6765776563</v>
-      </c>
-      <c r="D208" t="str">
-        <v>2026-05-22</v>
-      </c>
-      <c r="E208" t="str">
-        <v/>
-      </c>
-      <c r="F208" t="str">
-        <v>From A Distance</v>
-      </c>
-      <c r="G208" t="str">
-        <v>3:43</v>
-      </c>
-      <c r="H208" t="str">
-        <v>156/Silence</v>
-      </c>
-      <c r="I208" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/156-silence/1071395282</v>
-      </c>
-      <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/no-arms/1896069437</v>
-      </c>
-      <c r="L208" t="str">
-        <v>No Arms - 156/Silence</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="str">
-        <v>It's Neverending</v>
-      </c>
-      <c r="B209" t="str">
-        <v/>
-      </c>
-      <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
-      </c>
-      <c r="D209" t="str">
-        <v>2026-05-22</v>
-      </c>
-      <c r="E209" t="str">
-        <v/>
-      </c>
-      <c r="F209" t="str">
-        <v>Neverending</v>
-      </c>
-      <c r="G209" t="str">
-        <v>8:35</v>
-      </c>
-      <c r="H209" t="str">
-        <v>Monolord</v>
-      </c>
-      <c r="I209" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
-      </c>
-      <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/its-neverending/1871211801</v>
-      </c>
-      <c r="L209" t="str">
-        <v>It's Neverending - Monolord</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="str">
-        <v>The Kids Will Kill Us</v>
-      </c>
-      <c r="B210" t="str">
-        <v/>
-      </c>
-      <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
-      </c>
-      <c r="D210" t="str">
-        <v>2026-05-22</v>
-      </c>
-      <c r="E210" t="str">
-        <v/>
-      </c>
-      <c r="F210" t="str">
-        <v>The Kids Will Kill Us - Single</v>
-      </c>
-      <c r="G210" t="str">
-        <v>3:45</v>
-      </c>
-      <c r="H210" t="str">
-        <v>Witch Club Satan</v>
-      </c>
-      <c r="I210" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/witch-club-satan/1626477576</v>
-      </c>
-      <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/the-kids-will-kill-us/6766343272</v>
-      </c>
-      <c r="L210" t="str">
-        <v>The Kids Will Kill Us - Witch Club Satan</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe")</v>
-      </c>
-      <c r="B211" t="str">
-        <v/>
-      </c>
-      <c r="C211" t="str">
-        <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
-      </c>
-      <c r="D211" t="str">
-        <v>2026-05-22</v>
-      </c>
-      <c r="E211" t="str">
-        <v/>
-      </c>
-      <c r="F211" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe") - Single</v>
-      </c>
-      <c r="G211" t="str">
-        <v>3:20</v>
-      </c>
-      <c r="H211" t="str">
-        <v>The Darkness</v>
-      </c>
-      <c r="I211" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J211" t="str">
-        <v>https://music.apple.com/us/artist/the-darkness/2417388</v>
-      </c>
-      <c r="K211" t="str">
-        <v>https://music.apple.com/us/album/masters-of-the-universe-from-masters-of-the-universe/6769065779</v>
-      </c>
-      <c r="L211" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe") - The Darkness</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="str">
-        <v>All Day</v>
-      </c>
-      <c r="B212" t="str">
-        <v/>
-      </c>
-      <c r="C212" t="str">
-        <v>https://music.apple.com/us/song/all-day/1880746584</v>
-      </c>
-      <c r="D212" t="str">
-        <v>2026-05-22</v>
-      </c>
-      <c r="E212" t="str">
-        <v/>
-      </c>
-      <c r="F212" t="str">
-        <v>Feet On Fire</v>
-      </c>
-      <c r="G212" t="str">
-        <v>2:29</v>
-      </c>
-      <c r="H212" t="str">
-        <v>Ben Chapman</v>
-      </c>
-      <c r="I212" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J212" t="str">
-        <v>https://music.apple.com/us/artist/ben-chapman/1581192612</v>
-      </c>
-      <c r="K212" t="str">
-        <v>https://music.apple.com/us/album/all-day/1880746349</v>
-      </c>
-      <c r="L212" t="str">
-        <v>All Day - Ben Chapman</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="str">
-        <v>Sigui</v>
-      </c>
-      <c r="B213" t="str">
-        <v/>
-      </c>
-      <c r="C213" t="str">
-        <v>https://music.apple.com/us/song/sigui/1890241955</v>
-      </c>
-      <c r="D213" t="str">
-        <v>2026-05-22</v>
-      </c>
-      <c r="E213" t="str">
-        <v/>
-      </c>
-      <c r="F213" t="str">
-        <v>Massa</v>
-      </c>
-      <c r="G213" t="str">
-        <v>3:17</v>
-      </c>
-      <c r="H213" t="str">
-        <v>Fatoumata Diawara</v>
-      </c>
-      <c r="I213" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J213" t="str">
-        <v>https://music.apple.com/us/artist/fatoumata-diawara/466213610</v>
-      </c>
-      <c r="K213" t="str">
-        <v>https://music.apple.com/us/album/sigui/1890241617</v>
-      </c>
-      <c r="L213" t="str">
-        <v>Sigui - Fatoumata Diawara</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="str">
-        <v>High Tail</v>
-      </c>
-      <c r="B214" t="str">
-        <v/>
-      </c>
-      <c r="C214" t="str">
-        <v>https://music.apple.com/us/song/high-tail/1870432994</v>
-      </c>
-      <c r="D214" t="str">
-        <v>2026-05-22</v>
-      </c>
-      <c r="E214" t="str">
-        <v/>
-      </c>
-      <c r="F214" t="str">
-        <v>Where the South Winds Wail</v>
-      </c>
-      <c r="G214" t="str">
-        <v>2:31</v>
-      </c>
-      <c r="H214" t="str">
-        <v>Gitkin</v>
-      </c>
-      <c r="I214" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J214" t="str">
-        <v>https://music.apple.com/us/artist/gitkin/1345281815</v>
-      </c>
-      <c r="K214" t="str">
-        <v>https://music.apple.com/us/album/high-tail/1870432670</v>
-      </c>
-      <c r="L214" t="str">
-        <v>High Tail - Gitkin</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="str">
-        <v>Mice Protection</v>
-      </c>
-      <c r="B215" t="str">
-        <v/>
-      </c>
-      <c r="C215" t="str">
-        <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
-      </c>
-      <c r="D215" t="str">
-        <v>2026-05-22</v>
-      </c>
-      <c r="E215" t="str">
-        <v/>
-      </c>
-      <c r="F215" t="str">
-        <v>Ugly Duckling Union</v>
-      </c>
-      <c r="G215" t="str">
-        <v>3:34</v>
-      </c>
-      <c r="H215" t="str">
-        <v>Lowertown</v>
-      </c>
-      <c r="I215" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J215" t="str">
-        <v>https://music.apple.com/us/artist/lowertown/1448207323</v>
-      </c>
-      <c r="K215" t="str">
-        <v>https://music.apple.com/us/album/mice-protection/1872171971</v>
-      </c>
-      <c r="L215" t="str">
-        <v>Mice Protection - Lowertown</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="str">
-        <v>Tóxica</v>
-      </c>
-      <c r="B216" t="str">
-        <v/>
-      </c>
-      <c r="C216" t="str">
-        <v>https://music.apple.com/us/song/t%C3%B3xica/6763056240</v>
-      </c>
-      <c r="D216" t="str">
-        <v>2026-05-22</v>
-      </c>
-      <c r="E216" t="str">
-        <v/>
-      </c>
-      <c r="F216" t="str">
-        <v>Caribenya</v>
-      </c>
-      <c r="G216" t="str">
-        <v>3:48</v>
-      </c>
-      <c r="H216" t="str">
-        <v>Lido Pimienta</v>
-      </c>
-      <c r="I216" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J216" t="str">
-        <v>https://music.apple.com/us/artist/lido-pimienta/389475023</v>
-      </c>
-      <c r="K216" t="str">
-        <v>https://music.apple.com/us/album/t%C3%B3xica/1895141218</v>
-      </c>
-      <c r="L216" t="str">
         <v>Tóxica - Lido Pimienta</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L216"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week04/titles.xlsx
+++ b/data/global/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L200"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>דניאלה גולדפיין – Like a Swing</v>
       </c>
       <c r="B2" t="str">
-        <v>5 days ago</v>
+        <v>2026-05-22</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://yosmusic.com/%d7%93%d7%a0%d7%99%d7%90%d7%9c%d7%94-%d7%92%d7%95%d7%9c%d7%93%d7%a4%d7%99%d7%99%d7%9f-like-a-swing/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-22</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5 days ago</v>
+        <v>השיר “Like a Swing” של דניאלה גולדפיין נוגע ומגיע מתוך הפשטות שלו. אין כאן ניסיון להרשים בהפקה גדולה, מהלכים דרמטיים או כתיבה מתוחכמת מדי, אלא יצירה קטנה, אינטימית וכמעט חשופה, שנשמעת כמו מכתב אישי שהולחן ברגע שקט באמצע הלילה. הרעיון</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Eurovision Song Contest</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>דניאלה גולדפיין – Like a Swing</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>5 days ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-22</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5 days ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B4" t="str">
-        <v>5 days ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-22</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>5 days ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>5 days ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-22</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>5 days ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>5 days ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-22</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>5 days ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>5 days ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-22</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>5 days ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>RUEL</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B8" t="str">
-        <v>6 days ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-22</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>6 days ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Evanescence</v>
+        <v>TINI</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>9 days ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-22</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>9 days ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B10" t="str">
-        <v>5 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-22</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>5 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Armin van Buuren</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-22</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Madison Cunningham</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B12" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-22</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Johnny Orlando</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B13" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-22</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Carver Jones</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B14" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-22</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Jazmin bean</v>
+        <v>kesha</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B15" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-22</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Baby Queen</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-22</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Switchfoot</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B17" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-22</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Grace Potter</v>
+        <v>The Analogues</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B18" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-22</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-22</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>The All-American Rejects</v>
+        <v>Blue October</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-22</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Henry Moodie</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B21" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-22</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Spacey Jane</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>Kenia Os - Love Bombing - Kenia Os</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B22" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-22</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Megan Moroney</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B23" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-22</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Matt Hansen</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B24" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-22</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Matt Hansen</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Keith Urban - Steal Away (Visualizer)</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B25" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-22</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Keith Urban</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>VALÉ - Mugshot (Official Video)</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B26" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-22</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>VALÉ</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio)</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B27" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-22</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Mackenzie Carpenter</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B28" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-22</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Towa Bird</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-22</v>
@@ -1483,7 +1483,7 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Sabrina Sterling</v>
+        <v>Evanescence</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-22</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Little Big Town</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Becky G - EPA (Official Video)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-22</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Becky G</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Becky G - EPA (Official Video) - Becky G</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-22</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Daisy the Great</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Towa Bird - Dog (Official Music Video)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-22</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Towa Bird</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-22</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Madonna</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video)</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B35" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-22</v>
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Ally Salort</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Bella White - Better - Official Music Video</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B36" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-22</v>
@@ -1749,7 +1749,7 @@
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Bella White</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Bella White - Better - Official Music Video - Bella White</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B37" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-22</v>
@@ -1787,7 +1787,7 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B38" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-22</v>
@@ -1825,7 +1825,7 @@
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Towa Bird</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer)</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B39" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-22</v>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Miranda Lambert</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B40" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-22</v>
@@ -1901,7 +1901,7 @@
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Lady Gaga</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B41" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-22</v>
@@ -1939,7 +1939,7 @@
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Gracie Abrams</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-22</v>
@@ -1977,7 +1977,7 @@
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B43" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-22</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Martin Garrix</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Jorja Smith - What's Done Is Done</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B44" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-22</v>
@@ -2053,7 +2053,7 @@
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Jorja Smith</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>LP - Shelly (Official Music Video)</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
+        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-22</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>LP</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>LP - Shelly (Official Music Video) - LP</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
+        <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
+        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-22</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>The Rolling Stones</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
+        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
+        <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
+        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-22</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Oasis</v>
+        <v>VALÉ</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
+        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
+        <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B48" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
+        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-22</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Breaking Benjamin</v>
+        <v>Mackenzie Carpenter</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
+        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
+        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-22</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>VictorBiliac</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
+        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-22</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Linkin Park</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Harry Styles - Dance No More (Official Video)</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
+        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-22</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Harry Styles</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
+        <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
+        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-22</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Eagles</v>
+        <v>Becky G</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
+        <v>Becky G - EPA (Official Video) - Becky G</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
+        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-22</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Nora Fatehi</v>
+        <v>Daisy the Great</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
+        <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>2 months ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
+        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-22</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 months ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B55" t="str">
-        <v>2 months ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
+        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-22</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 months ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Eurovision Song Contest and Alis</v>
+        <v>Madonna</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
+        <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>2 months ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
+        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-22</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 months ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video)</v>
+        <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B57" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
+        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-22</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>The Head And The Heart</v>
+        <v>Bella White</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
+        <v>Bella White - Better - Official Music Video - Bella White</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
+        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-22</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Simply Red</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video)</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B59" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
+        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-22</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Talking Heads</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Ellise - Liplock (Official Music Video)</v>
+        <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
+        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-22</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Ellise</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
+        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Tori Kelly - Dive (Official Music Video)</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B61" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
+        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-22</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Tori Kelly</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
+        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-22</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>David Gilmour</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
+        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-22</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Scorpions</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B64" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
+        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-22</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Claire Leslie</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Michael Schulte - Lovesick (Official Video)</v>
+        <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B65" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
+        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-22</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Michael Schulte</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
+        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Caity Baser - Holiday Song (Official Video)</v>
+        <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
+        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-22</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Caity Baser</v>
+        <v>LP</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
+        <v>LP - Shelly (Official Music Video) - LP</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
+        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-22</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Sam Fischer</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Porches- HABIT (Official Video)</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B68" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
+        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-22</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Porches</v>
+        <v>Oasis</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Porches- HABIT (Official Video) - Porches</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Charli xcx - Rock Music (Official Video)</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
+        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-22</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Charli xcx</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Jon Batiste - Alla Blues (Audio)</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B70" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
+        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-22</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Jon Batiste</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B71" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
+        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-22</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Tigirlily Gold</v>
+        <v>Linkin Park</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
+        <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
+        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-22</v>
@@ -3117,7 +3117,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
+        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-22</v>
@@ -3155,7 +3155,7 @@
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Bruno Mars</v>
+        <v>Eagles</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Tori Kelly - Control (Official Visualizer)</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
+        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-22</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Tori Kelly</v>
+        <v>Nora Fatehi</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
+        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-22</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>bea miller</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
+        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-22</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>The Chainsmokers</v>
+        <v>Eurovision Song Contest and Alis</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Madison Beer - free (Official Audio)</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
+        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-22</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Madison Beer</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Tori Kelly - Dive (Official Audio)</v>
+        <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
+        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-22</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Tori Kelly</v>
+        <v>The Head And The Heart</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
+        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio)</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
+        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-22</v>
@@ -3383,7 +3383,7 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Simply Red</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
+        <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
+        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-22</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>The Chainsmokers</v>
+        <v>Talking Heads</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
+        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Ashley Cooke - high school sweetheart</v>
+        <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
+        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-22</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Ashley Cooke</v>
+        <v>Ellise</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
+        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Ari Abdul - Ego (Visualizer)</v>
+        <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
+        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-22</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Ari Abdul</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Ari Abdul - Ego (Visualizer) - Ari Abdul</v>
+        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Quinn XCII - HOOPLA (Official Music Video)</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
+        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-22</v>
@@ -3535,7 +3535,7 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Quinn XCII</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Quinn XCII - HOOPLA (Official Music Video) - Quinn XCII</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Madison Beer - lovergirl (Official Music Video)</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
+        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-22</v>
@@ -3573,7 +3573,7 @@
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Madison Beer</v>
+        <v>Scorpions</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Madison Beer - lovergirl (Official Music Video) - Madison Beer</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
+        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-22</v>
@@ -3611,7 +3611,7 @@
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>David J</v>
+        <v>Claire Leslie</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>David J - WHAT IF I'M IN LOVE (Official Video) - David J</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>The Last Dinner Party - Big Dog (On The Road)</v>
+        <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
+        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-22</v>
@@ -3649,7 +3649,7 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Michael Schulte</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>The Last Dinner Party - Big Dog (On The Road) - The Last Dinner Party</v>
+        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
+        <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
+        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-22</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Ocean Alley</v>
+        <v>Caity Baser</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>OCEAN ALLEY - HOLD ON (Official Video) - Ocean Alley</v>
+        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Dagny - Closet Disco Queen (Lyric Video)</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
+        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-22</v>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Dagny</v>
+        <v>Sam Fischer</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Dagny - Closet Disco Queen (Lyric Video) - Dagny</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
+        <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
+        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-22</v>
@@ -3763,7 +3763,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Porches</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Purple Disco Machine - Disco Cherry (Official Video) - Purple Disco Machine</v>
+        <v>Porches- HABIT (Official Video) - Porches</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
+        <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
+        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-22</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Paris Paloma</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Paris Paloma - Stem the Flow [Official Music Video] - Paris Paloma</v>
+        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Lucy Blue - Who you love (Visualiser)</v>
+        <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
+        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-22</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Lucy Blue</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Lucy Blue - Who you love (Visualiser) - Lucy Blue</v>
+        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
+        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-22</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Olivia Dean</v>
+        <v>Tigirlily Gold</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026) - Olivia Dean</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Aaron Frazer - It's A Shame (Official Video)</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
+        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-22</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Aaron Frazer</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Aaron Frazer - It's A Shame (Official Video) - Aaron Frazer</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
+        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-22</v>
@@ -3953,7 +3953,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Holly Humberstone</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>DANNA - OUT OF MY BODY</v>
+        <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
+        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-22</v>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Danna</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>DANNA - OUT OF MY BODY - Danna</v>
+        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
+        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-22</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>The Rolling Stones</v>
+        <v>bea miller</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>The Rolling Stones - In The Stars (Official Lyric Video) - The Rolling Stones</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
+        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-22</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Dermot Kennedy</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser) - Dermot Kennedy</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
+        <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
+        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-22</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
+        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Rick Astley - Raindrops (Official Video)</v>
+        <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
+        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-22</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Rick Astley</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
+        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video)</v>
+        <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
+        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-22</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Jessie J</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
+        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>The Takes - Ain't Love (Lyric Video)</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
+        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-22</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>The Takes</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>From Down Here</v>
+        <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
+        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-22</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>From Down Here - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>4:01</v>
+        <v/>
       </c>
       <c r="H102" t="str">
-        <v>Lola Young</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/lola-young/452271760</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/from-down-here/6768357139</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>From Down Here - Lola Young</v>
+        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>the cure</v>
+        <v>From Down Here</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/the-cure/1889992123</v>
+        <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-22</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>you seem pretty sad for a girl so in love</v>
+        <v>From Down Here - Single</v>
       </c>
       <c r="G103" t="str">
-        <v>4:57</v>
+        <v>4:01</v>
       </c>
       <c r="H103" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Lola Young</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
+        <v>https://music.apple.com/us/artist/lola-young/452271760</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/the-cure/1889992111</v>
+        <v>https://music.apple.com/us/album/from-down-here/6768357139</v>
       </c>
       <c r="L103" t="str">
-        <v>the cure - Olivia Rodrigo</v>
+        <v>From Down Here - Lola Young</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>SS26</v>
+        <v>the cure</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/ss26/6771061782</v>
+        <v>https://music.apple.com/us/song/the-cure/1889992123</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-22</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>SS26 - Single</v>
+        <v>you seem pretty sad for a girl so in love</v>
       </c>
       <c r="G104" t="str">
-        <v>2:47</v>
+        <v>4:57</v>
       </c>
       <c r="H104" t="str">
-        <v>Charli xcx</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/ss26/6771061771</v>
+        <v>https://music.apple.com/us/album/the-cure/1889992111</v>
       </c>
       <c r="L104" t="str">
-        <v>SS26 - Charli xcx</v>
+        <v>the cure - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>White Flag</v>
+        <v>SS26</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/white-flag/1887627840</v>
+        <v>https://music.apple.com/us/song/ss26/6771061782</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-22</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Cry Baby</v>
+        <v>SS26 - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>2:34</v>
+        <v>2:47</v>
       </c>
       <c r="H105" t="str">
-        <v>Vince Staples</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/white-flag/1887627836</v>
+        <v>https://music.apple.com/us/album/ss26/6771061771</v>
       </c>
       <c r="L105" t="str">
-        <v>White Flag - Vince Staples</v>
+        <v>SS26 - Charli xcx</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Knew Better Part Two</v>
+        <v>White Flag</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
+        <v>https://music.apple.com/us/song/white-flag/1887627840</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-22</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Dangerous Woman (Tenth Anniversary Edition)</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G106" t="str">
-        <v>2:44</v>
+        <v>2:34</v>
       </c>
       <c r="H106" t="str">
-        <v>Ariana Grande</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/knew-better-part-two/6770600996</v>
+        <v>https://music.apple.com/us/album/white-flag/1887627836</v>
       </c>
       <c r="L106" t="str">
-        <v>Knew Better Part Two - Ariana Grande</v>
+        <v>White Flag - Vince Staples</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Goals</v>
+        <v>Knew Better Part Two</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/goals/6769251838</v>
+        <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-22</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Goals (FIFA World Cup 2026™) - Single</v>
+        <v>Dangerous Woman (Tenth Anniversary Edition)</v>
       </c>
       <c r="G107" t="str">
-        <v>3:00</v>
+        <v>2:44</v>
       </c>
       <c r="H107" t="str">
-        <v>LISA</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/lisa/1583908668</v>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/goals/6769251829</v>
+        <v>https://music.apple.com/us/album/knew-better-part-two/6770600996</v>
       </c>
       <c r="L107" t="str">
-        <v>Goals - LISA</v>
+        <v>Knew Better Part Two - Ariana Grande</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>we should talk</v>
+        <v>Goals</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
+        <v>https://music.apple.com/us/song/goals/6769251838</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-22</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Goals (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:04</v>
+        <v>3:00</v>
       </c>
       <c r="H108" t="str">
-        <v>Bleachers</v>
+        <v>LISA</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/lisa/1583908668</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/we-should-talk/1872842313</v>
+        <v>https://music.apple.com/us/album/goals/6769251829</v>
       </c>
       <c r="L108" t="str">
-        <v>we should talk - Bleachers</v>
+        <v>Goals - LISA</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Do What You Gotta Do</v>
+        <v>we should talk</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
+        <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-22</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>NeverAlways (Vol. 2)</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G109" t="str">
-        <v>3:26</v>
+        <v>3:04</v>
       </c>
       <c r="H109" t="str">
-        <v>The Band CAMINO</v>
+        <v>Bleachers</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/do-what-you-gotta-do/1887616173</v>
+        <v>https://music.apple.com/us/album/we-should-talk/1872842313</v>
       </c>
       <c r="L109" t="str">
-        <v>Do What You Gotta Do - The Band CAMINO</v>
+        <v>we should talk - Bleachers</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Ego</v>
+        <v>Do What You Gotta Do</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/ego/6769207667</v>
+        <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-22</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Ego - Single</v>
+        <v>NeverAlways (Vol. 2)</v>
       </c>
       <c r="G110" t="str">
-        <v>2:53</v>
+        <v>3:26</v>
       </c>
       <c r="H110" t="str">
-        <v>The Warning</v>
+        <v>The Band CAMINO</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/ego/6769207665</v>
+        <v>https://music.apple.com/us/album/do-what-you-gotta-do/1887616173</v>
       </c>
       <c r="L110" t="str">
-        <v>Ego - The Warning</v>
+        <v>Do What You Gotta Do - The Band CAMINO</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Light up (From the Netflix Documentary 'kylie')</v>
+        <v>Ego</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
+        <v>https://music.apple.com/us/song/ego/6769207667</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-22</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Light up (From the Netflix Documentary 'Kylie') - Single</v>
+        <v>Ego - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:17</v>
+        <v>2:53</v>
       </c>
       <c r="H111" t="str">
-        <v>Kylie Minogue</v>
+        <v>The Warning</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/kylie-minogue/465031</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/light-up-from-the-netflix-documentary-kylie/6768013505</v>
+        <v>https://music.apple.com/us/album/ego/6769207665</v>
       </c>
       <c r="L111" t="str">
-        <v>Light up (From the Netflix Documentary 'kylie') - Kylie Minogue</v>
+        <v>Ego - The Warning</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>All That Matters</v>
+        <v>Light up (From the Netflix Documentary 'kylie')</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
+        <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-22</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Light up (From the Netflix Documentary 'Kylie') - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:43</v>
+        <v>3:17</v>
       </c>
       <c r="H112" t="str">
-        <v>6LACK</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/kylie-minogue/465031</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/all-that-matters/1884792154</v>
+        <v>https://music.apple.com/us/album/light-up-from-the-netflix-documentary-kylie/6768013505</v>
       </c>
       <c r="L112" t="str">
-        <v>All That Matters - 6LACK</v>
+        <v>Light up (From the Netflix Documentary 'kylie') - Kylie Minogue</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Like A Virgin</v>
+        <v>All That Matters</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
+        <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-22</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Terrified .</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G113" t="str">
-        <v>2:34</v>
+        <v>3:43</v>
       </c>
       <c r="H113" t="str">
-        <v>fakemink</v>
+        <v>6LACK</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/like-a-virgin/6768157748</v>
+        <v>https://music.apple.com/us/album/all-that-matters/1884792154</v>
       </c>
       <c r="L113" t="str">
-        <v>Like A Virgin - fakemink</v>
+        <v>All That Matters - 6LACK</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>24 Hours</v>
+        <v>Like A Virgin</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/24-hours/6771060076</v>
+        <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-22</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>24 Hours - Single</v>
+        <v>Terrified .</v>
       </c>
       <c r="G114" t="str">
-        <v>3:17</v>
+        <v>2:34</v>
       </c>
       <c r="H114" t="str">
-        <v>Stormzy</v>
+        <v>fakemink</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/stormzy/394865154</v>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/24-hours/6771060073</v>
+        <v>https://music.apple.com/us/album/like-a-virgin/6768157748</v>
       </c>
       <c r="L114" t="str">
-        <v>24 Hours - Stormzy</v>
+        <v>Like A Virgin - fakemink</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>HOES (From Scary Movie)</v>
+        <v>24 Hours</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
+        <v>https://music.apple.com/us/song/24-hours/6771060076</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-22</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>HOES (From Scary Movie) - Single</v>
+        <v>24 Hours - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>2:09</v>
+        <v>3:17</v>
       </c>
       <c r="H115" t="str">
-        <v>Lizzo</v>
+        <v>Stormzy</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/stormzy/394865154</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/hoes-from-scary-movie/6770661290</v>
+        <v>https://music.apple.com/us/album/24-hours/6771060073</v>
       </c>
       <c r="L115" t="str">
-        <v>HOES (From Scary Movie) - Lizzo</v>
+        <v>24 Hours - Stormzy</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Ms. Tundra</v>
+        <v>HOES (From Scary Movie)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
+        <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-22</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Highway 79</v>
+        <v>HOES (From Scary Movie) - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:12</v>
+        <v>2:09</v>
       </c>
       <c r="H116" t="str">
-        <v>Ne-Yo</v>
+        <v>Lizzo</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/ms-tundra/6770614875</v>
+        <v>https://music.apple.com/us/album/hoes-from-scary-movie/6770661290</v>
       </c>
       <c r="L116" t="str">
-        <v>Ms. Tundra - Ne-Yo</v>
+        <v>HOES (From Scary Movie) - Lizzo</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>TARENTINO</v>
+        <v>Ms. Tundra</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/tarentino/6769927265</v>
+        <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-22</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>TARENTINO - Single</v>
+        <v>Highway 79</v>
       </c>
       <c r="G117" t="str">
-        <v>2:23</v>
+        <v>3:12</v>
       </c>
       <c r="H117" t="str">
-        <v>Labrinth</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/tarentino/6769927262</v>
+        <v>https://music.apple.com/us/album/ms-tundra/6770614875</v>
       </c>
       <c r="L117" t="str">
-        <v>TARENTINO - Labrinth</v>
+        <v>Ms. Tundra - Ne-Yo</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Daydreamin’</v>
+        <v>TARENTINO</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
+        <v>https://music.apple.com/us/song/tarentino/6769927265</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-22</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>KONNAKOL (Deluxe)</v>
+        <v>TARENTINO - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:58</v>
+        <v>2:23</v>
       </c>
       <c r="H118" t="str">
-        <v>ZAYN</v>
+        <v>Labrinth</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/daydreamin/6769559345</v>
+        <v>https://music.apple.com/us/album/tarentino/6769927262</v>
       </c>
       <c r="L118" t="str">
-        <v>Daydreamin’ - ZAYN</v>
+        <v>TARENTINO - Labrinth</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>End of an Era</v>
+        <v>Daydreamin’</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
+        <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-22</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Dinner Party</v>
+        <v>KONNAKOL (Deluxe)</v>
       </c>
       <c r="G119" t="str">
-        <v>3:38</v>
+        <v>2:58</v>
       </c>
       <c r="H119" t="str">
-        <v>Niall Horan</v>
+        <v>ZAYN</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/end-of-an-era/1884418567</v>
+        <v>https://music.apple.com/us/album/daydreamin/6769559345</v>
       </c>
       <c r="L119" t="str">
-        <v>End of an Era - Niall Horan</v>
+        <v>Daydreamin’ - ZAYN</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Questions</v>
+        <v>End of an Era</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/questions/1871502847</v>
+        <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-22</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Florescence</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G120" t="str">
-        <v>3:07</v>
+        <v>3:38</v>
       </c>
       <c r="H120" t="str">
-        <v>Maisie Peters</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/questions/1871502372</v>
+        <v>https://music.apple.com/us/album/end-of-an-era/1884418567</v>
       </c>
       <c r="L120" t="str">
-        <v>Questions - Maisie Peters</v>
+        <v>End of an Era - Niall Horan</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Heart Has To Work So Hard</v>
+        <v>Questions</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
+        <v>https://music.apple.com/us/song/questions/1871502847</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-22</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Heart Has To Work So Hard - Single</v>
+        <v>Florescence</v>
       </c>
       <c r="G121" t="str">
-        <v>3:12</v>
+        <v>3:07</v>
       </c>
       <c r="H121" t="str">
-        <v>Blondshell</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/blondshell/1624592688</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/heart-has-to-work-so-hard/1895982147</v>
+        <v>https://music.apple.com/us/album/questions/1871502372</v>
       </c>
       <c r="L121" t="str">
-        <v>Heart Has To Work So Hard - Blondshell</v>
+        <v>Questions - Maisie Peters</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski)</v>
+        <v>Heart Has To Work So Hard</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
+        <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-22</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski) - Single</v>
+        <v>Heart Has To Work So Hard - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:44</v>
+        <v>3:12</v>
       </c>
       <c r="H122" t="str">
-        <v>Kygo</v>
+        <v>Blondshell</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/blondshell/1624592688</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-your-mind-feat-dan-tyminski/6769007431</v>
+        <v>https://music.apple.com/us/album/heart-has-to-work-so-hard/1895982147</v>
       </c>
       <c r="L122" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski) - Kygo</v>
+        <v>Heart Has To Work So Hard - Blondshell</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>PERDISTE EL EMMY.</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
+        <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-22</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>OMAKASE</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski) - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>4:03</v>
+        <v>3:44</v>
       </c>
       <c r="H123" t="str">
-        <v>Álvaro Díaz</v>
+        <v>Kygo</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/perdiste-el-emmy/6771082594</v>
+        <v>https://music.apple.com/us/album/heaven-on-your-mind-feat-dan-tyminski/6769007431</v>
       </c>
       <c r="L123" t="str">
-        <v>PERDISTE EL EMMY. - Álvaro Díaz</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski) - Kygo</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Dosis</v>
+        <v>PERDISTE EL EMMY.</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/dosis/6762929729</v>
+        <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-22</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>DOSIS</v>
+        <v>OMAKASE</v>
       </c>
       <c r="G124" t="str">
-        <v>3:00</v>
+        <v>4:03</v>
       </c>
       <c r="H124" t="str">
-        <v>Xavi</v>
+        <v>Álvaro Díaz</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/dosis/1895081885</v>
+        <v>https://music.apple.com/us/album/perdiste-el-emmy/6771082594</v>
       </c>
       <c r="L124" t="str">
-        <v>Dosis - Xavi</v>
+        <v>PERDISTE EL EMMY. - Álvaro Díaz</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Would U Still Love Me</v>
+        <v>Dosis</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
+        <v>https://music.apple.com/us/song/dosis/6762929729</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-22</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Whitcomb vs. Flores - Single</v>
+        <v>DOSIS</v>
       </c>
       <c r="G125" t="str">
-        <v>2:36</v>
+        <v>3:00</v>
       </c>
       <c r="H125" t="str">
-        <v>Diplo</v>
+        <v>Xavi</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/would-u-still-love-me/6769907832</v>
+        <v>https://music.apple.com/us/album/dosis/1895081885</v>
       </c>
       <c r="L125" t="str">
-        <v>Would U Still Love Me - Diplo</v>
+        <v>Dosis - Xavi</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Saving This Bottle</v>
+        <v>Would U Still Love Me</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
+        <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-22</v>
@@ -5166,7 +5166,7 @@
         <v>Whitcomb vs. Flores - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:05</v>
+        <v>2:36</v>
       </c>
       <c r="H126" t="str">
         <v>Diplo</v>
@@ -5178,21 +5178,21 @@
         <v>https://music.apple.com/us/artist/diplo/1468290871</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/saving-this-bottle/6769907832</v>
+        <v>https://music.apple.com/us/album/would-u-still-love-me/6769907832</v>
       </c>
       <c r="L126" t="str">
-        <v>Saving This Bottle - Diplo</v>
+        <v>Would U Still Love Me - Diplo</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>The Climb</v>
+        <v>Saving This Bottle</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/the-climb/6769546149</v>
+        <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-22</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>The Climb - Single</v>
+        <v>Whitcomb vs. Flores - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:50</v>
+        <v>3:05</v>
       </c>
       <c r="H127" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Diplo</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/the-climb/6769546147</v>
+        <v>https://music.apple.com/us/album/saving-this-bottle/6769907832</v>
       </c>
       <c r="L127" t="str">
-        <v>The Climb - Bailey Zimmerman</v>
+        <v>Saving This Bottle - Diplo</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>everything tatted</v>
+        <v>The Climb</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
+        <v>https://music.apple.com/us/song/the-climb/6769546149</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-22</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>everything tatted - Single</v>
+        <v>The Climb - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:25</v>
+        <v>3:50</v>
       </c>
       <c r="H128" t="str">
-        <v>mgk</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/everything-tatted/6770773606</v>
+        <v>https://music.apple.com/us/album/the-climb/6769546147</v>
       </c>
       <c r="L128" t="str">
-        <v>everything tatted - mgk</v>
+        <v>The Climb - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>BOOMPALA</v>
+        <v>everything tatted</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/boompala/1894802726</v>
+        <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-22</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>'PUREFLOW', Pt. 1</v>
+        <v>everything tatted - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:56</v>
+        <v>3:25</v>
       </c>
       <c r="H129" t="str">
-        <v>LE SSERAFIM</v>
+        <v>mgk</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/boompala/1894802719</v>
+        <v>https://music.apple.com/us/album/everything-tatted/6770773606</v>
       </c>
       <c r="L129" t="str">
-        <v>BOOMPALA - LE SSERAFIM</v>
+        <v>everything tatted - mgk</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Let Me Be In Your Arms</v>
+        <v>BOOMPALA</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
+        <v>https://music.apple.com/us/song/boompala/1894802726</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-22</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>can we do it all again?</v>
+        <v>'PUREFLOW', Pt. 1</v>
       </c>
       <c r="G130" t="str">
-        <v>3:13</v>
+        <v>2:56</v>
       </c>
       <c r="H130" t="str">
-        <v>Sonny Fodera</v>
+        <v>LE SSERAFIM</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/let-me-be-in-your-arms/1881610862</v>
+        <v>https://music.apple.com/us/album/boompala/1894802719</v>
       </c>
       <c r="L130" t="str">
-        <v>Let Me Be In Your Arms - Sonny Fodera</v>
+        <v>BOOMPALA - LE SSERAFIM</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Eat, Work, Pray</v>
+        <v>Let Me Be In Your Arms</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
+        <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-22</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Eat, Work, Pray - Single</v>
+        <v>can we do it all again?</v>
       </c>
       <c r="G131" t="str">
-        <v>2:28</v>
+        <v>3:13</v>
       </c>
       <c r="H131" t="str">
-        <v>Sheff G</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/eat-work-pray/6769134493</v>
+        <v>https://music.apple.com/us/album/let-me-be-in-your-arms/1881610862</v>
       </c>
       <c r="L131" t="str">
-        <v>Eat, Work, Pray - Sheff G</v>
+        <v>Let Me Be In Your Arms - Sonny Fodera</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>touch myself</v>
+        <v>Eat, Work, Pray</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
+        <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-22</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>and all pride aside</v>
+        <v>Eat, Work, Pray - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>4:09</v>
+        <v>2:28</v>
       </c>
       <c r="H132" t="str">
-        <v>kwn</v>
+        <v>Sheff G</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/touch-myself/6769880663</v>
+        <v>https://music.apple.com/us/album/eat-work-pray/6769134493</v>
       </c>
       <c r="L132" t="str">
-        <v>touch myself - kwn</v>
+        <v>Eat, Work, Pray - Sheff G</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Comes and Goes</v>
+        <v>touch myself</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
+        <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-22</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Comes and Goes - Single</v>
+        <v>and all pride aside</v>
       </c>
       <c r="G133" t="str">
-        <v>4:22</v>
+        <v>4:09</v>
       </c>
       <c r="H133" t="str">
-        <v>KETTAMA</v>
+        <v>kwn</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/kettama/1425703970</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/comes-and-goes/6766618930</v>
+        <v>https://music.apple.com/us/album/touch-myself/6769880663</v>
       </c>
       <c r="L133" t="str">
-        <v>Comes and Goes - KETTAMA</v>
+        <v>touch myself - kwn</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Dear God</v>
+        <v>Comes and Goes</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/dear-god/1878237813</v>
+        <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-22</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Dear God</v>
+        <v>Comes and Goes - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>6:08</v>
+        <v>4:22</v>
       </c>
       <c r="H134" t="str">
-        <v>The Pretty Reckless</v>
+        <v>KETTAMA</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/kettama/1425703970</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/dear-god/1878237662</v>
+        <v>https://music.apple.com/us/album/comes-and-goes/6766618930</v>
       </c>
       <c r="L134" t="str">
-        <v>Dear God - The Pretty Reckless</v>
+        <v>Comes and Goes - KETTAMA</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Hexagons</v>
+        <v>Dear God</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/hexagons/1885607736</v>
+        <v>https://music.apple.com/us/song/dear-god/1878237813</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-22</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>The Wow! Signal</v>
+        <v>Dear God</v>
       </c>
       <c r="G135" t="str">
-        <v>5:26</v>
+        <v>6:08</v>
       </c>
       <c r="H135" t="str">
-        <v>Muse</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/hexagons/1885607338</v>
+        <v>https://music.apple.com/us/album/dear-god/1878237662</v>
       </c>
       <c r="L135" t="str">
-        <v>Hexagons - Muse</v>
+        <v>Dear God - The Pretty Reckless</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Facile-Batiste</v>
+        <v>Hexagons</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
+        <v>https://music.apple.com/us/song/hexagons/1885607736</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-22</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Black Mozart</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G136" t="str">
-        <v>4:55</v>
+        <v>5:26</v>
       </c>
       <c r="H136" t="str">
-        <v>Jon Batiste</v>
+        <v>Muse</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/facile-batiste/1895866355</v>
+        <v>https://music.apple.com/us/album/hexagons/1885607338</v>
       </c>
       <c r="L136" t="str">
-        <v>Facile-Batiste - Jon Batiste</v>
+        <v>Hexagons - Muse</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Pop Pop</v>
+        <v>Facile-Batiste</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
+        <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-22</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Pop Pop - Single</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G137" t="str">
-        <v>2:57</v>
+        <v>4:55</v>
       </c>
       <c r="H137" t="str">
-        <v>Channel Tres</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/pop-pop/1896269430</v>
+        <v>https://music.apple.com/us/album/facile-batiste/1895866355</v>
       </c>
       <c r="L137" t="str">
-        <v>Pop Pop - Channel Tres</v>
+        <v>Facile-Batiste - Jon Batiste</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>One Of Us</v>
+        <v>Pop Pop</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
+        <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-22</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>One Of Us - Single</v>
+        <v>Pop Pop - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:35</v>
+        <v>2:57</v>
       </c>
       <c r="H138" t="str">
-        <v>Chris Young</v>
+        <v>Channel Tres</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/chris-young/4779205</v>
+        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/one-of-us/1895402922</v>
+        <v>https://music.apple.com/us/album/pop-pop/1896269430</v>
       </c>
       <c r="L138" t="str">
-        <v>One Of Us - Chris Young</v>
+        <v>Pop Pop - Channel Tres</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Sins of the Father</v>
+        <v>One Of Us</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
+        <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-22</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Is God Is (Original Motion Picture Soundtrack)</v>
+        <v>One Of Us - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:20</v>
+        <v>3:35</v>
       </c>
       <c r="H139" t="str">
-        <v>Moses Sumney</v>
+        <v>Chris Young</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/moses-sumney/843536848</v>
+        <v>https://music.apple.com/us/artist/chris-young/4779205</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/sins-of-the-father/6771012707</v>
+        <v>https://music.apple.com/us/album/one-of-us/1895402922</v>
       </c>
       <c r="L139" t="str">
-        <v>Sins of the Father - Moses Sumney</v>
+        <v>One Of Us - Chris Young</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Life On The Run</v>
+        <v>Sins of the Father</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
+        <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-22</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Life On The Run - Single</v>
+        <v>Is God Is (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G140" t="str">
-        <v>3:49</v>
+        <v>3:20</v>
       </c>
       <c r="H140" t="str">
-        <v>Brandi Carlile</v>
+        <v>Moses Sumney</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/brandi-carlile/64387579</v>
+        <v>https://music.apple.com/us/artist/moses-sumney/843536848</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/life-on-the-run/6766761019</v>
+        <v>https://music.apple.com/us/album/sins-of-the-father/6771012707</v>
       </c>
       <c r="L140" t="str">
-        <v>Life On The Run - Brandi Carlile</v>
+        <v>Sins of the Father - Moses Sumney</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>New York Confident</v>
+        <v>Life On The Run</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
+        <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-22</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>New York Confident - Single</v>
+        <v>Life On The Run - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:27</v>
+        <v>3:49</v>
       </c>
       <c r="H141" t="str">
-        <v>Mark Ambor</v>
+        <v>Brandi Carlile</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/mark-ambor/1459754985</v>
+        <v>https://music.apple.com/us/artist/brandi-carlile/64387579</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/new-york-confident/6765558036</v>
+        <v>https://music.apple.com/us/album/life-on-the-run/6766761019</v>
       </c>
       <c r="L141" t="str">
-        <v>New York Confident - Mark Ambor</v>
+        <v>Life On The Run - Brandi Carlile</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>pequeñita!</v>
+        <v>New York Confident</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
+        <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-22</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>pequeñita! - Single</v>
+        <v>New York Confident - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:39</v>
+        <v>2:27</v>
       </c>
       <c r="H142" t="str">
-        <v>Judeline</v>
+        <v>Mark Ambor</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/judeline/1487503245</v>
+        <v>https://music.apple.com/us/artist/mark-ambor/1459754985</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/peque%C3%B1ita/6769827604</v>
+        <v>https://music.apple.com/us/album/new-york-confident/6765558036</v>
       </c>
       <c r="L142" t="str">
-        <v>pequeñita! - Judeline</v>
+        <v>New York Confident - Mark Ambor</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Opaline</v>
+        <v>pequeñita!</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/opaline/1886737060</v>
+        <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-22</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>pequeñita! - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:17</v>
+        <v>2:39</v>
       </c>
       <c r="H143" t="str">
-        <v>Stephan Moccio</v>
+        <v>Judeline</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/judeline/1487503245</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/opaline/1886736650</v>
+        <v>https://music.apple.com/us/album/peque%C3%B1ita/6769827604</v>
       </c>
       <c r="L143" t="str">
-        <v>Opaline - Stephan Moccio</v>
+        <v>pequeñita! - Judeline</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Pretty Little Things</v>
+        <v>Opaline</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
+        <v>https://music.apple.com/us/song/opaline/1886737060</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-22</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Pretty Little Things - Single</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G144" t="str">
-        <v>2:51</v>
+        <v>3:17</v>
       </c>
       <c r="H144" t="str">
-        <v>Lauv</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/pretty-little-things/6767353963</v>
+        <v>https://music.apple.com/us/album/opaline/1886736650</v>
       </c>
       <c r="L144" t="str">
-        <v>Pretty Little Things - Lauv</v>
+        <v>Opaline - Stephan Moccio</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>COLORADO</v>
+        <v>Pretty Little Things</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/colorado/6769065232</v>
+        <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-22</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>COLORADO - Single</v>
+        <v>Pretty Little Things - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>1:54</v>
+        <v>2:51</v>
       </c>
       <c r="H145" t="str">
-        <v>Loud Luxury</v>
+        <v>Lauv</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/colorado/6769064981</v>
+        <v>https://music.apple.com/us/album/pretty-little-things/6767353963</v>
       </c>
       <c r="L145" t="str">
-        <v>COLORADO - Loud Luxury</v>
+        <v>Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Infidelidad</v>
+        <v>COLORADO</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
+        <v>https://music.apple.com/us/song/colorado/6769065232</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-22</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>El Disco de Salsa</v>
+        <v>COLORADO - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:29</v>
+        <v>1:54</v>
       </c>
       <c r="H146" t="str">
-        <v>Neutro Shorty</v>
+        <v>Loud Luxury</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/neutro-shorty/1066850977</v>
+        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/infidelidad/6768853655</v>
+        <v>https://music.apple.com/us/album/colorado/6769064981</v>
       </c>
       <c r="L146" t="str">
-        <v>Infidelidad - Neutro Shorty</v>
+        <v>COLORADO - Loud Luxury</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Wrong Place, Wrong time</v>
+        <v>Infidelidad</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
+        <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-22</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Y'all Won</v>
+        <v>El Disco de Salsa</v>
       </c>
       <c r="G147" t="str">
-        <v>2:57</v>
+        <v>3:29</v>
       </c>
       <c r="H147" t="str">
-        <v>Veeze</v>
+        <v>Neutro Shorty</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
+        <v>https://music.apple.com/us/artist/neutro-shorty/1066850977</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/wrong-place-wrong-time/6771553812</v>
+        <v>https://music.apple.com/us/album/infidelidad/6768853655</v>
       </c>
       <c r="L147" t="str">
-        <v>Wrong Place, Wrong time - Veeze</v>
+        <v>Infidelidad - Neutro Shorty</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>La Semana</v>
+        <v>Wrong Place, Wrong time</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/la-semana/6769913466</v>
+        <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-22</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>No Quiero Que Se Acabe Este Bendito Verano - EP</v>
+        <v>Y'all Won</v>
       </c>
       <c r="G148" t="str">
-        <v>3:30</v>
+        <v>2:57</v>
       </c>
       <c r="H148" t="str">
-        <v>ELENA ROSE</v>
+        <v>Veeze</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/la-semana/6769913464</v>
+        <v>https://music.apple.com/us/album/wrong-place-wrong-time/6771553812</v>
       </c>
       <c r="L148" t="str">
-        <v>La Semana - ELENA ROSE</v>
+        <v>Wrong Place, Wrong time - Veeze</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Una Mujer Como la Suya</v>
+        <v>La Semana</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
+        <v>https://music.apple.com/us/song/la-semana/6769913466</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-22</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Bandera Blanca</v>
+        <v>No Quiero Que Se Acabe Este Bendito Verano - EP</v>
       </c>
       <c r="G149" t="str">
-        <v>3:34</v>
+        <v>3:30</v>
       </c>
       <c r="H149" t="str">
-        <v>Christian Nodal</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/una-mujer-como-la-suya/1895154946</v>
+        <v>https://music.apple.com/us/album/la-semana/6769913464</v>
       </c>
       <c r="L149" t="str">
-        <v>Una Mujer Como la Suya - Christian Nodal</v>
+        <v>La Semana - ELENA ROSE</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Cold</v>
+        <v>Una Mujer Como la Suya</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/cold/6763763802</v>
+        <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-22</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Cold - Single</v>
+        <v>Bandera Blanca</v>
       </c>
       <c r="G150" t="str">
-        <v>2:52</v>
+        <v>3:34</v>
       </c>
       <c r="H150" t="str">
-        <v>Majid Jordan</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/majid-jordan/684530590</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/cold/1895478371</v>
+        <v>https://music.apple.com/us/album/una-mujer-como-la-suya/1895154946</v>
       </c>
       <c r="L150" t="str">
-        <v>Cold - Majid Jordan</v>
+        <v>Una Mujer Como la Suya - Christian Nodal</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>VERTICAL WORLDS</v>
+        <v>Cold</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
+        <v>https://music.apple.com/us/song/cold/6763763802</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-22</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
+        <v>Cold - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:15</v>
+        <v>2:52</v>
       </c>
       <c r="H151" t="str">
-        <v>Ecca Vandal</v>
+        <v>Majid Jordan</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
+        <v>https://music.apple.com/us/artist/majid-jordan/684530590</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/vertical-worlds/1886485694</v>
+        <v>https://music.apple.com/us/album/cold/1895478371</v>
       </c>
       <c r="L151" t="str">
-        <v>VERTICAL WORLDS - Ecca Vandal</v>
+        <v>Cold - Majid Jordan</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Child of Divorce</v>
+        <v>VERTICAL WORLDS</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
+        <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-22</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>soft pop</v>
+        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
       </c>
       <c r="G152" t="str">
-        <v>3:24</v>
+        <v>3:15</v>
       </c>
       <c r="H152" t="str">
-        <v>Amy Shark</v>
+        <v>Ecca Vandal</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
+        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/child-of-divorce/1880496743</v>
+        <v>https://music.apple.com/us/album/vertical-worlds/1886485694</v>
       </c>
       <c r="L152" t="str">
-        <v>Child of Divorce - Amy Shark</v>
+        <v>VERTICAL WORLDS - Ecca Vandal</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Taboo</v>
+        <v>Child of Divorce</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/taboo/6762838716</v>
+        <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-22</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Taboo - Single</v>
+        <v>soft pop</v>
       </c>
       <c r="G153" t="str">
-        <v>3:38</v>
+        <v>3:24</v>
       </c>
       <c r="H153" t="str">
-        <v>Jensen McRae</v>
+        <v>Amy Shark</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/jensen-mcrae/591974463</v>
+        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/taboo/1895036934</v>
+        <v>https://music.apple.com/us/album/child-of-divorce/1880496743</v>
       </c>
       <c r="L153" t="str">
-        <v>Taboo - Jensen McRae</v>
+        <v>Child of Divorce - Amy Shark</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>I'M OK</v>
+        <v>Taboo</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/im-ok/1893392647</v>
+        <v>https://music.apple.com/us/song/taboo/6762838716</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-22</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>A Rii Set</v>
+        <v>Taboo - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:37</v>
+        <v>3:38</v>
       </c>
       <c r="H154" t="str">
-        <v>Pheelz</v>
+        <v>Jensen McRae</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
+        <v>https://music.apple.com/us/artist/jensen-mcrae/591974463</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/im-ok/1893392643</v>
+        <v>https://music.apple.com/us/album/taboo/1895036934</v>
       </c>
       <c r="L154" t="str">
-        <v>I'M OK - Pheelz</v>
+        <v>Taboo - Jensen McRae</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Butterfly Feelings</v>
+        <v>I'M OK</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
+        <v>https://music.apple.com/us/song/im-ok/1893392647</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-22</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Ritual</v>
+        <v>A Rii Set</v>
       </c>
       <c r="G155" t="str">
-        <v>2:35</v>
+        <v>2:37</v>
       </c>
       <c r="H155" t="str">
-        <v>Icona Pop</v>
+        <v>Pheelz</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/butterfly-feelings/1892426976</v>
+        <v>https://music.apple.com/us/album/im-ok/1893392643</v>
       </c>
       <c r="L155" t="str">
-        <v>Butterfly Feelings - Icona Pop</v>
+        <v>I'M OK - Pheelz</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>F**k the DJ</v>
+        <v>Butterfly Feelings</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
+        <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-22</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Stage Girl (Not A Dream Anymore)</v>
+        <v>Ritual</v>
       </c>
       <c r="G156" t="str">
-        <v>2:57</v>
+        <v>2:35</v>
       </c>
       <c r="H156" t="str">
-        <v>Eli</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/f-k-the-dj/6769903867</v>
+        <v>https://music.apple.com/us/album/butterfly-feelings/1892426976</v>
       </c>
       <c r="L156" t="str">
-        <v>F**k the DJ - Eli</v>
+        <v>Butterfly Feelings - Icona Pop</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Grateful</v>
+        <v>F**k the DJ</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/grateful/1887166624</v>
+        <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-22</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>24</v>
+        <v>Stage Girl (Not A Dream Anymore)</v>
       </c>
       <c r="G157" t="str">
-        <v>2:18</v>
+        <v>2:57</v>
       </c>
       <c r="H157" t="str">
-        <v>Alexis Ffrench</v>
+        <v>Eli</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/grateful/1887166427</v>
+        <v>https://music.apple.com/us/album/f-k-the-dj/6769903867</v>
       </c>
       <c r="L157" t="str">
-        <v>Grateful - Alexis Ffrench</v>
+        <v>F**k the DJ - Eli</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Second Chance</v>
+        <v>Grateful</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/second-chance/6766778687</v>
+        <v>https://music.apple.com/us/song/grateful/1887166624</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-22</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Second Chance - Single</v>
+        <v>24</v>
       </c>
       <c r="G158" t="str">
-        <v>3:06</v>
+        <v>2:18</v>
       </c>
       <c r="H158" t="str">
-        <v>Lukas Graham</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/lukas-graham/473219952</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/second-chance/6766778682</v>
+        <v>https://music.apple.com/us/album/grateful/1887166427</v>
       </c>
       <c r="L158" t="str">
-        <v>Second Chance - Lukas Graham</v>
+        <v>Grateful - Alexis Ffrench</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Stupid World (feat. Chad Tepper) [Bonus Track]</v>
+        <v>Second Chance</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
+        <v>https://music.apple.com/us/song/second-chance/6766778687</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-22</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Tommyland Rides Again</v>
+        <v>Second Chance - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:49</v>
+        <v>3:06</v>
       </c>
       <c r="H159" t="str">
-        <v>Tommy Lee</v>
+        <v>Lukas Graham</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/tommy-lee/68696</v>
+        <v>https://music.apple.com/us/artist/lukas-graham/473219952</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/stupid-world-feat-chad-tepper-bonus-track/1893473875</v>
+        <v>https://music.apple.com/us/album/second-chance/6766778682</v>
       </c>
       <c r="L159" t="str">
-        <v>Stupid World (feat. Chad Tepper) [Bonus Track] - Tommy Lee</v>
+        <v>Second Chance - Lukas Graham</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>DOOM LOOP</v>
+        <v>Stupid World (feat. Chad Tepper) [Bonus Track]</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
+        <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-22</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Blood Of Your Empire</v>
+        <v>Tommyland Rides Again</v>
       </c>
       <c r="G160" t="str">
-        <v>4:00</v>
+        <v>3:49</v>
       </c>
       <c r="H160" t="str">
-        <v>PRESIDENT</v>
+        <v>Tommy Lee</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/tommy-lee/68696</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/doom-loop/6769905842</v>
+        <v>https://music.apple.com/us/album/stupid-world-feat-chad-tepper-bonus-track/1893473875</v>
       </c>
       <c r="L160" t="str">
-        <v>DOOM LOOP - PRESIDENT</v>
+        <v>Stupid World (feat. Chad Tepper) [Bonus Track] - Tommy Lee</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>New York City</v>
+        <v>DOOM LOOP</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
+        <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-22</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>New York City - Single</v>
+        <v>Blood Of Your Empire</v>
       </c>
       <c r="G161" t="str">
-        <v>3:30</v>
+        <v>4:00</v>
       </c>
       <c r="H161" t="str">
-        <v>Anthony Ramos</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/anthony-ramos/1313064678</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/new-york-city/6770624324</v>
+        <v>https://music.apple.com/us/album/doom-loop/6769905842</v>
       </c>
       <c r="L161" t="str">
-        <v>New York City - Anthony Ramos</v>
+        <v>DOOM LOOP - PRESIDENT</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>I Found You</v>
+        <v>New York City</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
+        <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-22</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>I Found You - Single</v>
+        <v>New York City - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:18</v>
+        <v>3:30</v>
       </c>
       <c r="H162" t="str">
-        <v>TA Thomas</v>
+        <v>Anthony Ramos</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/ta-thomas/1232189106</v>
+        <v>https://music.apple.com/us/artist/anthony-ramos/1313064678</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/i-found-you/1894024530</v>
+        <v>https://music.apple.com/us/album/new-york-city/6770624324</v>
       </c>
       <c r="L162" t="str">
-        <v>I Found You - TA Thomas</v>
+        <v>New York City - Anthony Ramos</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Just My Type</v>
+        <v>I Found You</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
+        <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-22</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Labor Of Love</v>
+        <v>I Found You - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:40</v>
+        <v>3:18</v>
       </c>
       <c r="H163" t="str">
-        <v>Blxst</v>
+        <v>TA Thomas</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
+        <v>https://music.apple.com/us/artist/ta-thomas/1232189106</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/just-my-type/1895199881</v>
+        <v>https://music.apple.com/us/album/i-found-you/1894024530</v>
       </c>
       <c r="L163" t="str">
-        <v>Just My Type - Blxst</v>
+        <v>I Found You - TA Thomas</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>teenage drama</v>
+        <v>Just My Type</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
+        <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-22</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>teenage drama - Single</v>
+        <v>Labor Of Love</v>
       </c>
       <c r="G164" t="str">
-        <v>3:06</v>
+        <v>2:40</v>
       </c>
       <c r="H164" t="str">
-        <v>paris jackson</v>
+        <v>Blxst</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/teenage-drama/6768447515</v>
+        <v>https://music.apple.com/us/album/just-my-type/1895199881</v>
       </c>
       <c r="L164" t="str">
-        <v>teenage drama - paris jackson</v>
+        <v>Just My Type - Blxst</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>does it still mean something?</v>
+        <v>teenage drama</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
+        <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-22</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>only if it matters</v>
+        <v>teenage drama - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:48</v>
+        <v>3:06</v>
       </c>
       <c r="H165" t="str">
-        <v>Kevian Kraemer</v>
+        <v>paris jackson</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/does-it-still-mean-something/6768446154</v>
+        <v>https://music.apple.com/us/album/teenage-drama/6768447515</v>
       </c>
       <c r="L165" t="str">
-        <v>does it still mean something? - Kevian Kraemer</v>
+        <v>teenage drama - paris jackson</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Debbie Don't Cry</v>
+        <v>does it still mean something?</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
+        <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-22</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Debbie Don't Cry - Single</v>
+        <v>only if it matters</v>
       </c>
       <c r="G166" t="str">
-        <v>3:00</v>
+        <v>3:48</v>
       </c>
       <c r="H166" t="str">
-        <v>Ruel</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/debbie-dont-cry/6768206616</v>
+        <v>https://music.apple.com/us/album/does-it-still-mean-something/6768446154</v>
       </c>
       <c r="L166" t="str">
-        <v>Debbie Don't Cry - Ruel</v>
+        <v>does it still mean something? - Kevian Kraemer</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>YEAH YEAH YEAH</v>
+        <v>Debbie Don't Cry</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
+        <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-22</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>YEAH YEAH YEAH - Single</v>
+        <v>Debbie Don't Cry - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:25</v>
+        <v>3:00</v>
       </c>
       <c r="H167" t="str">
-        <v>Cruz Beckham</v>
+        <v>Ruel</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/yeah-yeah-yeah/6767515610</v>
+        <v>https://music.apple.com/us/album/debbie-dont-cry/6768206616</v>
       </c>
       <c r="L167" t="str">
-        <v>YEAH YEAH YEAH - Cruz Beckham</v>
+        <v>Debbie Don't Cry - Ruel</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Cotton Flower</v>
+        <v>YEAH YEAH YEAH</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
+        <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-22</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>YEAH YEAH YEAH - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:53</v>
+        <v>2:25</v>
       </c>
       <c r="H168" t="str">
-        <v>Future Islands</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/cotton-flower/1883045480</v>
+        <v>https://music.apple.com/us/album/yeah-yeah-yeah/6767515610</v>
       </c>
       <c r="L168" t="str">
-        <v>Cotton Flower - Future Islands</v>
+        <v>YEAH YEAH YEAH - Cruz Beckham</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>WAHALA RIDDIM</v>
+        <v>Cotton Flower</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
+        <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-22</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>WAHALA RIDDIM - Single</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G169" t="str">
-        <v>3:22</v>
+        <v>3:53</v>
       </c>
       <c r="H169" t="str">
-        <v>THEHONESTGUY</v>
+        <v>Future Islands</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/wahala-riddim/1895810537</v>
+        <v>https://music.apple.com/us/album/cotton-flower/1883045480</v>
       </c>
       <c r="L169" t="str">
-        <v>WAHALA RIDDIM - THEHONESTGUY</v>
+        <v>Cotton Flower - Future Islands</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Comfort</v>
+        <v>WAHALA RIDDIM</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/comfort/1876521401</v>
+        <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-22</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>So Help Me God</v>
+        <v>WAHALA RIDDIM - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>5:35</v>
+        <v>3:22</v>
       </c>
       <c r="H170" t="str">
-        <v>Kelsey Lu</v>
+        <v>THEHONESTGUY</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
+        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/comfort/1876521144</v>
+        <v>https://music.apple.com/us/album/wahala-riddim/1895810537</v>
       </c>
       <c r="L170" t="str">
-        <v>Comfort - Kelsey Lu</v>
+        <v>WAHALA RIDDIM - THEHONESTGUY</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Skin</v>
+        <v>Comfort</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/skin/6764651585</v>
+        <v>https://music.apple.com/us/song/comfort/1876521401</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-22</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Skin - Single</v>
+        <v>So Help Me God</v>
       </c>
       <c r="G171" t="str">
-        <v>3:00</v>
+        <v>5:35</v>
       </c>
       <c r="H171" t="str">
-        <v>Alessi Rose</v>
+        <v>Kelsey Lu</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/alessi-rose/1628689028</v>
+        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/skin/1895865252</v>
+        <v>https://music.apple.com/us/album/comfort/1876521144</v>
       </c>
       <c r="L171" t="str">
-        <v>Skin - Alessi Rose</v>
+        <v>Comfort - Kelsey Lu</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>IDGAF</v>
+        <v>Skin</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/idgaf/6764422210</v>
+        <v>https://music.apple.com/us/song/skin/6764651585</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-22</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>IDGAF - Single</v>
+        <v>Skin - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:55</v>
+        <v>3:00</v>
       </c>
       <c r="H172" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Alessi Rose</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/alessi-rose/1628689028</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/idgaf/1895773358</v>
+        <v>https://music.apple.com/us/album/skin/1895865252</v>
       </c>
       <c r="L172" t="str">
-        <v>IDGAF - Katelyn Tarver</v>
+        <v>Skin - Alessi Rose</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Run Rabbit</v>
+        <v>IDGAF</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
+        <v>https://music.apple.com/us/song/idgaf/6764422210</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-22</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Run Rabbit - Single</v>
+        <v>IDGAF - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:09</v>
+        <v>2:55</v>
       </c>
       <c r="H173" t="str">
-        <v>Mollie Elizabeth</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/mollie-elizabeth/1780515318</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/run-rabbit/6767354664</v>
+        <v>https://music.apple.com/us/album/idgaf/1895773358</v>
       </c>
       <c r="L173" t="str">
-        <v>Run Rabbit - Mollie Elizabeth</v>
+        <v>IDGAF - Katelyn Tarver</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>So Good (feat. Kuuda)</v>
+        <v>Run Rabbit</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
+        <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-22</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>So Good (feat. Kuuda) - Single</v>
+        <v>Run Rabbit - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:03</v>
+        <v>3:09</v>
       </c>
       <c r="H174" t="str">
-        <v>CamelPhat</v>
+        <v>Mollie Elizabeth</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/camelphat/385810888</v>
+        <v>https://music.apple.com/us/artist/mollie-elizabeth/1780515318</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/so-good-feat-kuuda/6766655768</v>
+        <v>https://music.apple.com/us/album/run-rabbit/6767354664</v>
       </c>
       <c r="L174" t="str">
-        <v>So Good (feat. Kuuda) - CamelPhat</v>
+        <v>Run Rabbit - Mollie Elizabeth</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Empty Theatre, Pretty Picture</v>
+        <v>So Good (feat. Kuuda)</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
+        <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-22</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Empty Theatre, Pretty Picture</v>
+        <v>So Good (feat. Kuuda) - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>5:01</v>
+        <v>3:03</v>
       </c>
       <c r="H175" t="str">
-        <v>Lane 8</v>
+        <v>CamelPhat</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/camelphat/385810888</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/empty-theatre-pretty-picture/1895395993</v>
+        <v>https://music.apple.com/us/album/so-good-feat-kuuda/6766655768</v>
       </c>
       <c r="L175" t="str">
-        <v>Empty Theatre, Pretty Picture - Lane 8</v>
+        <v>So Good (feat. Kuuda) - CamelPhat</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>regalametutiempo</v>
+        <v>Empty Theatre, Pretty Picture</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
+        <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-22</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>PROYECTANDO</v>
+        <v>Empty Theatre, Pretty Picture</v>
       </c>
       <c r="G176" t="str">
-        <v>3:01</v>
+        <v>5:01</v>
       </c>
       <c r="H176" t="str">
-        <v>Julio Caesar</v>
+        <v>Lane 8</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/regalametutiempo/6769922866</v>
+        <v>https://music.apple.com/us/album/empty-theatre-pretty-picture/1895395993</v>
       </c>
       <c r="L176" t="str">
-        <v>regalametutiempo - Julio Caesar</v>
+        <v>Empty Theatre, Pretty Picture - Lane 8</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>On Sight</v>
+        <v>regalametutiempo</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/on-sight/6763971220</v>
+        <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-22</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Left on RED</v>
+        <v>PROYECTANDO</v>
       </c>
       <c r="G177" t="str">
-        <v>2:25</v>
+        <v>3:01</v>
       </c>
       <c r="H177" t="str">
-        <v>REMI</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/remi/1716510008</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/on-sight/1895580736</v>
+        <v>https://music.apple.com/us/album/regalametutiempo/6769922866</v>
       </c>
       <c r="L177" t="str">
-        <v>On Sight - REMI</v>
+        <v>regalametutiempo - Julio Caesar</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Masks Off</v>
+        <v>On Sight</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/masks-off/6764077133</v>
+        <v>https://music.apple.com/us/song/on-sight/6763971220</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-22</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Masks Off - Single</v>
+        <v>Left on RED</v>
       </c>
       <c r="G178" t="str">
-        <v>3:24</v>
+        <v>2:25</v>
       </c>
       <c r="H178" t="str">
-        <v>Jesse Welles</v>
+        <v>REMI</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/jesse-welles/1737507146</v>
+        <v>https://music.apple.com/us/artist/remi/1716510008</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/masks-off/1895628310</v>
+        <v>https://music.apple.com/us/album/on-sight/1895580736</v>
       </c>
       <c r="L178" t="str">
-        <v>Masks Off - Jesse Welles</v>
+        <v>On Sight - REMI</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>I'm Just A Girl</v>
+        <v>Masks Off</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
+        <v>https://music.apple.com/us/song/masks-off/6764077133</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-22</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Di Hotel Malibu</v>
+        <v>Masks Off - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:49</v>
+        <v>3:24</v>
       </c>
       <c r="H179" t="str">
-        <v>Thee Marloes</v>
+        <v>Jesse Welles</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/thee-marloes/1541376632</v>
+        <v>https://music.apple.com/us/artist/jesse-welles/1737507146</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/im-just-a-girl/1878399768</v>
+        <v>https://music.apple.com/us/album/masks-off/1895628310</v>
       </c>
       <c r="L179" t="str">
-        <v>I'm Just A Girl - Thee Marloes</v>
+        <v>Masks Off - Jesse Welles</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Soleil (feat. Isabella Lovestory)</v>
+        <v>I'm Just A Girl</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
+        <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-22</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>EXIT 2B</v>
+        <v>Di Hotel Malibu</v>
       </c>
       <c r="G180" t="str">
-        <v>2:11</v>
+        <v>2:49</v>
       </c>
       <c r="H180" t="str">
-        <v>B0YG1RL</v>
+        <v>Thee Marloes</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/b0yg1rl/1847766665</v>
+        <v>https://music.apple.com/us/artist/thee-marloes/1541376632</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/soleil-feat-isabella-lovestory/6769526101</v>
+        <v>https://music.apple.com/us/album/im-just-a-girl/1878399768</v>
       </c>
       <c r="L180" t="str">
-        <v>Soleil (feat. Isabella Lovestory) - B0YG1RL</v>
+        <v>I'm Just A Girl - Thee Marloes</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Money Tree</v>
+        <v>Soleil (feat. Isabella Lovestory)</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/money-tree/6763211637</v>
+        <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-22</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Money Tree - Single</v>
+        <v>EXIT 2B</v>
       </c>
       <c r="G181" t="str">
-        <v>2:39</v>
+        <v>2:11</v>
       </c>
       <c r="H181" t="str">
-        <v>Olympia Vitalis</v>
+        <v>B0YG1RL</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/b0yg1rl/1847766665</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/money-tree/1895216986</v>
+        <v>https://music.apple.com/us/album/soleil-feat-isabella-lovestory/6769526101</v>
       </c>
       <c r="L181" t="str">
-        <v>Money Tree - Olympia Vitalis</v>
+        <v>Soleil (feat. Isabella Lovestory) - B0YG1RL</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Homerunner</v>
+        <v>Money Tree</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/homerunner/6770682178</v>
+        <v>https://music.apple.com/us/song/money-tree/6763211637</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-22</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Homerunner - Single</v>
+        <v>Money Tree - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:36</v>
+        <v>2:39</v>
       </c>
       <c r="H182" t="str">
-        <v>slayr</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/homerunner/6770682177</v>
+        <v>https://music.apple.com/us/album/money-tree/1895216986</v>
       </c>
       <c r="L182" t="str">
-        <v>Homerunner - slayr</v>
+        <v>Money Tree - Olympia Vitalis</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Mail</v>
+        <v>Homerunner</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/mail/6769190635</v>
+        <v>https://music.apple.com/us/song/homerunner/6770682178</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-22</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Mail - Single</v>
+        <v>Homerunner - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:14</v>
+        <v>2:36</v>
       </c>
       <c r="H183" t="str">
-        <v>MexikoDro</v>
+        <v>slayr</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/mail/6769190634</v>
+        <v>https://music.apple.com/us/album/homerunner/6770682177</v>
       </c>
       <c r="L183" t="str">
-        <v>Mail - MexikoDro</v>
+        <v>Homerunner - slayr</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Waste Your Heart</v>
+        <v>Mail</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
+        <v>https://music.apple.com/us/song/mail/6769190635</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-22</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Waste Your Heart - Single</v>
+        <v>Mail - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:31</v>
+        <v>2:14</v>
       </c>
       <c r="H184" t="str">
-        <v>Magnus Ferrell</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/waste-your-heart/6769241913</v>
+        <v>https://music.apple.com/us/album/mail/6769190634</v>
       </c>
       <c r="L184" t="str">
-        <v>Waste Your Heart - Magnus Ferrell</v>
+        <v>Mail - MexikoDro</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Sleeping Pills</v>
+        <v>Waste Your Heart</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
+        <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-22</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Sleeping Pills - Single</v>
+        <v>Waste Your Heart - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:03</v>
+        <v>2:31</v>
       </c>
       <c r="H185" t="str">
-        <v>Dolder</v>
+        <v>Magnus Ferrell</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
+        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/sleeping-pills/1896452689</v>
+        <v>https://music.apple.com/us/album/waste-your-heart/6769241913</v>
       </c>
       <c r="L185" t="str">
-        <v>Sleeping Pills - Dolder</v>
+        <v>Waste Your Heart - Magnus Ferrell</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>KODACHROMATIC</v>
+        <v>Sleeping Pills</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
+        <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-22</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>KODACHROMATIC - Single</v>
+        <v>Sleeping Pills - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:53</v>
+        <v>3:03</v>
       </c>
       <c r="H186" t="str">
-        <v>Tiger La Flor</v>
+        <v>Dolder</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/tiger-la-flor/1613113982</v>
+        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/kodachromatic/6770724719</v>
+        <v>https://music.apple.com/us/album/sleeping-pills/1896452689</v>
       </c>
       <c r="L186" t="str">
-        <v>KODACHROMATIC - Tiger La Flor</v>
+        <v>Sleeping Pills - Dolder</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>FOMO</v>
+        <v>KODACHROMATIC</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/fomo/1890190631</v>
+        <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-22</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Map Of Her Shadow</v>
+        <v>KODACHROMATIC - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:01</v>
+        <v>2:53</v>
       </c>
       <c r="H187" t="str">
-        <v>Anais Cardot</v>
+        <v>Tiger La Flor</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/tiger-la-flor/1613113982</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/fomo/1890190623</v>
+        <v>https://music.apple.com/us/album/kodachromatic/6770724719</v>
       </c>
       <c r="L187" t="str">
-        <v>FOMO - Anais Cardot</v>
+        <v>KODACHROMATIC - Tiger La Flor</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Black Fire</v>
+        <v>FOMO</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/black-fire/6770696877</v>
+        <v>https://music.apple.com/us/song/fomo/1890190631</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-22</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Sulfur Surfer</v>
+        <v>Map Of Her Shadow</v>
       </c>
       <c r="G188" t="str">
-        <v>3:37</v>
+        <v>3:01</v>
       </c>
       <c r="H188" t="str">
-        <v>Bladee</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/bladee/861359576</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/black-fire/6770696743</v>
+        <v>https://music.apple.com/us/album/fomo/1890190623</v>
       </c>
       <c r="L188" t="str">
-        <v>Black Fire - Bladee</v>
+        <v>FOMO - Anais Cardot</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>As Seen in the Unseen</v>
+        <v>Black Fire</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
+        <v>https://music.apple.com/us/song/black-fire/6770696877</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-22</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Grand Serpent Rising</v>
+        <v>Sulfur Surfer</v>
       </c>
       <c r="G189" t="str">
-        <v>6:59</v>
+        <v>3:37</v>
       </c>
       <c r="H189" t="str">
-        <v>Dimmu Borgir</v>
+        <v>Bladee</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+        <v>https://music.apple.com/us/artist/bladee/861359576</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/as-seen-in-the-unseen/1883121436</v>
+        <v>https://music.apple.com/us/album/black-fire/6770696743</v>
       </c>
       <c r="L189" t="str">
-        <v>As Seen in the Unseen - Dimmu Borgir</v>
+        <v>Black Fire - Bladee</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Every Man-Any Man</v>
+        <v>As Seen in the Unseen</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
+        <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-22</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Emotion Factory Reset</v>
+        <v>Grand Serpent Rising</v>
       </c>
       <c r="G190" t="str">
-        <v>4:20</v>
+        <v>6:59</v>
       </c>
       <c r="H190" t="str">
-        <v>Armored Saint</v>
+        <v>Dimmu Borgir</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/every-man-any-man/1872193859</v>
+        <v>https://music.apple.com/us/album/as-seen-in-the-unseen/1883121436</v>
       </c>
       <c r="L190" t="str">
-        <v>Every Man-Any Man - Armored Saint</v>
+        <v>As Seen in the Unseen - Dimmu Borgir</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>No Arms</v>
+        <v>Every Man-Any Man</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/no-arms/6765776563</v>
+        <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-22</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>From A Distance</v>
+        <v>Emotion Factory Reset</v>
       </c>
       <c r="G191" t="str">
-        <v>3:43</v>
+        <v>4:20</v>
       </c>
       <c r="H191" t="str">
-        <v>156/Silence</v>
+        <v>Armored Saint</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/156-silence/1071395282</v>
+        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/no-arms/1896069437</v>
+        <v>https://music.apple.com/us/album/every-man-any-man/1872193859</v>
       </c>
       <c r="L191" t="str">
-        <v>No Arms - 156/Silence</v>
+        <v>Every Man-Any Man - Armored Saint</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>It's Neverending</v>
+        <v>No Arms</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
+        <v>https://music.apple.com/us/song/no-arms/6765776563</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-22</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Neverending</v>
+        <v>From A Distance</v>
       </c>
       <c r="G192" t="str">
-        <v>8:35</v>
+        <v>3:43</v>
       </c>
       <c r="H192" t="str">
-        <v>Monolord</v>
+        <v>156/Silence</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+        <v>https://music.apple.com/us/artist/156-silence/1071395282</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/its-neverending/1871211801</v>
+        <v>https://music.apple.com/us/album/no-arms/1896069437</v>
       </c>
       <c r="L192" t="str">
-        <v>It's Neverending - Monolord</v>
+        <v>No Arms - 156/Silence</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>The Kids Will Kill Us</v>
+        <v>It's Neverending</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
+        <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-22</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>The Kids Will Kill Us - Single</v>
+        <v>Neverending</v>
       </c>
       <c r="G193" t="str">
-        <v>3:45</v>
+        <v>8:35</v>
       </c>
       <c r="H193" t="str">
-        <v>Witch Club Satan</v>
+        <v>Monolord</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/witch-club-satan/1626477576</v>
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/the-kids-will-kill-us/6766343272</v>
+        <v>https://music.apple.com/us/album/its-neverending/1871211801</v>
       </c>
       <c r="L193" t="str">
-        <v>The Kids Will Kill Us - Witch Club Satan</v>
+        <v>It's Neverending - Monolord</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe")</v>
+        <v>The Kids Will Kill Us</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
+        <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-22</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe") - Single</v>
+        <v>The Kids Will Kill Us - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:20</v>
+        <v>3:45</v>
       </c>
       <c r="H194" t="str">
-        <v>The Darkness</v>
+        <v>Witch Club Satan</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/the-darkness/2417388</v>
+        <v>https://music.apple.com/us/artist/witch-club-satan/1626477576</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/masters-of-the-universe-from-masters-of-the-universe/6769065779</v>
+        <v>https://music.apple.com/us/album/the-kids-will-kill-us/6766343272</v>
       </c>
       <c r="L194" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe") - The Darkness</v>
+        <v>The Kids Will Kill Us - Witch Club Satan</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>All Day</v>
+        <v>Masters of the Universe (from "Masters of the Universe")</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/all-day/1880746584</v>
+        <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-22</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Feet On Fire</v>
+        <v>Masters of the Universe (from "Masters of the Universe") - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>2:29</v>
+        <v>3:20</v>
       </c>
       <c r="H195" t="str">
-        <v>Ben Chapman</v>
+        <v>The Darkness</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/ben-chapman/1581192612</v>
+        <v>https://music.apple.com/us/artist/the-darkness/2417388</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/all-day/1880746349</v>
+        <v>https://music.apple.com/us/album/masters-of-the-universe-from-masters-of-the-universe/6769065779</v>
       </c>
       <c r="L195" t="str">
-        <v>All Day - Ben Chapman</v>
+        <v>Masters of the Universe (from "Masters of the Universe") - The Darkness</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Sigui</v>
+        <v>All Day</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/sigui/1890241955</v>
+        <v>https://music.apple.com/us/song/all-day/1880746584</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-22</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Massa</v>
+        <v>Feet On Fire</v>
       </c>
       <c r="G196" t="str">
-        <v>3:17</v>
+        <v>2:29</v>
       </c>
       <c r="H196" t="str">
-        <v>Fatoumata Diawara</v>
+        <v>Ben Chapman</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/fatoumata-diawara/466213610</v>
+        <v>https://music.apple.com/us/artist/ben-chapman/1581192612</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/sigui/1890241617</v>
+        <v>https://music.apple.com/us/album/all-day/1880746349</v>
       </c>
       <c r="L196" t="str">
-        <v>Sigui - Fatoumata Diawara</v>
+        <v>All Day - Ben Chapman</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>High Tail</v>
+        <v>Sigui</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/high-tail/1870432994</v>
+        <v>https://music.apple.com/us/song/sigui/1890241955</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-22</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Where the South Winds Wail</v>
+        <v>Massa</v>
       </c>
       <c r="G197" t="str">
-        <v>2:31</v>
+        <v>3:17</v>
       </c>
       <c r="H197" t="str">
-        <v>Gitkin</v>
+        <v>Fatoumata Diawara</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/gitkin/1345281815</v>
+        <v>https://music.apple.com/us/artist/fatoumata-diawara/466213610</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/high-tail/1870432670</v>
+        <v>https://music.apple.com/us/album/sigui/1890241617</v>
       </c>
       <c r="L197" t="str">
-        <v>High Tail - Gitkin</v>
+        <v>Sigui - Fatoumata Diawara</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Mice Protection</v>
+        <v>High Tail</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
+        <v>https://music.apple.com/us/song/high-tail/1870432994</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-22</v>
@@ -7899,68 +7899,106 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Ugly Duckling Union</v>
+        <v>Where the South Winds Wail</v>
       </c>
       <c r="G198" t="str">
-        <v>3:34</v>
+        <v>2:31</v>
       </c>
       <c r="H198" t="str">
-        <v>Lowertown</v>
+        <v>Gitkin</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/lowertown/1448207323</v>
+        <v>https://music.apple.com/us/artist/gitkin/1345281815</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/mice-protection/1872171971</v>
+        <v>https://music.apple.com/us/album/high-tail/1870432670</v>
       </c>
       <c r="L198" t="str">
-        <v>Mice Protection - Lowertown</v>
+        <v>High Tail - Gitkin</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
+        <v>Mice Protection</v>
+      </c>
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
+        <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
+      </c>
+      <c r="D199" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v>Ugly Duckling Union</v>
+      </c>
+      <c r="G199" t="str">
+        <v>3:34</v>
+      </c>
+      <c r="H199" t="str">
+        <v>Lowertown</v>
+      </c>
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
+        <v>https://music.apple.com/us/artist/lowertown/1448207323</v>
+      </c>
+      <c r="K199" t="str">
+        <v>https://music.apple.com/us/album/mice-protection/1872171971</v>
+      </c>
+      <c r="L199" t="str">
+        <v>Mice Protection - Lowertown</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
         <v>Tóxica</v>
       </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
         <v>https://music.apple.com/us/song/t%C3%B3xica/6763056240</v>
       </c>
-      <c r="D199" t="str">
-        <v>2026-05-22</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
+      <c r="D200" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
         <v>Caribenya</v>
       </c>
-      <c r="G199" t="str">
+      <c r="G200" t="str">
         <v>3:48</v>
       </c>
-      <c r="H199" t="str">
+      <c r="H200" t="str">
         <v>Lido Pimienta</v>
       </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
         <v>https://music.apple.com/us/artist/lido-pimienta/389475023</v>
       </c>
-      <c r="K199" t="str">
+      <c r="K200" t="str">
         <v>https://music.apple.com/us/album/t%C3%B3xica/1895141218</v>
       </c>
-      <c r="L199" t="str">
+      <c r="L200" t="str">
         <v>Tóxica - Lido Pimienta</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L200"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week04/titles.xlsx
+++ b/data/global/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L200"/>
+  <dimension ref="A1:L199"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>דניאלה גולדפיין – Like a Swing</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-22</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a0%d7%99%d7%90%d7%9c%d7%94-%d7%92%d7%95%d7%9c%d7%93%d7%a4%d7%99%d7%99%d7%9f-like-a-swing/</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-22</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר “Like a Swing” של דניאלה גולדפיין נוגע ומגיע מתוך הפשטות שלו. אין כאן ניסיון להרשים בהפקה גדולה, מהלכים דרמטיים או כתיבה מתוחכמת מדי, אלא יצירה קטנה, אינטימית וכמעט חשופה, שנשמעת כמו מכתב אישי שהולחן ברגע שקט באמצע הלילה. הרעיון</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Dean Lewis</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>דניאלה גולדפיין – Like a Swing</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B3" t="str">
-        <v>12 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-22</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>12 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Dean Lewis</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>17 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-22</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>17 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>12 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-22</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>12 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Niall Horan</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>12 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-22</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>12 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>RUEL</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B7" t="str">
-        <v>14 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-22</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>14 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>RUEL</v>
+        <v>TINI</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>16 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-22</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>16 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>TINI</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B9" t="str">
-        <v>17 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-22</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>17 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Charli xcx</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-22</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Dua Lipa</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B11" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-22</v>
@@ -799,7 +799,7 @@
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Matilda Mann</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-22</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Ella Langley</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-22</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Nothing But Thieves</v>
+        <v>kesha</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-22</v>
@@ -913,7 +913,7 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>kesha</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-22</v>
@@ -951,7 +951,7 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Holly Humberstone</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-22</v>
@@ -989,7 +989,7 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Foo Fighters</v>
+        <v>The Analogues</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-22</v>
@@ -1027,7 +1027,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>The Analogues</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-22</v>
@@ -1065,7 +1065,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Rod Stewart</v>
+        <v>Blue October</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
+        <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
+        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-22</v>
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Blue October</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
+        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Far Caspian - hum (Official Video)</v>
+        <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
+        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-22</v>
@@ -1141,7 +1141,7 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Far Caspian</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
+        <v>Kenia Os - Love Bombing - Kenia Os</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Kenia Os - Love Bombing</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
+        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-22</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Kenia Os</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Kenia Os - Love Bombing - Kenia Os</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B22" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-22</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B23" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-22</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B24" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-22</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B25" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-22</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B26" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-22</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B27" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-22</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-22</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Evanescence</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>7 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-22</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Evanescence</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B30" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-22</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B31" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-22</v>
@@ -1559,7 +1559,7 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Armin van Buuren</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-22</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Madison Cunningham</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-22</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Johnny Orlando</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-22</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Carver Jones</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B35" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-22</v>
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Jazmin bean</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B36" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-22</v>
@@ -1749,7 +1749,7 @@
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Baby Queen</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B37" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-22</v>
@@ -1787,7 +1787,7 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Switchfoot</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B38" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-22</v>
@@ -1825,7 +1825,7 @@
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Grace Potter</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-22</v>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B40" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-22</v>
@@ -1901,7 +1901,7 @@
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>The All-American Rejects</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B41" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-22</v>
@@ -1939,7 +1939,7 @@
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Henry Moodie</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-22</v>
@@ -1977,7 +1977,7 @@
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Spacey Jane</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B43" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-22</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Megan Moroney</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B44" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-22</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
+        <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B45" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
+        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-22</v>
@@ -2091,7 +2091,7 @@
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Matt Hansen</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
+        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Keith Urban - Steal Away (Visualizer)</v>
+        <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B46" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
+        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-22</v>
@@ -2129,7 +2129,7 @@
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Keith Urban</v>
+        <v>VALÉ</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
+        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>VALÉ - Mugshot (Official Video)</v>
+        <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B47" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
+        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-22</v>
@@ -2167,7 +2167,7 @@
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>VALÉ</v>
+        <v>Mackenzie Carpenter</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
+        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio)</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B48" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
+        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-22</v>
@@ -2205,7 +2205,7 @@
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Mackenzie Carpenter</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B49" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
+        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-22</v>
@@ -2243,7 +2243,7 @@
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Towa Bird</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
+        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-22</v>
@@ -2281,7 +2281,7 @@
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Sabrina Sterling</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
+        <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B51" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
+        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-22</v>
@@ -2319,7 +2319,7 @@
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Little Big Town</v>
+        <v>Becky G</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
+        <v>Becky G - EPA (Official Video) - Becky G</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Becky G - EPA (Official Video)</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B52" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
+        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-22</v>
@@ -2357,7 +2357,7 @@
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Becky G</v>
+        <v>Daisy the Great</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Becky G - EPA (Official Video) - Becky G</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
+        <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B53" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
+        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-22</v>
@@ -2395,7 +2395,7 @@
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Daisy the Great</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
+        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Towa Bird - Dog (Official Music Video)</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B54" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
+        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-22</v>
@@ -2433,7 +2433,7 @@
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Towa Bird</v>
+        <v>Madonna</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
+        <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B55" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
+        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-22</v>
@@ -2471,7 +2471,7 @@
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Madonna</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
+        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video)</v>
+        <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B56" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
+        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-22</v>
@@ -2509,7 +2509,7 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Ally Salort</v>
+        <v>Bella White</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
+        <v>Bella White - Better - Official Music Video - Bella White</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Bella White - Better - Official Music Video</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B57" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
+        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-22</v>
@@ -2547,7 +2547,7 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Bella White</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Bella White - Better - Official Music Video - Bella White</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B58" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
+        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-22</v>
@@ -2585,7 +2585,7 @@
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
+        <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B59" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
+        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-22</v>
@@ -2623,7 +2623,7 @@
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Towa Bird</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
+        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer)</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B60" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
+        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-22</v>
@@ -2661,7 +2661,7 @@
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Miranda Lambert</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
+        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-22</v>
@@ -2699,7 +2699,7 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Lady Gaga</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B62" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
+        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-22</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Gracie Abrams</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B63" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
+        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-22</v>
@@ -2775,7 +2775,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
+        <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B64" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
+        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-22</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Martin Garrix</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
+        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Jorja Smith - What's Done Is Done</v>
+        <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
+        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-22</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Jorja Smith</v>
+        <v>LP</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
+        <v>LP - Shelly (Official Music Video) - LP</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>LP - Shelly (Official Music Video)</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B66" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
+        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-22</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>LP</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>LP - Shelly (Official Music Video) - LP</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B67" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
+        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-22</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>The Rolling Stones</v>
+        <v>Oasis</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
+        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-22</v>
@@ -2965,7 +2965,7 @@
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Oasis</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
+        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-22</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Breaking Benjamin</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B70" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
+        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-22</v>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>VictorBiliac</v>
+        <v>Linkin Park</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
+        <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
+        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-22</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Linkin Park</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
+        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Harry Styles - Dance No More (Official Video)</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
+        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-22</v>
@@ -3117,7 +3117,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Harry Styles</v>
+        <v>Eagles</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
+        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-22</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Eagles</v>
+        <v>Nora Fatehi</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B74" t="str">
-        <v>13 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
+        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-22</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>13 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Nora Fatehi</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B75" t="str">
         <v>2 months ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
+        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-22</v>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Eurovision Song Contest and Alis</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B76" t="str">
         <v>2 months ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
+        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-22</v>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Eurovision Song Contest and Alis</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
+        <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>2 months ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
+        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-22</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 months ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>The Head And The Heart</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
+        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video)</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B78" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
+        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-22</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>The Head And The Heart</v>
+        <v>Simply Red</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
+        <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
+        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-22</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Simply Red</v>
+        <v>Talking Heads</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
+        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video)</v>
+        <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
+        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-22</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Talking Heads</v>
+        <v>Ellise</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
+        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Ellise - Liplock (Official Music Video)</v>
+        <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
+        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-22</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Ellise</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
+        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Tori Kelly - Dive (Official Music Video)</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B82" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
+        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-22</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Tori Kelly</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
+        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-22</v>
@@ -3535,7 +3535,7 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>David Gilmour</v>
+        <v>Scorpions</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
+        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-22</v>
@@ -3573,7 +3573,7 @@
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Scorpions</v>
+        <v>Claire Leslie</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
+        <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
+        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-22</v>
@@ -3611,7 +3611,7 @@
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Claire Leslie</v>
+        <v>Michael Schulte</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
+        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Michael Schulte - Lovesick (Official Video)</v>
+        <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
+        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-22</v>
@@ -3649,7 +3649,7 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Michael Schulte</v>
+        <v>Caity Baser</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
+        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Caity Baser - Holiday Song (Official Video)</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
+        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-22</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Caity Baser</v>
+        <v>Sam Fischer</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
+        <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
+        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-22</v>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Sam Fischer</v>
+        <v>Porches</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
+        <v>Porches- HABIT (Official Video) - Porches</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Porches- HABIT (Official Video)</v>
+        <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
+        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-22</v>
@@ -3763,7 +3763,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Porches</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Porches- HABIT (Official Video) - Porches</v>
+        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Charli xcx - Rock Music (Official Video)</v>
+        <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
+        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-22</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Charli xcx</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
+        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Jon Batiste - Alla Blues (Audio)</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
+        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-22</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Jon Batiste</v>
+        <v>Tigirlily Gold</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
+        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-22</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Tigirlily Gold</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
+        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-22</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
+        <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
+        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-22</v>
@@ -3953,7 +3953,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Bruno Mars</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
+        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Tori Kelly - Control (Official Visualizer)</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
+        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-22</v>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Tori Kelly</v>
+        <v>bea miller</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
+        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-22</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>bea miller</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
+        <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
+        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-22</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>The Chainsmokers</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
+        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Madison Beer - free (Official Audio)</v>
+        <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
+        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-22</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Madison Beer</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
+        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Tori Kelly - Dive (Official Audio)</v>
+        <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
+        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-22</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Tori Kelly</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
+        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio)</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
+        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-22</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>JeremyCampMusic</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
+        <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
+        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-22</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>The Chainsmokers</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
+        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Ashley Cooke - high school sweetheart</v>
+        <v>From Down Here</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
+        <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-22</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>From Down Here - Single</v>
       </c>
       <c r="G102" t="str">
-        <v/>
+        <v>4:01</v>
       </c>
       <c r="H102" t="str">
-        <v>Ashley Cooke</v>
+        <v>Lola Young</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/lola-young/452271760</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/from-down-here/6768357139</v>
       </c>
       <c r="L102" t="str">
-        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
+        <v>From Down Here - Lola Young</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>From Down Here</v>
+        <v>the cure</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
+        <v>https://music.apple.com/us/song/the-cure/1889992123</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-22</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>From Down Here - Single</v>
+        <v>you seem pretty sad for a girl so in love</v>
       </c>
       <c r="G103" t="str">
-        <v>4:01</v>
+        <v>4:57</v>
       </c>
       <c r="H103" t="str">
-        <v>Lola Young</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/lola-young/452271760</v>
+        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/from-down-here/6768357139</v>
+        <v>https://music.apple.com/us/album/the-cure/1889992111</v>
       </c>
       <c r="L103" t="str">
-        <v>From Down Here - Lola Young</v>
+        <v>the cure - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>the cure</v>
+        <v>SS26</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/the-cure/1889992123</v>
+        <v>https://music.apple.com/us/song/ss26/6771061782</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-22</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>you seem pretty sad for a girl so in love</v>
+        <v>SS26 - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>4:57</v>
+        <v>2:47</v>
       </c>
       <c r="H104" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
+        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/the-cure/1889992111</v>
+        <v>https://music.apple.com/us/album/ss26/6771061771</v>
       </c>
       <c r="L104" t="str">
-        <v>the cure - Olivia Rodrigo</v>
+        <v>SS26 - Charli xcx</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>SS26</v>
+        <v>White Flag</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/ss26/6771061782</v>
+        <v>https://music.apple.com/us/song/white-flag/1887627840</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-22</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>SS26 - Single</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G105" t="str">
-        <v>2:47</v>
+        <v>2:34</v>
       </c>
       <c r="H105" t="str">
-        <v>Charli xcx</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/ss26/6771061771</v>
+        <v>https://music.apple.com/us/album/white-flag/1887627836</v>
       </c>
       <c r="L105" t="str">
-        <v>SS26 - Charli xcx</v>
+        <v>White Flag - Vince Staples</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>White Flag</v>
+        <v>Knew Better Part Two</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/white-flag/1887627840</v>
+        <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-22</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Cry Baby</v>
+        <v>Dangerous Woman (Tenth Anniversary Edition)</v>
       </c>
       <c r="G106" t="str">
-        <v>2:34</v>
+        <v>2:44</v>
       </c>
       <c r="H106" t="str">
-        <v>Vince Staples</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/white-flag/1887627836</v>
+        <v>https://music.apple.com/us/album/knew-better-part-two/6770600996</v>
       </c>
       <c r="L106" t="str">
-        <v>White Flag - Vince Staples</v>
+        <v>Knew Better Part Two - Ariana Grande</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Knew Better Part Two</v>
+        <v>Goals</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
+        <v>https://music.apple.com/us/song/goals/6769251838</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-22</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Dangerous Woman (Tenth Anniversary Edition)</v>
+        <v>Goals (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>2:44</v>
+        <v>3:00</v>
       </c>
       <c r="H107" t="str">
-        <v>Ariana Grande</v>
+        <v>LISA</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v>https://music.apple.com/us/artist/lisa/1583908668</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/knew-better-part-two/6770600996</v>
+        <v>https://music.apple.com/us/album/goals/6769251829</v>
       </c>
       <c r="L107" t="str">
-        <v>Knew Better Part Two - Ariana Grande</v>
+        <v>Goals - LISA</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Goals</v>
+        <v>we should talk</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/goals/6769251838</v>
+        <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-22</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Goals (FIFA World Cup 2026™) - Single</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G108" t="str">
-        <v>3:00</v>
+        <v>3:04</v>
       </c>
       <c r="H108" t="str">
-        <v>LISA</v>
+        <v>Bleachers</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/lisa/1583908668</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/goals/6769251829</v>
+        <v>https://music.apple.com/us/album/we-should-talk/1872842313</v>
       </c>
       <c r="L108" t="str">
-        <v>Goals - LISA</v>
+        <v>we should talk - Bleachers</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>we should talk</v>
+        <v>Do What You Gotta Do</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
+        <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-22</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>everyone for ten minutes</v>
+        <v>NeverAlways (Vol. 2)</v>
       </c>
       <c r="G109" t="str">
-        <v>3:04</v>
+        <v>3:26</v>
       </c>
       <c r="H109" t="str">
-        <v>Bleachers</v>
+        <v>The Band CAMINO</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/we-should-talk/1872842313</v>
+        <v>https://music.apple.com/us/album/do-what-you-gotta-do/1887616173</v>
       </c>
       <c r="L109" t="str">
-        <v>we should talk - Bleachers</v>
+        <v>Do What You Gotta Do - The Band CAMINO</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Do What You Gotta Do</v>
+        <v>Ego</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
+        <v>https://music.apple.com/us/song/ego/6769207667</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-22</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>NeverAlways (Vol. 2)</v>
+        <v>Ego - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:26</v>
+        <v>2:53</v>
       </c>
       <c r="H110" t="str">
-        <v>The Band CAMINO</v>
+        <v>The Warning</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/do-what-you-gotta-do/1887616173</v>
+        <v>https://music.apple.com/us/album/ego/6769207665</v>
       </c>
       <c r="L110" t="str">
-        <v>Do What You Gotta Do - The Band CAMINO</v>
+        <v>Ego - The Warning</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Ego</v>
+        <v>Light up (From the Netflix Documentary 'kylie')</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/ego/6769207667</v>
+        <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-22</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Ego - Single</v>
+        <v>Light up (From the Netflix Documentary 'Kylie') - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>2:53</v>
+        <v>3:17</v>
       </c>
       <c r="H111" t="str">
-        <v>The Warning</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/kylie-minogue/465031</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/ego/6769207665</v>
+        <v>https://music.apple.com/us/album/light-up-from-the-netflix-documentary-kylie/6768013505</v>
       </c>
       <c r="L111" t="str">
-        <v>Ego - The Warning</v>
+        <v>Light up (From the Netflix Documentary 'kylie') - Kylie Minogue</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Light up (From the Netflix Documentary 'kylie')</v>
+        <v>All That Matters</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
+        <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-22</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Light up (From the Netflix Documentary 'Kylie') - Single</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G112" t="str">
-        <v>3:17</v>
+        <v>3:43</v>
       </c>
       <c r="H112" t="str">
-        <v>Kylie Minogue</v>
+        <v>6LACK</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/kylie-minogue/465031</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/light-up-from-the-netflix-documentary-kylie/6768013505</v>
+        <v>https://music.apple.com/us/album/all-that-matters/1884792154</v>
       </c>
       <c r="L112" t="str">
-        <v>Light up (From the Netflix Documentary 'kylie') - Kylie Minogue</v>
+        <v>All That Matters - 6LACK</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>All That Matters</v>
+        <v>Like A Virgin</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
+        <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-22</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Terrified .</v>
       </c>
       <c r="G113" t="str">
-        <v>3:43</v>
+        <v>2:34</v>
       </c>
       <c r="H113" t="str">
-        <v>6LACK</v>
+        <v>fakemink</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/all-that-matters/1884792154</v>
+        <v>https://music.apple.com/us/album/like-a-virgin/6768157748</v>
       </c>
       <c r="L113" t="str">
-        <v>All That Matters - 6LACK</v>
+        <v>Like A Virgin - fakemink</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Like A Virgin</v>
+        <v>24 Hours</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
+        <v>https://music.apple.com/us/song/24-hours/6771060076</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-22</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Terrified .</v>
+        <v>24 Hours - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>2:34</v>
+        <v>3:17</v>
       </c>
       <c r="H114" t="str">
-        <v>fakemink</v>
+        <v>Stormzy</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/stormzy/394865154</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/like-a-virgin/6768157748</v>
+        <v>https://music.apple.com/us/album/24-hours/6771060073</v>
       </c>
       <c r="L114" t="str">
-        <v>Like A Virgin - fakemink</v>
+        <v>24 Hours - Stormzy</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>24 Hours</v>
+        <v>HOES (From Scary Movie)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/24-hours/6771060076</v>
+        <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-22</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>24 Hours - Single</v>
+        <v>HOES (From Scary Movie) - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:17</v>
+        <v>2:09</v>
       </c>
       <c r="H115" t="str">
-        <v>Stormzy</v>
+        <v>Lizzo</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/stormzy/394865154</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/24-hours/6771060073</v>
+        <v>https://music.apple.com/us/album/hoes-from-scary-movie/6770661290</v>
       </c>
       <c r="L115" t="str">
-        <v>24 Hours - Stormzy</v>
+        <v>HOES (From Scary Movie) - Lizzo</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>HOES (From Scary Movie)</v>
+        <v>Ms. Tundra</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
+        <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-22</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>HOES (From Scary Movie) - Single</v>
+        <v>Highway 79</v>
       </c>
       <c r="G116" t="str">
-        <v>2:09</v>
+        <v>3:12</v>
       </c>
       <c r="H116" t="str">
-        <v>Lizzo</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/hoes-from-scary-movie/6770661290</v>
+        <v>https://music.apple.com/us/album/ms-tundra/6770614875</v>
       </c>
       <c r="L116" t="str">
-        <v>HOES (From Scary Movie) - Lizzo</v>
+        <v>Ms. Tundra - Ne-Yo</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Ms. Tundra</v>
+        <v>TARENTINO</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
+        <v>https://music.apple.com/us/song/tarentino/6769927265</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-22</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Highway 79</v>
+        <v>TARENTINO - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:12</v>
+        <v>2:23</v>
       </c>
       <c r="H117" t="str">
-        <v>Ne-Yo</v>
+        <v>Labrinth</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/ms-tundra/6770614875</v>
+        <v>https://music.apple.com/us/album/tarentino/6769927262</v>
       </c>
       <c r="L117" t="str">
-        <v>Ms. Tundra - Ne-Yo</v>
+        <v>TARENTINO - Labrinth</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>TARENTINO</v>
+        <v>Daydreamin’</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/tarentino/6769927265</v>
+        <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-22</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>TARENTINO - Single</v>
+        <v>KONNAKOL (Deluxe)</v>
       </c>
       <c r="G118" t="str">
-        <v>2:23</v>
+        <v>2:58</v>
       </c>
       <c r="H118" t="str">
-        <v>Labrinth</v>
+        <v>ZAYN</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/tarentino/6769927262</v>
+        <v>https://music.apple.com/us/album/daydreamin/6769559345</v>
       </c>
       <c r="L118" t="str">
-        <v>TARENTINO - Labrinth</v>
+        <v>Daydreamin’ - ZAYN</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Daydreamin’</v>
+        <v>End of an Era</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
+        <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-22</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>KONNAKOL (Deluxe)</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G119" t="str">
-        <v>2:58</v>
+        <v>3:38</v>
       </c>
       <c r="H119" t="str">
-        <v>ZAYN</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/daydreamin/6769559345</v>
+        <v>https://music.apple.com/us/album/end-of-an-era/1884418567</v>
       </c>
       <c r="L119" t="str">
-        <v>Daydreamin’ - ZAYN</v>
+        <v>End of an Era - Niall Horan</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>End of an Era</v>
+        <v>Questions</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
+        <v>https://music.apple.com/us/song/questions/1871502847</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-22</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Dinner Party</v>
+        <v>Florescence</v>
       </c>
       <c r="G120" t="str">
-        <v>3:38</v>
+        <v>3:07</v>
       </c>
       <c r="H120" t="str">
-        <v>Niall Horan</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/end-of-an-era/1884418567</v>
+        <v>https://music.apple.com/us/album/questions/1871502372</v>
       </c>
       <c r="L120" t="str">
-        <v>End of an Era - Niall Horan</v>
+        <v>Questions - Maisie Peters</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Questions</v>
+        <v>Heart Has To Work So Hard</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/questions/1871502847</v>
+        <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-22</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Florescence</v>
+        <v>Heart Has To Work So Hard - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:07</v>
+        <v>3:12</v>
       </c>
       <c r="H121" t="str">
-        <v>Maisie Peters</v>
+        <v>Blondshell</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/blondshell/1624592688</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/questions/1871502372</v>
+        <v>https://music.apple.com/us/album/heart-has-to-work-so-hard/1895982147</v>
       </c>
       <c r="L121" t="str">
-        <v>Questions - Maisie Peters</v>
+        <v>Heart Has To Work So Hard - Blondshell</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Heart Has To Work So Hard</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
+        <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-22</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Heart Has To Work So Hard - Single</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski) - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:12</v>
+        <v>3:44</v>
       </c>
       <c r="H122" t="str">
-        <v>Blondshell</v>
+        <v>Kygo</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/blondshell/1624592688</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/heart-has-to-work-so-hard/1895982147</v>
+        <v>https://music.apple.com/us/album/heaven-on-your-mind-feat-dan-tyminski/6769007431</v>
       </c>
       <c r="L122" t="str">
-        <v>Heart Has To Work So Hard - Blondshell</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski) - Kygo</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski)</v>
+        <v>PERDISTE EL EMMY.</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
+        <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-22</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski) - Single</v>
+        <v>OMAKASE</v>
       </c>
       <c r="G123" t="str">
-        <v>3:44</v>
+        <v>4:03</v>
       </c>
       <c r="H123" t="str">
-        <v>Kygo</v>
+        <v>Álvaro Díaz</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-your-mind-feat-dan-tyminski/6769007431</v>
+        <v>https://music.apple.com/us/album/perdiste-el-emmy/6771082594</v>
       </c>
       <c r="L123" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski) - Kygo</v>
+        <v>PERDISTE EL EMMY. - Álvaro Díaz</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>PERDISTE EL EMMY.</v>
+        <v>Dosis</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
+        <v>https://music.apple.com/us/song/dosis/6762929729</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-22</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>OMAKASE</v>
+        <v>DOSIS</v>
       </c>
       <c r="G124" t="str">
-        <v>4:03</v>
+        <v>3:00</v>
       </c>
       <c r="H124" t="str">
-        <v>Álvaro Díaz</v>
+        <v>Xavi</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/perdiste-el-emmy/6771082594</v>
+        <v>https://music.apple.com/us/album/dosis/1895081885</v>
       </c>
       <c r="L124" t="str">
-        <v>PERDISTE EL EMMY. - Álvaro Díaz</v>
+        <v>Dosis - Xavi</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Dosis</v>
+        <v>Would U Still Love Me</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/dosis/6762929729</v>
+        <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-22</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>DOSIS</v>
+        <v>Whitcomb vs. Flores - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:00</v>
+        <v>2:36</v>
       </c>
       <c r="H125" t="str">
-        <v>Xavi</v>
+        <v>Diplo</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/dosis/1895081885</v>
+        <v>https://music.apple.com/us/album/would-u-still-love-me/6769907832</v>
       </c>
       <c r="L125" t="str">
-        <v>Dosis - Xavi</v>
+        <v>Would U Still Love Me - Diplo</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Would U Still Love Me</v>
+        <v>Saving This Bottle</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
+        <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-22</v>
@@ -5166,7 +5166,7 @@
         <v>Whitcomb vs. Flores - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:36</v>
+        <v>3:05</v>
       </c>
       <c r="H126" t="str">
         <v>Diplo</v>
@@ -5178,21 +5178,21 @@
         <v>https://music.apple.com/us/artist/diplo/1468290871</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/would-u-still-love-me/6769907832</v>
+        <v>https://music.apple.com/us/album/saving-this-bottle/6769907832</v>
       </c>
       <c r="L126" t="str">
-        <v>Would U Still Love Me - Diplo</v>
+        <v>Saving This Bottle - Diplo</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Saving This Bottle</v>
+        <v>The Climb</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
+        <v>https://music.apple.com/us/song/the-climb/6769546149</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-22</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Whitcomb vs. Flores - Single</v>
+        <v>The Climb - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:05</v>
+        <v>3:50</v>
       </c>
       <c r="H127" t="str">
-        <v>Diplo</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/saving-this-bottle/6769907832</v>
+        <v>https://music.apple.com/us/album/the-climb/6769546147</v>
       </c>
       <c r="L127" t="str">
-        <v>Saving This Bottle - Diplo</v>
+        <v>The Climb - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>The Climb</v>
+        <v>everything tatted</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/the-climb/6769546149</v>
+        <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-22</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>The Climb - Single</v>
+        <v>everything tatted - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:50</v>
+        <v>3:25</v>
       </c>
       <c r="H128" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>mgk</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/the-climb/6769546147</v>
+        <v>https://music.apple.com/us/album/everything-tatted/6770773606</v>
       </c>
       <c r="L128" t="str">
-        <v>The Climb - Bailey Zimmerman</v>
+        <v>everything tatted - mgk</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>everything tatted</v>
+        <v>BOOMPALA</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
+        <v>https://music.apple.com/us/song/boompala/1894802726</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-22</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>everything tatted - Single</v>
+        <v>'PUREFLOW', Pt. 1</v>
       </c>
       <c r="G129" t="str">
-        <v>3:25</v>
+        <v>2:56</v>
       </c>
       <c r="H129" t="str">
-        <v>mgk</v>
+        <v>LE SSERAFIM</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/everything-tatted/6770773606</v>
+        <v>https://music.apple.com/us/album/boompala/1894802719</v>
       </c>
       <c r="L129" t="str">
-        <v>everything tatted - mgk</v>
+        <v>BOOMPALA - LE SSERAFIM</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>BOOMPALA</v>
+        <v>Let Me Be In Your Arms</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/boompala/1894802726</v>
+        <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-22</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>'PUREFLOW', Pt. 1</v>
+        <v>can we do it all again?</v>
       </c>
       <c r="G130" t="str">
-        <v>2:56</v>
+        <v>3:13</v>
       </c>
       <c r="H130" t="str">
-        <v>LE SSERAFIM</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/boompala/1894802719</v>
+        <v>https://music.apple.com/us/album/let-me-be-in-your-arms/1881610862</v>
       </c>
       <c r="L130" t="str">
-        <v>BOOMPALA - LE SSERAFIM</v>
+        <v>Let Me Be In Your Arms - Sonny Fodera</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Let Me Be In Your Arms</v>
+        <v>Eat, Work, Pray</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
+        <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-22</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>can we do it all again?</v>
+        <v>Eat, Work, Pray - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:13</v>
+        <v>2:28</v>
       </c>
       <c r="H131" t="str">
-        <v>Sonny Fodera</v>
+        <v>Sheff G</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/let-me-be-in-your-arms/1881610862</v>
+        <v>https://music.apple.com/us/album/eat-work-pray/6769134493</v>
       </c>
       <c r="L131" t="str">
-        <v>Let Me Be In Your Arms - Sonny Fodera</v>
+        <v>Eat, Work, Pray - Sheff G</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Eat, Work, Pray</v>
+        <v>touch myself</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
+        <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-22</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Eat, Work, Pray - Single</v>
+        <v>and all pride aside</v>
       </c>
       <c r="G132" t="str">
-        <v>2:28</v>
+        <v>4:09</v>
       </c>
       <c r="H132" t="str">
-        <v>Sheff G</v>
+        <v>kwn</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/eat-work-pray/6769134493</v>
+        <v>https://music.apple.com/us/album/touch-myself/6769880663</v>
       </c>
       <c r="L132" t="str">
-        <v>Eat, Work, Pray - Sheff G</v>
+        <v>touch myself - kwn</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>touch myself</v>
+        <v>Comes and Goes</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
+        <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-22</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>and all pride aside</v>
+        <v>Comes and Goes - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>4:09</v>
+        <v>4:22</v>
       </c>
       <c r="H133" t="str">
-        <v>kwn</v>
+        <v>KETTAMA</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/kettama/1425703970</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/touch-myself/6769880663</v>
+        <v>https://music.apple.com/us/album/comes-and-goes/6766618930</v>
       </c>
       <c r="L133" t="str">
-        <v>touch myself - kwn</v>
+        <v>Comes and Goes - KETTAMA</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Comes and Goes</v>
+        <v>Dear God</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
+        <v>https://music.apple.com/us/song/dear-god/1878237813</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-22</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Comes and Goes - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G134" t="str">
-        <v>4:22</v>
+        <v>6:08</v>
       </c>
       <c r="H134" t="str">
-        <v>KETTAMA</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/kettama/1425703970</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/comes-and-goes/6766618930</v>
+        <v>https://music.apple.com/us/album/dear-god/1878237662</v>
       </c>
       <c r="L134" t="str">
-        <v>Comes and Goes - KETTAMA</v>
+        <v>Dear God - The Pretty Reckless</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Dear God</v>
+        <v>Hexagons</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/dear-god/1878237813</v>
+        <v>https://music.apple.com/us/song/hexagons/1885607736</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-22</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Dear God</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G135" t="str">
-        <v>6:08</v>
+        <v>5:26</v>
       </c>
       <c r="H135" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Muse</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/dear-god/1878237662</v>
+        <v>https://music.apple.com/us/album/hexagons/1885607338</v>
       </c>
       <c r="L135" t="str">
-        <v>Dear God - The Pretty Reckless</v>
+        <v>Hexagons - Muse</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Hexagons</v>
+        <v>Facile-Batiste</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/hexagons/1885607736</v>
+        <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-22</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>The Wow! Signal</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G136" t="str">
-        <v>5:26</v>
+        <v>4:55</v>
       </c>
       <c r="H136" t="str">
-        <v>Muse</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/hexagons/1885607338</v>
+        <v>https://music.apple.com/us/album/facile-batiste/1895866355</v>
       </c>
       <c r="L136" t="str">
-        <v>Hexagons - Muse</v>
+        <v>Facile-Batiste - Jon Batiste</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Facile-Batiste</v>
+        <v>Pop Pop</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
+        <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-22</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Black Mozart</v>
+        <v>Pop Pop - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>4:55</v>
+        <v>2:57</v>
       </c>
       <c r="H137" t="str">
-        <v>Jon Batiste</v>
+        <v>Channel Tres</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/facile-batiste/1895866355</v>
+        <v>https://music.apple.com/us/album/pop-pop/1896269430</v>
       </c>
       <c r="L137" t="str">
-        <v>Facile-Batiste - Jon Batiste</v>
+        <v>Pop Pop - Channel Tres</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Pop Pop</v>
+        <v>One Of Us</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
+        <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-22</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Pop Pop - Single</v>
+        <v>One Of Us - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:57</v>
+        <v>3:35</v>
       </c>
       <c r="H138" t="str">
-        <v>Channel Tres</v>
+        <v>Chris Young</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
+        <v>https://music.apple.com/us/artist/chris-young/4779205</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/pop-pop/1896269430</v>
+        <v>https://music.apple.com/us/album/one-of-us/1895402922</v>
       </c>
       <c r="L138" t="str">
-        <v>Pop Pop - Channel Tres</v>
+        <v>One Of Us - Chris Young</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>One Of Us</v>
+        <v>Sins of the Father</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
+        <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-22</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>One Of Us - Single</v>
+        <v>Is God Is (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G139" t="str">
-        <v>3:35</v>
+        <v>3:20</v>
       </c>
       <c r="H139" t="str">
-        <v>Chris Young</v>
+        <v>Moses Sumney</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/chris-young/4779205</v>
+        <v>https://music.apple.com/us/artist/moses-sumney/843536848</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/one-of-us/1895402922</v>
+        <v>https://music.apple.com/us/album/sins-of-the-father/6771012707</v>
       </c>
       <c r="L139" t="str">
-        <v>One Of Us - Chris Young</v>
+        <v>Sins of the Father - Moses Sumney</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Sins of the Father</v>
+        <v>Life On The Run</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
+        <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-22</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Is God Is (Original Motion Picture Soundtrack)</v>
+        <v>Life On The Run - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:20</v>
+        <v>3:49</v>
       </c>
       <c r="H140" t="str">
-        <v>Moses Sumney</v>
+        <v>Brandi Carlile</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/moses-sumney/843536848</v>
+        <v>https://music.apple.com/us/artist/brandi-carlile/64387579</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/sins-of-the-father/6771012707</v>
+        <v>https://music.apple.com/us/album/life-on-the-run/6766761019</v>
       </c>
       <c r="L140" t="str">
-        <v>Sins of the Father - Moses Sumney</v>
+        <v>Life On The Run - Brandi Carlile</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Life On The Run</v>
+        <v>New York Confident</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
+        <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-22</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Life On The Run - Single</v>
+        <v>New York Confident - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:49</v>
+        <v>2:27</v>
       </c>
       <c r="H141" t="str">
-        <v>Brandi Carlile</v>
+        <v>Mark Ambor</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/brandi-carlile/64387579</v>
+        <v>https://music.apple.com/us/artist/mark-ambor/1459754985</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/life-on-the-run/6766761019</v>
+        <v>https://music.apple.com/us/album/new-york-confident/6765558036</v>
       </c>
       <c r="L141" t="str">
-        <v>Life On The Run - Brandi Carlile</v>
+        <v>New York Confident - Mark Ambor</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>New York Confident</v>
+        <v>pequeñita!</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
+        <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-22</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>New York Confident - Single</v>
+        <v>pequeñita! - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:27</v>
+        <v>2:39</v>
       </c>
       <c r="H142" t="str">
-        <v>Mark Ambor</v>
+        <v>Judeline</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/mark-ambor/1459754985</v>
+        <v>https://music.apple.com/us/artist/judeline/1487503245</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/new-york-confident/6765558036</v>
+        <v>https://music.apple.com/us/album/peque%C3%B1ita/6769827604</v>
       </c>
       <c r="L142" t="str">
-        <v>New York Confident - Mark Ambor</v>
+        <v>pequeñita! - Judeline</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>pequeñita!</v>
+        <v>Opaline</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
+        <v>https://music.apple.com/us/song/opaline/1886737060</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-22</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>pequeñita! - Single</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G143" t="str">
-        <v>2:39</v>
+        <v>3:17</v>
       </c>
       <c r="H143" t="str">
-        <v>Judeline</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/judeline/1487503245</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/peque%C3%B1ita/6769827604</v>
+        <v>https://music.apple.com/us/album/opaline/1886736650</v>
       </c>
       <c r="L143" t="str">
-        <v>pequeñita! - Judeline</v>
+        <v>Opaline - Stephan Moccio</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Opaline</v>
+        <v>Pretty Little Things</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/opaline/1886737060</v>
+        <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-22</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>Pretty Little Things - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:17</v>
+        <v>2:51</v>
       </c>
       <c r="H144" t="str">
-        <v>Stephan Moccio</v>
+        <v>Lauv</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/opaline/1886736650</v>
+        <v>https://music.apple.com/us/album/pretty-little-things/6767353963</v>
       </c>
       <c r="L144" t="str">
-        <v>Opaline - Stephan Moccio</v>
+        <v>Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Pretty Little Things</v>
+        <v>COLORADO</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
+        <v>https://music.apple.com/us/song/colorado/6769065232</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-22</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Pretty Little Things - Single</v>
+        <v>COLORADO - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:51</v>
+        <v>1:54</v>
       </c>
       <c r="H145" t="str">
-        <v>Lauv</v>
+        <v>Loud Luxury</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/pretty-little-things/6767353963</v>
+        <v>https://music.apple.com/us/album/colorado/6769064981</v>
       </c>
       <c r="L145" t="str">
-        <v>Pretty Little Things - Lauv</v>
+        <v>COLORADO - Loud Luxury</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>COLORADO</v>
+        <v>Infidelidad</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/colorado/6769065232</v>
+        <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-22</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>COLORADO - Single</v>
+        <v>El Disco de Salsa</v>
       </c>
       <c r="G146" t="str">
-        <v>1:54</v>
+        <v>3:29</v>
       </c>
       <c r="H146" t="str">
-        <v>Loud Luxury</v>
+        <v>Neutro Shorty</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
+        <v>https://music.apple.com/us/artist/neutro-shorty/1066850977</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/colorado/6769064981</v>
+        <v>https://music.apple.com/us/album/infidelidad/6768853655</v>
       </c>
       <c r="L146" t="str">
-        <v>COLORADO - Loud Luxury</v>
+        <v>Infidelidad - Neutro Shorty</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Infidelidad</v>
+        <v>Wrong Place, Wrong time</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
+        <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-22</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>El Disco de Salsa</v>
+        <v>Y'all Won</v>
       </c>
       <c r="G147" t="str">
-        <v>3:29</v>
+        <v>2:57</v>
       </c>
       <c r="H147" t="str">
-        <v>Neutro Shorty</v>
+        <v>Veeze</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/neutro-shorty/1066850977</v>
+        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/infidelidad/6768853655</v>
+        <v>https://music.apple.com/us/album/wrong-place-wrong-time/6771553812</v>
       </c>
       <c r="L147" t="str">
-        <v>Infidelidad - Neutro Shorty</v>
+        <v>Wrong Place, Wrong time - Veeze</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Wrong Place, Wrong time</v>
+        <v>La Semana</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
+        <v>https://music.apple.com/us/song/la-semana/6769913466</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-22</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Y'all Won</v>
+        <v>No Quiero Que Se Acabe Este Bendito Verano - EP</v>
       </c>
       <c r="G148" t="str">
-        <v>2:57</v>
+        <v>3:30</v>
       </c>
       <c r="H148" t="str">
-        <v>Veeze</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/wrong-place-wrong-time/6771553812</v>
+        <v>https://music.apple.com/us/album/la-semana/6769913464</v>
       </c>
       <c r="L148" t="str">
-        <v>Wrong Place, Wrong time - Veeze</v>
+        <v>La Semana - ELENA ROSE</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>La Semana</v>
+        <v>Una Mujer Como la Suya</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/la-semana/6769913466</v>
+        <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-22</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>No Quiero Que Se Acabe Este Bendito Verano - EP</v>
+        <v>Bandera Blanca</v>
       </c>
       <c r="G149" t="str">
-        <v>3:30</v>
+        <v>3:34</v>
       </c>
       <c r="H149" t="str">
-        <v>ELENA ROSE</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/la-semana/6769913464</v>
+        <v>https://music.apple.com/us/album/una-mujer-como-la-suya/1895154946</v>
       </c>
       <c r="L149" t="str">
-        <v>La Semana - ELENA ROSE</v>
+        <v>Una Mujer Como la Suya - Christian Nodal</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Una Mujer Como la Suya</v>
+        <v>Cold</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
+        <v>https://music.apple.com/us/song/cold/6763763802</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-22</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Bandera Blanca</v>
+        <v>Cold - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:34</v>
+        <v>2:52</v>
       </c>
       <c r="H150" t="str">
-        <v>Christian Nodal</v>
+        <v>Majid Jordan</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/majid-jordan/684530590</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/una-mujer-como-la-suya/1895154946</v>
+        <v>https://music.apple.com/us/album/cold/1895478371</v>
       </c>
       <c r="L150" t="str">
-        <v>Una Mujer Como la Suya - Christian Nodal</v>
+        <v>Cold - Majid Jordan</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Cold</v>
+        <v>VERTICAL WORLDS</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/cold/6763763802</v>
+        <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-22</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Cold - Single</v>
+        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
       </c>
       <c r="G151" t="str">
-        <v>2:52</v>
+        <v>3:15</v>
       </c>
       <c r="H151" t="str">
-        <v>Majid Jordan</v>
+        <v>Ecca Vandal</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/majid-jordan/684530590</v>
+        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/cold/1895478371</v>
+        <v>https://music.apple.com/us/album/vertical-worlds/1886485694</v>
       </c>
       <c r="L151" t="str">
-        <v>Cold - Majid Jordan</v>
+        <v>VERTICAL WORLDS - Ecca Vandal</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>VERTICAL WORLDS</v>
+        <v>Child of Divorce</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
+        <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-22</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
+        <v>soft pop</v>
       </c>
       <c r="G152" t="str">
-        <v>3:15</v>
+        <v>3:24</v>
       </c>
       <c r="H152" t="str">
-        <v>Ecca Vandal</v>
+        <v>Amy Shark</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
+        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/vertical-worlds/1886485694</v>
+        <v>https://music.apple.com/us/album/child-of-divorce/1880496743</v>
       </c>
       <c r="L152" t="str">
-        <v>VERTICAL WORLDS - Ecca Vandal</v>
+        <v>Child of Divorce - Amy Shark</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Child of Divorce</v>
+        <v>Taboo</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
+        <v>https://music.apple.com/us/song/taboo/6762838716</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-22</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>soft pop</v>
+        <v>Taboo - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:24</v>
+        <v>3:38</v>
       </c>
       <c r="H153" t="str">
-        <v>Amy Shark</v>
+        <v>Jensen McRae</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
+        <v>https://music.apple.com/us/artist/jensen-mcrae/591974463</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/child-of-divorce/1880496743</v>
+        <v>https://music.apple.com/us/album/taboo/1895036934</v>
       </c>
       <c r="L153" t="str">
-        <v>Child of Divorce - Amy Shark</v>
+        <v>Taboo - Jensen McRae</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Taboo</v>
+        <v>I'M OK</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/taboo/6762838716</v>
+        <v>https://music.apple.com/us/song/im-ok/1893392647</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-22</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Taboo - Single</v>
+        <v>A Rii Set</v>
       </c>
       <c r="G154" t="str">
-        <v>3:38</v>
+        <v>2:37</v>
       </c>
       <c r="H154" t="str">
-        <v>Jensen McRae</v>
+        <v>Pheelz</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/jensen-mcrae/591974463</v>
+        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/taboo/1895036934</v>
+        <v>https://music.apple.com/us/album/im-ok/1893392643</v>
       </c>
       <c r="L154" t="str">
-        <v>Taboo - Jensen McRae</v>
+        <v>I'M OK - Pheelz</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>I'M OK</v>
+        <v>Butterfly Feelings</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/im-ok/1893392647</v>
+        <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-22</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>A Rii Set</v>
+        <v>Ritual</v>
       </c>
       <c r="G155" t="str">
-        <v>2:37</v>
+        <v>2:35</v>
       </c>
       <c r="H155" t="str">
-        <v>Pheelz</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/im-ok/1893392643</v>
+        <v>https://music.apple.com/us/album/butterfly-feelings/1892426976</v>
       </c>
       <c r="L155" t="str">
-        <v>I'M OK - Pheelz</v>
+        <v>Butterfly Feelings - Icona Pop</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Butterfly Feelings</v>
+        <v>F**k the DJ</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
+        <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-22</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Ritual</v>
+        <v>Stage Girl (Not A Dream Anymore)</v>
       </c>
       <c r="G156" t="str">
-        <v>2:35</v>
+        <v>2:57</v>
       </c>
       <c r="H156" t="str">
-        <v>Icona Pop</v>
+        <v>Eli</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/butterfly-feelings/1892426976</v>
+        <v>https://music.apple.com/us/album/f-k-the-dj/6769903867</v>
       </c>
       <c r="L156" t="str">
-        <v>Butterfly Feelings - Icona Pop</v>
+        <v>F**k the DJ - Eli</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>F**k the DJ</v>
+        <v>Grateful</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
+        <v>https://music.apple.com/us/song/grateful/1887166624</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-22</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Stage Girl (Not A Dream Anymore)</v>
+        <v>24</v>
       </c>
       <c r="G157" t="str">
-        <v>2:57</v>
+        <v>2:18</v>
       </c>
       <c r="H157" t="str">
-        <v>Eli</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/f-k-the-dj/6769903867</v>
+        <v>https://music.apple.com/us/album/grateful/1887166427</v>
       </c>
       <c r="L157" t="str">
-        <v>F**k the DJ - Eli</v>
+        <v>Grateful - Alexis Ffrench</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Grateful</v>
+        <v>Second Chance</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/grateful/1887166624</v>
+        <v>https://music.apple.com/us/song/second-chance/6766778687</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-22</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>24</v>
+        <v>Second Chance - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:18</v>
+        <v>3:06</v>
       </c>
       <c r="H158" t="str">
-        <v>Alexis Ffrench</v>
+        <v>Lukas Graham</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/lukas-graham/473219952</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/grateful/1887166427</v>
+        <v>https://music.apple.com/us/album/second-chance/6766778682</v>
       </c>
       <c r="L158" t="str">
-        <v>Grateful - Alexis Ffrench</v>
+        <v>Second Chance - Lukas Graham</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Second Chance</v>
+        <v>Stupid World (feat. Chad Tepper) [Bonus Track]</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/second-chance/6766778687</v>
+        <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-22</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Second Chance - Single</v>
+        <v>Tommyland Rides Again</v>
       </c>
       <c r="G159" t="str">
-        <v>3:06</v>
+        <v>3:49</v>
       </c>
       <c r="H159" t="str">
-        <v>Lukas Graham</v>
+        <v>Tommy Lee</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/lukas-graham/473219952</v>
+        <v>https://music.apple.com/us/artist/tommy-lee/68696</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/second-chance/6766778682</v>
+        <v>https://music.apple.com/us/album/stupid-world-feat-chad-tepper-bonus-track/1893473875</v>
       </c>
       <c r="L159" t="str">
-        <v>Second Chance - Lukas Graham</v>
+        <v>Stupid World (feat. Chad Tepper) [Bonus Track] - Tommy Lee</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Stupid World (feat. Chad Tepper) [Bonus Track]</v>
+        <v>DOOM LOOP</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
+        <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-22</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Tommyland Rides Again</v>
+        <v>Blood Of Your Empire</v>
       </c>
       <c r="G160" t="str">
-        <v>3:49</v>
+        <v>4:00</v>
       </c>
       <c r="H160" t="str">
-        <v>Tommy Lee</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/tommy-lee/68696</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/stupid-world-feat-chad-tepper-bonus-track/1893473875</v>
+        <v>https://music.apple.com/us/album/doom-loop/6769905842</v>
       </c>
       <c r="L160" t="str">
-        <v>Stupid World (feat. Chad Tepper) [Bonus Track] - Tommy Lee</v>
+        <v>DOOM LOOP - PRESIDENT</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>DOOM LOOP</v>
+        <v>New York City</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
+        <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-22</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Blood Of Your Empire</v>
+        <v>New York City - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>4:00</v>
+        <v>3:30</v>
       </c>
       <c r="H161" t="str">
-        <v>PRESIDENT</v>
+        <v>Anthony Ramos</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/anthony-ramos/1313064678</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/doom-loop/6769905842</v>
+        <v>https://music.apple.com/us/album/new-york-city/6770624324</v>
       </c>
       <c r="L161" t="str">
-        <v>DOOM LOOP - PRESIDENT</v>
+        <v>New York City - Anthony Ramos</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>New York City</v>
+        <v>I Found You</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
+        <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-22</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>New York City - Single</v>
+        <v>I Found You - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:30</v>
+        <v>3:18</v>
       </c>
       <c r="H162" t="str">
-        <v>Anthony Ramos</v>
+        <v>TA Thomas</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/anthony-ramos/1313064678</v>
+        <v>https://music.apple.com/us/artist/ta-thomas/1232189106</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/new-york-city/6770624324</v>
+        <v>https://music.apple.com/us/album/i-found-you/1894024530</v>
       </c>
       <c r="L162" t="str">
-        <v>New York City - Anthony Ramos</v>
+        <v>I Found You - TA Thomas</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>I Found You</v>
+        <v>Just My Type</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
+        <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-22</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>I Found You - Single</v>
+        <v>Labor Of Love</v>
       </c>
       <c r="G163" t="str">
-        <v>3:18</v>
+        <v>2:40</v>
       </c>
       <c r="H163" t="str">
-        <v>TA Thomas</v>
+        <v>Blxst</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/ta-thomas/1232189106</v>
+        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/i-found-you/1894024530</v>
+        <v>https://music.apple.com/us/album/just-my-type/1895199881</v>
       </c>
       <c r="L163" t="str">
-        <v>I Found You - TA Thomas</v>
+        <v>Just My Type - Blxst</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Just My Type</v>
+        <v>teenage drama</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
+        <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-22</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Labor Of Love</v>
+        <v>teenage drama - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:40</v>
+        <v>3:06</v>
       </c>
       <c r="H164" t="str">
-        <v>Blxst</v>
+        <v>paris jackson</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/just-my-type/1895199881</v>
+        <v>https://music.apple.com/us/album/teenage-drama/6768447515</v>
       </c>
       <c r="L164" t="str">
-        <v>Just My Type - Blxst</v>
+        <v>teenage drama - paris jackson</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>teenage drama</v>
+        <v>does it still mean something?</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
+        <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-22</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>teenage drama - Single</v>
+        <v>only if it matters</v>
       </c>
       <c r="G165" t="str">
-        <v>3:06</v>
+        <v>3:48</v>
       </c>
       <c r="H165" t="str">
-        <v>paris jackson</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/teenage-drama/6768447515</v>
+        <v>https://music.apple.com/us/album/does-it-still-mean-something/6768446154</v>
       </c>
       <c r="L165" t="str">
-        <v>teenage drama - paris jackson</v>
+        <v>does it still mean something? - Kevian Kraemer</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>does it still mean something?</v>
+        <v>Debbie Don't Cry</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
+        <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-22</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>only if it matters</v>
+        <v>Debbie Don't Cry - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:48</v>
+        <v>3:00</v>
       </c>
       <c r="H166" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Ruel</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/does-it-still-mean-something/6768446154</v>
+        <v>https://music.apple.com/us/album/debbie-dont-cry/6768206616</v>
       </c>
       <c r="L166" t="str">
-        <v>does it still mean something? - Kevian Kraemer</v>
+        <v>Debbie Don't Cry - Ruel</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Debbie Don't Cry</v>
+        <v>YEAH YEAH YEAH</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
+        <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-22</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Debbie Don't Cry - Single</v>
+        <v>YEAH YEAH YEAH - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:00</v>
+        <v>2:25</v>
       </c>
       <c r="H167" t="str">
-        <v>Ruel</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/debbie-dont-cry/6768206616</v>
+        <v>https://music.apple.com/us/album/yeah-yeah-yeah/6767515610</v>
       </c>
       <c r="L167" t="str">
-        <v>Debbie Don't Cry - Ruel</v>
+        <v>YEAH YEAH YEAH - Cruz Beckham</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>YEAH YEAH YEAH</v>
+        <v>Cotton Flower</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
+        <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-22</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>YEAH YEAH YEAH - Single</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G168" t="str">
-        <v>2:25</v>
+        <v>3:53</v>
       </c>
       <c r="H168" t="str">
-        <v>Cruz Beckham</v>
+        <v>Future Islands</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/yeah-yeah-yeah/6767515610</v>
+        <v>https://music.apple.com/us/album/cotton-flower/1883045480</v>
       </c>
       <c r="L168" t="str">
-        <v>YEAH YEAH YEAH - Cruz Beckham</v>
+        <v>Cotton Flower - Future Islands</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Cotton Flower</v>
+        <v>WAHALA RIDDIM</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
+        <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-22</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>WAHALA RIDDIM - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:53</v>
+        <v>3:22</v>
       </c>
       <c r="H169" t="str">
-        <v>Future Islands</v>
+        <v>THEHONESTGUY</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/cotton-flower/1883045480</v>
+        <v>https://music.apple.com/us/album/wahala-riddim/1895810537</v>
       </c>
       <c r="L169" t="str">
-        <v>Cotton Flower - Future Islands</v>
+        <v>WAHALA RIDDIM - THEHONESTGUY</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>WAHALA RIDDIM</v>
+        <v>Comfort</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
+        <v>https://music.apple.com/us/song/comfort/1876521401</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-22</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>WAHALA RIDDIM - Single</v>
+        <v>So Help Me God</v>
       </c>
       <c r="G170" t="str">
-        <v>3:22</v>
+        <v>5:35</v>
       </c>
       <c r="H170" t="str">
-        <v>THEHONESTGUY</v>
+        <v>Kelsey Lu</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
+        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/wahala-riddim/1895810537</v>
+        <v>https://music.apple.com/us/album/comfort/1876521144</v>
       </c>
       <c r="L170" t="str">
-        <v>WAHALA RIDDIM - THEHONESTGUY</v>
+        <v>Comfort - Kelsey Lu</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Comfort</v>
+        <v>Skin</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/comfort/1876521401</v>
+        <v>https://music.apple.com/us/song/skin/6764651585</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-22</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>So Help Me God</v>
+        <v>Skin - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>5:35</v>
+        <v>3:00</v>
       </c>
       <c r="H171" t="str">
-        <v>Kelsey Lu</v>
+        <v>Alessi Rose</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
+        <v>https://music.apple.com/us/artist/alessi-rose/1628689028</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/comfort/1876521144</v>
+        <v>https://music.apple.com/us/album/skin/1895865252</v>
       </c>
       <c r="L171" t="str">
-        <v>Comfort - Kelsey Lu</v>
+        <v>Skin - Alessi Rose</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Skin</v>
+        <v>IDGAF</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/skin/6764651585</v>
+        <v>https://music.apple.com/us/song/idgaf/6764422210</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-22</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Skin - Single</v>
+        <v>IDGAF - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:00</v>
+        <v>2:55</v>
       </c>
       <c r="H172" t="str">
-        <v>Alessi Rose</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/alessi-rose/1628689028</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/skin/1895865252</v>
+        <v>https://music.apple.com/us/album/idgaf/1895773358</v>
       </c>
       <c r="L172" t="str">
-        <v>Skin - Alessi Rose</v>
+        <v>IDGAF - Katelyn Tarver</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>IDGAF</v>
+        <v>Run Rabbit</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/idgaf/6764422210</v>
+        <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-22</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>IDGAF - Single</v>
+        <v>Run Rabbit - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:55</v>
+        <v>3:09</v>
       </c>
       <c r="H173" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Mollie Elizabeth</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/mollie-elizabeth/1780515318</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/idgaf/1895773358</v>
+        <v>https://music.apple.com/us/album/run-rabbit/6767354664</v>
       </c>
       <c r="L173" t="str">
-        <v>IDGAF - Katelyn Tarver</v>
+        <v>Run Rabbit - Mollie Elizabeth</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Run Rabbit</v>
+        <v>So Good (feat. Kuuda)</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
+        <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-22</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Run Rabbit - Single</v>
+        <v>So Good (feat. Kuuda) - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:09</v>
+        <v>3:03</v>
       </c>
       <c r="H174" t="str">
-        <v>Mollie Elizabeth</v>
+        <v>CamelPhat</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/mollie-elizabeth/1780515318</v>
+        <v>https://music.apple.com/us/artist/camelphat/385810888</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/run-rabbit/6767354664</v>
+        <v>https://music.apple.com/us/album/so-good-feat-kuuda/6766655768</v>
       </c>
       <c r="L174" t="str">
-        <v>Run Rabbit - Mollie Elizabeth</v>
+        <v>So Good (feat. Kuuda) - CamelPhat</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>So Good (feat. Kuuda)</v>
+        <v>Empty Theatre, Pretty Picture</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
+        <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-22</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>So Good (feat. Kuuda) - Single</v>
+        <v>Empty Theatre, Pretty Picture</v>
       </c>
       <c r="G175" t="str">
-        <v>3:03</v>
+        <v>5:01</v>
       </c>
       <c r="H175" t="str">
-        <v>CamelPhat</v>
+        <v>Lane 8</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/camelphat/385810888</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/so-good-feat-kuuda/6766655768</v>
+        <v>https://music.apple.com/us/album/empty-theatre-pretty-picture/1895395993</v>
       </c>
       <c r="L175" t="str">
-        <v>So Good (feat. Kuuda) - CamelPhat</v>
+        <v>Empty Theatre, Pretty Picture - Lane 8</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Empty Theatre, Pretty Picture</v>
+        <v>regalametutiempo</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
+        <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-22</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Empty Theatre, Pretty Picture</v>
+        <v>PROYECTANDO</v>
       </c>
       <c r="G176" t="str">
-        <v>5:01</v>
+        <v>3:01</v>
       </c>
       <c r="H176" t="str">
-        <v>Lane 8</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/empty-theatre-pretty-picture/1895395993</v>
+        <v>https://music.apple.com/us/album/regalametutiempo/6769922866</v>
       </c>
       <c r="L176" t="str">
-        <v>Empty Theatre, Pretty Picture - Lane 8</v>
+        <v>regalametutiempo - Julio Caesar</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>regalametutiempo</v>
+        <v>On Sight</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
+        <v>https://music.apple.com/us/song/on-sight/6763971220</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-22</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>PROYECTANDO</v>
+        <v>Left on RED</v>
       </c>
       <c r="G177" t="str">
-        <v>3:01</v>
+        <v>2:25</v>
       </c>
       <c r="H177" t="str">
-        <v>Julio Caesar</v>
+        <v>REMI</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/remi/1716510008</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/regalametutiempo/6769922866</v>
+        <v>https://music.apple.com/us/album/on-sight/1895580736</v>
       </c>
       <c r="L177" t="str">
-        <v>regalametutiempo - Julio Caesar</v>
+        <v>On Sight - REMI</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>On Sight</v>
+        <v>Masks Off</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/on-sight/6763971220</v>
+        <v>https://music.apple.com/us/song/masks-off/6764077133</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-22</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Left on RED</v>
+        <v>Masks Off - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:25</v>
+        <v>3:24</v>
       </c>
       <c r="H178" t="str">
-        <v>REMI</v>
+        <v>Jesse Welles</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/remi/1716510008</v>
+        <v>https://music.apple.com/us/artist/jesse-welles/1737507146</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/on-sight/1895580736</v>
+        <v>https://music.apple.com/us/album/masks-off/1895628310</v>
       </c>
       <c r="L178" t="str">
-        <v>On Sight - REMI</v>
+        <v>Masks Off - Jesse Welles</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Masks Off</v>
+        <v>I'm Just A Girl</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/masks-off/6764077133</v>
+        <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-22</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Masks Off - Single</v>
+        <v>Di Hotel Malibu</v>
       </c>
       <c r="G179" t="str">
-        <v>3:24</v>
+        <v>2:49</v>
       </c>
       <c r="H179" t="str">
-        <v>Jesse Welles</v>
+        <v>Thee Marloes</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/jesse-welles/1737507146</v>
+        <v>https://music.apple.com/us/artist/thee-marloes/1541376632</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/masks-off/1895628310</v>
+        <v>https://music.apple.com/us/album/im-just-a-girl/1878399768</v>
       </c>
       <c r="L179" t="str">
-        <v>Masks Off - Jesse Welles</v>
+        <v>I'm Just A Girl - Thee Marloes</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>I'm Just A Girl</v>
+        <v>Soleil (feat. Isabella Lovestory)</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
+        <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-22</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Di Hotel Malibu</v>
+        <v>EXIT 2B</v>
       </c>
       <c r="G180" t="str">
-        <v>2:49</v>
+        <v>2:11</v>
       </c>
       <c r="H180" t="str">
-        <v>Thee Marloes</v>
+        <v>B0YG1RL</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/thee-marloes/1541376632</v>
+        <v>https://music.apple.com/us/artist/b0yg1rl/1847766665</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/im-just-a-girl/1878399768</v>
+        <v>https://music.apple.com/us/album/soleil-feat-isabella-lovestory/6769526101</v>
       </c>
       <c r="L180" t="str">
-        <v>I'm Just A Girl - Thee Marloes</v>
+        <v>Soleil (feat. Isabella Lovestory) - B0YG1RL</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Soleil (feat. Isabella Lovestory)</v>
+        <v>Money Tree</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
+        <v>https://music.apple.com/us/song/money-tree/6763211637</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-22</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>EXIT 2B</v>
+        <v>Money Tree - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:11</v>
+        <v>2:39</v>
       </c>
       <c r="H181" t="str">
-        <v>B0YG1RL</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/b0yg1rl/1847766665</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/soleil-feat-isabella-lovestory/6769526101</v>
+        <v>https://music.apple.com/us/album/money-tree/1895216986</v>
       </c>
       <c r="L181" t="str">
-        <v>Soleil (feat. Isabella Lovestory) - B0YG1RL</v>
+        <v>Money Tree - Olympia Vitalis</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Money Tree</v>
+        <v>Homerunner</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/money-tree/6763211637</v>
+        <v>https://music.apple.com/us/song/homerunner/6770682178</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-22</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Money Tree - Single</v>
+        <v>Homerunner - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:39</v>
+        <v>2:36</v>
       </c>
       <c r="H182" t="str">
-        <v>Olympia Vitalis</v>
+        <v>slayr</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/money-tree/1895216986</v>
+        <v>https://music.apple.com/us/album/homerunner/6770682177</v>
       </c>
       <c r="L182" t="str">
-        <v>Money Tree - Olympia Vitalis</v>
+        <v>Homerunner - slayr</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Homerunner</v>
+        <v>Mail</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/homerunner/6770682178</v>
+        <v>https://music.apple.com/us/song/mail/6769190635</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-22</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Homerunner - Single</v>
+        <v>Mail - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:36</v>
+        <v>2:14</v>
       </c>
       <c r="H183" t="str">
-        <v>slayr</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/homerunner/6770682177</v>
+        <v>https://music.apple.com/us/album/mail/6769190634</v>
       </c>
       <c r="L183" t="str">
-        <v>Homerunner - slayr</v>
+        <v>Mail - MexikoDro</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Mail</v>
+        <v>Waste Your Heart</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/mail/6769190635</v>
+        <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-22</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Mail - Single</v>
+        <v>Waste Your Heart - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:14</v>
+        <v>2:31</v>
       </c>
       <c r="H184" t="str">
-        <v>MexikoDro</v>
+        <v>Magnus Ferrell</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/mail/6769190634</v>
+        <v>https://music.apple.com/us/album/waste-your-heart/6769241913</v>
       </c>
       <c r="L184" t="str">
-        <v>Mail - MexikoDro</v>
+        <v>Waste Your Heart - Magnus Ferrell</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Waste Your Heart</v>
+        <v>Sleeping Pills</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
+        <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-22</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Waste Your Heart - Single</v>
+        <v>Sleeping Pills - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:31</v>
+        <v>3:03</v>
       </c>
       <c r="H185" t="str">
-        <v>Magnus Ferrell</v>
+        <v>Dolder</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
+        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/waste-your-heart/6769241913</v>
+        <v>https://music.apple.com/us/album/sleeping-pills/1896452689</v>
       </c>
       <c r="L185" t="str">
-        <v>Waste Your Heart - Magnus Ferrell</v>
+        <v>Sleeping Pills - Dolder</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Sleeping Pills</v>
+        <v>KODACHROMATIC</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
+        <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-22</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Sleeping Pills - Single</v>
+        <v>KODACHROMATIC - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:03</v>
+        <v>2:53</v>
       </c>
       <c r="H186" t="str">
-        <v>Dolder</v>
+        <v>Tiger La Flor</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
+        <v>https://music.apple.com/us/artist/tiger-la-flor/1613113982</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/sleeping-pills/1896452689</v>
+        <v>https://music.apple.com/us/album/kodachromatic/6770724719</v>
       </c>
       <c r="L186" t="str">
-        <v>Sleeping Pills - Dolder</v>
+        <v>KODACHROMATIC - Tiger La Flor</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>KODACHROMATIC</v>
+        <v>FOMO</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
+        <v>https://music.apple.com/us/song/fomo/1890190631</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-22</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>KODACHROMATIC - Single</v>
+        <v>Map Of Her Shadow</v>
       </c>
       <c r="G187" t="str">
-        <v>2:53</v>
+        <v>3:01</v>
       </c>
       <c r="H187" t="str">
-        <v>Tiger La Flor</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/tiger-la-flor/1613113982</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/kodachromatic/6770724719</v>
+        <v>https://music.apple.com/us/album/fomo/1890190623</v>
       </c>
       <c r="L187" t="str">
-        <v>KODACHROMATIC - Tiger La Flor</v>
+        <v>FOMO - Anais Cardot</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>FOMO</v>
+        <v>Black Fire</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/fomo/1890190631</v>
+        <v>https://music.apple.com/us/song/black-fire/6770696877</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-22</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Map Of Her Shadow</v>
+        <v>Sulfur Surfer</v>
       </c>
       <c r="G188" t="str">
-        <v>3:01</v>
+        <v>3:37</v>
       </c>
       <c r="H188" t="str">
-        <v>Anais Cardot</v>
+        <v>Bladee</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/bladee/861359576</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/fomo/1890190623</v>
+        <v>https://music.apple.com/us/album/black-fire/6770696743</v>
       </c>
       <c r="L188" t="str">
-        <v>FOMO - Anais Cardot</v>
+        <v>Black Fire - Bladee</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Black Fire</v>
+        <v>As Seen in the Unseen</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/black-fire/6770696877</v>
+        <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-22</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Sulfur Surfer</v>
+        <v>Grand Serpent Rising</v>
       </c>
       <c r="G189" t="str">
-        <v>3:37</v>
+        <v>6:59</v>
       </c>
       <c r="H189" t="str">
-        <v>Bladee</v>
+        <v>Dimmu Borgir</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/bladee/861359576</v>
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/black-fire/6770696743</v>
+        <v>https://music.apple.com/us/album/as-seen-in-the-unseen/1883121436</v>
       </c>
       <c r="L189" t="str">
-        <v>Black Fire - Bladee</v>
+        <v>As Seen in the Unseen - Dimmu Borgir</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>As Seen in the Unseen</v>
+        <v>Every Man-Any Man</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
+        <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-22</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Grand Serpent Rising</v>
+        <v>Emotion Factory Reset</v>
       </c>
       <c r="G190" t="str">
-        <v>6:59</v>
+        <v>4:20</v>
       </c>
       <c r="H190" t="str">
-        <v>Dimmu Borgir</v>
+        <v>Armored Saint</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/as-seen-in-the-unseen/1883121436</v>
+        <v>https://music.apple.com/us/album/every-man-any-man/1872193859</v>
       </c>
       <c r="L190" t="str">
-        <v>As Seen in the Unseen - Dimmu Borgir</v>
+        <v>Every Man-Any Man - Armored Saint</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Every Man-Any Man</v>
+        <v>No Arms</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
+        <v>https://music.apple.com/us/song/no-arms/6765776563</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-22</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Emotion Factory Reset</v>
+        <v>From A Distance</v>
       </c>
       <c r="G191" t="str">
-        <v>4:20</v>
+        <v>3:43</v>
       </c>
       <c r="H191" t="str">
-        <v>Armored Saint</v>
+        <v>156/Silence</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
+        <v>https://music.apple.com/us/artist/156-silence/1071395282</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/every-man-any-man/1872193859</v>
+        <v>https://music.apple.com/us/album/no-arms/1896069437</v>
       </c>
       <c r="L191" t="str">
-        <v>Every Man-Any Man - Armored Saint</v>
+        <v>No Arms - 156/Silence</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>No Arms</v>
+        <v>It's Neverending</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/no-arms/6765776563</v>
+        <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-22</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>From A Distance</v>
+        <v>Neverending</v>
       </c>
       <c r="G192" t="str">
-        <v>3:43</v>
+        <v>8:35</v>
       </c>
       <c r="H192" t="str">
-        <v>156/Silence</v>
+        <v>Monolord</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/156-silence/1071395282</v>
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/no-arms/1896069437</v>
+        <v>https://music.apple.com/us/album/its-neverending/1871211801</v>
       </c>
       <c r="L192" t="str">
-        <v>No Arms - 156/Silence</v>
+        <v>It's Neverending - Monolord</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>It's Neverending</v>
+        <v>The Kids Will Kill Us</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
+        <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-22</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Neverending</v>
+        <v>The Kids Will Kill Us - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>8:35</v>
+        <v>3:45</v>
       </c>
       <c r="H193" t="str">
-        <v>Monolord</v>
+        <v>Witch Club Satan</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+        <v>https://music.apple.com/us/artist/witch-club-satan/1626477576</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/its-neverending/1871211801</v>
+        <v>https://music.apple.com/us/album/the-kids-will-kill-us/6766343272</v>
       </c>
       <c r="L193" t="str">
-        <v>It's Neverending - Monolord</v>
+        <v>The Kids Will Kill Us - Witch Club Satan</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>The Kids Will Kill Us</v>
+        <v>Masters of the Universe (from "Masters of the Universe")</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
+        <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-22</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>The Kids Will Kill Us - Single</v>
+        <v>Masters of the Universe (from "Masters of the Universe") - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:45</v>
+        <v>3:20</v>
       </c>
       <c r="H194" t="str">
-        <v>Witch Club Satan</v>
+        <v>The Darkness</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/witch-club-satan/1626477576</v>
+        <v>https://music.apple.com/us/artist/the-darkness/2417388</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/the-kids-will-kill-us/6766343272</v>
+        <v>https://music.apple.com/us/album/masters-of-the-universe-from-masters-of-the-universe/6769065779</v>
       </c>
       <c r="L194" t="str">
-        <v>The Kids Will Kill Us - Witch Club Satan</v>
+        <v>Masters of the Universe (from "Masters of the Universe") - The Darkness</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe")</v>
+        <v>All Day</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
+        <v>https://music.apple.com/us/song/all-day/1880746584</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-22</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe") - Single</v>
+        <v>Feet On Fire</v>
       </c>
       <c r="G195" t="str">
-        <v>3:20</v>
+        <v>2:29</v>
       </c>
       <c r="H195" t="str">
-        <v>The Darkness</v>
+        <v>Ben Chapman</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/the-darkness/2417388</v>
+        <v>https://music.apple.com/us/artist/ben-chapman/1581192612</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/masters-of-the-universe-from-masters-of-the-universe/6769065779</v>
+        <v>https://music.apple.com/us/album/all-day/1880746349</v>
       </c>
       <c r="L195" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe") - The Darkness</v>
+        <v>All Day - Ben Chapman</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>All Day</v>
+        <v>Sigui</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/all-day/1880746584</v>
+        <v>https://music.apple.com/us/song/sigui/1890241955</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-22</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Feet On Fire</v>
+        <v>Massa</v>
       </c>
       <c r="G196" t="str">
-        <v>2:29</v>
+        <v>3:17</v>
       </c>
       <c r="H196" t="str">
-        <v>Ben Chapman</v>
+        <v>Fatoumata Diawara</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/ben-chapman/1581192612</v>
+        <v>https://music.apple.com/us/artist/fatoumata-diawara/466213610</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/all-day/1880746349</v>
+        <v>https://music.apple.com/us/album/sigui/1890241617</v>
       </c>
       <c r="L196" t="str">
-        <v>All Day - Ben Chapman</v>
+        <v>Sigui - Fatoumata Diawara</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Sigui</v>
+        <v>High Tail</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/sigui/1890241955</v>
+        <v>https://music.apple.com/us/song/high-tail/1870432994</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-22</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Massa</v>
+        <v>Where the South Winds Wail</v>
       </c>
       <c r="G197" t="str">
-        <v>3:17</v>
+        <v>2:31</v>
       </c>
       <c r="H197" t="str">
-        <v>Fatoumata Diawara</v>
+        <v>Gitkin</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/fatoumata-diawara/466213610</v>
+        <v>https://music.apple.com/us/artist/gitkin/1345281815</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/sigui/1890241617</v>
+        <v>https://music.apple.com/us/album/high-tail/1870432670</v>
       </c>
       <c r="L197" t="str">
-        <v>Sigui - Fatoumata Diawara</v>
+        <v>High Tail - Gitkin</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>High Tail</v>
+        <v>Mice Protection</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/high-tail/1870432994</v>
+        <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-22</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Where the South Winds Wail</v>
+        <v>Ugly Duckling Union</v>
       </c>
       <c r="G198" t="str">
-        <v>2:31</v>
+        <v>3:34</v>
       </c>
       <c r="H198" t="str">
-        <v>Gitkin</v>
+        <v>Lowertown</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/gitkin/1345281815</v>
+        <v>https://music.apple.com/us/artist/lowertown/1448207323</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/high-tail/1870432670</v>
+        <v>https://music.apple.com/us/album/mice-protection/1872171971</v>
       </c>
       <c r="L198" t="str">
-        <v>High Tail - Gitkin</v>
+        <v>Mice Protection - Lowertown</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Mice Protection</v>
+        <v>Tóxica</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
+        <v>https://music.apple.com/us/song/t%C3%B3xica/6763056240</v>
       </c>
       <c r="D199" t="str">
         <v>2026-05-22</v>
@@ -7937,68 +7937,30 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Ugly Duckling Union</v>
+        <v>Caribenya</v>
       </c>
       <c r="G199" t="str">
-        <v>3:34</v>
+        <v>3:48</v>
       </c>
       <c r="H199" t="str">
-        <v>Lowertown</v>
+        <v>Lido Pimienta</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/lowertown/1448207323</v>
+        <v>https://music.apple.com/us/artist/lido-pimienta/389475023</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/mice-protection/1872171971</v>
+        <v>https://music.apple.com/us/album/t%C3%B3xica/1895141218</v>
       </c>
       <c r="L199" t="str">
-        <v>Mice Protection - Lowertown</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>Tóxica</v>
-      </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/t%C3%B3xica/6763056240</v>
-      </c>
-      <c r="D200" t="str">
-        <v>2026-05-22</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
-        <v>Caribenya</v>
-      </c>
-      <c r="G200" t="str">
-        <v>3:48</v>
-      </c>
-      <c r="H200" t="str">
-        <v>Lido Pimienta</v>
-      </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/lido-pimienta/389475023</v>
-      </c>
-      <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/t%C3%B3xica/1895141218</v>
-      </c>
-      <c r="L200" t="str">
         <v>Tóxica - Lido Pimienta</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week04/titles.xlsx
+++ b/data/global/2026-05-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B3" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B7" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>

--- a/data/global/2026-05-week04/titles.xlsx
+++ b/data/global/2026-05-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B3" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B7" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B22" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B25" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B26" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B63" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>

--- a/data/global/2026-05-week04/titles.xlsx
+++ b/data/global/2026-05-week04/titles.xlsx
@@ -439,19 +439,19 @@
         <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,19 +477,19 @@
         <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,19 +515,19 @@
         <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,19 +553,19 @@
         <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,19 +591,19 @@
         <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,19 +629,19 @@
         <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B7" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,19 +667,19 @@
         <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1009,19 +1009,19 @@
         <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,19 +1047,19 @@
         <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,19 +1085,19 @@
         <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,19 +1123,19 @@
         <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1389,19 +1389,19 @@
         <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B27" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2681,19 +2681,19 @@
         <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,19 +2719,19 @@
         <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/the-cure/1889992123</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/ss26/6771061782</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/white-flag/1887627840</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/goals/6769251838</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/ego/6769207667</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/24-hours/6771060076</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/tarentino/6769927265</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/questions/1871502847</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/dosis/6762929729</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/the-climb/6769546149</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/boompala/1894802726</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/dear-god/1878237813</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/hexagons/1885607736</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/opaline/1886737060</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/colorado/6769065232</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/la-semana/6769913466</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/cold/6763763802</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/taboo/6762838716</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/im-ok/1893392647</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/grateful/1887166624</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/second-chance/6766778687</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/comfort/1876521401</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/skin/6764651585</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/idgaf/6764422210</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/on-sight/6763971220</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/masks-off/6764077133</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/money-tree/6763211637</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/homerunner/6770682178</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/mail/6769190635</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/fomo/1890190631</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/black-fire/6770696877</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/no-arms/6765776563</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/all-day/1880746584</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/sigui/1890241955</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/high-tail/1870432994</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/t%C3%B3xica/6763056240</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E199" t="str">
         <v/>

--- a/data/global/2026-05-week04/titles.xlsx
+++ b/data/global/2026-05-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v/>

--- a/data/global/2026-05-week04/titles.xlsx
+++ b/data/global/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L200"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>אסתר שמיר ויהל דורון – בצד השני של הפחד</v>
       </c>
       <c r="B2" t="str">
-        <v>22 hours ago</v>
+        <v>2026-05-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://yosmusic.com/%d7%90%d7%a1%d7%aa%d7%a8-%d7%a9%d7%9e%d7%99%d7%a8-%d7%95%d7%99%d7%94%d7%9c-%d7%93%d7%95%d7%a8%d7%95%d7%9f-%d7%91%d7%a6%d7%93-%d7%94%d7%a9%d7%a0%d7%99-%d7%a9%d7%9c-%d7%94%d7%a4%d7%97%d7%93/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-23</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>22 hours ago</v>
+        <v>שיתוף הפעולה בין אסתר שמיר ליהל דורון ב״בצד השני של הפחד״ הוא לא רק דואט מוזיקלי  אלא מפגש בין שתי תפיסות של רגש, כתיבה ונחמה במוזיקה הישראלית. מצד אחד קול שנושא איתו היסטוריה תרבותית שלמה, ומצד שני יוצר עכשווי שמביא</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Dean Lewis</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>אסתר שמיר ויהל דורון – בצד השני של הפחד</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B3" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-23</v>
@@ -495,7 +495,7 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B4" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-23</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Niall Horan</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-23</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-23</v>
@@ -609,7 +609,7 @@
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>RUEL</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-23</v>
@@ -647,7 +647,7 @@
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>TINI</v>
+        <v>RUEL</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-23</v>
@@ -685,7 +685,7 @@
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Charli xcx</v>
+        <v>TINI</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-23</v>
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Dua Lipa</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B10" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-23</v>
@@ -761,7 +761,7 @@
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Matilda Mann</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-23</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Ella Langley</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-23</v>
@@ -837,7 +837,7 @@
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-23</v>
@@ -875,7 +875,7 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>kesha</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-23</v>
@@ -913,7 +913,7 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Holly Humberstone</v>
+        <v>kesha</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-23</v>
@@ -951,7 +951,7 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Foo Fighters</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-23</v>
@@ -989,7 +989,7 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>The Analogues</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B17" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-23</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Rod Stewart</v>
+        <v>The Analogues</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B18" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-23</v>
@@ -1065,7 +1065,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Blue October</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Far Caspian - hum (Official Video)</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
+        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-23</v>
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Far Caspian</v>
+        <v>Blue October</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Kenia Os - Love Bombing</v>
+        <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B20" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
+        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-23</v>
@@ -1141,7 +1141,7 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Kenia Os</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Kenia Os - Love Bombing - Kenia Os</v>
+        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
+        <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B21" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
+        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-23</v>
@@ -1179,7 +1179,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
+        <v>Kenia Os - Love Bombing - Kenia Os</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B22" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-23</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B23" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-23</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B24" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-23</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B25" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-23</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B26" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-23</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B27" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-23</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B28" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-23</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Evanescence</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-23</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Evanescence</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-23</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Armin van Buuren</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B31" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-23</v>
@@ -1559,7 +1559,7 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Madison Cunningham</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-23</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Johnny Orlando</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B33" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-23</v>
@@ -1635,7 +1635,7 @@
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Carver Jones</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B34" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-23</v>
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Jazmin bean</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B35" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-23</v>
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Baby Queen</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B36" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-23</v>
@@ -1749,7 +1749,7 @@
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Switchfoot</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B37" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-23</v>
@@ -1787,7 +1787,7 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Grace Potter</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B38" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-23</v>
@@ -1825,7 +1825,7 @@
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-23</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>The All-American Rejects</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-23</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Henry Moodie</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-23</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Spacey Jane</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-23</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Megan Moroney</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-23</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Matt Hansen</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-23</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Keith Urban - Steal Away (Visualizer)</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
+        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-23</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Keith Urban</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>VALÉ - Mugshot (Official Video)</v>
+        <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
+        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-23</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>VALÉ</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
+        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio)</v>
+        <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
+        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-23</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Mackenzie Carpenter</v>
+        <v>VALÉ</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
+        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
+        <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
+        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-23</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Towa Bird</v>
+        <v>Mackenzie Carpenter</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
+        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
+        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-23</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Sabrina Sterling</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
+        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-23</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Little Big Town</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Becky G - EPA (Official Video)</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
+        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-23</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Becky G</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Becky G - EPA (Official Video) - Becky G</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
+        <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
+        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-23</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Daisy the Great</v>
+        <v>Becky G</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
+        <v>Becky G - EPA (Official Video) - Becky G</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Towa Bird - Dog (Official Music Video)</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
+        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-23</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Towa Bird</v>
+        <v>Daisy the Great</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
+        <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
+        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-23</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Madonna</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
+        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video)</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B55" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
+        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-23</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Ally Salort</v>
+        <v>Madonna</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Bella White - Better - Official Music Video</v>
+        <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
+        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-23</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Bella White</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Bella White - Better - Official Music Video - Bella White</v>
+        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
+        <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B57" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
+        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-23</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Bella White</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
+        <v>Bella White - Better - Official Music Video - Bella White</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
+        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-23</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Towa Bird</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer)</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B59" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
+        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-23</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Miranda Lambert</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
+        <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
+        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-23</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Lady Gaga</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
+        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B61" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
+        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-23</v>
@@ -2699,7 +2699,7 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Gracie Abrams</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
+        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-23</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B63" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
+        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-23</v>
@@ -2775,7 +2775,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Martin Garrix</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Jorja Smith - What's Done Is Done</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B64" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
+        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-23</v>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Jorja Smith</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>LP - Shelly (Official Music Video)</v>
+        <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B65" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
+        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-23</v>
@@ -2851,7 +2851,7 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>LP</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>LP - Shelly (Official Music Video) - LP</v>
+        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
+        <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
+        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-23</v>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>The Rolling Stones</v>
+        <v>LP</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
+        <v>LP - Shelly (Official Music Video) - LP</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
+        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-23</v>
@@ -2927,7 +2927,7 @@
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Oasis</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
+        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-23</v>
@@ -2965,7 +2965,7 @@
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Breaking Benjamin</v>
+        <v>Oasis</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B69" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
+        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-23</v>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>VictorBiliac</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B70" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
+        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-23</v>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Linkin Park</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Harry Styles - Dance No More (Official Video)</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B71" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
+        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-23</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Harry Styles</v>
+        <v>Linkin Park</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
+        <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
+        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-23</v>
@@ -3117,7 +3117,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Eagles</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
+        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
+        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-23</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Nora Fatehi</v>
+        <v>Eagles</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B74" t="str">
-        <v>2 months ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
+        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-23</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 months ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Nora Fatehi</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B75" t="str">
         <v>2 months ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
+        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-23</v>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Eurovision Song Contest and Alis</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B76" t="str">
         <v>2 months ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
+        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-23</v>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Eurovision Song Contest and Alis</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video)</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
+        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-23</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>The Head And The Heart</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
+        <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
+        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-23</v>
@@ -3345,7 +3345,7 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Simply Red</v>
+        <v>The Head And The Heart</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
+        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video)</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B79" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
+        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-23</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Talking Heads</v>
+        <v>Simply Red</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Ellise - Liplock (Official Music Video)</v>
+        <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
+        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-23</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Ellise</v>
+        <v>Talking Heads</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
+        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Tori Kelly - Dive (Official Music Video)</v>
+        <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
+        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-23</v>
@@ -3459,7 +3459,7 @@
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Tori Kelly</v>
+        <v>Ellise</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
+        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
+        <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
+        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-23</v>
@@ -3497,7 +3497,7 @@
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>David Gilmour</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
+        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
+        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-23</v>
@@ -3535,7 +3535,7 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Scorpions</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
+        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-23</v>
@@ -3573,7 +3573,7 @@
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Claire Leslie</v>
+        <v>Scorpions</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Michael Schulte - Lovesick (Official Video)</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
+        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-23</v>
@@ -3611,7 +3611,7 @@
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Michael Schulte</v>
+        <v>Claire Leslie</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Caity Baser - Holiday Song (Official Video)</v>
+        <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
+        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-23</v>
@@ -3649,7 +3649,7 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Caity Baser</v>
+        <v>Michael Schulte</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
+        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
+        <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
+        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-23</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Sam Fischer</v>
+        <v>Caity Baser</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
+        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Porches- HABIT (Official Video)</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
+        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-23</v>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Porches</v>
+        <v>Sam Fischer</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Porches- HABIT (Official Video) - Porches</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Charli xcx - Rock Music (Official Video)</v>
+        <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
+        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-23</v>
@@ -3763,7 +3763,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Charli xcx</v>
+        <v>Porches</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
+        <v>Porches- HABIT (Official Video) - Porches</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Jon Batiste - Alla Blues (Audio)</v>
+        <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
+        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-23</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Jon Batiste</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
+        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
+        <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
+        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-23</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Tigirlily Gold</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
+        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
+        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-23</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Tigirlily Gold</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
+        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-23</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Bruno Mars</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Tori Kelly - Control (Official Visualizer)</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
+        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-23</v>
@@ -3953,7 +3953,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Tori Kelly</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
+        <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
+        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-23</v>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>bea miller</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
+        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
+        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-23</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>The Chainsmokers</v>
+        <v>bea miller</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Madison Beer - free (Official Audio)</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
+        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-23</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Madison Beer</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Tori Kelly - Dive (Official Audio)</v>
+        <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
+        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-23</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Tori Kelly</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
+        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio)</v>
+        <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
+        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-23</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
+        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
+        <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
+        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-23</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>The Chainsmokers</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
+        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Ashley Cooke - high school sweetheart</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
+        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-23</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Ashley Cooke</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>From Down Here</v>
+        <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
+        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-23</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>From Down Here - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>4:01</v>
+        <v/>
       </c>
       <c r="H102" t="str">
-        <v>Lola Young</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/lola-young/452271760</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/from-down-here/6768357139</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>From Down Here - Lola Young</v>
+        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>the cure</v>
+        <v>From Down Here</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/the-cure/1889992123</v>
+        <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-23</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>you seem pretty sad for a girl so in love</v>
+        <v>From Down Here - Single</v>
       </c>
       <c r="G103" t="str">
-        <v>4:57</v>
+        <v>4:01</v>
       </c>
       <c r="H103" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Lola Young</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
+        <v>https://music.apple.com/us/artist/lola-young/452271760</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/the-cure/1889992111</v>
+        <v>https://music.apple.com/us/album/from-down-here/6768357139</v>
       </c>
       <c r="L103" t="str">
-        <v>the cure - Olivia Rodrigo</v>
+        <v>From Down Here - Lola Young</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>SS26</v>
+        <v>the cure</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/ss26/6771061782</v>
+        <v>https://music.apple.com/us/song/the-cure/1889992123</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-23</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>SS26 - Single</v>
+        <v>you seem pretty sad for a girl so in love</v>
       </c>
       <c r="G104" t="str">
-        <v>2:47</v>
+        <v>4:57</v>
       </c>
       <c r="H104" t="str">
-        <v>Charli xcx</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/ss26/6771061771</v>
+        <v>https://music.apple.com/us/album/the-cure/1889992111</v>
       </c>
       <c r="L104" t="str">
-        <v>SS26 - Charli xcx</v>
+        <v>the cure - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>White Flag</v>
+        <v>SS26</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/white-flag/1887627840</v>
+        <v>https://music.apple.com/us/song/ss26/6771061782</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-23</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Cry Baby</v>
+        <v>SS26 - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>2:34</v>
+        <v>2:47</v>
       </c>
       <c r="H105" t="str">
-        <v>Vince Staples</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/white-flag/1887627836</v>
+        <v>https://music.apple.com/us/album/ss26/6771061771</v>
       </c>
       <c r="L105" t="str">
-        <v>White Flag - Vince Staples</v>
+        <v>SS26 - Charli xcx</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Knew Better Part Two</v>
+        <v>White Flag</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
+        <v>https://music.apple.com/us/song/white-flag/1887627840</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-23</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Dangerous Woman (Tenth Anniversary Edition)</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G106" t="str">
-        <v>2:44</v>
+        <v>2:34</v>
       </c>
       <c r="H106" t="str">
-        <v>Ariana Grande</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/knew-better-part-two/6770600996</v>
+        <v>https://music.apple.com/us/album/white-flag/1887627836</v>
       </c>
       <c r="L106" t="str">
-        <v>Knew Better Part Two - Ariana Grande</v>
+        <v>White Flag - Vince Staples</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Goals</v>
+        <v>Knew Better Part Two</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/goals/6769251838</v>
+        <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-23</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Goals (FIFA World Cup 2026™) - Single</v>
+        <v>Dangerous Woman (Tenth Anniversary Edition)</v>
       </c>
       <c r="G107" t="str">
-        <v>3:00</v>
+        <v>2:44</v>
       </c>
       <c r="H107" t="str">
-        <v>LISA</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/lisa/1583908668</v>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/goals/6769251829</v>
+        <v>https://music.apple.com/us/album/knew-better-part-two/6770600996</v>
       </c>
       <c r="L107" t="str">
-        <v>Goals - LISA</v>
+        <v>Knew Better Part Two - Ariana Grande</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>we should talk</v>
+        <v>Goals</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
+        <v>https://music.apple.com/us/song/goals/6769251838</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-23</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Goals (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:04</v>
+        <v>3:00</v>
       </c>
       <c r="H108" t="str">
-        <v>Bleachers</v>
+        <v>LISA</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/lisa/1583908668</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/we-should-talk/1872842313</v>
+        <v>https://music.apple.com/us/album/goals/6769251829</v>
       </c>
       <c r="L108" t="str">
-        <v>we should talk - Bleachers</v>
+        <v>Goals - LISA</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Do What You Gotta Do</v>
+        <v>we should talk</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
+        <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-23</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>NeverAlways (Vol. 2)</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G109" t="str">
-        <v>3:26</v>
+        <v>3:04</v>
       </c>
       <c r="H109" t="str">
-        <v>The Band CAMINO</v>
+        <v>Bleachers</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/do-what-you-gotta-do/1887616173</v>
+        <v>https://music.apple.com/us/album/we-should-talk/1872842313</v>
       </c>
       <c r="L109" t="str">
-        <v>Do What You Gotta Do - The Band CAMINO</v>
+        <v>we should talk - Bleachers</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Ego</v>
+        <v>Do What You Gotta Do</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/ego/6769207667</v>
+        <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-23</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Ego - Single</v>
+        <v>NeverAlways (Vol. 2)</v>
       </c>
       <c r="G110" t="str">
-        <v>2:53</v>
+        <v>3:26</v>
       </c>
       <c r="H110" t="str">
-        <v>The Warning</v>
+        <v>The Band CAMINO</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/ego/6769207665</v>
+        <v>https://music.apple.com/us/album/do-what-you-gotta-do/1887616173</v>
       </c>
       <c r="L110" t="str">
-        <v>Ego - The Warning</v>
+        <v>Do What You Gotta Do - The Band CAMINO</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Light up (From the Netflix Documentary 'kylie')</v>
+        <v>Ego</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
+        <v>https://music.apple.com/us/song/ego/6769207667</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-23</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Light up (From the Netflix Documentary 'Kylie') - Single</v>
+        <v>Ego - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:17</v>
+        <v>2:53</v>
       </c>
       <c r="H111" t="str">
-        <v>Kylie Minogue</v>
+        <v>The Warning</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/kylie-minogue/465031</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/light-up-from-the-netflix-documentary-kylie/6768013505</v>
+        <v>https://music.apple.com/us/album/ego/6769207665</v>
       </c>
       <c r="L111" t="str">
-        <v>Light up (From the Netflix Documentary 'kylie') - Kylie Minogue</v>
+        <v>Ego - The Warning</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>All That Matters</v>
+        <v>Light up (From the Netflix Documentary 'kylie')</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
+        <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-23</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Light up (From the Netflix Documentary 'Kylie') - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:43</v>
+        <v>3:17</v>
       </c>
       <c r="H112" t="str">
-        <v>6LACK</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/kylie-minogue/465031</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/all-that-matters/1884792154</v>
+        <v>https://music.apple.com/us/album/light-up-from-the-netflix-documentary-kylie/6768013505</v>
       </c>
       <c r="L112" t="str">
-        <v>All That Matters - 6LACK</v>
+        <v>Light up (From the Netflix Documentary 'kylie') - Kylie Minogue</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Like A Virgin</v>
+        <v>All That Matters</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
+        <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-23</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Terrified .</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G113" t="str">
-        <v>2:34</v>
+        <v>3:43</v>
       </c>
       <c r="H113" t="str">
-        <v>fakemink</v>
+        <v>6LACK</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/like-a-virgin/6768157748</v>
+        <v>https://music.apple.com/us/album/all-that-matters/1884792154</v>
       </c>
       <c r="L113" t="str">
-        <v>Like A Virgin - fakemink</v>
+        <v>All That Matters - 6LACK</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>24 Hours</v>
+        <v>Like A Virgin</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/24-hours/6771060076</v>
+        <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-23</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>24 Hours - Single</v>
+        <v>Terrified .</v>
       </c>
       <c r="G114" t="str">
-        <v>3:17</v>
+        <v>2:34</v>
       </c>
       <c r="H114" t="str">
-        <v>Stormzy</v>
+        <v>fakemink</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/stormzy/394865154</v>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/24-hours/6771060073</v>
+        <v>https://music.apple.com/us/album/like-a-virgin/6768157748</v>
       </c>
       <c r="L114" t="str">
-        <v>24 Hours - Stormzy</v>
+        <v>Like A Virgin - fakemink</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>HOES (From Scary Movie)</v>
+        <v>24 Hours</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
+        <v>https://music.apple.com/us/song/24-hours/6771060076</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-23</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>HOES (From Scary Movie) - Single</v>
+        <v>24 Hours - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>2:09</v>
+        <v>3:17</v>
       </c>
       <c r="H115" t="str">
-        <v>Lizzo</v>
+        <v>Stormzy</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/stormzy/394865154</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/hoes-from-scary-movie/6770661290</v>
+        <v>https://music.apple.com/us/album/24-hours/6771060073</v>
       </c>
       <c r="L115" t="str">
-        <v>HOES (From Scary Movie) - Lizzo</v>
+        <v>24 Hours - Stormzy</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Ms. Tundra</v>
+        <v>HOES (From Scary Movie)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
+        <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-23</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Highway 79</v>
+        <v>HOES (From Scary Movie) - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:12</v>
+        <v>2:09</v>
       </c>
       <c r="H116" t="str">
-        <v>Ne-Yo</v>
+        <v>Lizzo</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/ms-tundra/6770614875</v>
+        <v>https://music.apple.com/us/album/hoes-from-scary-movie/6770661290</v>
       </c>
       <c r="L116" t="str">
-        <v>Ms. Tundra - Ne-Yo</v>
+        <v>HOES (From Scary Movie) - Lizzo</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>TARENTINO</v>
+        <v>Ms. Tundra</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/tarentino/6769927265</v>
+        <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-23</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>TARENTINO - Single</v>
+        <v>Highway 79</v>
       </c>
       <c r="G117" t="str">
-        <v>2:23</v>
+        <v>3:12</v>
       </c>
       <c r="H117" t="str">
-        <v>Labrinth</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/tarentino/6769927262</v>
+        <v>https://music.apple.com/us/album/ms-tundra/6770614875</v>
       </c>
       <c r="L117" t="str">
-        <v>TARENTINO - Labrinth</v>
+        <v>Ms. Tundra - Ne-Yo</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Daydreamin’</v>
+        <v>TARENTINO</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
+        <v>https://music.apple.com/us/song/tarentino/6769927265</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-23</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>KONNAKOL (Deluxe)</v>
+        <v>TARENTINO - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:58</v>
+        <v>2:23</v>
       </c>
       <c r="H118" t="str">
-        <v>ZAYN</v>
+        <v>Labrinth</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/daydreamin/6769559345</v>
+        <v>https://music.apple.com/us/album/tarentino/6769927262</v>
       </c>
       <c r="L118" t="str">
-        <v>Daydreamin’ - ZAYN</v>
+        <v>TARENTINO - Labrinth</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>End of an Era</v>
+        <v>Daydreamin’</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
+        <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-23</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Dinner Party</v>
+        <v>KONNAKOL (Deluxe)</v>
       </c>
       <c r="G119" t="str">
-        <v>3:38</v>
+        <v>2:58</v>
       </c>
       <c r="H119" t="str">
-        <v>Niall Horan</v>
+        <v>ZAYN</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/end-of-an-era/1884418567</v>
+        <v>https://music.apple.com/us/album/daydreamin/6769559345</v>
       </c>
       <c r="L119" t="str">
-        <v>End of an Era - Niall Horan</v>
+        <v>Daydreamin’ - ZAYN</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Questions</v>
+        <v>End of an Era</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/questions/1871502847</v>
+        <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-23</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Florescence</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G120" t="str">
-        <v>3:07</v>
+        <v>3:38</v>
       </c>
       <c r="H120" t="str">
-        <v>Maisie Peters</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/questions/1871502372</v>
+        <v>https://music.apple.com/us/album/end-of-an-era/1884418567</v>
       </c>
       <c r="L120" t="str">
-        <v>Questions - Maisie Peters</v>
+        <v>End of an Era - Niall Horan</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Heart Has To Work So Hard</v>
+        <v>Questions</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
+        <v>https://music.apple.com/us/song/questions/1871502847</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-23</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Heart Has To Work So Hard - Single</v>
+        <v>Florescence</v>
       </c>
       <c r="G121" t="str">
-        <v>3:12</v>
+        <v>3:07</v>
       </c>
       <c r="H121" t="str">
-        <v>Blondshell</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/blondshell/1624592688</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/heart-has-to-work-so-hard/1895982147</v>
+        <v>https://music.apple.com/us/album/questions/1871502372</v>
       </c>
       <c r="L121" t="str">
-        <v>Heart Has To Work So Hard - Blondshell</v>
+        <v>Questions - Maisie Peters</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski)</v>
+        <v>Heart Has To Work So Hard</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
+        <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-23</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski) - Single</v>
+        <v>Heart Has To Work So Hard - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:44</v>
+        <v>3:12</v>
       </c>
       <c r="H122" t="str">
-        <v>Kygo</v>
+        <v>Blondshell</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/blondshell/1624592688</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-your-mind-feat-dan-tyminski/6769007431</v>
+        <v>https://music.apple.com/us/album/heart-has-to-work-so-hard/1895982147</v>
       </c>
       <c r="L122" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski) - Kygo</v>
+        <v>Heart Has To Work So Hard - Blondshell</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>PERDISTE EL EMMY.</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
+        <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-23</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>OMAKASE</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski) - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>4:03</v>
+        <v>3:44</v>
       </c>
       <c r="H123" t="str">
-        <v>Álvaro Díaz</v>
+        <v>Kygo</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/perdiste-el-emmy/6771082594</v>
+        <v>https://music.apple.com/us/album/heaven-on-your-mind-feat-dan-tyminski/6769007431</v>
       </c>
       <c r="L123" t="str">
-        <v>PERDISTE EL EMMY. - Álvaro Díaz</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski) - Kygo</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Dosis</v>
+        <v>PERDISTE EL EMMY.</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/dosis/6762929729</v>
+        <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-23</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>DOSIS</v>
+        <v>OMAKASE</v>
       </c>
       <c r="G124" t="str">
-        <v>3:00</v>
+        <v>4:03</v>
       </c>
       <c r="H124" t="str">
-        <v>Xavi</v>
+        <v>Álvaro Díaz</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/dosis/1895081885</v>
+        <v>https://music.apple.com/us/album/perdiste-el-emmy/6771082594</v>
       </c>
       <c r="L124" t="str">
-        <v>Dosis - Xavi</v>
+        <v>PERDISTE EL EMMY. - Álvaro Díaz</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Would U Still Love Me</v>
+        <v>Dosis</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
+        <v>https://music.apple.com/us/song/dosis/6762929729</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-23</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Whitcomb vs. Flores - Single</v>
+        <v>DOSIS</v>
       </c>
       <c r="G125" t="str">
-        <v>2:36</v>
+        <v>3:00</v>
       </c>
       <c r="H125" t="str">
-        <v>Diplo</v>
+        <v>Xavi</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/would-u-still-love-me/6769907832</v>
+        <v>https://music.apple.com/us/album/dosis/1895081885</v>
       </c>
       <c r="L125" t="str">
-        <v>Would U Still Love Me - Diplo</v>
+        <v>Dosis - Xavi</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Saving This Bottle</v>
+        <v>Would U Still Love Me</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
+        <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-23</v>
@@ -5166,7 +5166,7 @@
         <v>Whitcomb vs. Flores - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:05</v>
+        <v>2:36</v>
       </c>
       <c r="H126" t="str">
         <v>Diplo</v>
@@ -5178,21 +5178,21 @@
         <v>https://music.apple.com/us/artist/diplo/1468290871</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/saving-this-bottle/6769907832</v>
+        <v>https://music.apple.com/us/album/would-u-still-love-me/6769907832</v>
       </c>
       <c r="L126" t="str">
-        <v>Saving This Bottle - Diplo</v>
+        <v>Would U Still Love Me - Diplo</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>The Climb</v>
+        <v>Saving This Bottle</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/the-climb/6769546149</v>
+        <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-23</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>The Climb - Single</v>
+        <v>Whitcomb vs. Flores - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:50</v>
+        <v>3:05</v>
       </c>
       <c r="H127" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Diplo</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/the-climb/6769546147</v>
+        <v>https://music.apple.com/us/album/saving-this-bottle/6769907832</v>
       </c>
       <c r="L127" t="str">
-        <v>The Climb - Bailey Zimmerman</v>
+        <v>Saving This Bottle - Diplo</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>everything tatted</v>
+        <v>The Climb</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
+        <v>https://music.apple.com/us/song/the-climb/6769546149</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-23</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>everything tatted - Single</v>
+        <v>The Climb - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:25</v>
+        <v>3:50</v>
       </c>
       <c r="H128" t="str">
-        <v>mgk</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/everything-tatted/6770773606</v>
+        <v>https://music.apple.com/us/album/the-climb/6769546147</v>
       </c>
       <c r="L128" t="str">
-        <v>everything tatted - mgk</v>
+        <v>The Climb - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>BOOMPALA</v>
+        <v>everything tatted</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/boompala/1894802726</v>
+        <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-23</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>'PUREFLOW', Pt. 1</v>
+        <v>everything tatted - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:56</v>
+        <v>3:25</v>
       </c>
       <c r="H129" t="str">
-        <v>LE SSERAFIM</v>
+        <v>mgk</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/boompala/1894802719</v>
+        <v>https://music.apple.com/us/album/everything-tatted/6770773606</v>
       </c>
       <c r="L129" t="str">
-        <v>BOOMPALA - LE SSERAFIM</v>
+        <v>everything tatted - mgk</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Let Me Be In Your Arms</v>
+        <v>BOOMPALA</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
+        <v>https://music.apple.com/us/song/boompala/1894802726</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-23</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>can we do it all again?</v>
+        <v>'PUREFLOW', Pt. 1</v>
       </c>
       <c r="G130" t="str">
-        <v>3:13</v>
+        <v>2:56</v>
       </c>
       <c r="H130" t="str">
-        <v>Sonny Fodera</v>
+        <v>LE SSERAFIM</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/let-me-be-in-your-arms/1881610862</v>
+        <v>https://music.apple.com/us/album/boompala/1894802719</v>
       </c>
       <c r="L130" t="str">
-        <v>Let Me Be In Your Arms - Sonny Fodera</v>
+        <v>BOOMPALA - LE SSERAFIM</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Eat, Work, Pray</v>
+        <v>Let Me Be In Your Arms</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
+        <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-23</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Eat, Work, Pray - Single</v>
+        <v>can we do it all again?</v>
       </c>
       <c r="G131" t="str">
-        <v>2:28</v>
+        <v>3:13</v>
       </c>
       <c r="H131" t="str">
-        <v>Sheff G</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/eat-work-pray/6769134493</v>
+        <v>https://music.apple.com/us/album/let-me-be-in-your-arms/1881610862</v>
       </c>
       <c r="L131" t="str">
-        <v>Eat, Work, Pray - Sheff G</v>
+        <v>Let Me Be In Your Arms - Sonny Fodera</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>touch myself</v>
+        <v>Eat, Work, Pray</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
+        <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-23</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>and all pride aside</v>
+        <v>Eat, Work, Pray - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>4:09</v>
+        <v>2:28</v>
       </c>
       <c r="H132" t="str">
-        <v>kwn</v>
+        <v>Sheff G</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/touch-myself/6769880663</v>
+        <v>https://music.apple.com/us/album/eat-work-pray/6769134493</v>
       </c>
       <c r="L132" t="str">
-        <v>touch myself - kwn</v>
+        <v>Eat, Work, Pray - Sheff G</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Comes and Goes</v>
+        <v>touch myself</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
+        <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-23</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Comes and Goes - Single</v>
+        <v>and all pride aside</v>
       </c>
       <c r="G133" t="str">
-        <v>4:22</v>
+        <v>4:09</v>
       </c>
       <c r="H133" t="str">
-        <v>KETTAMA</v>
+        <v>kwn</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/kettama/1425703970</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/comes-and-goes/6766618930</v>
+        <v>https://music.apple.com/us/album/touch-myself/6769880663</v>
       </c>
       <c r="L133" t="str">
-        <v>Comes and Goes - KETTAMA</v>
+        <v>touch myself - kwn</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Dear God</v>
+        <v>Comes and Goes</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/dear-god/1878237813</v>
+        <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-23</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Dear God</v>
+        <v>Comes and Goes - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>6:08</v>
+        <v>4:22</v>
       </c>
       <c r="H134" t="str">
-        <v>The Pretty Reckless</v>
+        <v>KETTAMA</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/kettama/1425703970</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/dear-god/1878237662</v>
+        <v>https://music.apple.com/us/album/comes-and-goes/6766618930</v>
       </c>
       <c r="L134" t="str">
-        <v>Dear God - The Pretty Reckless</v>
+        <v>Comes and Goes - KETTAMA</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Hexagons</v>
+        <v>Dear God</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/hexagons/1885607736</v>
+        <v>https://music.apple.com/us/song/dear-god/1878237813</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-23</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>The Wow! Signal</v>
+        <v>Dear God</v>
       </c>
       <c r="G135" t="str">
-        <v>5:26</v>
+        <v>6:08</v>
       </c>
       <c r="H135" t="str">
-        <v>Muse</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/hexagons/1885607338</v>
+        <v>https://music.apple.com/us/album/dear-god/1878237662</v>
       </c>
       <c r="L135" t="str">
-        <v>Hexagons - Muse</v>
+        <v>Dear God - The Pretty Reckless</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Facile-Batiste</v>
+        <v>Hexagons</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
+        <v>https://music.apple.com/us/song/hexagons/1885607736</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-23</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Black Mozart</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G136" t="str">
-        <v>4:55</v>
+        <v>5:26</v>
       </c>
       <c r="H136" t="str">
-        <v>Jon Batiste</v>
+        <v>Muse</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/facile-batiste/1895866355</v>
+        <v>https://music.apple.com/us/album/hexagons/1885607338</v>
       </c>
       <c r="L136" t="str">
-        <v>Facile-Batiste - Jon Batiste</v>
+        <v>Hexagons - Muse</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Pop Pop</v>
+        <v>Facile-Batiste</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
+        <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-23</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Pop Pop - Single</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G137" t="str">
-        <v>2:57</v>
+        <v>4:55</v>
       </c>
       <c r="H137" t="str">
-        <v>Channel Tres</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/pop-pop/1896269430</v>
+        <v>https://music.apple.com/us/album/facile-batiste/1895866355</v>
       </c>
       <c r="L137" t="str">
-        <v>Pop Pop - Channel Tres</v>
+        <v>Facile-Batiste - Jon Batiste</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>One Of Us</v>
+        <v>Pop Pop</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
+        <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-23</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>One Of Us - Single</v>
+        <v>Pop Pop - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:35</v>
+        <v>2:57</v>
       </c>
       <c r="H138" t="str">
-        <v>Chris Young</v>
+        <v>Channel Tres</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/chris-young/4779205</v>
+        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/one-of-us/1895402922</v>
+        <v>https://music.apple.com/us/album/pop-pop/1896269430</v>
       </c>
       <c r="L138" t="str">
-        <v>One Of Us - Chris Young</v>
+        <v>Pop Pop - Channel Tres</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Sins of the Father</v>
+        <v>One Of Us</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
+        <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-23</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Is God Is (Original Motion Picture Soundtrack)</v>
+        <v>One Of Us - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:20</v>
+        <v>3:35</v>
       </c>
       <c r="H139" t="str">
-        <v>Moses Sumney</v>
+        <v>Chris Young</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/moses-sumney/843536848</v>
+        <v>https://music.apple.com/us/artist/chris-young/4779205</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/sins-of-the-father/6771012707</v>
+        <v>https://music.apple.com/us/album/one-of-us/1895402922</v>
       </c>
       <c r="L139" t="str">
-        <v>Sins of the Father - Moses Sumney</v>
+        <v>One Of Us - Chris Young</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Life On The Run</v>
+        <v>Sins of the Father</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
+        <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-23</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Life On The Run - Single</v>
+        <v>Is God Is (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G140" t="str">
-        <v>3:49</v>
+        <v>3:20</v>
       </c>
       <c r="H140" t="str">
-        <v>Brandi Carlile</v>
+        <v>Moses Sumney</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/brandi-carlile/64387579</v>
+        <v>https://music.apple.com/us/artist/moses-sumney/843536848</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/life-on-the-run/6766761019</v>
+        <v>https://music.apple.com/us/album/sins-of-the-father/6771012707</v>
       </c>
       <c r="L140" t="str">
-        <v>Life On The Run - Brandi Carlile</v>
+        <v>Sins of the Father - Moses Sumney</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>New York Confident</v>
+        <v>Life On The Run</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
+        <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-23</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>New York Confident - Single</v>
+        <v>Life On The Run - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:27</v>
+        <v>3:49</v>
       </c>
       <c r="H141" t="str">
-        <v>Mark Ambor</v>
+        <v>Brandi Carlile</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/mark-ambor/1459754985</v>
+        <v>https://music.apple.com/us/artist/brandi-carlile/64387579</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/new-york-confident/6765558036</v>
+        <v>https://music.apple.com/us/album/life-on-the-run/6766761019</v>
       </c>
       <c r="L141" t="str">
-        <v>New York Confident - Mark Ambor</v>
+        <v>Life On The Run - Brandi Carlile</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>pequeñita!</v>
+        <v>New York Confident</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
+        <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-23</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>pequeñita! - Single</v>
+        <v>New York Confident - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:39</v>
+        <v>2:27</v>
       </c>
       <c r="H142" t="str">
-        <v>Judeline</v>
+        <v>Mark Ambor</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/judeline/1487503245</v>
+        <v>https://music.apple.com/us/artist/mark-ambor/1459754985</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/peque%C3%B1ita/6769827604</v>
+        <v>https://music.apple.com/us/album/new-york-confident/6765558036</v>
       </c>
       <c r="L142" t="str">
-        <v>pequeñita! - Judeline</v>
+        <v>New York Confident - Mark Ambor</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Opaline</v>
+        <v>pequeñita!</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/opaline/1886737060</v>
+        <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-23</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>pequeñita! - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:17</v>
+        <v>2:39</v>
       </c>
       <c r="H143" t="str">
-        <v>Stephan Moccio</v>
+        <v>Judeline</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/judeline/1487503245</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/opaline/1886736650</v>
+        <v>https://music.apple.com/us/album/peque%C3%B1ita/6769827604</v>
       </c>
       <c r="L143" t="str">
-        <v>Opaline - Stephan Moccio</v>
+        <v>pequeñita! - Judeline</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Pretty Little Things</v>
+        <v>Opaline</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
+        <v>https://music.apple.com/us/song/opaline/1886737060</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-23</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Pretty Little Things - Single</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G144" t="str">
-        <v>2:51</v>
+        <v>3:17</v>
       </c>
       <c r="H144" t="str">
-        <v>Lauv</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/pretty-little-things/6767353963</v>
+        <v>https://music.apple.com/us/album/opaline/1886736650</v>
       </c>
       <c r="L144" t="str">
-        <v>Pretty Little Things - Lauv</v>
+        <v>Opaline - Stephan Moccio</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>COLORADO</v>
+        <v>Pretty Little Things</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/colorado/6769065232</v>
+        <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-23</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>COLORADO - Single</v>
+        <v>Pretty Little Things - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>1:54</v>
+        <v>2:51</v>
       </c>
       <c r="H145" t="str">
-        <v>Loud Luxury</v>
+        <v>Lauv</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/colorado/6769064981</v>
+        <v>https://music.apple.com/us/album/pretty-little-things/6767353963</v>
       </c>
       <c r="L145" t="str">
-        <v>COLORADO - Loud Luxury</v>
+        <v>Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Infidelidad</v>
+        <v>COLORADO</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
+        <v>https://music.apple.com/us/song/colorado/6769065232</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-23</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>El Disco de Salsa</v>
+        <v>COLORADO - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:29</v>
+        <v>1:54</v>
       </c>
       <c r="H146" t="str">
-        <v>Neutro Shorty</v>
+        <v>Loud Luxury</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/neutro-shorty/1066850977</v>
+        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/infidelidad/6768853655</v>
+        <v>https://music.apple.com/us/album/colorado/6769064981</v>
       </c>
       <c r="L146" t="str">
-        <v>Infidelidad - Neutro Shorty</v>
+        <v>COLORADO - Loud Luxury</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Wrong Place, Wrong time</v>
+        <v>Infidelidad</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
+        <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-23</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Y'all Won</v>
+        <v>El Disco de Salsa</v>
       </c>
       <c r="G147" t="str">
-        <v>2:57</v>
+        <v>3:29</v>
       </c>
       <c r="H147" t="str">
-        <v>Veeze</v>
+        <v>Neutro Shorty</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
+        <v>https://music.apple.com/us/artist/neutro-shorty/1066850977</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/wrong-place-wrong-time/6771553812</v>
+        <v>https://music.apple.com/us/album/infidelidad/6768853655</v>
       </c>
       <c r="L147" t="str">
-        <v>Wrong Place, Wrong time - Veeze</v>
+        <v>Infidelidad - Neutro Shorty</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>La Semana</v>
+        <v>Wrong Place, Wrong time</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/la-semana/6769913466</v>
+        <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-23</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>No Quiero Que Se Acabe Este Bendito Verano - EP</v>
+        <v>Y'all Won</v>
       </c>
       <c r="G148" t="str">
-        <v>3:30</v>
+        <v>2:57</v>
       </c>
       <c r="H148" t="str">
-        <v>ELENA ROSE</v>
+        <v>Veeze</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/la-semana/6769913464</v>
+        <v>https://music.apple.com/us/album/wrong-place-wrong-time/6771553812</v>
       </c>
       <c r="L148" t="str">
-        <v>La Semana - ELENA ROSE</v>
+        <v>Wrong Place, Wrong time - Veeze</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Una Mujer Como la Suya</v>
+        <v>La Semana</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
+        <v>https://music.apple.com/us/song/la-semana/6769913466</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-23</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Bandera Blanca</v>
+        <v>No Quiero Que Se Acabe Este Bendito Verano - EP</v>
       </c>
       <c r="G149" t="str">
-        <v>3:34</v>
+        <v>3:30</v>
       </c>
       <c r="H149" t="str">
-        <v>Christian Nodal</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/una-mujer-como-la-suya/1895154946</v>
+        <v>https://music.apple.com/us/album/la-semana/6769913464</v>
       </c>
       <c r="L149" t="str">
-        <v>Una Mujer Como la Suya - Christian Nodal</v>
+        <v>La Semana - ELENA ROSE</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Cold</v>
+        <v>Una Mujer Como la Suya</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/cold/6763763802</v>
+        <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-23</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Cold - Single</v>
+        <v>Bandera Blanca</v>
       </c>
       <c r="G150" t="str">
-        <v>2:52</v>
+        <v>3:34</v>
       </c>
       <c r="H150" t="str">
-        <v>Majid Jordan</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/majid-jordan/684530590</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/cold/1895478371</v>
+        <v>https://music.apple.com/us/album/una-mujer-como-la-suya/1895154946</v>
       </c>
       <c r="L150" t="str">
-        <v>Cold - Majid Jordan</v>
+        <v>Una Mujer Como la Suya - Christian Nodal</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>VERTICAL WORLDS</v>
+        <v>Cold</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
+        <v>https://music.apple.com/us/song/cold/6763763802</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-23</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
+        <v>Cold - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:15</v>
+        <v>2:52</v>
       </c>
       <c r="H151" t="str">
-        <v>Ecca Vandal</v>
+        <v>Majid Jordan</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
+        <v>https://music.apple.com/us/artist/majid-jordan/684530590</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/vertical-worlds/1886485694</v>
+        <v>https://music.apple.com/us/album/cold/1895478371</v>
       </c>
       <c r="L151" t="str">
-        <v>VERTICAL WORLDS - Ecca Vandal</v>
+        <v>Cold - Majid Jordan</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Child of Divorce</v>
+        <v>VERTICAL WORLDS</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
+        <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-23</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>soft pop</v>
+        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
       </c>
       <c r="G152" t="str">
-        <v>3:24</v>
+        <v>3:15</v>
       </c>
       <c r="H152" t="str">
-        <v>Amy Shark</v>
+        <v>Ecca Vandal</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
+        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/child-of-divorce/1880496743</v>
+        <v>https://music.apple.com/us/album/vertical-worlds/1886485694</v>
       </c>
       <c r="L152" t="str">
-        <v>Child of Divorce - Amy Shark</v>
+        <v>VERTICAL WORLDS - Ecca Vandal</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Taboo</v>
+        <v>Child of Divorce</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/taboo/6762838716</v>
+        <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-23</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Taboo - Single</v>
+        <v>soft pop</v>
       </c>
       <c r="G153" t="str">
-        <v>3:38</v>
+        <v>3:24</v>
       </c>
       <c r="H153" t="str">
-        <v>Jensen McRae</v>
+        <v>Amy Shark</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/jensen-mcrae/591974463</v>
+        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/taboo/1895036934</v>
+        <v>https://music.apple.com/us/album/child-of-divorce/1880496743</v>
       </c>
       <c r="L153" t="str">
-        <v>Taboo - Jensen McRae</v>
+        <v>Child of Divorce - Amy Shark</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>I'M OK</v>
+        <v>Taboo</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/im-ok/1893392647</v>
+        <v>https://music.apple.com/us/song/taboo/6762838716</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-23</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>A Rii Set</v>
+        <v>Taboo - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:37</v>
+        <v>3:38</v>
       </c>
       <c r="H154" t="str">
-        <v>Pheelz</v>
+        <v>Jensen McRae</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
+        <v>https://music.apple.com/us/artist/jensen-mcrae/591974463</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/im-ok/1893392643</v>
+        <v>https://music.apple.com/us/album/taboo/1895036934</v>
       </c>
       <c r="L154" t="str">
-        <v>I'M OK - Pheelz</v>
+        <v>Taboo - Jensen McRae</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Butterfly Feelings</v>
+        <v>I'M OK</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
+        <v>https://music.apple.com/us/song/im-ok/1893392647</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-23</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Ritual</v>
+        <v>A Rii Set</v>
       </c>
       <c r="G155" t="str">
-        <v>2:35</v>
+        <v>2:37</v>
       </c>
       <c r="H155" t="str">
-        <v>Icona Pop</v>
+        <v>Pheelz</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/butterfly-feelings/1892426976</v>
+        <v>https://music.apple.com/us/album/im-ok/1893392643</v>
       </c>
       <c r="L155" t="str">
-        <v>Butterfly Feelings - Icona Pop</v>
+        <v>I'M OK - Pheelz</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>F**k the DJ</v>
+        <v>Butterfly Feelings</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
+        <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-23</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Stage Girl (Not A Dream Anymore)</v>
+        <v>Ritual</v>
       </c>
       <c r="G156" t="str">
-        <v>2:57</v>
+        <v>2:35</v>
       </c>
       <c r="H156" t="str">
-        <v>Eli</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/f-k-the-dj/6769903867</v>
+        <v>https://music.apple.com/us/album/butterfly-feelings/1892426976</v>
       </c>
       <c r="L156" t="str">
-        <v>F**k the DJ - Eli</v>
+        <v>Butterfly Feelings - Icona Pop</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Grateful</v>
+        <v>F**k the DJ</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/grateful/1887166624</v>
+        <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-23</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>24</v>
+        <v>Stage Girl (Not A Dream Anymore)</v>
       </c>
       <c r="G157" t="str">
-        <v>2:18</v>
+        <v>2:57</v>
       </c>
       <c r="H157" t="str">
-        <v>Alexis Ffrench</v>
+        <v>Eli</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/grateful/1887166427</v>
+        <v>https://music.apple.com/us/album/f-k-the-dj/6769903867</v>
       </c>
       <c r="L157" t="str">
-        <v>Grateful - Alexis Ffrench</v>
+        <v>F**k the DJ - Eli</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Second Chance</v>
+        <v>Grateful</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/second-chance/6766778687</v>
+        <v>https://music.apple.com/us/song/grateful/1887166624</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-23</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Second Chance - Single</v>
+        <v>24</v>
       </c>
       <c r="G158" t="str">
-        <v>3:06</v>
+        <v>2:18</v>
       </c>
       <c r="H158" t="str">
-        <v>Lukas Graham</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/lukas-graham/473219952</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/second-chance/6766778682</v>
+        <v>https://music.apple.com/us/album/grateful/1887166427</v>
       </c>
       <c r="L158" t="str">
-        <v>Second Chance - Lukas Graham</v>
+        <v>Grateful - Alexis Ffrench</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Stupid World (feat. Chad Tepper) [Bonus Track]</v>
+        <v>Second Chance</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
+        <v>https://music.apple.com/us/song/second-chance/6766778687</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-23</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Tommyland Rides Again</v>
+        <v>Second Chance - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:49</v>
+        <v>3:06</v>
       </c>
       <c r="H159" t="str">
-        <v>Tommy Lee</v>
+        <v>Lukas Graham</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/tommy-lee/68696</v>
+        <v>https://music.apple.com/us/artist/lukas-graham/473219952</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/stupid-world-feat-chad-tepper-bonus-track/1893473875</v>
+        <v>https://music.apple.com/us/album/second-chance/6766778682</v>
       </c>
       <c r="L159" t="str">
-        <v>Stupid World (feat. Chad Tepper) [Bonus Track] - Tommy Lee</v>
+        <v>Second Chance - Lukas Graham</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>DOOM LOOP</v>
+        <v>Stupid World (feat. Chad Tepper) [Bonus Track]</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
+        <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-23</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Blood Of Your Empire</v>
+        <v>Tommyland Rides Again</v>
       </c>
       <c r="G160" t="str">
-        <v>4:00</v>
+        <v>3:49</v>
       </c>
       <c r="H160" t="str">
-        <v>PRESIDENT</v>
+        <v>Tommy Lee</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/tommy-lee/68696</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/doom-loop/6769905842</v>
+        <v>https://music.apple.com/us/album/stupid-world-feat-chad-tepper-bonus-track/1893473875</v>
       </c>
       <c r="L160" t="str">
-        <v>DOOM LOOP - PRESIDENT</v>
+        <v>Stupid World (feat. Chad Tepper) [Bonus Track] - Tommy Lee</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>New York City</v>
+        <v>DOOM LOOP</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
+        <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-23</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>New York City - Single</v>
+        <v>Blood Of Your Empire</v>
       </c>
       <c r="G161" t="str">
-        <v>3:30</v>
+        <v>4:00</v>
       </c>
       <c r="H161" t="str">
-        <v>Anthony Ramos</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/anthony-ramos/1313064678</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/new-york-city/6770624324</v>
+        <v>https://music.apple.com/us/album/doom-loop/6769905842</v>
       </c>
       <c r="L161" t="str">
-        <v>New York City - Anthony Ramos</v>
+        <v>DOOM LOOP - PRESIDENT</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>I Found You</v>
+        <v>New York City</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
+        <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-23</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>I Found You - Single</v>
+        <v>New York City - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:18</v>
+        <v>3:30</v>
       </c>
       <c r="H162" t="str">
-        <v>TA Thomas</v>
+        <v>Anthony Ramos</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/ta-thomas/1232189106</v>
+        <v>https://music.apple.com/us/artist/anthony-ramos/1313064678</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/i-found-you/1894024530</v>
+        <v>https://music.apple.com/us/album/new-york-city/6770624324</v>
       </c>
       <c r="L162" t="str">
-        <v>I Found You - TA Thomas</v>
+        <v>New York City - Anthony Ramos</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Just My Type</v>
+        <v>I Found You</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
+        <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-23</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Labor Of Love</v>
+        <v>I Found You - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:40</v>
+        <v>3:18</v>
       </c>
       <c r="H163" t="str">
-        <v>Blxst</v>
+        <v>TA Thomas</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
+        <v>https://music.apple.com/us/artist/ta-thomas/1232189106</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/just-my-type/1895199881</v>
+        <v>https://music.apple.com/us/album/i-found-you/1894024530</v>
       </c>
       <c r="L163" t="str">
-        <v>Just My Type - Blxst</v>
+        <v>I Found You - TA Thomas</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>teenage drama</v>
+        <v>Just My Type</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
+        <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-23</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>teenage drama - Single</v>
+        <v>Labor Of Love</v>
       </c>
       <c r="G164" t="str">
-        <v>3:06</v>
+        <v>2:40</v>
       </c>
       <c r="H164" t="str">
-        <v>paris jackson</v>
+        <v>Blxst</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/teenage-drama/6768447515</v>
+        <v>https://music.apple.com/us/album/just-my-type/1895199881</v>
       </c>
       <c r="L164" t="str">
-        <v>teenage drama - paris jackson</v>
+        <v>Just My Type - Blxst</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>does it still mean something?</v>
+        <v>teenage drama</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
+        <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-23</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>only if it matters</v>
+        <v>teenage drama - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:48</v>
+        <v>3:06</v>
       </c>
       <c r="H165" t="str">
-        <v>Kevian Kraemer</v>
+        <v>paris jackson</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/does-it-still-mean-something/6768446154</v>
+        <v>https://music.apple.com/us/album/teenage-drama/6768447515</v>
       </c>
       <c r="L165" t="str">
-        <v>does it still mean something? - Kevian Kraemer</v>
+        <v>teenage drama - paris jackson</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Debbie Don't Cry</v>
+        <v>does it still mean something?</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
+        <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-23</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Debbie Don't Cry - Single</v>
+        <v>only if it matters</v>
       </c>
       <c r="G166" t="str">
-        <v>3:00</v>
+        <v>3:48</v>
       </c>
       <c r="H166" t="str">
-        <v>Ruel</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/debbie-dont-cry/6768206616</v>
+        <v>https://music.apple.com/us/album/does-it-still-mean-something/6768446154</v>
       </c>
       <c r="L166" t="str">
-        <v>Debbie Don't Cry - Ruel</v>
+        <v>does it still mean something? - Kevian Kraemer</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>YEAH YEAH YEAH</v>
+        <v>Debbie Don't Cry</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
+        <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-23</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>YEAH YEAH YEAH - Single</v>
+        <v>Debbie Don't Cry - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:25</v>
+        <v>3:00</v>
       </c>
       <c r="H167" t="str">
-        <v>Cruz Beckham</v>
+        <v>Ruel</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/yeah-yeah-yeah/6767515610</v>
+        <v>https://music.apple.com/us/album/debbie-dont-cry/6768206616</v>
       </c>
       <c r="L167" t="str">
-        <v>YEAH YEAH YEAH - Cruz Beckham</v>
+        <v>Debbie Don't Cry - Ruel</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Cotton Flower</v>
+        <v>YEAH YEAH YEAH</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
+        <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-23</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>YEAH YEAH YEAH - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:53</v>
+        <v>2:25</v>
       </c>
       <c r="H168" t="str">
-        <v>Future Islands</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/cotton-flower/1883045480</v>
+        <v>https://music.apple.com/us/album/yeah-yeah-yeah/6767515610</v>
       </c>
       <c r="L168" t="str">
-        <v>Cotton Flower - Future Islands</v>
+        <v>YEAH YEAH YEAH - Cruz Beckham</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>WAHALA RIDDIM</v>
+        <v>Cotton Flower</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
+        <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-23</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>WAHALA RIDDIM - Single</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G169" t="str">
-        <v>3:22</v>
+        <v>3:53</v>
       </c>
       <c r="H169" t="str">
-        <v>THEHONESTGUY</v>
+        <v>Future Islands</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/wahala-riddim/1895810537</v>
+        <v>https://music.apple.com/us/album/cotton-flower/1883045480</v>
       </c>
       <c r="L169" t="str">
-        <v>WAHALA RIDDIM - THEHONESTGUY</v>
+        <v>Cotton Flower - Future Islands</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Comfort</v>
+        <v>WAHALA RIDDIM</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/comfort/1876521401</v>
+        <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-23</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>So Help Me God</v>
+        <v>WAHALA RIDDIM - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>5:35</v>
+        <v>3:22</v>
       </c>
       <c r="H170" t="str">
-        <v>Kelsey Lu</v>
+        <v>THEHONESTGUY</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
+        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/comfort/1876521144</v>
+        <v>https://music.apple.com/us/album/wahala-riddim/1895810537</v>
       </c>
       <c r="L170" t="str">
-        <v>Comfort - Kelsey Lu</v>
+        <v>WAHALA RIDDIM - THEHONESTGUY</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Skin</v>
+        <v>Comfort</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/skin/6764651585</v>
+        <v>https://music.apple.com/us/song/comfort/1876521401</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-23</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Skin - Single</v>
+        <v>So Help Me God</v>
       </c>
       <c r="G171" t="str">
-        <v>3:00</v>
+        <v>5:35</v>
       </c>
       <c r="H171" t="str">
-        <v>Alessi Rose</v>
+        <v>Kelsey Lu</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/alessi-rose/1628689028</v>
+        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/skin/1895865252</v>
+        <v>https://music.apple.com/us/album/comfort/1876521144</v>
       </c>
       <c r="L171" t="str">
-        <v>Skin - Alessi Rose</v>
+        <v>Comfort - Kelsey Lu</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>IDGAF</v>
+        <v>Skin</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/idgaf/6764422210</v>
+        <v>https://music.apple.com/us/song/skin/6764651585</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-23</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>IDGAF - Single</v>
+        <v>Skin - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:55</v>
+        <v>3:00</v>
       </c>
       <c r="H172" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Alessi Rose</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/alessi-rose/1628689028</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/idgaf/1895773358</v>
+        <v>https://music.apple.com/us/album/skin/1895865252</v>
       </c>
       <c r="L172" t="str">
-        <v>IDGAF - Katelyn Tarver</v>
+        <v>Skin - Alessi Rose</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Run Rabbit</v>
+        <v>IDGAF</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
+        <v>https://music.apple.com/us/song/idgaf/6764422210</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-23</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Run Rabbit - Single</v>
+        <v>IDGAF - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:09</v>
+        <v>2:55</v>
       </c>
       <c r="H173" t="str">
-        <v>Mollie Elizabeth</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/mollie-elizabeth/1780515318</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/run-rabbit/6767354664</v>
+        <v>https://music.apple.com/us/album/idgaf/1895773358</v>
       </c>
       <c r="L173" t="str">
-        <v>Run Rabbit - Mollie Elizabeth</v>
+        <v>IDGAF - Katelyn Tarver</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>So Good (feat. Kuuda)</v>
+        <v>Run Rabbit</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
+        <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-23</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>So Good (feat. Kuuda) - Single</v>
+        <v>Run Rabbit - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:03</v>
+        <v>3:09</v>
       </c>
       <c r="H174" t="str">
-        <v>CamelPhat</v>
+        <v>Mollie Elizabeth</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/camelphat/385810888</v>
+        <v>https://music.apple.com/us/artist/mollie-elizabeth/1780515318</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/so-good-feat-kuuda/6766655768</v>
+        <v>https://music.apple.com/us/album/run-rabbit/6767354664</v>
       </c>
       <c r="L174" t="str">
-        <v>So Good (feat. Kuuda) - CamelPhat</v>
+        <v>Run Rabbit - Mollie Elizabeth</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Empty Theatre, Pretty Picture</v>
+        <v>So Good (feat. Kuuda)</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
+        <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-23</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Empty Theatre, Pretty Picture</v>
+        <v>So Good (feat. Kuuda) - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>5:01</v>
+        <v>3:03</v>
       </c>
       <c r="H175" t="str">
-        <v>Lane 8</v>
+        <v>CamelPhat</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/camelphat/385810888</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/empty-theatre-pretty-picture/1895395993</v>
+        <v>https://music.apple.com/us/album/so-good-feat-kuuda/6766655768</v>
       </c>
       <c r="L175" t="str">
-        <v>Empty Theatre, Pretty Picture - Lane 8</v>
+        <v>So Good (feat. Kuuda) - CamelPhat</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>regalametutiempo</v>
+        <v>Empty Theatre, Pretty Picture</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
+        <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-23</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>PROYECTANDO</v>
+        <v>Empty Theatre, Pretty Picture</v>
       </c>
       <c r="G176" t="str">
-        <v>3:01</v>
+        <v>5:01</v>
       </c>
       <c r="H176" t="str">
-        <v>Julio Caesar</v>
+        <v>Lane 8</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/regalametutiempo/6769922866</v>
+        <v>https://music.apple.com/us/album/empty-theatre-pretty-picture/1895395993</v>
       </c>
       <c r="L176" t="str">
-        <v>regalametutiempo - Julio Caesar</v>
+        <v>Empty Theatre, Pretty Picture - Lane 8</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>On Sight</v>
+        <v>regalametutiempo</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/on-sight/6763971220</v>
+        <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-23</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Left on RED</v>
+        <v>PROYECTANDO</v>
       </c>
       <c r="G177" t="str">
-        <v>2:25</v>
+        <v>3:01</v>
       </c>
       <c r="H177" t="str">
-        <v>REMI</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/remi/1716510008</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/on-sight/1895580736</v>
+        <v>https://music.apple.com/us/album/regalametutiempo/6769922866</v>
       </c>
       <c r="L177" t="str">
-        <v>On Sight - REMI</v>
+        <v>regalametutiempo - Julio Caesar</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Masks Off</v>
+        <v>On Sight</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/masks-off/6764077133</v>
+        <v>https://music.apple.com/us/song/on-sight/6763971220</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-23</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Masks Off - Single</v>
+        <v>Left on RED</v>
       </c>
       <c r="G178" t="str">
-        <v>3:24</v>
+        <v>2:25</v>
       </c>
       <c r="H178" t="str">
-        <v>Jesse Welles</v>
+        <v>REMI</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/jesse-welles/1737507146</v>
+        <v>https://music.apple.com/us/artist/remi/1716510008</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/masks-off/1895628310</v>
+        <v>https://music.apple.com/us/album/on-sight/1895580736</v>
       </c>
       <c r="L178" t="str">
-        <v>Masks Off - Jesse Welles</v>
+        <v>On Sight - REMI</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>I'm Just A Girl</v>
+        <v>Masks Off</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
+        <v>https://music.apple.com/us/song/masks-off/6764077133</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-23</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Di Hotel Malibu</v>
+        <v>Masks Off - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:49</v>
+        <v>3:24</v>
       </c>
       <c r="H179" t="str">
-        <v>Thee Marloes</v>
+        <v>Jesse Welles</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/thee-marloes/1541376632</v>
+        <v>https://music.apple.com/us/artist/jesse-welles/1737507146</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/im-just-a-girl/1878399768</v>
+        <v>https://music.apple.com/us/album/masks-off/1895628310</v>
       </c>
       <c r="L179" t="str">
-        <v>I'm Just A Girl - Thee Marloes</v>
+        <v>Masks Off - Jesse Welles</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Soleil (feat. Isabella Lovestory)</v>
+        <v>I'm Just A Girl</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
+        <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-23</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>EXIT 2B</v>
+        <v>Di Hotel Malibu</v>
       </c>
       <c r="G180" t="str">
-        <v>2:11</v>
+        <v>2:49</v>
       </c>
       <c r="H180" t="str">
-        <v>B0YG1RL</v>
+        <v>Thee Marloes</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/b0yg1rl/1847766665</v>
+        <v>https://music.apple.com/us/artist/thee-marloes/1541376632</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/soleil-feat-isabella-lovestory/6769526101</v>
+        <v>https://music.apple.com/us/album/im-just-a-girl/1878399768</v>
       </c>
       <c r="L180" t="str">
-        <v>Soleil (feat. Isabella Lovestory) - B0YG1RL</v>
+        <v>I'm Just A Girl - Thee Marloes</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Money Tree</v>
+        <v>Soleil (feat. Isabella Lovestory)</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/money-tree/6763211637</v>
+        <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-23</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Money Tree - Single</v>
+        <v>EXIT 2B</v>
       </c>
       <c r="G181" t="str">
-        <v>2:39</v>
+        <v>2:11</v>
       </c>
       <c r="H181" t="str">
-        <v>Olympia Vitalis</v>
+        <v>B0YG1RL</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/b0yg1rl/1847766665</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/money-tree/1895216986</v>
+        <v>https://music.apple.com/us/album/soleil-feat-isabella-lovestory/6769526101</v>
       </c>
       <c r="L181" t="str">
-        <v>Money Tree - Olympia Vitalis</v>
+        <v>Soleil (feat. Isabella Lovestory) - B0YG1RL</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Homerunner</v>
+        <v>Money Tree</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/homerunner/6770682178</v>
+        <v>https://music.apple.com/us/song/money-tree/6763211637</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-23</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Homerunner - Single</v>
+        <v>Money Tree - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:36</v>
+        <v>2:39</v>
       </c>
       <c r="H182" t="str">
-        <v>slayr</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/homerunner/6770682177</v>
+        <v>https://music.apple.com/us/album/money-tree/1895216986</v>
       </c>
       <c r="L182" t="str">
-        <v>Homerunner - slayr</v>
+        <v>Money Tree - Olympia Vitalis</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Mail</v>
+        <v>Homerunner</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/mail/6769190635</v>
+        <v>https://music.apple.com/us/song/homerunner/6770682178</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-23</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Mail - Single</v>
+        <v>Homerunner - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:14</v>
+        <v>2:36</v>
       </c>
       <c r="H183" t="str">
-        <v>MexikoDro</v>
+        <v>slayr</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/mail/6769190634</v>
+        <v>https://music.apple.com/us/album/homerunner/6770682177</v>
       </c>
       <c r="L183" t="str">
-        <v>Mail - MexikoDro</v>
+        <v>Homerunner - slayr</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Waste Your Heart</v>
+        <v>Mail</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
+        <v>https://music.apple.com/us/song/mail/6769190635</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-23</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Waste Your Heart - Single</v>
+        <v>Mail - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:31</v>
+        <v>2:14</v>
       </c>
       <c r="H184" t="str">
-        <v>Magnus Ferrell</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/waste-your-heart/6769241913</v>
+        <v>https://music.apple.com/us/album/mail/6769190634</v>
       </c>
       <c r="L184" t="str">
-        <v>Waste Your Heart - Magnus Ferrell</v>
+        <v>Mail - MexikoDro</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Sleeping Pills</v>
+        <v>Waste Your Heart</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
+        <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-23</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Sleeping Pills - Single</v>
+        <v>Waste Your Heart - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:03</v>
+        <v>2:31</v>
       </c>
       <c r="H185" t="str">
-        <v>Dolder</v>
+        <v>Magnus Ferrell</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
+        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/sleeping-pills/1896452689</v>
+        <v>https://music.apple.com/us/album/waste-your-heart/6769241913</v>
       </c>
       <c r="L185" t="str">
-        <v>Sleeping Pills - Dolder</v>
+        <v>Waste Your Heart - Magnus Ferrell</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>KODACHROMATIC</v>
+        <v>Sleeping Pills</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
+        <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-23</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>KODACHROMATIC - Single</v>
+        <v>Sleeping Pills - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:53</v>
+        <v>3:03</v>
       </c>
       <c r="H186" t="str">
-        <v>Tiger La Flor</v>
+        <v>Dolder</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/tiger-la-flor/1613113982</v>
+        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/kodachromatic/6770724719</v>
+        <v>https://music.apple.com/us/album/sleeping-pills/1896452689</v>
       </c>
       <c r="L186" t="str">
-        <v>KODACHROMATIC - Tiger La Flor</v>
+        <v>Sleeping Pills - Dolder</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>FOMO</v>
+        <v>KODACHROMATIC</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/fomo/1890190631</v>
+        <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-23</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Map Of Her Shadow</v>
+        <v>KODACHROMATIC - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:01</v>
+        <v>2:53</v>
       </c>
       <c r="H187" t="str">
-        <v>Anais Cardot</v>
+        <v>Tiger La Flor</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/tiger-la-flor/1613113982</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/fomo/1890190623</v>
+        <v>https://music.apple.com/us/album/kodachromatic/6770724719</v>
       </c>
       <c r="L187" t="str">
-        <v>FOMO - Anais Cardot</v>
+        <v>KODACHROMATIC - Tiger La Flor</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Black Fire</v>
+        <v>FOMO</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/black-fire/6770696877</v>
+        <v>https://music.apple.com/us/song/fomo/1890190631</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-23</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Sulfur Surfer</v>
+        <v>Map Of Her Shadow</v>
       </c>
       <c r="G188" t="str">
-        <v>3:37</v>
+        <v>3:01</v>
       </c>
       <c r="H188" t="str">
-        <v>Bladee</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/bladee/861359576</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/black-fire/6770696743</v>
+        <v>https://music.apple.com/us/album/fomo/1890190623</v>
       </c>
       <c r="L188" t="str">
-        <v>Black Fire - Bladee</v>
+        <v>FOMO - Anais Cardot</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>As Seen in the Unseen</v>
+        <v>Black Fire</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
+        <v>https://music.apple.com/us/song/black-fire/6770696877</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-23</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Grand Serpent Rising</v>
+        <v>Sulfur Surfer</v>
       </c>
       <c r="G189" t="str">
-        <v>6:59</v>
+        <v>3:37</v>
       </c>
       <c r="H189" t="str">
-        <v>Dimmu Borgir</v>
+        <v>Bladee</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+        <v>https://music.apple.com/us/artist/bladee/861359576</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/as-seen-in-the-unseen/1883121436</v>
+        <v>https://music.apple.com/us/album/black-fire/6770696743</v>
       </c>
       <c r="L189" t="str">
-        <v>As Seen in the Unseen - Dimmu Borgir</v>
+        <v>Black Fire - Bladee</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Every Man-Any Man</v>
+        <v>As Seen in the Unseen</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
+        <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-23</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Emotion Factory Reset</v>
+        <v>Grand Serpent Rising</v>
       </c>
       <c r="G190" t="str">
-        <v>4:20</v>
+        <v>6:59</v>
       </c>
       <c r="H190" t="str">
-        <v>Armored Saint</v>
+        <v>Dimmu Borgir</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/every-man-any-man/1872193859</v>
+        <v>https://music.apple.com/us/album/as-seen-in-the-unseen/1883121436</v>
       </c>
       <c r="L190" t="str">
-        <v>Every Man-Any Man - Armored Saint</v>
+        <v>As Seen in the Unseen - Dimmu Borgir</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>No Arms</v>
+        <v>Every Man-Any Man</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/no-arms/6765776563</v>
+        <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-23</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>From A Distance</v>
+        <v>Emotion Factory Reset</v>
       </c>
       <c r="G191" t="str">
-        <v>3:43</v>
+        <v>4:20</v>
       </c>
       <c r="H191" t="str">
-        <v>156/Silence</v>
+        <v>Armored Saint</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/156-silence/1071395282</v>
+        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/no-arms/1896069437</v>
+        <v>https://music.apple.com/us/album/every-man-any-man/1872193859</v>
       </c>
       <c r="L191" t="str">
-        <v>No Arms - 156/Silence</v>
+        <v>Every Man-Any Man - Armored Saint</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>It's Neverending</v>
+        <v>No Arms</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
+        <v>https://music.apple.com/us/song/no-arms/6765776563</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-23</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Neverending</v>
+        <v>From A Distance</v>
       </c>
       <c r="G192" t="str">
-        <v>8:35</v>
+        <v>3:43</v>
       </c>
       <c r="H192" t="str">
-        <v>Monolord</v>
+        <v>156/Silence</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+        <v>https://music.apple.com/us/artist/156-silence/1071395282</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/its-neverending/1871211801</v>
+        <v>https://music.apple.com/us/album/no-arms/1896069437</v>
       </c>
       <c r="L192" t="str">
-        <v>It's Neverending - Monolord</v>
+        <v>No Arms - 156/Silence</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>The Kids Will Kill Us</v>
+        <v>It's Neverending</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
+        <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-23</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>The Kids Will Kill Us - Single</v>
+        <v>Neverending</v>
       </c>
       <c r="G193" t="str">
-        <v>3:45</v>
+        <v>8:35</v>
       </c>
       <c r="H193" t="str">
-        <v>Witch Club Satan</v>
+        <v>Monolord</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/witch-club-satan/1626477576</v>
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/the-kids-will-kill-us/6766343272</v>
+        <v>https://music.apple.com/us/album/its-neverending/1871211801</v>
       </c>
       <c r="L193" t="str">
-        <v>The Kids Will Kill Us - Witch Club Satan</v>
+        <v>It's Neverending - Monolord</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe")</v>
+        <v>The Kids Will Kill Us</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
+        <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-23</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe") - Single</v>
+        <v>The Kids Will Kill Us - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:20</v>
+        <v>3:45</v>
       </c>
       <c r="H194" t="str">
-        <v>The Darkness</v>
+        <v>Witch Club Satan</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/the-darkness/2417388</v>
+        <v>https://music.apple.com/us/artist/witch-club-satan/1626477576</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/masters-of-the-universe-from-masters-of-the-universe/6769065779</v>
+        <v>https://music.apple.com/us/album/the-kids-will-kill-us/6766343272</v>
       </c>
       <c r="L194" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe") - The Darkness</v>
+        <v>The Kids Will Kill Us - Witch Club Satan</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>All Day</v>
+        <v>Masters of the Universe (from "Masters of the Universe")</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/all-day/1880746584</v>
+        <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-23</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Feet On Fire</v>
+        <v>Masters of the Universe (from "Masters of the Universe") - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>2:29</v>
+        <v>3:20</v>
       </c>
       <c r="H195" t="str">
-        <v>Ben Chapman</v>
+        <v>The Darkness</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/ben-chapman/1581192612</v>
+        <v>https://music.apple.com/us/artist/the-darkness/2417388</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/all-day/1880746349</v>
+        <v>https://music.apple.com/us/album/masters-of-the-universe-from-masters-of-the-universe/6769065779</v>
       </c>
       <c r="L195" t="str">
-        <v>All Day - Ben Chapman</v>
+        <v>Masters of the Universe (from "Masters of the Universe") - The Darkness</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Sigui</v>
+        <v>All Day</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/sigui/1890241955</v>
+        <v>https://music.apple.com/us/song/all-day/1880746584</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-23</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Massa</v>
+        <v>Feet On Fire</v>
       </c>
       <c r="G196" t="str">
-        <v>3:17</v>
+        <v>2:29</v>
       </c>
       <c r="H196" t="str">
-        <v>Fatoumata Diawara</v>
+        <v>Ben Chapman</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/fatoumata-diawara/466213610</v>
+        <v>https://music.apple.com/us/artist/ben-chapman/1581192612</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/sigui/1890241617</v>
+        <v>https://music.apple.com/us/album/all-day/1880746349</v>
       </c>
       <c r="L196" t="str">
-        <v>Sigui - Fatoumata Diawara</v>
+        <v>All Day - Ben Chapman</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>High Tail</v>
+        <v>Sigui</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/high-tail/1870432994</v>
+        <v>https://music.apple.com/us/song/sigui/1890241955</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-23</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Where the South Winds Wail</v>
+        <v>Massa</v>
       </c>
       <c r="G197" t="str">
-        <v>2:31</v>
+        <v>3:17</v>
       </c>
       <c r="H197" t="str">
-        <v>Gitkin</v>
+        <v>Fatoumata Diawara</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/gitkin/1345281815</v>
+        <v>https://music.apple.com/us/artist/fatoumata-diawara/466213610</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/high-tail/1870432670</v>
+        <v>https://music.apple.com/us/album/sigui/1890241617</v>
       </c>
       <c r="L197" t="str">
-        <v>High Tail - Gitkin</v>
+        <v>Sigui - Fatoumata Diawara</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Mice Protection</v>
+        <v>High Tail</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
+        <v>https://music.apple.com/us/song/high-tail/1870432994</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-23</v>
@@ -7899,68 +7899,106 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Ugly Duckling Union</v>
+        <v>Where the South Winds Wail</v>
       </c>
       <c r="G198" t="str">
-        <v>3:34</v>
+        <v>2:31</v>
       </c>
       <c r="H198" t="str">
-        <v>Lowertown</v>
+        <v>Gitkin</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/lowertown/1448207323</v>
+        <v>https://music.apple.com/us/artist/gitkin/1345281815</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/mice-protection/1872171971</v>
+        <v>https://music.apple.com/us/album/high-tail/1870432670</v>
       </c>
       <c r="L198" t="str">
-        <v>Mice Protection - Lowertown</v>
+        <v>High Tail - Gitkin</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
+        <v>Mice Protection</v>
+      </c>
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
+        <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
+      </c>
+      <c r="D199" t="str">
+        <v>2026-05-23</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v>Ugly Duckling Union</v>
+      </c>
+      <c r="G199" t="str">
+        <v>3:34</v>
+      </c>
+      <c r="H199" t="str">
+        <v>Lowertown</v>
+      </c>
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
+        <v>https://music.apple.com/us/artist/lowertown/1448207323</v>
+      </c>
+      <c r="K199" t="str">
+        <v>https://music.apple.com/us/album/mice-protection/1872171971</v>
+      </c>
+      <c r="L199" t="str">
+        <v>Mice Protection - Lowertown</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
         <v>Tóxica</v>
       </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
         <v>https://music.apple.com/us/song/t%C3%B3xica/6763056240</v>
       </c>
-      <c r="D199" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
+      <c r="D200" t="str">
+        <v>2026-05-23</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
         <v>Caribenya</v>
       </c>
-      <c r="G199" t="str">
+      <c r="G200" t="str">
         <v>3:48</v>
       </c>
-      <c r="H199" t="str">
+      <c r="H200" t="str">
         <v>Lido Pimienta</v>
       </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
         <v>https://music.apple.com/us/artist/lido-pimienta/389475023</v>
       </c>
-      <c r="K199" t="str">
+      <c r="K200" t="str">
         <v>https://music.apple.com/us/album/t%C3%B3xica/1895141218</v>
       </c>
-      <c r="L199" t="str">
+      <c r="L200" t="str">
         <v>Tóxica - Lido Pimienta</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L200"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week04/titles.xlsx
+++ b/data/global/2026-05-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אסתר שמיר ויהל דורון – בצד השני של הפחד</v>
+        <v>עומר אדם - אלבום הופעה איצטדיון רמת גן 2026</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-22</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%a1%d7%aa%d7%a8-%d7%a9%d7%9e%d7%99%d7%a8-%d7%95%d7%99%d7%94%d7%9c-%d7%93%d7%95%d7%a8%d7%95%d7%9f-%d7%91%d7%a6%d7%93-%d7%94%d7%a9%d7%a0%d7%99-%d7%a9%d7%9c-%d7%94%d7%a4%d7%97%d7%93/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24471&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-23</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>שיתוף הפעולה בין אסתר שמיר ליהל דורון ב״בצד השני של הפחד״ הוא לא רק דואט מוזיקלי  אלא מפגש בין שתי תפיסות של רגש, כתיבה ונחמה במוזיקה הישראלית. מצד אחד קול שנושא איתו היסטוריה תרבותית שלמה, ומצד שני יוצר עכשווי שמביא</v>
+        <v>14:04</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -460,7 +460,7 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אסתר שמיר ויהל דורון – בצד השני של הפחד</v>
+        <v>עומר אדם - אלבום הופעה איצטדיון רמת גן 2026</v>
       </c>
     </row>
     <row r="3">
@@ -1009,7 +1009,7 @@
         <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>

--- a/data/global/2026-05-week04/titles.xlsx
+++ b/data/global/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L200"/>
+  <dimension ref="A1:L199"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עומר אדם - אלבום הופעה איצטדיון רמת גן 2026</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-22</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24471&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-23</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>14:04</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Dean Lewis</v>
       </c>
       <c r="I2" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עומר אדם - אלבום הופעה איצטדיון רמת גן 2026</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B3" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-23</v>
@@ -495,7 +495,7 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Dean Lewis</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-23</v>
@@ -533,7 +533,7 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-23</v>
@@ -571,7 +571,7 @@
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Niall Horan</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-23</v>
@@ -609,7 +609,7 @@
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>RUEL</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-23</v>
@@ -647,7 +647,7 @@
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>RUEL</v>
+        <v>TINI</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-23</v>
@@ -685,7 +685,7 @@
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>TINI</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-23</v>
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Charli xcx</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-23</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Dua Lipa</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-23</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Matilda Mann</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-23</v>
@@ -837,7 +837,7 @@
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Ella Langley</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-23</v>
@@ -875,7 +875,7 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Nothing But Thieves</v>
+        <v>kesha</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-23</v>
@@ -913,7 +913,7 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>kesha</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-23</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Holly Humberstone</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-23</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Foo Fighters</v>
+        <v>The Analogues</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B17" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-23</v>
@@ -1027,7 +1027,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>The Analogues</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-23</v>
@@ -1065,7 +1065,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Rod Stewart</v>
+        <v>Blue October</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
+        <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B19" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
+        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-23</v>
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Blue October</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
+        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Far Caspian - hum (Official Video)</v>
+        <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B20" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
+        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-23</v>
@@ -1141,7 +1141,7 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Far Caspian</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
+        <v>Kenia Os - Love Bombing - Kenia Os</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Kenia Os - Love Bombing</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B21" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
+        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-23</v>
@@ -1179,7 +1179,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Kenia Os</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Kenia Os - Love Bombing - Kenia Os</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B22" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-23</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B23" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-23</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B24" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-23</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B25" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-23</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B26" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-23</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B27" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-23</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-23</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Evanescence</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>7 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-23</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Evanescence</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B30" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-23</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B31" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-23</v>
@@ -1559,7 +1559,7 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Armin van Buuren</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-23</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Madison Cunningham</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B33" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-23</v>
@@ -1635,7 +1635,7 @@
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Johnny Orlando</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B34" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-23</v>
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Carver Jones</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B35" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-23</v>
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Jazmin bean</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B36" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-23</v>
@@ -1749,7 +1749,7 @@
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Baby Queen</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-23</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Switchfoot</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-23</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Grace Potter</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-23</v>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B40" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-23</v>
@@ -1901,7 +1901,7 @@
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>The All-American Rejects</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B41" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-23</v>
@@ -1939,7 +1939,7 @@
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Henry Moodie</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-23</v>
@@ -1977,7 +1977,7 @@
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Spacey Jane</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B43" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-23</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Megan Moroney</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B44" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-23</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
+        <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B45" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
+        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-23</v>
@@ -2091,7 +2091,7 @@
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Matt Hansen</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
+        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Keith Urban - Steal Away (Visualizer)</v>
+        <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B46" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
+        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-23</v>
@@ -2129,7 +2129,7 @@
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Keith Urban</v>
+        <v>VALÉ</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
+        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>VALÉ - Mugshot (Official Video)</v>
+        <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B47" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
+        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-23</v>
@@ -2167,7 +2167,7 @@
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>VALÉ</v>
+        <v>Mackenzie Carpenter</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
+        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio)</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B48" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
+        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-23</v>
@@ -2205,7 +2205,7 @@
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Mackenzie Carpenter</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B49" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
+        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-23</v>
@@ -2243,7 +2243,7 @@
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Towa Bird</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
+        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-23</v>
@@ -2281,7 +2281,7 @@
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Sabrina Sterling</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
+        <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B51" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
+        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-23</v>
@@ -2319,7 +2319,7 @@
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Little Big Town</v>
+        <v>Becky G</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
+        <v>Becky G - EPA (Official Video) - Becky G</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Becky G - EPA (Official Video)</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B52" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
+        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-23</v>
@@ -2357,7 +2357,7 @@
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Becky G</v>
+        <v>Daisy the Great</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Becky G - EPA (Official Video) - Becky G</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
+        <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B53" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
+        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-23</v>
@@ -2395,7 +2395,7 @@
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Daisy the Great</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
+        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Towa Bird - Dog (Official Music Video)</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B54" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
+        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-23</v>
@@ -2433,7 +2433,7 @@
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Towa Bird</v>
+        <v>Madonna</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
+        <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B55" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
+        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-23</v>
@@ -2471,7 +2471,7 @@
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Madonna</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
+        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video)</v>
+        <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B56" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
+        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-23</v>
@@ -2509,7 +2509,7 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Ally Salort</v>
+        <v>Bella White</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
+        <v>Bella White - Better - Official Music Video - Bella White</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Bella White - Better - Official Music Video</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B57" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
+        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-23</v>
@@ -2547,7 +2547,7 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Bella White</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Bella White - Better - Official Music Video - Bella White</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B58" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
+        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-23</v>
@@ -2585,7 +2585,7 @@
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
+        <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B59" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
+        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-23</v>
@@ -2623,7 +2623,7 @@
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Towa Bird</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
+        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer)</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B60" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
+        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-23</v>
@@ -2661,7 +2661,7 @@
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Miranda Lambert</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
+        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-23</v>
@@ -2699,7 +2699,7 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Lady Gaga</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B62" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
+        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-23</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Gracie Abrams</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B63" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
+        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-23</v>
@@ -2775,7 +2775,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
+        <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B64" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
+        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-23</v>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Martin Garrix</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
+        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Jorja Smith - What's Done Is Done</v>
+        <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
+        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-23</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Jorja Smith</v>
+        <v>LP</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
+        <v>LP - Shelly (Official Music Video) - LP</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>LP - Shelly (Official Music Video)</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
+        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-23</v>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>LP</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>LP - Shelly (Official Music Video) - LP</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
+        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-23</v>
@@ -2927,7 +2927,7 @@
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>The Rolling Stones</v>
+        <v>Oasis</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B68" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
+        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-23</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Oasis</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B69" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
+        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-23</v>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Breaking Benjamin</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B70" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
+        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-23</v>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>VictorBiliac</v>
+        <v>Linkin Park</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
+        <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
+        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-23</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Linkin Park</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
+        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Harry Styles - Dance No More (Official Video)</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
+        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-23</v>
@@ -3117,7 +3117,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Harry Styles</v>
+        <v>Eagles</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
+        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-23</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Eagles</v>
+        <v>Nora Fatehi</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B74" t="str">
-        <v>13 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
+        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-23</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>13 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Nora Fatehi</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B75" t="str">
         <v>2 months ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
+        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-23</v>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Eurovision Song Contest and Alis</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B76" t="str">
         <v>2 months ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
+        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-23</v>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Eurovision Song Contest and Alis</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
+        <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
+        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-23</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>The Head And The Heart</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
+        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video)</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
+        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-23</v>
@@ -3345,7 +3345,7 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>The Head And The Heart</v>
+        <v>Simply Red</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
+        <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
+        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-23</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Simply Red</v>
+        <v>Talking Heads</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
+        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video)</v>
+        <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
+        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-23</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Talking Heads</v>
+        <v>Ellise</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
+        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Ellise - Liplock (Official Music Video)</v>
+        <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
+        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-23</v>
@@ -3459,7 +3459,7 @@
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Ellise</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
+        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Tori Kelly - Dive (Official Music Video)</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
+        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-23</v>
@@ -3497,7 +3497,7 @@
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Tori Kelly</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
+        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-23</v>
@@ -3535,7 +3535,7 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>David Gilmour</v>
+        <v>Scorpions</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
+        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-23</v>
@@ -3573,7 +3573,7 @@
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Scorpions</v>
+        <v>Claire Leslie</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
+        <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
+        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-23</v>
@@ -3611,7 +3611,7 @@
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Claire Leslie</v>
+        <v>Michael Schulte</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
+        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Michael Schulte - Lovesick (Official Video)</v>
+        <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
+        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-23</v>
@@ -3649,7 +3649,7 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Michael Schulte</v>
+        <v>Caity Baser</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
+        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Caity Baser - Holiday Song (Official Video)</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
+        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-23</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Caity Baser</v>
+        <v>Sam Fischer</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
+        <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
+        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-23</v>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Sam Fischer</v>
+        <v>Porches</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
+        <v>Porches- HABIT (Official Video) - Porches</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Porches- HABIT (Official Video)</v>
+        <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
+        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-23</v>
@@ -3763,7 +3763,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Porches</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Porches- HABIT (Official Video) - Porches</v>
+        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Charli xcx - Rock Music (Official Video)</v>
+        <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
+        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-23</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Charli xcx</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
+        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Jon Batiste - Alla Blues (Audio)</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
+        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-23</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Jon Batiste</v>
+        <v>Tigirlily Gold</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
+        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-23</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Tigirlily Gold</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
+        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-23</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
+        <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
+        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-23</v>
@@ -3953,7 +3953,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Bruno Mars</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
+        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Tori Kelly - Control (Official Visualizer)</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
+        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-23</v>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Tori Kelly</v>
+        <v>bea miller</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
+        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-23</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>bea miller</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
+        <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
+        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-23</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>The Chainsmokers</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
+        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Madison Beer - free (Official Audio)</v>
+        <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
+        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-23</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Madison Beer</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
+        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Tori Kelly - Dive (Official Audio)</v>
+        <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
+        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-23</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Tori Kelly</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
+        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio)</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
+        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-23</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>JeremyCampMusic</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
+        <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
+        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-23</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>The Chainsmokers</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
+        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Ashley Cooke - high school sweetheart</v>
+        <v>From Down Here</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
+        <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-23</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>From Down Here - Single</v>
       </c>
       <c r="G102" t="str">
-        <v/>
+        <v>4:01</v>
       </c>
       <c r="H102" t="str">
-        <v>Ashley Cooke</v>
+        <v>Lola Young</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/lola-young/452271760</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/from-down-here/6768357139</v>
       </c>
       <c r="L102" t="str">
-        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
+        <v>From Down Here - Lola Young</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>From Down Here</v>
+        <v>the cure</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
+        <v>https://music.apple.com/us/song/the-cure/1889992123</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-23</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>From Down Here - Single</v>
+        <v>you seem pretty sad for a girl so in love</v>
       </c>
       <c r="G103" t="str">
-        <v>4:01</v>
+        <v>4:57</v>
       </c>
       <c r="H103" t="str">
-        <v>Lola Young</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/lola-young/452271760</v>
+        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/from-down-here/6768357139</v>
+        <v>https://music.apple.com/us/album/the-cure/1889992111</v>
       </c>
       <c r="L103" t="str">
-        <v>From Down Here - Lola Young</v>
+        <v>the cure - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>the cure</v>
+        <v>SS26</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/the-cure/1889992123</v>
+        <v>https://music.apple.com/us/song/ss26/6771061782</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-23</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>you seem pretty sad for a girl so in love</v>
+        <v>SS26 - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>4:57</v>
+        <v>2:47</v>
       </c>
       <c r="H104" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
+        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/the-cure/1889992111</v>
+        <v>https://music.apple.com/us/album/ss26/6771061771</v>
       </c>
       <c r="L104" t="str">
-        <v>the cure - Olivia Rodrigo</v>
+        <v>SS26 - Charli xcx</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>SS26</v>
+        <v>White Flag</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/ss26/6771061782</v>
+        <v>https://music.apple.com/us/song/white-flag/1887627840</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-23</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>SS26 - Single</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G105" t="str">
-        <v>2:47</v>
+        <v>2:34</v>
       </c>
       <c r="H105" t="str">
-        <v>Charli xcx</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/ss26/6771061771</v>
+        <v>https://music.apple.com/us/album/white-flag/1887627836</v>
       </c>
       <c r="L105" t="str">
-        <v>SS26 - Charli xcx</v>
+        <v>White Flag - Vince Staples</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>White Flag</v>
+        <v>Knew Better Part Two</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/white-flag/1887627840</v>
+        <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-23</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Cry Baby</v>
+        <v>Dangerous Woman (Tenth Anniversary Edition)</v>
       </c>
       <c r="G106" t="str">
-        <v>2:34</v>
+        <v>2:44</v>
       </c>
       <c r="H106" t="str">
-        <v>Vince Staples</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/white-flag/1887627836</v>
+        <v>https://music.apple.com/us/album/knew-better-part-two/6770600996</v>
       </c>
       <c r="L106" t="str">
-        <v>White Flag - Vince Staples</v>
+        <v>Knew Better Part Two - Ariana Grande</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Knew Better Part Two</v>
+        <v>Goals</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
+        <v>https://music.apple.com/us/song/goals/6769251838</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-23</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Dangerous Woman (Tenth Anniversary Edition)</v>
+        <v>Goals (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>2:44</v>
+        <v>3:00</v>
       </c>
       <c r="H107" t="str">
-        <v>Ariana Grande</v>
+        <v>LISA</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v>https://music.apple.com/us/artist/lisa/1583908668</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/knew-better-part-two/6770600996</v>
+        <v>https://music.apple.com/us/album/goals/6769251829</v>
       </c>
       <c r="L107" t="str">
-        <v>Knew Better Part Two - Ariana Grande</v>
+        <v>Goals - LISA</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Goals</v>
+        <v>we should talk</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/goals/6769251838</v>
+        <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-23</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Goals (FIFA World Cup 2026™) - Single</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G108" t="str">
-        <v>3:00</v>
+        <v>3:04</v>
       </c>
       <c r="H108" t="str">
-        <v>LISA</v>
+        <v>Bleachers</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/lisa/1583908668</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/goals/6769251829</v>
+        <v>https://music.apple.com/us/album/we-should-talk/1872842313</v>
       </c>
       <c r="L108" t="str">
-        <v>Goals - LISA</v>
+        <v>we should talk - Bleachers</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>we should talk</v>
+        <v>Do What You Gotta Do</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
+        <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-23</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>everyone for ten minutes</v>
+        <v>NeverAlways (Vol. 2)</v>
       </c>
       <c r="G109" t="str">
-        <v>3:04</v>
+        <v>3:26</v>
       </c>
       <c r="H109" t="str">
-        <v>Bleachers</v>
+        <v>The Band CAMINO</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/we-should-talk/1872842313</v>
+        <v>https://music.apple.com/us/album/do-what-you-gotta-do/1887616173</v>
       </c>
       <c r="L109" t="str">
-        <v>we should talk - Bleachers</v>
+        <v>Do What You Gotta Do - The Band CAMINO</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Do What You Gotta Do</v>
+        <v>Ego</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
+        <v>https://music.apple.com/us/song/ego/6769207667</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-23</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>NeverAlways (Vol. 2)</v>
+        <v>Ego - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:26</v>
+        <v>2:53</v>
       </c>
       <c r="H110" t="str">
-        <v>The Band CAMINO</v>
+        <v>The Warning</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/do-what-you-gotta-do/1887616173</v>
+        <v>https://music.apple.com/us/album/ego/6769207665</v>
       </c>
       <c r="L110" t="str">
-        <v>Do What You Gotta Do - The Band CAMINO</v>
+        <v>Ego - The Warning</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Ego</v>
+        <v>Light up (From the Netflix Documentary 'kylie')</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/ego/6769207667</v>
+        <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-23</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Ego - Single</v>
+        <v>Light up (From the Netflix Documentary 'Kylie') - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>2:53</v>
+        <v>3:17</v>
       </c>
       <c r="H111" t="str">
-        <v>The Warning</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/kylie-minogue/465031</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/ego/6769207665</v>
+        <v>https://music.apple.com/us/album/light-up-from-the-netflix-documentary-kylie/6768013505</v>
       </c>
       <c r="L111" t="str">
-        <v>Ego - The Warning</v>
+        <v>Light up (From the Netflix Documentary 'kylie') - Kylie Minogue</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Light up (From the Netflix Documentary 'kylie')</v>
+        <v>All That Matters</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
+        <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-23</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Light up (From the Netflix Documentary 'Kylie') - Single</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G112" t="str">
-        <v>3:17</v>
+        <v>3:43</v>
       </c>
       <c r="H112" t="str">
-        <v>Kylie Minogue</v>
+        <v>6LACK</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/kylie-minogue/465031</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/light-up-from-the-netflix-documentary-kylie/6768013505</v>
+        <v>https://music.apple.com/us/album/all-that-matters/1884792154</v>
       </c>
       <c r="L112" t="str">
-        <v>Light up (From the Netflix Documentary 'kylie') - Kylie Minogue</v>
+        <v>All That Matters - 6LACK</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>All That Matters</v>
+        <v>Like A Virgin</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
+        <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-23</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Terrified .</v>
       </c>
       <c r="G113" t="str">
-        <v>3:43</v>
+        <v>2:34</v>
       </c>
       <c r="H113" t="str">
-        <v>6LACK</v>
+        <v>fakemink</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/all-that-matters/1884792154</v>
+        <v>https://music.apple.com/us/album/like-a-virgin/6768157748</v>
       </c>
       <c r="L113" t="str">
-        <v>All That Matters - 6LACK</v>
+        <v>Like A Virgin - fakemink</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Like A Virgin</v>
+        <v>24 Hours</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
+        <v>https://music.apple.com/us/song/24-hours/6771060076</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-23</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Terrified .</v>
+        <v>24 Hours - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>2:34</v>
+        <v>3:17</v>
       </c>
       <c r="H114" t="str">
-        <v>fakemink</v>
+        <v>Stormzy</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/stormzy/394865154</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/like-a-virgin/6768157748</v>
+        <v>https://music.apple.com/us/album/24-hours/6771060073</v>
       </c>
       <c r="L114" t="str">
-        <v>Like A Virgin - fakemink</v>
+        <v>24 Hours - Stormzy</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>24 Hours</v>
+        <v>HOES (From Scary Movie)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/24-hours/6771060076</v>
+        <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-23</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>24 Hours - Single</v>
+        <v>HOES (From Scary Movie) - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:17</v>
+        <v>2:09</v>
       </c>
       <c r="H115" t="str">
-        <v>Stormzy</v>
+        <v>Lizzo</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/stormzy/394865154</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/24-hours/6771060073</v>
+        <v>https://music.apple.com/us/album/hoes-from-scary-movie/6770661290</v>
       </c>
       <c r="L115" t="str">
-        <v>24 Hours - Stormzy</v>
+        <v>HOES (From Scary Movie) - Lizzo</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>HOES (From Scary Movie)</v>
+        <v>Ms. Tundra</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
+        <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-23</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>HOES (From Scary Movie) - Single</v>
+        <v>Highway 79</v>
       </c>
       <c r="G116" t="str">
-        <v>2:09</v>
+        <v>3:12</v>
       </c>
       <c r="H116" t="str">
-        <v>Lizzo</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/hoes-from-scary-movie/6770661290</v>
+        <v>https://music.apple.com/us/album/ms-tundra/6770614875</v>
       </c>
       <c r="L116" t="str">
-        <v>HOES (From Scary Movie) - Lizzo</v>
+        <v>Ms. Tundra - Ne-Yo</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Ms. Tundra</v>
+        <v>TARENTINO</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
+        <v>https://music.apple.com/us/song/tarentino/6769927265</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-23</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Highway 79</v>
+        <v>TARENTINO - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:12</v>
+        <v>2:23</v>
       </c>
       <c r="H117" t="str">
-        <v>Ne-Yo</v>
+        <v>Labrinth</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/ms-tundra/6770614875</v>
+        <v>https://music.apple.com/us/album/tarentino/6769927262</v>
       </c>
       <c r="L117" t="str">
-        <v>Ms. Tundra - Ne-Yo</v>
+        <v>TARENTINO - Labrinth</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>TARENTINO</v>
+        <v>Daydreamin’</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/tarentino/6769927265</v>
+        <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-23</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>TARENTINO - Single</v>
+        <v>KONNAKOL (Deluxe)</v>
       </c>
       <c r="G118" t="str">
-        <v>2:23</v>
+        <v>2:58</v>
       </c>
       <c r="H118" t="str">
-        <v>Labrinth</v>
+        <v>ZAYN</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/tarentino/6769927262</v>
+        <v>https://music.apple.com/us/album/daydreamin/6769559345</v>
       </c>
       <c r="L118" t="str">
-        <v>TARENTINO - Labrinth</v>
+        <v>Daydreamin’ - ZAYN</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Daydreamin’</v>
+        <v>End of an Era</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
+        <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-23</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>KONNAKOL (Deluxe)</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G119" t="str">
-        <v>2:58</v>
+        <v>3:38</v>
       </c>
       <c r="H119" t="str">
-        <v>ZAYN</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/daydreamin/6769559345</v>
+        <v>https://music.apple.com/us/album/end-of-an-era/1884418567</v>
       </c>
       <c r="L119" t="str">
-        <v>Daydreamin’ - ZAYN</v>
+        <v>End of an Era - Niall Horan</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>End of an Era</v>
+        <v>Questions</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
+        <v>https://music.apple.com/us/song/questions/1871502847</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-23</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Dinner Party</v>
+        <v>Florescence</v>
       </c>
       <c r="G120" t="str">
-        <v>3:38</v>
+        <v>3:07</v>
       </c>
       <c r="H120" t="str">
-        <v>Niall Horan</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/end-of-an-era/1884418567</v>
+        <v>https://music.apple.com/us/album/questions/1871502372</v>
       </c>
       <c r="L120" t="str">
-        <v>End of an Era - Niall Horan</v>
+        <v>Questions - Maisie Peters</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Questions</v>
+        <v>Heart Has To Work So Hard</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/questions/1871502847</v>
+        <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-23</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Florescence</v>
+        <v>Heart Has To Work So Hard - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:07</v>
+        <v>3:12</v>
       </c>
       <c r="H121" t="str">
-        <v>Maisie Peters</v>
+        <v>Blondshell</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/blondshell/1624592688</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/questions/1871502372</v>
+        <v>https://music.apple.com/us/album/heart-has-to-work-so-hard/1895982147</v>
       </c>
       <c r="L121" t="str">
-        <v>Questions - Maisie Peters</v>
+        <v>Heart Has To Work So Hard - Blondshell</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Heart Has To Work So Hard</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
+        <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-23</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Heart Has To Work So Hard - Single</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski) - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:12</v>
+        <v>3:44</v>
       </c>
       <c r="H122" t="str">
-        <v>Blondshell</v>
+        <v>Kygo</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/blondshell/1624592688</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/heart-has-to-work-so-hard/1895982147</v>
+        <v>https://music.apple.com/us/album/heaven-on-your-mind-feat-dan-tyminski/6769007431</v>
       </c>
       <c r="L122" t="str">
-        <v>Heart Has To Work So Hard - Blondshell</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski) - Kygo</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski)</v>
+        <v>PERDISTE EL EMMY.</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
+        <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-23</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski) - Single</v>
+        <v>OMAKASE</v>
       </c>
       <c r="G123" t="str">
-        <v>3:44</v>
+        <v>4:03</v>
       </c>
       <c r="H123" t="str">
-        <v>Kygo</v>
+        <v>Álvaro Díaz</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-your-mind-feat-dan-tyminski/6769007431</v>
+        <v>https://music.apple.com/us/album/perdiste-el-emmy/6771082594</v>
       </c>
       <c r="L123" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski) - Kygo</v>
+        <v>PERDISTE EL EMMY. - Álvaro Díaz</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>PERDISTE EL EMMY.</v>
+        <v>Dosis</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
+        <v>https://music.apple.com/us/song/dosis/6762929729</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-23</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>OMAKASE</v>
+        <v>DOSIS</v>
       </c>
       <c r="G124" t="str">
-        <v>4:03</v>
+        <v>3:00</v>
       </c>
       <c r="H124" t="str">
-        <v>Álvaro Díaz</v>
+        <v>Xavi</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/perdiste-el-emmy/6771082594</v>
+        <v>https://music.apple.com/us/album/dosis/1895081885</v>
       </c>
       <c r="L124" t="str">
-        <v>PERDISTE EL EMMY. - Álvaro Díaz</v>
+        <v>Dosis - Xavi</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Dosis</v>
+        <v>Would U Still Love Me</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/dosis/6762929729</v>
+        <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-23</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>DOSIS</v>
+        <v>Whitcomb vs. Flores - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:00</v>
+        <v>2:36</v>
       </c>
       <c r="H125" t="str">
-        <v>Xavi</v>
+        <v>Diplo</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/dosis/1895081885</v>
+        <v>https://music.apple.com/us/album/would-u-still-love-me/6769907832</v>
       </c>
       <c r="L125" t="str">
-        <v>Dosis - Xavi</v>
+        <v>Would U Still Love Me - Diplo</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Would U Still Love Me</v>
+        <v>Saving This Bottle</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
+        <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-23</v>
@@ -5166,7 +5166,7 @@
         <v>Whitcomb vs. Flores - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:36</v>
+        <v>3:05</v>
       </c>
       <c r="H126" t="str">
         <v>Diplo</v>
@@ -5178,21 +5178,21 @@
         <v>https://music.apple.com/us/artist/diplo/1468290871</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/would-u-still-love-me/6769907832</v>
+        <v>https://music.apple.com/us/album/saving-this-bottle/6769907832</v>
       </c>
       <c r="L126" t="str">
-        <v>Would U Still Love Me - Diplo</v>
+        <v>Saving This Bottle - Diplo</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Saving This Bottle</v>
+        <v>The Climb</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
+        <v>https://music.apple.com/us/song/the-climb/6769546149</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-23</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Whitcomb vs. Flores - Single</v>
+        <v>The Climb - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:05</v>
+        <v>3:50</v>
       </c>
       <c r="H127" t="str">
-        <v>Diplo</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/saving-this-bottle/6769907832</v>
+        <v>https://music.apple.com/us/album/the-climb/6769546147</v>
       </c>
       <c r="L127" t="str">
-        <v>Saving This Bottle - Diplo</v>
+        <v>The Climb - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>The Climb</v>
+        <v>everything tatted</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/the-climb/6769546149</v>
+        <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-23</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>The Climb - Single</v>
+        <v>everything tatted - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:50</v>
+        <v>3:25</v>
       </c>
       <c r="H128" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>mgk</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/the-climb/6769546147</v>
+        <v>https://music.apple.com/us/album/everything-tatted/6770773606</v>
       </c>
       <c r="L128" t="str">
-        <v>The Climb - Bailey Zimmerman</v>
+        <v>everything tatted - mgk</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>everything tatted</v>
+        <v>BOOMPALA</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
+        <v>https://music.apple.com/us/song/boompala/1894802726</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-23</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>everything tatted - Single</v>
+        <v>'PUREFLOW', Pt. 1</v>
       </c>
       <c r="G129" t="str">
-        <v>3:25</v>
+        <v>2:56</v>
       </c>
       <c r="H129" t="str">
-        <v>mgk</v>
+        <v>LE SSERAFIM</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/everything-tatted/6770773606</v>
+        <v>https://music.apple.com/us/album/boompala/1894802719</v>
       </c>
       <c r="L129" t="str">
-        <v>everything tatted - mgk</v>
+        <v>BOOMPALA - LE SSERAFIM</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>BOOMPALA</v>
+        <v>Let Me Be In Your Arms</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/boompala/1894802726</v>
+        <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-23</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>'PUREFLOW', Pt. 1</v>
+        <v>can we do it all again?</v>
       </c>
       <c r="G130" t="str">
-        <v>2:56</v>
+        <v>3:13</v>
       </c>
       <c r="H130" t="str">
-        <v>LE SSERAFIM</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/boompala/1894802719</v>
+        <v>https://music.apple.com/us/album/let-me-be-in-your-arms/1881610862</v>
       </c>
       <c r="L130" t="str">
-        <v>BOOMPALA - LE SSERAFIM</v>
+        <v>Let Me Be In Your Arms - Sonny Fodera</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Let Me Be In Your Arms</v>
+        <v>Eat, Work, Pray</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
+        <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-23</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>can we do it all again?</v>
+        <v>Eat, Work, Pray - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:13</v>
+        <v>2:28</v>
       </c>
       <c r="H131" t="str">
-        <v>Sonny Fodera</v>
+        <v>Sheff G</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/let-me-be-in-your-arms/1881610862</v>
+        <v>https://music.apple.com/us/album/eat-work-pray/6769134493</v>
       </c>
       <c r="L131" t="str">
-        <v>Let Me Be In Your Arms - Sonny Fodera</v>
+        <v>Eat, Work, Pray - Sheff G</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Eat, Work, Pray</v>
+        <v>touch myself</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
+        <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-23</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Eat, Work, Pray - Single</v>
+        <v>and all pride aside</v>
       </c>
       <c r="G132" t="str">
-        <v>2:28</v>
+        <v>4:09</v>
       </c>
       <c r="H132" t="str">
-        <v>Sheff G</v>
+        <v>kwn</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/eat-work-pray/6769134493</v>
+        <v>https://music.apple.com/us/album/touch-myself/6769880663</v>
       </c>
       <c r="L132" t="str">
-        <v>Eat, Work, Pray - Sheff G</v>
+        <v>touch myself - kwn</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>touch myself</v>
+        <v>Comes and Goes</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
+        <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-23</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>and all pride aside</v>
+        <v>Comes and Goes - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>4:09</v>
+        <v>4:22</v>
       </c>
       <c r="H133" t="str">
-        <v>kwn</v>
+        <v>KETTAMA</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/kettama/1425703970</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/touch-myself/6769880663</v>
+        <v>https://music.apple.com/us/album/comes-and-goes/6766618930</v>
       </c>
       <c r="L133" t="str">
-        <v>touch myself - kwn</v>
+        <v>Comes and Goes - KETTAMA</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Comes and Goes</v>
+        <v>Dear God</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
+        <v>https://music.apple.com/us/song/dear-god/1878237813</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-23</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Comes and Goes - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G134" t="str">
-        <v>4:22</v>
+        <v>6:08</v>
       </c>
       <c r="H134" t="str">
-        <v>KETTAMA</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/kettama/1425703970</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/comes-and-goes/6766618930</v>
+        <v>https://music.apple.com/us/album/dear-god/1878237662</v>
       </c>
       <c r="L134" t="str">
-        <v>Comes and Goes - KETTAMA</v>
+        <v>Dear God - The Pretty Reckless</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Dear God</v>
+        <v>Hexagons</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/dear-god/1878237813</v>
+        <v>https://music.apple.com/us/song/hexagons/1885607736</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-23</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Dear God</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G135" t="str">
-        <v>6:08</v>
+        <v>5:26</v>
       </c>
       <c r="H135" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Muse</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/dear-god/1878237662</v>
+        <v>https://music.apple.com/us/album/hexagons/1885607338</v>
       </c>
       <c r="L135" t="str">
-        <v>Dear God - The Pretty Reckless</v>
+        <v>Hexagons - Muse</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Hexagons</v>
+        <v>Facile-Batiste</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/hexagons/1885607736</v>
+        <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-23</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>The Wow! Signal</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G136" t="str">
-        <v>5:26</v>
+        <v>4:55</v>
       </c>
       <c r="H136" t="str">
-        <v>Muse</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/hexagons/1885607338</v>
+        <v>https://music.apple.com/us/album/facile-batiste/1895866355</v>
       </c>
       <c r="L136" t="str">
-        <v>Hexagons - Muse</v>
+        <v>Facile-Batiste - Jon Batiste</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Facile-Batiste</v>
+        <v>Pop Pop</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
+        <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-23</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Black Mozart</v>
+        <v>Pop Pop - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>4:55</v>
+        <v>2:57</v>
       </c>
       <c r="H137" t="str">
-        <v>Jon Batiste</v>
+        <v>Channel Tres</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/facile-batiste/1895866355</v>
+        <v>https://music.apple.com/us/album/pop-pop/1896269430</v>
       </c>
       <c r="L137" t="str">
-        <v>Facile-Batiste - Jon Batiste</v>
+        <v>Pop Pop - Channel Tres</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Pop Pop</v>
+        <v>One Of Us</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
+        <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-23</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Pop Pop - Single</v>
+        <v>One Of Us - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:57</v>
+        <v>3:35</v>
       </c>
       <c r="H138" t="str">
-        <v>Channel Tres</v>
+        <v>Chris Young</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
+        <v>https://music.apple.com/us/artist/chris-young/4779205</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/pop-pop/1896269430</v>
+        <v>https://music.apple.com/us/album/one-of-us/1895402922</v>
       </c>
       <c r="L138" t="str">
-        <v>Pop Pop - Channel Tres</v>
+        <v>One Of Us - Chris Young</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>One Of Us</v>
+        <v>Sins of the Father</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
+        <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-23</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>One Of Us - Single</v>
+        <v>Is God Is (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G139" t="str">
-        <v>3:35</v>
+        <v>3:20</v>
       </c>
       <c r="H139" t="str">
-        <v>Chris Young</v>
+        <v>Moses Sumney</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/chris-young/4779205</v>
+        <v>https://music.apple.com/us/artist/moses-sumney/843536848</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/one-of-us/1895402922</v>
+        <v>https://music.apple.com/us/album/sins-of-the-father/6771012707</v>
       </c>
       <c r="L139" t="str">
-        <v>One Of Us - Chris Young</v>
+        <v>Sins of the Father - Moses Sumney</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Sins of the Father</v>
+        <v>Life On The Run</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
+        <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-23</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Is God Is (Original Motion Picture Soundtrack)</v>
+        <v>Life On The Run - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:20</v>
+        <v>3:49</v>
       </c>
       <c r="H140" t="str">
-        <v>Moses Sumney</v>
+        <v>Brandi Carlile</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/moses-sumney/843536848</v>
+        <v>https://music.apple.com/us/artist/brandi-carlile/64387579</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/sins-of-the-father/6771012707</v>
+        <v>https://music.apple.com/us/album/life-on-the-run/6766761019</v>
       </c>
       <c r="L140" t="str">
-        <v>Sins of the Father - Moses Sumney</v>
+        <v>Life On The Run - Brandi Carlile</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Life On The Run</v>
+        <v>New York Confident</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
+        <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-23</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Life On The Run - Single</v>
+        <v>New York Confident - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:49</v>
+        <v>2:27</v>
       </c>
       <c r="H141" t="str">
-        <v>Brandi Carlile</v>
+        <v>Mark Ambor</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/brandi-carlile/64387579</v>
+        <v>https://music.apple.com/us/artist/mark-ambor/1459754985</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/life-on-the-run/6766761019</v>
+        <v>https://music.apple.com/us/album/new-york-confident/6765558036</v>
       </c>
       <c r="L141" t="str">
-        <v>Life On The Run - Brandi Carlile</v>
+        <v>New York Confident - Mark Ambor</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>New York Confident</v>
+        <v>pequeñita!</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
+        <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-23</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>New York Confident - Single</v>
+        <v>pequeñita! - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:27</v>
+        <v>2:39</v>
       </c>
       <c r="H142" t="str">
-        <v>Mark Ambor</v>
+        <v>Judeline</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/mark-ambor/1459754985</v>
+        <v>https://music.apple.com/us/artist/judeline/1487503245</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/new-york-confident/6765558036</v>
+        <v>https://music.apple.com/us/album/peque%C3%B1ita/6769827604</v>
       </c>
       <c r="L142" t="str">
-        <v>New York Confident - Mark Ambor</v>
+        <v>pequeñita! - Judeline</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>pequeñita!</v>
+        <v>Opaline</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
+        <v>https://music.apple.com/us/song/opaline/1886737060</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-23</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>pequeñita! - Single</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G143" t="str">
-        <v>2:39</v>
+        <v>3:17</v>
       </c>
       <c r="H143" t="str">
-        <v>Judeline</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/judeline/1487503245</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/peque%C3%B1ita/6769827604</v>
+        <v>https://music.apple.com/us/album/opaline/1886736650</v>
       </c>
       <c r="L143" t="str">
-        <v>pequeñita! - Judeline</v>
+        <v>Opaline - Stephan Moccio</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Opaline</v>
+        <v>Pretty Little Things</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/opaline/1886737060</v>
+        <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-23</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>Pretty Little Things - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:17</v>
+        <v>2:51</v>
       </c>
       <c r="H144" t="str">
-        <v>Stephan Moccio</v>
+        <v>Lauv</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/opaline/1886736650</v>
+        <v>https://music.apple.com/us/album/pretty-little-things/6767353963</v>
       </c>
       <c r="L144" t="str">
-        <v>Opaline - Stephan Moccio</v>
+        <v>Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Pretty Little Things</v>
+        <v>COLORADO</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
+        <v>https://music.apple.com/us/song/colorado/6769065232</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-23</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Pretty Little Things - Single</v>
+        <v>COLORADO - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:51</v>
+        <v>1:54</v>
       </c>
       <c r="H145" t="str">
-        <v>Lauv</v>
+        <v>Loud Luxury</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/pretty-little-things/6767353963</v>
+        <v>https://music.apple.com/us/album/colorado/6769064981</v>
       </c>
       <c r="L145" t="str">
-        <v>Pretty Little Things - Lauv</v>
+        <v>COLORADO - Loud Luxury</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>COLORADO</v>
+        <v>Infidelidad</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/colorado/6769065232</v>
+        <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-23</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>COLORADO - Single</v>
+        <v>El Disco de Salsa</v>
       </c>
       <c r="G146" t="str">
-        <v>1:54</v>
+        <v>3:29</v>
       </c>
       <c r="H146" t="str">
-        <v>Loud Luxury</v>
+        <v>Neutro Shorty</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
+        <v>https://music.apple.com/us/artist/neutro-shorty/1066850977</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/colorado/6769064981</v>
+        <v>https://music.apple.com/us/album/infidelidad/6768853655</v>
       </c>
       <c r="L146" t="str">
-        <v>COLORADO - Loud Luxury</v>
+        <v>Infidelidad - Neutro Shorty</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Infidelidad</v>
+        <v>Wrong Place, Wrong time</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
+        <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-23</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>El Disco de Salsa</v>
+        <v>Y'all Won</v>
       </c>
       <c r="G147" t="str">
-        <v>3:29</v>
+        <v>2:57</v>
       </c>
       <c r="H147" t="str">
-        <v>Neutro Shorty</v>
+        <v>Veeze</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/neutro-shorty/1066850977</v>
+        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/infidelidad/6768853655</v>
+        <v>https://music.apple.com/us/album/wrong-place-wrong-time/6771553812</v>
       </c>
       <c r="L147" t="str">
-        <v>Infidelidad - Neutro Shorty</v>
+        <v>Wrong Place, Wrong time - Veeze</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Wrong Place, Wrong time</v>
+        <v>La Semana</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
+        <v>https://music.apple.com/us/song/la-semana/6769913466</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-23</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Y'all Won</v>
+        <v>No Quiero Que Se Acabe Este Bendito Verano - EP</v>
       </c>
       <c r="G148" t="str">
-        <v>2:57</v>
+        <v>3:30</v>
       </c>
       <c r="H148" t="str">
-        <v>Veeze</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/wrong-place-wrong-time/6771553812</v>
+        <v>https://music.apple.com/us/album/la-semana/6769913464</v>
       </c>
       <c r="L148" t="str">
-        <v>Wrong Place, Wrong time - Veeze</v>
+        <v>La Semana - ELENA ROSE</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>La Semana</v>
+        <v>Una Mujer Como la Suya</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/la-semana/6769913466</v>
+        <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-23</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>No Quiero Que Se Acabe Este Bendito Verano - EP</v>
+        <v>Bandera Blanca</v>
       </c>
       <c r="G149" t="str">
-        <v>3:30</v>
+        <v>3:34</v>
       </c>
       <c r="H149" t="str">
-        <v>ELENA ROSE</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/la-semana/6769913464</v>
+        <v>https://music.apple.com/us/album/una-mujer-como-la-suya/1895154946</v>
       </c>
       <c r="L149" t="str">
-        <v>La Semana - ELENA ROSE</v>
+        <v>Una Mujer Como la Suya - Christian Nodal</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Una Mujer Como la Suya</v>
+        <v>Cold</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
+        <v>https://music.apple.com/us/song/cold/6763763802</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-23</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Bandera Blanca</v>
+        <v>Cold - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:34</v>
+        <v>2:52</v>
       </c>
       <c r="H150" t="str">
-        <v>Christian Nodal</v>
+        <v>Majid Jordan</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/majid-jordan/684530590</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/una-mujer-como-la-suya/1895154946</v>
+        <v>https://music.apple.com/us/album/cold/1895478371</v>
       </c>
       <c r="L150" t="str">
-        <v>Una Mujer Como la Suya - Christian Nodal</v>
+        <v>Cold - Majid Jordan</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Cold</v>
+        <v>VERTICAL WORLDS</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/cold/6763763802</v>
+        <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-23</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Cold - Single</v>
+        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
       </c>
       <c r="G151" t="str">
-        <v>2:52</v>
+        <v>3:15</v>
       </c>
       <c r="H151" t="str">
-        <v>Majid Jordan</v>
+        <v>Ecca Vandal</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/majid-jordan/684530590</v>
+        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/cold/1895478371</v>
+        <v>https://music.apple.com/us/album/vertical-worlds/1886485694</v>
       </c>
       <c r="L151" t="str">
-        <v>Cold - Majid Jordan</v>
+        <v>VERTICAL WORLDS - Ecca Vandal</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>VERTICAL WORLDS</v>
+        <v>Child of Divorce</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
+        <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-23</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
+        <v>soft pop</v>
       </c>
       <c r="G152" t="str">
-        <v>3:15</v>
+        <v>3:24</v>
       </c>
       <c r="H152" t="str">
-        <v>Ecca Vandal</v>
+        <v>Amy Shark</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
+        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/vertical-worlds/1886485694</v>
+        <v>https://music.apple.com/us/album/child-of-divorce/1880496743</v>
       </c>
       <c r="L152" t="str">
-        <v>VERTICAL WORLDS - Ecca Vandal</v>
+        <v>Child of Divorce - Amy Shark</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Child of Divorce</v>
+        <v>Taboo</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
+        <v>https://music.apple.com/us/song/taboo/6762838716</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-23</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>soft pop</v>
+        <v>Taboo - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:24</v>
+        <v>3:38</v>
       </c>
       <c r="H153" t="str">
-        <v>Amy Shark</v>
+        <v>Jensen McRae</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
+        <v>https://music.apple.com/us/artist/jensen-mcrae/591974463</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/child-of-divorce/1880496743</v>
+        <v>https://music.apple.com/us/album/taboo/1895036934</v>
       </c>
       <c r="L153" t="str">
-        <v>Child of Divorce - Amy Shark</v>
+        <v>Taboo - Jensen McRae</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Taboo</v>
+        <v>I'M OK</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/taboo/6762838716</v>
+        <v>https://music.apple.com/us/song/im-ok/1893392647</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-23</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Taboo - Single</v>
+        <v>A Rii Set</v>
       </c>
       <c r="G154" t="str">
-        <v>3:38</v>
+        <v>2:37</v>
       </c>
       <c r="H154" t="str">
-        <v>Jensen McRae</v>
+        <v>Pheelz</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/jensen-mcrae/591974463</v>
+        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/taboo/1895036934</v>
+        <v>https://music.apple.com/us/album/im-ok/1893392643</v>
       </c>
       <c r="L154" t="str">
-        <v>Taboo - Jensen McRae</v>
+        <v>I'M OK - Pheelz</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>I'M OK</v>
+        <v>Butterfly Feelings</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/im-ok/1893392647</v>
+        <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-23</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>A Rii Set</v>
+        <v>Ritual</v>
       </c>
       <c r="G155" t="str">
-        <v>2:37</v>
+        <v>2:35</v>
       </c>
       <c r="H155" t="str">
-        <v>Pheelz</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/im-ok/1893392643</v>
+        <v>https://music.apple.com/us/album/butterfly-feelings/1892426976</v>
       </c>
       <c r="L155" t="str">
-        <v>I'M OK - Pheelz</v>
+        <v>Butterfly Feelings - Icona Pop</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Butterfly Feelings</v>
+        <v>F**k the DJ</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
+        <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-23</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Ritual</v>
+        <v>Stage Girl (Not A Dream Anymore)</v>
       </c>
       <c r="G156" t="str">
-        <v>2:35</v>
+        <v>2:57</v>
       </c>
       <c r="H156" t="str">
-        <v>Icona Pop</v>
+        <v>Eli</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/butterfly-feelings/1892426976</v>
+        <v>https://music.apple.com/us/album/f-k-the-dj/6769903867</v>
       </c>
       <c r="L156" t="str">
-        <v>Butterfly Feelings - Icona Pop</v>
+        <v>F**k the DJ - Eli</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>F**k the DJ</v>
+        <v>Grateful</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
+        <v>https://music.apple.com/us/song/grateful/1887166624</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-23</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Stage Girl (Not A Dream Anymore)</v>
+        <v>24</v>
       </c>
       <c r="G157" t="str">
-        <v>2:57</v>
+        <v>2:18</v>
       </c>
       <c r="H157" t="str">
-        <v>Eli</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/f-k-the-dj/6769903867</v>
+        <v>https://music.apple.com/us/album/grateful/1887166427</v>
       </c>
       <c r="L157" t="str">
-        <v>F**k the DJ - Eli</v>
+        <v>Grateful - Alexis Ffrench</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Grateful</v>
+        <v>Second Chance</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/grateful/1887166624</v>
+        <v>https://music.apple.com/us/song/second-chance/6766778687</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-23</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>24</v>
+        <v>Second Chance - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:18</v>
+        <v>3:06</v>
       </c>
       <c r="H158" t="str">
-        <v>Alexis Ffrench</v>
+        <v>Lukas Graham</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/lukas-graham/473219952</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/grateful/1887166427</v>
+        <v>https://music.apple.com/us/album/second-chance/6766778682</v>
       </c>
       <c r="L158" t="str">
-        <v>Grateful - Alexis Ffrench</v>
+        <v>Second Chance - Lukas Graham</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Second Chance</v>
+        <v>Stupid World (feat. Chad Tepper) [Bonus Track]</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/second-chance/6766778687</v>
+        <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-23</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Second Chance - Single</v>
+        <v>Tommyland Rides Again</v>
       </c>
       <c r="G159" t="str">
-        <v>3:06</v>
+        <v>3:49</v>
       </c>
       <c r="H159" t="str">
-        <v>Lukas Graham</v>
+        <v>Tommy Lee</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/lukas-graham/473219952</v>
+        <v>https://music.apple.com/us/artist/tommy-lee/68696</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/second-chance/6766778682</v>
+        <v>https://music.apple.com/us/album/stupid-world-feat-chad-tepper-bonus-track/1893473875</v>
       </c>
       <c r="L159" t="str">
-        <v>Second Chance - Lukas Graham</v>
+        <v>Stupid World (feat. Chad Tepper) [Bonus Track] - Tommy Lee</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Stupid World (feat. Chad Tepper) [Bonus Track]</v>
+        <v>DOOM LOOP</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
+        <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-23</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Tommyland Rides Again</v>
+        <v>Blood Of Your Empire</v>
       </c>
       <c r="G160" t="str">
-        <v>3:49</v>
+        <v>4:00</v>
       </c>
       <c r="H160" t="str">
-        <v>Tommy Lee</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/tommy-lee/68696</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/stupid-world-feat-chad-tepper-bonus-track/1893473875</v>
+        <v>https://music.apple.com/us/album/doom-loop/6769905842</v>
       </c>
       <c r="L160" t="str">
-        <v>Stupid World (feat. Chad Tepper) [Bonus Track] - Tommy Lee</v>
+        <v>DOOM LOOP - PRESIDENT</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>DOOM LOOP</v>
+        <v>New York City</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
+        <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-23</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Blood Of Your Empire</v>
+        <v>New York City - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>4:00</v>
+        <v>3:30</v>
       </c>
       <c r="H161" t="str">
-        <v>PRESIDENT</v>
+        <v>Anthony Ramos</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/anthony-ramos/1313064678</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/doom-loop/6769905842</v>
+        <v>https://music.apple.com/us/album/new-york-city/6770624324</v>
       </c>
       <c r="L161" t="str">
-        <v>DOOM LOOP - PRESIDENT</v>
+        <v>New York City - Anthony Ramos</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>New York City</v>
+        <v>I Found You</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
+        <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-23</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>New York City - Single</v>
+        <v>I Found You - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:30</v>
+        <v>3:18</v>
       </c>
       <c r="H162" t="str">
-        <v>Anthony Ramos</v>
+        <v>TA Thomas</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/anthony-ramos/1313064678</v>
+        <v>https://music.apple.com/us/artist/ta-thomas/1232189106</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/new-york-city/6770624324</v>
+        <v>https://music.apple.com/us/album/i-found-you/1894024530</v>
       </c>
       <c r="L162" t="str">
-        <v>New York City - Anthony Ramos</v>
+        <v>I Found You - TA Thomas</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>I Found You</v>
+        <v>Just My Type</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
+        <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-23</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>I Found You - Single</v>
+        <v>Labor Of Love</v>
       </c>
       <c r="G163" t="str">
-        <v>3:18</v>
+        <v>2:40</v>
       </c>
       <c r="H163" t="str">
-        <v>TA Thomas</v>
+        <v>Blxst</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/ta-thomas/1232189106</v>
+        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/i-found-you/1894024530</v>
+        <v>https://music.apple.com/us/album/just-my-type/1895199881</v>
       </c>
       <c r="L163" t="str">
-        <v>I Found You - TA Thomas</v>
+        <v>Just My Type - Blxst</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Just My Type</v>
+        <v>teenage drama</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
+        <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-23</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Labor Of Love</v>
+        <v>teenage drama - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:40</v>
+        <v>3:06</v>
       </c>
       <c r="H164" t="str">
-        <v>Blxst</v>
+        <v>paris jackson</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/just-my-type/1895199881</v>
+        <v>https://music.apple.com/us/album/teenage-drama/6768447515</v>
       </c>
       <c r="L164" t="str">
-        <v>Just My Type - Blxst</v>
+        <v>teenage drama - paris jackson</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>teenage drama</v>
+        <v>does it still mean something?</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
+        <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-23</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>teenage drama - Single</v>
+        <v>only if it matters</v>
       </c>
       <c r="G165" t="str">
-        <v>3:06</v>
+        <v>3:48</v>
       </c>
       <c r="H165" t="str">
-        <v>paris jackson</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/teenage-drama/6768447515</v>
+        <v>https://music.apple.com/us/album/does-it-still-mean-something/6768446154</v>
       </c>
       <c r="L165" t="str">
-        <v>teenage drama - paris jackson</v>
+        <v>does it still mean something? - Kevian Kraemer</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>does it still mean something?</v>
+        <v>Debbie Don't Cry</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
+        <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-23</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>only if it matters</v>
+        <v>Debbie Don't Cry - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:48</v>
+        <v>3:00</v>
       </c>
       <c r="H166" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Ruel</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/does-it-still-mean-something/6768446154</v>
+        <v>https://music.apple.com/us/album/debbie-dont-cry/6768206616</v>
       </c>
       <c r="L166" t="str">
-        <v>does it still mean something? - Kevian Kraemer</v>
+        <v>Debbie Don't Cry - Ruel</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Debbie Don't Cry</v>
+        <v>YEAH YEAH YEAH</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
+        <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-23</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Debbie Don't Cry - Single</v>
+        <v>YEAH YEAH YEAH - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:00</v>
+        <v>2:25</v>
       </c>
       <c r="H167" t="str">
-        <v>Ruel</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/debbie-dont-cry/6768206616</v>
+        <v>https://music.apple.com/us/album/yeah-yeah-yeah/6767515610</v>
       </c>
       <c r="L167" t="str">
-        <v>Debbie Don't Cry - Ruel</v>
+        <v>YEAH YEAH YEAH - Cruz Beckham</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>YEAH YEAH YEAH</v>
+        <v>Cotton Flower</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
+        <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-23</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>YEAH YEAH YEAH - Single</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G168" t="str">
-        <v>2:25</v>
+        <v>3:53</v>
       </c>
       <c r="H168" t="str">
-        <v>Cruz Beckham</v>
+        <v>Future Islands</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/yeah-yeah-yeah/6767515610</v>
+        <v>https://music.apple.com/us/album/cotton-flower/1883045480</v>
       </c>
       <c r="L168" t="str">
-        <v>YEAH YEAH YEAH - Cruz Beckham</v>
+        <v>Cotton Flower - Future Islands</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Cotton Flower</v>
+        <v>WAHALA RIDDIM</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
+        <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-23</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>WAHALA RIDDIM - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:53</v>
+        <v>3:22</v>
       </c>
       <c r="H169" t="str">
-        <v>Future Islands</v>
+        <v>THEHONESTGUY</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/cotton-flower/1883045480</v>
+        <v>https://music.apple.com/us/album/wahala-riddim/1895810537</v>
       </c>
       <c r="L169" t="str">
-        <v>Cotton Flower - Future Islands</v>
+        <v>WAHALA RIDDIM - THEHONESTGUY</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>WAHALA RIDDIM</v>
+        <v>Comfort</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
+        <v>https://music.apple.com/us/song/comfort/1876521401</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-23</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>WAHALA RIDDIM - Single</v>
+        <v>So Help Me God</v>
       </c>
       <c r="G170" t="str">
-        <v>3:22</v>
+        <v>5:35</v>
       </c>
       <c r="H170" t="str">
-        <v>THEHONESTGUY</v>
+        <v>Kelsey Lu</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
+        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/wahala-riddim/1895810537</v>
+        <v>https://music.apple.com/us/album/comfort/1876521144</v>
       </c>
       <c r="L170" t="str">
-        <v>WAHALA RIDDIM - THEHONESTGUY</v>
+        <v>Comfort - Kelsey Lu</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Comfort</v>
+        <v>Skin</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/comfort/1876521401</v>
+        <v>https://music.apple.com/us/song/skin/6764651585</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-23</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>So Help Me God</v>
+        <v>Skin - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>5:35</v>
+        <v>3:00</v>
       </c>
       <c r="H171" t="str">
-        <v>Kelsey Lu</v>
+        <v>Alessi Rose</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
+        <v>https://music.apple.com/us/artist/alessi-rose/1628689028</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/comfort/1876521144</v>
+        <v>https://music.apple.com/us/album/skin/1895865252</v>
       </c>
       <c r="L171" t="str">
-        <v>Comfort - Kelsey Lu</v>
+        <v>Skin - Alessi Rose</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Skin</v>
+        <v>IDGAF</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/skin/6764651585</v>
+        <v>https://music.apple.com/us/song/idgaf/6764422210</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-23</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Skin - Single</v>
+        <v>IDGAF - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:00</v>
+        <v>2:55</v>
       </c>
       <c r="H172" t="str">
-        <v>Alessi Rose</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/alessi-rose/1628689028</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/skin/1895865252</v>
+        <v>https://music.apple.com/us/album/idgaf/1895773358</v>
       </c>
       <c r="L172" t="str">
-        <v>Skin - Alessi Rose</v>
+        <v>IDGAF - Katelyn Tarver</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>IDGAF</v>
+        <v>Run Rabbit</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/idgaf/6764422210</v>
+        <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-23</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>IDGAF - Single</v>
+        <v>Run Rabbit - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:55</v>
+        <v>3:09</v>
       </c>
       <c r="H173" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Mollie Elizabeth</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/mollie-elizabeth/1780515318</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/idgaf/1895773358</v>
+        <v>https://music.apple.com/us/album/run-rabbit/6767354664</v>
       </c>
       <c r="L173" t="str">
-        <v>IDGAF - Katelyn Tarver</v>
+        <v>Run Rabbit - Mollie Elizabeth</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Run Rabbit</v>
+        <v>So Good (feat. Kuuda)</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
+        <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-23</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Run Rabbit - Single</v>
+        <v>So Good (feat. Kuuda) - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:09</v>
+        <v>3:03</v>
       </c>
       <c r="H174" t="str">
-        <v>Mollie Elizabeth</v>
+        <v>CamelPhat</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/mollie-elizabeth/1780515318</v>
+        <v>https://music.apple.com/us/artist/camelphat/385810888</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/run-rabbit/6767354664</v>
+        <v>https://music.apple.com/us/album/so-good-feat-kuuda/6766655768</v>
       </c>
       <c r="L174" t="str">
-        <v>Run Rabbit - Mollie Elizabeth</v>
+        <v>So Good (feat. Kuuda) - CamelPhat</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>So Good (feat. Kuuda)</v>
+        <v>Empty Theatre, Pretty Picture</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
+        <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-23</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>So Good (feat. Kuuda) - Single</v>
+        <v>Empty Theatre, Pretty Picture</v>
       </c>
       <c r="G175" t="str">
-        <v>3:03</v>
+        <v>5:01</v>
       </c>
       <c r="H175" t="str">
-        <v>CamelPhat</v>
+        <v>Lane 8</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/camelphat/385810888</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/so-good-feat-kuuda/6766655768</v>
+        <v>https://music.apple.com/us/album/empty-theatre-pretty-picture/1895395993</v>
       </c>
       <c r="L175" t="str">
-        <v>So Good (feat. Kuuda) - CamelPhat</v>
+        <v>Empty Theatre, Pretty Picture - Lane 8</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Empty Theatre, Pretty Picture</v>
+        <v>regalametutiempo</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
+        <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-23</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Empty Theatre, Pretty Picture</v>
+        <v>PROYECTANDO</v>
       </c>
       <c r="G176" t="str">
-        <v>5:01</v>
+        <v>3:01</v>
       </c>
       <c r="H176" t="str">
-        <v>Lane 8</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/empty-theatre-pretty-picture/1895395993</v>
+        <v>https://music.apple.com/us/album/regalametutiempo/6769922866</v>
       </c>
       <c r="L176" t="str">
-        <v>Empty Theatre, Pretty Picture - Lane 8</v>
+        <v>regalametutiempo - Julio Caesar</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>regalametutiempo</v>
+        <v>On Sight</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
+        <v>https://music.apple.com/us/song/on-sight/6763971220</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-23</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>PROYECTANDO</v>
+        <v>Left on RED</v>
       </c>
       <c r="G177" t="str">
-        <v>3:01</v>
+        <v>2:25</v>
       </c>
       <c r="H177" t="str">
-        <v>Julio Caesar</v>
+        <v>REMI</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/remi/1716510008</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/regalametutiempo/6769922866</v>
+        <v>https://music.apple.com/us/album/on-sight/1895580736</v>
       </c>
       <c r="L177" t="str">
-        <v>regalametutiempo - Julio Caesar</v>
+        <v>On Sight - REMI</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>On Sight</v>
+        <v>Masks Off</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/on-sight/6763971220</v>
+        <v>https://music.apple.com/us/song/masks-off/6764077133</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-23</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Left on RED</v>
+        <v>Masks Off - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:25</v>
+        <v>3:24</v>
       </c>
       <c r="H178" t="str">
-        <v>REMI</v>
+        <v>Jesse Welles</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/remi/1716510008</v>
+        <v>https://music.apple.com/us/artist/jesse-welles/1737507146</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/on-sight/1895580736</v>
+        <v>https://music.apple.com/us/album/masks-off/1895628310</v>
       </c>
       <c r="L178" t="str">
-        <v>On Sight - REMI</v>
+        <v>Masks Off - Jesse Welles</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Masks Off</v>
+        <v>I'm Just A Girl</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/masks-off/6764077133</v>
+        <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-23</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Masks Off - Single</v>
+        <v>Di Hotel Malibu</v>
       </c>
       <c r="G179" t="str">
-        <v>3:24</v>
+        <v>2:49</v>
       </c>
       <c r="H179" t="str">
-        <v>Jesse Welles</v>
+        <v>Thee Marloes</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/jesse-welles/1737507146</v>
+        <v>https://music.apple.com/us/artist/thee-marloes/1541376632</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/masks-off/1895628310</v>
+        <v>https://music.apple.com/us/album/im-just-a-girl/1878399768</v>
       </c>
       <c r="L179" t="str">
-        <v>Masks Off - Jesse Welles</v>
+        <v>I'm Just A Girl - Thee Marloes</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>I'm Just A Girl</v>
+        <v>Soleil (feat. Isabella Lovestory)</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
+        <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-23</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Di Hotel Malibu</v>
+        <v>EXIT 2B</v>
       </c>
       <c r="G180" t="str">
-        <v>2:49</v>
+        <v>2:11</v>
       </c>
       <c r="H180" t="str">
-        <v>Thee Marloes</v>
+        <v>B0YG1RL</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/thee-marloes/1541376632</v>
+        <v>https://music.apple.com/us/artist/b0yg1rl/1847766665</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/im-just-a-girl/1878399768</v>
+        <v>https://music.apple.com/us/album/soleil-feat-isabella-lovestory/6769526101</v>
       </c>
       <c r="L180" t="str">
-        <v>I'm Just A Girl - Thee Marloes</v>
+        <v>Soleil (feat. Isabella Lovestory) - B0YG1RL</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Soleil (feat. Isabella Lovestory)</v>
+        <v>Money Tree</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
+        <v>https://music.apple.com/us/song/money-tree/6763211637</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-23</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>EXIT 2B</v>
+        <v>Money Tree - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:11</v>
+        <v>2:39</v>
       </c>
       <c r="H181" t="str">
-        <v>B0YG1RL</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/b0yg1rl/1847766665</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/soleil-feat-isabella-lovestory/6769526101</v>
+        <v>https://music.apple.com/us/album/money-tree/1895216986</v>
       </c>
       <c r="L181" t="str">
-        <v>Soleil (feat. Isabella Lovestory) - B0YG1RL</v>
+        <v>Money Tree - Olympia Vitalis</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Money Tree</v>
+        <v>Homerunner</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/money-tree/6763211637</v>
+        <v>https://music.apple.com/us/song/homerunner/6770682178</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-23</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Money Tree - Single</v>
+        <v>Homerunner - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:39</v>
+        <v>2:36</v>
       </c>
       <c r="H182" t="str">
-        <v>Olympia Vitalis</v>
+        <v>slayr</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/money-tree/1895216986</v>
+        <v>https://music.apple.com/us/album/homerunner/6770682177</v>
       </c>
       <c r="L182" t="str">
-        <v>Money Tree - Olympia Vitalis</v>
+        <v>Homerunner - slayr</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Homerunner</v>
+        <v>Mail</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/homerunner/6770682178</v>
+        <v>https://music.apple.com/us/song/mail/6769190635</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-23</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Homerunner - Single</v>
+        <v>Mail - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:36</v>
+        <v>2:14</v>
       </c>
       <c r="H183" t="str">
-        <v>slayr</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/homerunner/6770682177</v>
+        <v>https://music.apple.com/us/album/mail/6769190634</v>
       </c>
       <c r="L183" t="str">
-        <v>Homerunner - slayr</v>
+        <v>Mail - MexikoDro</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Mail</v>
+        <v>Waste Your Heart</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/mail/6769190635</v>
+        <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-23</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Mail - Single</v>
+        <v>Waste Your Heart - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:14</v>
+        <v>2:31</v>
       </c>
       <c r="H184" t="str">
-        <v>MexikoDro</v>
+        <v>Magnus Ferrell</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/mail/6769190634</v>
+        <v>https://music.apple.com/us/album/waste-your-heart/6769241913</v>
       </c>
       <c r="L184" t="str">
-        <v>Mail - MexikoDro</v>
+        <v>Waste Your Heart - Magnus Ferrell</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Waste Your Heart</v>
+        <v>Sleeping Pills</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
+        <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-23</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Waste Your Heart - Single</v>
+        <v>Sleeping Pills - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:31</v>
+        <v>3:03</v>
       </c>
       <c r="H185" t="str">
-        <v>Magnus Ferrell</v>
+        <v>Dolder</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
+        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/waste-your-heart/6769241913</v>
+        <v>https://music.apple.com/us/album/sleeping-pills/1896452689</v>
       </c>
       <c r="L185" t="str">
-        <v>Waste Your Heart - Magnus Ferrell</v>
+        <v>Sleeping Pills - Dolder</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Sleeping Pills</v>
+        <v>KODACHROMATIC</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
+        <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-23</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Sleeping Pills - Single</v>
+        <v>KODACHROMATIC - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:03</v>
+        <v>2:53</v>
       </c>
       <c r="H186" t="str">
-        <v>Dolder</v>
+        <v>Tiger La Flor</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
+        <v>https://music.apple.com/us/artist/tiger-la-flor/1613113982</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/sleeping-pills/1896452689</v>
+        <v>https://music.apple.com/us/album/kodachromatic/6770724719</v>
       </c>
       <c r="L186" t="str">
-        <v>Sleeping Pills - Dolder</v>
+        <v>KODACHROMATIC - Tiger La Flor</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>KODACHROMATIC</v>
+        <v>FOMO</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
+        <v>https://music.apple.com/us/song/fomo/1890190631</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-23</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>KODACHROMATIC - Single</v>
+        <v>Map Of Her Shadow</v>
       </c>
       <c r="G187" t="str">
-        <v>2:53</v>
+        <v>3:01</v>
       </c>
       <c r="H187" t="str">
-        <v>Tiger La Flor</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/tiger-la-flor/1613113982</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/kodachromatic/6770724719</v>
+        <v>https://music.apple.com/us/album/fomo/1890190623</v>
       </c>
       <c r="L187" t="str">
-        <v>KODACHROMATIC - Tiger La Flor</v>
+        <v>FOMO - Anais Cardot</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>FOMO</v>
+        <v>Black Fire</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/fomo/1890190631</v>
+        <v>https://music.apple.com/us/song/black-fire/6770696877</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-23</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Map Of Her Shadow</v>
+        <v>Sulfur Surfer</v>
       </c>
       <c r="G188" t="str">
-        <v>3:01</v>
+        <v>3:37</v>
       </c>
       <c r="H188" t="str">
-        <v>Anais Cardot</v>
+        <v>Bladee</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/bladee/861359576</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/fomo/1890190623</v>
+        <v>https://music.apple.com/us/album/black-fire/6770696743</v>
       </c>
       <c r="L188" t="str">
-        <v>FOMO - Anais Cardot</v>
+        <v>Black Fire - Bladee</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Black Fire</v>
+        <v>As Seen in the Unseen</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/black-fire/6770696877</v>
+        <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-23</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Sulfur Surfer</v>
+        <v>Grand Serpent Rising</v>
       </c>
       <c r="G189" t="str">
-        <v>3:37</v>
+        <v>6:59</v>
       </c>
       <c r="H189" t="str">
-        <v>Bladee</v>
+        <v>Dimmu Borgir</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/bladee/861359576</v>
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/black-fire/6770696743</v>
+        <v>https://music.apple.com/us/album/as-seen-in-the-unseen/1883121436</v>
       </c>
       <c r="L189" t="str">
-        <v>Black Fire - Bladee</v>
+        <v>As Seen in the Unseen - Dimmu Borgir</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>As Seen in the Unseen</v>
+        <v>Every Man-Any Man</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
+        <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-23</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Grand Serpent Rising</v>
+        <v>Emotion Factory Reset</v>
       </c>
       <c r="G190" t="str">
-        <v>6:59</v>
+        <v>4:20</v>
       </c>
       <c r="H190" t="str">
-        <v>Dimmu Borgir</v>
+        <v>Armored Saint</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/as-seen-in-the-unseen/1883121436</v>
+        <v>https://music.apple.com/us/album/every-man-any-man/1872193859</v>
       </c>
       <c r="L190" t="str">
-        <v>As Seen in the Unseen - Dimmu Borgir</v>
+        <v>Every Man-Any Man - Armored Saint</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Every Man-Any Man</v>
+        <v>No Arms</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
+        <v>https://music.apple.com/us/song/no-arms/6765776563</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-23</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Emotion Factory Reset</v>
+        <v>From A Distance</v>
       </c>
       <c r="G191" t="str">
-        <v>4:20</v>
+        <v>3:43</v>
       </c>
       <c r="H191" t="str">
-        <v>Armored Saint</v>
+        <v>156/Silence</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
+        <v>https://music.apple.com/us/artist/156-silence/1071395282</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/every-man-any-man/1872193859</v>
+        <v>https://music.apple.com/us/album/no-arms/1896069437</v>
       </c>
       <c r="L191" t="str">
-        <v>Every Man-Any Man - Armored Saint</v>
+        <v>No Arms - 156/Silence</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>No Arms</v>
+        <v>It's Neverending</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/no-arms/6765776563</v>
+        <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-23</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>From A Distance</v>
+        <v>Neverending</v>
       </c>
       <c r="G192" t="str">
-        <v>3:43</v>
+        <v>8:35</v>
       </c>
       <c r="H192" t="str">
-        <v>156/Silence</v>
+        <v>Monolord</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/156-silence/1071395282</v>
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/no-arms/1896069437</v>
+        <v>https://music.apple.com/us/album/its-neverending/1871211801</v>
       </c>
       <c r="L192" t="str">
-        <v>No Arms - 156/Silence</v>
+        <v>It's Neverending - Monolord</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>It's Neverending</v>
+        <v>The Kids Will Kill Us</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
+        <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-23</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Neverending</v>
+        <v>The Kids Will Kill Us - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>8:35</v>
+        <v>3:45</v>
       </c>
       <c r="H193" t="str">
-        <v>Monolord</v>
+        <v>Witch Club Satan</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+        <v>https://music.apple.com/us/artist/witch-club-satan/1626477576</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/its-neverending/1871211801</v>
+        <v>https://music.apple.com/us/album/the-kids-will-kill-us/6766343272</v>
       </c>
       <c r="L193" t="str">
-        <v>It's Neverending - Monolord</v>
+        <v>The Kids Will Kill Us - Witch Club Satan</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>The Kids Will Kill Us</v>
+        <v>Masters of the Universe (from "Masters of the Universe")</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
+        <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-23</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>The Kids Will Kill Us - Single</v>
+        <v>Masters of the Universe (from "Masters of the Universe") - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:45</v>
+        <v>3:20</v>
       </c>
       <c r="H194" t="str">
-        <v>Witch Club Satan</v>
+        <v>The Darkness</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/witch-club-satan/1626477576</v>
+        <v>https://music.apple.com/us/artist/the-darkness/2417388</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/the-kids-will-kill-us/6766343272</v>
+        <v>https://music.apple.com/us/album/masters-of-the-universe-from-masters-of-the-universe/6769065779</v>
       </c>
       <c r="L194" t="str">
-        <v>The Kids Will Kill Us - Witch Club Satan</v>
+        <v>Masters of the Universe (from "Masters of the Universe") - The Darkness</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe")</v>
+        <v>All Day</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
+        <v>https://music.apple.com/us/song/all-day/1880746584</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-23</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe") - Single</v>
+        <v>Feet On Fire</v>
       </c>
       <c r="G195" t="str">
-        <v>3:20</v>
+        <v>2:29</v>
       </c>
       <c r="H195" t="str">
-        <v>The Darkness</v>
+        <v>Ben Chapman</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/the-darkness/2417388</v>
+        <v>https://music.apple.com/us/artist/ben-chapman/1581192612</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/masters-of-the-universe-from-masters-of-the-universe/6769065779</v>
+        <v>https://music.apple.com/us/album/all-day/1880746349</v>
       </c>
       <c r="L195" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe") - The Darkness</v>
+        <v>All Day - Ben Chapman</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>All Day</v>
+        <v>Sigui</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/all-day/1880746584</v>
+        <v>https://music.apple.com/us/song/sigui/1890241955</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-23</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Feet On Fire</v>
+        <v>Massa</v>
       </c>
       <c r="G196" t="str">
-        <v>2:29</v>
+        <v>3:17</v>
       </c>
       <c r="H196" t="str">
-        <v>Ben Chapman</v>
+        <v>Fatoumata Diawara</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/ben-chapman/1581192612</v>
+        <v>https://music.apple.com/us/artist/fatoumata-diawara/466213610</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/all-day/1880746349</v>
+        <v>https://music.apple.com/us/album/sigui/1890241617</v>
       </c>
       <c r="L196" t="str">
-        <v>All Day - Ben Chapman</v>
+        <v>Sigui - Fatoumata Diawara</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Sigui</v>
+        <v>High Tail</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/sigui/1890241955</v>
+        <v>https://music.apple.com/us/song/high-tail/1870432994</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-23</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Massa</v>
+        <v>Where the South Winds Wail</v>
       </c>
       <c r="G197" t="str">
-        <v>3:17</v>
+        <v>2:31</v>
       </c>
       <c r="H197" t="str">
-        <v>Fatoumata Diawara</v>
+        <v>Gitkin</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/fatoumata-diawara/466213610</v>
+        <v>https://music.apple.com/us/artist/gitkin/1345281815</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/sigui/1890241617</v>
+        <v>https://music.apple.com/us/album/high-tail/1870432670</v>
       </c>
       <c r="L197" t="str">
-        <v>Sigui - Fatoumata Diawara</v>
+        <v>High Tail - Gitkin</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>High Tail</v>
+        <v>Mice Protection</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/high-tail/1870432994</v>
+        <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-23</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Where the South Winds Wail</v>
+        <v>Ugly Duckling Union</v>
       </c>
       <c r="G198" t="str">
-        <v>2:31</v>
+        <v>3:34</v>
       </c>
       <c r="H198" t="str">
-        <v>Gitkin</v>
+        <v>Lowertown</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/gitkin/1345281815</v>
+        <v>https://music.apple.com/us/artist/lowertown/1448207323</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/high-tail/1870432670</v>
+        <v>https://music.apple.com/us/album/mice-protection/1872171971</v>
       </c>
       <c r="L198" t="str">
-        <v>High Tail - Gitkin</v>
+        <v>Mice Protection - Lowertown</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Mice Protection</v>
+        <v>Tóxica</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
+        <v>https://music.apple.com/us/song/t%C3%B3xica/6763056240</v>
       </c>
       <c r="D199" t="str">
         <v>2026-05-23</v>
@@ -7937,68 +7937,30 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Ugly Duckling Union</v>
+        <v>Caribenya</v>
       </c>
       <c r="G199" t="str">
-        <v>3:34</v>
+        <v>3:48</v>
       </c>
       <c r="H199" t="str">
-        <v>Lowertown</v>
+        <v>Lido Pimienta</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/lowertown/1448207323</v>
+        <v>https://music.apple.com/us/artist/lido-pimienta/389475023</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/mice-protection/1872171971</v>
+        <v>https://music.apple.com/us/album/t%C3%B3xica/1895141218</v>
       </c>
       <c r="L199" t="str">
-        <v>Mice Protection - Lowertown</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>Tóxica</v>
-      </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/t%C3%B3xica/6763056240</v>
-      </c>
-      <c r="D200" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
-        <v>Caribenya</v>
-      </c>
-      <c r="G200" t="str">
-        <v>3:48</v>
-      </c>
-      <c r="H200" t="str">
-        <v>Lido Pimienta</v>
-      </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/lido-pimienta/389475023</v>
-      </c>
-      <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/t%C3%B3xica/1895141218</v>
-      </c>
-      <c r="L200" t="str">
         <v>Tóxica - Lido Pimienta</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week04/titles.xlsx
+++ b/data/global/2026-05-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-23</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Dean Lewis</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Nico Santos - Optimist</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-23</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Nico Santos - Optimist - Nico Santos</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-23</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Niall Horan</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-23</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Will Linley</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-23</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>RUEL</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-23</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>TINI</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-23</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Charli xcx</v>
+        <v>The Offspring</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-23</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Dua Lipa</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-23</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Matilda Mann</v>
+        <v>Scorpions</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-23</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Ella Langley</v>
+        <v>Brandon Lake</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-23</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Kygo and Dan Tyminski</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-23</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>kesha</v>
+        <v>The Warning</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>The Warning - Ego (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-23</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Holly Humberstone</v>
+        <v>paris jackson</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B15" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-23</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Foo Fighters</v>
+        <v>Minelli</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-23</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>The Analogues</v>
+        <v>Maggie Rose</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B17" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-23</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Rod Stewart</v>
+        <v>David Guetta</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
+        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-23</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Blue October</v>
+        <v>Chris Young and Shaylen</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Far Caspian - hum (Official Video)</v>
+        <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B19" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
+        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-23</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Far Caspian</v>
+        <v>Lauv</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
+        <v>Lauv - Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Kenia Os - Love Bombing</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
+        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-23</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Kenia Os</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Kenia Os - Love Bombing - Kenia Os</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
+        <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
+        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-23</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
+        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-23</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B23" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-23</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-23</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-23</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-23</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>RUEL</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-23</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>TINI</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-23</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Evanescence</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B29" t="str">
-        <v>10 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-23</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>10 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-23</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Armin van Buuren</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B31" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-23</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Madison Cunningham</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-23</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Johnny Orlando</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-23</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Carver Jones</v>
+        <v>kesha</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-23</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Jazmin bean</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-23</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Baby Queen</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-23</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Switchfoot</v>
+        <v>The Analogues</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B37" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-23</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Grace Potter</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-23</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Blue October</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-23</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>The All-American Rejects</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B40" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-23</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Henry Moodie</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>Kenia Os - Love Bombing - Kenia Os</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B41" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-23</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Spacey Jane</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B42" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-23</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Megan Moroney</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B43" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-23</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Matt Hansen</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B44" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-23</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Matt Hansen</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Keith Urban - Steal Away (Visualizer)</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-23</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Keith Urban</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>VALÉ - Mugshot (Official Video)</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-23</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>VALÉ</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio)</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-23</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Mackenzie Carpenter</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-23</v>
@@ -2205,7 +2205,7 @@
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Towa Bird</v>
+        <v>Evanescence</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-23</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Sabrina Sterling</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B50" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-23</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Little Big Town</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Becky G - EPA (Official Video)</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-23</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Becky G</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Becky G - EPA (Official Video) - Becky G</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-23</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Daisy the Great</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Towa Bird - Dog (Official Music Video)</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-23</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Towa Bird</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-23</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Madonna</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-23</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Ally Salort</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Bella White - Better - Official Music Video</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B56" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-23</v>
@@ -2509,7 +2509,7 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Bella White</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Bella White - Better - Official Music Video - Bella White</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B57" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-23</v>
@@ -2547,7 +2547,7 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B58" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-23</v>
@@ -2585,7 +2585,7 @@
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Towa Bird</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-23</v>
@@ -2623,7 +2623,7 @@
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Miranda Lambert</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B60" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-23</v>
@@ -2661,7 +2661,7 @@
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Lady Gaga</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-23</v>
@@ -2699,7 +2699,7 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Gracie Abrams</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B62" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-23</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B63" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-23</v>
@@ -2775,7 +2775,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Martin Garrix</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Jorja Smith - What's Done Is Done</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B64" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
+        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-23</v>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Jorja Smith</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>LP - Shelly (Official Music Video)</v>
+        <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
+        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-23</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>LP</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>LP - Shelly (Official Music Video) - LP</v>
+        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
+        <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
+        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-23</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>The Rolling Stones</v>
+        <v>VALÉ</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
+        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
+        <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
+        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-23</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Oasis</v>
+        <v>Mackenzie Carpenter</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
+        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
+        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-23</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Breaking Benjamin</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B69" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
+        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-23</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>VictorBiliac</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
+        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-23</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Linkin Park</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Harry Styles - Dance No More (Official Video)</v>
+        <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
+        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-23</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Harry Styles</v>
+        <v>Becky G</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
+        <v>Becky G - EPA (Official Video) - Becky G</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
+        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-23</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Eagles</v>
+        <v>Daisy the Great</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
+        <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
+        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-23</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Nora Fatehi</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
+        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B74" t="str">
-        <v>2 months ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
+        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-23</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 months ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Madonna</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
+        <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>2 months ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
+        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-23</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 months ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Eurovision Song Contest and Alis</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
+        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
+        <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B76" t="str">
-        <v>2 months ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
+        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-23</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 months ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Bella White</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Bella White - Better - Official Music Video - Bella White</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video)</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
+        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-23</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>The Head And The Heart</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
+        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-23</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Simply Red</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video)</v>
+        <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B79" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
+        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-23</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Talking Heads</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
+        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Ellise - Liplock (Official Music Video)</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
+        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-23</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Ellise</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Tori Kelly - Dive (Official Music Video)</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
+        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-23</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Tori Kelly</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
+        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-23</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>David Gilmour</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
+        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-23</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Scorpions</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
+        <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
+        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-23</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Claire Leslie</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
+        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Michael Schulte - Lovesick (Official Video)</v>
+        <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
+        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-23</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Michael Schulte</v>
+        <v>LP</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
+        <v>LP - Shelly (Official Music Video) - LP</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Caity Baser - Holiday Song (Official Video)</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
+        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-23</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Caity Baser</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
+        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-23</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Sam Fischer</v>
+        <v>Oasis</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Porches- HABIT (Official Video)</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
+        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-23</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Porches</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Porches- HABIT (Official Video) - Porches</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Charli xcx - Rock Music (Official Video)</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
+        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-23</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Charli xcx</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Jon Batiste - Alla Blues (Audio)</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
+        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-23</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Jon Batiste</v>
+        <v>Linkin Park</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
+        <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
+        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-23</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Tigirlily Gold</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
+        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
+        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-23</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Eagles</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
+        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-23</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Bruno Mars</v>
+        <v>Nora Fatehi</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Tori Kelly - Control (Official Visualizer)</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
+        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-23</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Tori Kelly</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
+        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-23</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>bea miller</v>
+        <v>Eurovision Song Contest and Alis</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
+        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-23</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>The Chainsmokers</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Madison Beer - free (Official Audio)</v>
+        <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
+        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-23</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Madison Beer</v>
+        <v>The Head And The Heart</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
+        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Tori Kelly - Dive (Official Audio)</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
+        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-23</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Tori Kelly</v>
+        <v>Simply Red</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio)</v>
+        <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
+        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-23</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Talking Heads</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
+        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
+        <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
+        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-23</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>The Chainsmokers</v>
+        <v>Ellise</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
+        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Ashley Cooke - high school sweetheart</v>
+        <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
+        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-23</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Ashley Cooke</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
+        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
       </c>
     </row>
     <row r="102">

--- a/data/global/2026-05-week04/titles.xlsx
+++ b/data/global/2026-05-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Nico Santos - Optimist</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B4" t="str">
-        <v>2 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B5" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B8" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B9" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B10" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B55" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>

--- a/data/global/2026-05-week04/titles.xlsx
+++ b/data/global/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L202"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
+        <v>שמעון בניטה - אכאב בשקט קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>20 hours ago</v>
+        <v>2026-05-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410989&amp;sid=343b179fe8bb09f870415378e128ebb7</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-23</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20 hours ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Duran Duran</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
+        <v>שמעון בניטה - אכאב בשקט קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Nico Santos - Optimist</v>
+        <v>רונן לוגסי - אבא יקר קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>3 days ago</v>
+        <v>2026-05-23</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410988&amp;sid=343b179fe8bb09f870415378e128ebb7</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-23</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Nico Santos</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Nico Santos - Optimist - Nico Santos</v>
+        <v>רונן לוגסי - אבא יקר קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
+        <v>קורל אמויאל - עכשיו אתה חוזר בחזרה קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>3 hours ago</v>
+        <v>2026-05-23</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410987&amp;sid=343b179fe8bb09f870415378e128ebb7</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-23</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>3 hours ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>DEF LEPPARD</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
+        <v>קורל אמויאל - עכשיו אתה חוזר בחזרה קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
+        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-23</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Will Linley</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video)</v>
+        <v>Nico Santos - Optimist</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
+        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-23</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Kylie Minogue</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
+        <v>Nico Santos - Optimist - Nico Santos</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
+        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-23</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Billy Raffoul</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
+        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-23</v>
@@ -685,7 +685,7 @@
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>The Offspring</v>
+        <v>Will Linley</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
+        <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
+        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-23</v>
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>David Gilmour</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
+        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B10" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
+        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-23</v>
@@ -761,7 +761,7 @@
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Scorpions</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B11" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
+        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-23</v>
@@ -799,7 +799,7 @@
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Brandon Lake</v>
+        <v>The Offspring</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B12" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
+        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-23</v>
@@ -837,7 +837,7 @@
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Kygo and Dan Tyminski</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>The Warning - Ego (Official Video)</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B13" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
+        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-23</v>
@@ -875,7 +875,7 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>The Warning</v>
+        <v>Scorpions</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>The Warning - Ego (Official Video) - The Warning</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>paris jackson - teenage drama (official lyric video)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B14" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
+        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-23</v>
@@ -913,7 +913,7 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>paris jackson</v>
+        <v>Brandon Lake</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B15" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
+        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-23</v>
@@ -951,7 +951,7 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Minelli</v>
+        <v>Kygo and Dan Tyminski</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
+        <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B16" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
+        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-23</v>
@@ -989,7 +989,7 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Maggie Rose</v>
+        <v>The Warning</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
+        <v>The Warning - Ego (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
+        <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B17" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
+        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-23</v>
@@ -1027,7 +1027,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>David Guetta</v>
+        <v>paris jackson</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
+        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B18" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
+        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-23</v>
@@ -1065,7 +1065,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Chris Young and Shaylen</v>
+        <v>Minelli</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Lauv - Pretty Little Things</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B19" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
+        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-23</v>
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Lauv</v>
+        <v>Maggie Rose</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Lauv - Pretty Little Things - Lauv</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B20" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
+        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-23</v>
@@ -1141,7 +1141,7 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Icona Pop</v>
+        <v>David Guetta</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Will Swinton - Only One (Official Video)</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
+        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-23</v>
@@ -1179,7 +1179,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Will Swinton</v>
+        <v>Chris Young and Shaylen</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B22" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-23</v>
@@ -1217,7 +1217,7 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Dean Lewis</v>
+        <v>Lauv</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>Lauv - Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B23" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-23</v>
@@ -1255,7 +1255,7 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B24" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-23</v>
@@ -1293,7 +1293,7 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Niall Horan</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B25" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-23</v>
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B26" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-23</v>
@@ -1369,7 +1369,7 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>RUEL</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B27" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-23</v>
@@ -1407,7 +1407,7 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>TINI</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-23</v>
@@ -1445,7 +1445,7 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Charli xcx</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-23</v>
@@ -1483,7 +1483,7 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Dua Lipa</v>
+        <v>RUEL</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-23</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Matilda Mann</v>
+        <v>TINI</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-23</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Ella Langley</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B32" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-23</v>
@@ -1597,7 +1597,7 @@
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-23</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>kesha</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B34" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-23</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Holly Humberstone</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B35" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-23</v>
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Foo Fighters</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B36" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-23</v>
@@ -1749,7 +1749,7 @@
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>The Analogues</v>
+        <v>kesha</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B37" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-23</v>
@@ -1787,7 +1787,7 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Rod Stewart</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B38" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-23</v>
@@ -1825,7 +1825,7 @@
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Blue October</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Far Caspian - hum (Official Video)</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B39" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-23</v>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Far Caspian</v>
+        <v>The Analogues</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Kenia Os - Love Bombing</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B40" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-23</v>
@@ -1901,7 +1901,7 @@
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Kenia Os</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Kenia Os - Love Bombing - Kenia Os</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B41" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
+        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-23</v>
@@ -1939,7 +1939,7 @@
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Blue October</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-23</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B43" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-23</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>Kenia Os - Love Bombing - Kenia Os</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B44" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-23</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B45" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-23</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B46" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-23</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B47" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-23</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B48" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-23</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Evanescence</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B49" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-23</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-23</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Armin van Buuren</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-23</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Madison Cunningham</v>
+        <v>Evanescence</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-23</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Johnny Orlando</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-23</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Carver Jones</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-23</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Jazmin bean</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B55" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-23</v>
@@ -2471,7 +2471,7 @@
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Baby Queen</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B56" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-23</v>
@@ -2509,7 +2509,7 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Switchfoot</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B57" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-23</v>
@@ -2547,7 +2547,7 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Grace Potter</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B58" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-23</v>
@@ -2585,7 +2585,7 @@
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B59" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-23</v>
@@ -2623,7 +2623,7 @@
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>The All-American Rejects</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B60" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-23</v>
@@ -2661,7 +2661,7 @@
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Henry Moodie</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B61" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-23</v>
@@ -2699,7 +2699,7 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Spacey Jane</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B62" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-23</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Megan Moroney</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B63" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-23</v>
@@ -2775,7 +2775,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Matt Hansen</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-23</v>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Matt Hansen</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Keith Urban - Steal Away (Visualizer)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B65" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-23</v>
@@ -2851,7 +2851,7 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Keith Urban</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>VALÉ - Mugshot (Official Video)</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B66" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-23</v>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>VALÉ</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio)</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
+        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-23</v>
@@ -2927,7 +2927,7 @@
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Mackenzie Carpenter</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
+        <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B68" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
+        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-23</v>
@@ -2965,7 +2965,7 @@
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Towa Bird</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
+        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
+        <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B69" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
+        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-23</v>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Sabrina Sterling</v>
+        <v>VALÉ</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
+        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
+        <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B70" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
+        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-23</v>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Little Big Town</v>
+        <v>Mackenzie Carpenter</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
+        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Becky G - EPA (Official Video)</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
+        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-23</v>
@@ -3079,7 +3079,7 @@
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Becky G</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Becky G - EPA (Official Video) - Becky G</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B72" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
+        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-23</v>
@@ -3117,7 +3117,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Daisy the Great</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Towa Bird - Dog (Official Music Video)</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
+        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-23</v>
@@ -3155,7 +3155,7 @@
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Towa Bird</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
+        <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B74" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
+        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-23</v>
@@ -3193,7 +3193,7 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Madonna</v>
+        <v>Becky G</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
+        <v>Becky G - EPA (Official Video) - Becky G</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video)</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B75" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
+        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-23</v>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Ally Salort</v>
+        <v>Daisy the Great</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Bella White - Better - Official Music Video</v>
+        <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B76" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
+        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-23</v>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Bella White</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Bella White - Better - Official Music Video - Bella White</v>
+        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B77" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
+        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-23</v>
@@ -3307,7 +3307,7 @@
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Madonna</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
+        <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B78" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
+        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-23</v>
@@ -3345,7 +3345,7 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Towa Bird</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
+        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer)</v>
+        <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B79" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
+        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-23</v>
@@ -3383,7 +3383,7 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Miranda Lambert</v>
+        <v>Bella White</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
+        <v>Bella White - Better - Official Music Video - Bella White</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B80" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
+        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-23</v>
@@ -3421,7 +3421,7 @@
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Lady Gaga</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B81" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
+        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-23</v>
@@ -3459,7 +3459,7 @@
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Gracie Abrams</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
+        <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B82" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
+        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-23</v>
@@ -3497,7 +3497,7 @@
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
+        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B83" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
+        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-23</v>
@@ -3535,7 +3535,7 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Martin Garrix</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Jorja Smith - What's Done Is Done</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B84" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
+        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-23</v>
@@ -3573,7 +3573,7 @@
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Jorja Smith</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>LP - Shelly (Official Music Video)</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
+        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-23</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>LP</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>LP - Shelly (Official Music Video) - LP</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B86" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
+        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-23</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>The Rolling Stones</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
+        <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B87" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
+        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-23</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Oasis</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
+        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
+        <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
+        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-23</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Breaking Benjamin</v>
+        <v>LP</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
+        <v>LP - Shelly (Official Music Video) - LP</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B89" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
+        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-23</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>VictorBiliac</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B90" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
+        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-23</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Linkin Park</v>
+        <v>Oasis</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Harry Styles - Dance No More (Official Video)</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
+        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-23</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Harry Styles</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
+        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-23</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Eagles</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
+        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-23</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Nora Fatehi</v>
+        <v>Linkin Park</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
+        <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
+        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-23</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
+        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-23</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Eurovision Song Contest and Alis</v>
+        <v>Eagles</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B96" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
+        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-23</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Nora Fatehi</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video)</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
+        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-23</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>The Head And The Heart</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
+        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-23</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Simply Red</v>
+        <v>Eurovision Song Contest and Alis</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video)</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B99" t="str">
-        <v>13 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
+        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-23</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>13 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Talking Heads</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Ellise - Liplock (Official Music Video)</v>
+        <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
+        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-23</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Ellise</v>
+        <v>The Head And The Heart</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
+        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Tori Kelly - Dive (Official Music Video)</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
+        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-23</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Tori Kelly</v>
+        <v>Simply Red</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>From Down Here</v>
+        <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>13 days ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
+        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-23</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>From Down Here - Single</v>
+        <v>13 days ago</v>
       </c>
       <c r="G102" t="str">
-        <v>4:01</v>
+        <v/>
       </c>
       <c r="H102" t="str">
-        <v>Lola Young</v>
+        <v>Talking Heads</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/lola-young/452271760</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/from-down-here/6768357139</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>From Down Here - Lola Young</v>
+        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>the cure</v>
+        <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/the-cure/1889992123</v>
+        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-23</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>you seem pretty sad for a girl so in love</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>4:57</v>
+        <v/>
       </c>
       <c r="H103" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Ellise</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/the-cure/1889992111</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>the cure - Olivia Rodrigo</v>
+        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>SS26</v>
+        <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/ss26/6771061782</v>
+        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-23</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>SS26 - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G104" t="str">
-        <v>2:47</v>
+        <v/>
       </c>
       <c r="H104" t="str">
-        <v>Charli xcx</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/ss26/6771061771</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>SS26 - Charli xcx</v>
+        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>White Flag</v>
+        <v>From Down Here</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/white-flag/1887627840</v>
+        <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-23</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Cry Baby</v>
+        <v>From Down Here - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>2:34</v>
+        <v>4:01</v>
       </c>
       <c r="H105" t="str">
-        <v>Vince Staples</v>
+        <v>Lola Young</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/lola-young/452271760</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/white-flag/1887627836</v>
+        <v>https://music.apple.com/us/album/from-down-here/6768357139</v>
       </c>
       <c r="L105" t="str">
-        <v>White Flag - Vince Staples</v>
+        <v>From Down Here - Lola Young</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Knew Better Part Two</v>
+        <v>the cure</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
+        <v>https://music.apple.com/us/song/the-cure/1889992123</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-23</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Dangerous Woman (Tenth Anniversary Edition)</v>
+        <v>you seem pretty sad for a girl so in love</v>
       </c>
       <c r="G106" t="str">
-        <v>2:44</v>
+        <v>4:57</v>
       </c>
       <c r="H106" t="str">
-        <v>Ariana Grande</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/knew-better-part-two/6770600996</v>
+        <v>https://music.apple.com/us/album/the-cure/1889992111</v>
       </c>
       <c r="L106" t="str">
-        <v>Knew Better Part Two - Ariana Grande</v>
+        <v>the cure - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Goals</v>
+        <v>SS26</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/goals/6769251838</v>
+        <v>https://music.apple.com/us/song/ss26/6771061782</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-23</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Goals (FIFA World Cup 2026™) - Single</v>
+        <v>SS26 - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:00</v>
+        <v>2:47</v>
       </c>
       <c r="H107" t="str">
-        <v>LISA</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/lisa/1583908668</v>
+        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/goals/6769251829</v>
+        <v>https://music.apple.com/us/album/ss26/6771061771</v>
       </c>
       <c r="L107" t="str">
-        <v>Goals - LISA</v>
+        <v>SS26 - Charli xcx</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>we should talk</v>
+        <v>White Flag</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
+        <v>https://music.apple.com/us/song/white-flag/1887627840</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-23</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G108" t="str">
-        <v>3:04</v>
+        <v>2:34</v>
       </c>
       <c r="H108" t="str">
-        <v>Bleachers</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/we-should-talk/1872842313</v>
+        <v>https://music.apple.com/us/album/white-flag/1887627836</v>
       </c>
       <c r="L108" t="str">
-        <v>we should talk - Bleachers</v>
+        <v>White Flag - Vince Staples</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Do What You Gotta Do</v>
+        <v>Knew Better Part Two</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
+        <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-23</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>NeverAlways (Vol. 2)</v>
+        <v>Dangerous Woman (Tenth Anniversary Edition)</v>
       </c>
       <c r="G109" t="str">
-        <v>3:26</v>
+        <v>2:44</v>
       </c>
       <c r="H109" t="str">
-        <v>The Band CAMINO</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/do-what-you-gotta-do/1887616173</v>
+        <v>https://music.apple.com/us/album/knew-better-part-two/6770600996</v>
       </c>
       <c r="L109" t="str">
-        <v>Do What You Gotta Do - The Band CAMINO</v>
+        <v>Knew Better Part Two - Ariana Grande</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Ego</v>
+        <v>Goals</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/ego/6769207667</v>
+        <v>https://music.apple.com/us/song/goals/6769251838</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-23</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Ego - Single</v>
+        <v>Goals (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>2:53</v>
+        <v>3:00</v>
       </c>
       <c r="H110" t="str">
-        <v>The Warning</v>
+        <v>LISA</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/lisa/1583908668</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/ego/6769207665</v>
+        <v>https://music.apple.com/us/album/goals/6769251829</v>
       </c>
       <c r="L110" t="str">
-        <v>Ego - The Warning</v>
+        <v>Goals - LISA</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Light up (From the Netflix Documentary 'kylie')</v>
+        <v>we should talk</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
+        <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-23</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Light up (From the Netflix Documentary 'Kylie') - Single</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G111" t="str">
-        <v>3:17</v>
+        <v>3:04</v>
       </c>
       <c r="H111" t="str">
-        <v>Kylie Minogue</v>
+        <v>Bleachers</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/kylie-minogue/465031</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/light-up-from-the-netflix-documentary-kylie/6768013505</v>
+        <v>https://music.apple.com/us/album/we-should-talk/1872842313</v>
       </c>
       <c r="L111" t="str">
-        <v>Light up (From the Netflix Documentary 'kylie') - Kylie Minogue</v>
+        <v>we should talk - Bleachers</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>All That Matters</v>
+        <v>Do What You Gotta Do</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
+        <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-23</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>NeverAlways (Vol. 2)</v>
       </c>
       <c r="G112" t="str">
-        <v>3:43</v>
+        <v>3:26</v>
       </c>
       <c r="H112" t="str">
-        <v>6LACK</v>
+        <v>The Band CAMINO</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/all-that-matters/1884792154</v>
+        <v>https://music.apple.com/us/album/do-what-you-gotta-do/1887616173</v>
       </c>
       <c r="L112" t="str">
-        <v>All That Matters - 6LACK</v>
+        <v>Do What You Gotta Do - The Band CAMINO</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Like A Virgin</v>
+        <v>Ego</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
+        <v>https://music.apple.com/us/song/ego/6769207667</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-23</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Terrified .</v>
+        <v>Ego - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>2:34</v>
+        <v>2:53</v>
       </c>
       <c r="H113" t="str">
-        <v>fakemink</v>
+        <v>The Warning</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/like-a-virgin/6768157748</v>
+        <v>https://music.apple.com/us/album/ego/6769207665</v>
       </c>
       <c r="L113" t="str">
-        <v>Like A Virgin - fakemink</v>
+        <v>Ego - The Warning</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>24 Hours</v>
+        <v>Light up (From the Netflix Documentary 'kylie')</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/24-hours/6771060076</v>
+        <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-23</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>24 Hours - Single</v>
+        <v>Light up (From the Netflix Documentary 'Kylie') - Single</v>
       </c>
       <c r="G114" t="str">
         <v>3:17</v>
       </c>
       <c r="H114" t="str">
-        <v>Stormzy</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/stormzy/394865154</v>
+        <v>https://music.apple.com/us/artist/kylie-minogue/465031</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/24-hours/6771060073</v>
+        <v>https://music.apple.com/us/album/light-up-from-the-netflix-documentary-kylie/6768013505</v>
       </c>
       <c r="L114" t="str">
-        <v>24 Hours - Stormzy</v>
+        <v>Light up (From the Netflix Documentary 'kylie') - Kylie Minogue</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>HOES (From Scary Movie)</v>
+        <v>All That Matters</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
+        <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-23</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>HOES (From Scary Movie) - Single</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G115" t="str">
-        <v>2:09</v>
+        <v>3:43</v>
       </c>
       <c r="H115" t="str">
-        <v>Lizzo</v>
+        <v>6LACK</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/hoes-from-scary-movie/6770661290</v>
+        <v>https://music.apple.com/us/album/all-that-matters/1884792154</v>
       </c>
       <c r="L115" t="str">
-        <v>HOES (From Scary Movie) - Lizzo</v>
+        <v>All That Matters - 6LACK</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Ms. Tundra</v>
+        <v>Like A Virgin</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
+        <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-23</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Highway 79</v>
+        <v>Terrified .</v>
       </c>
       <c r="G116" t="str">
-        <v>3:12</v>
+        <v>2:34</v>
       </c>
       <c r="H116" t="str">
-        <v>Ne-Yo</v>
+        <v>fakemink</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/ms-tundra/6770614875</v>
+        <v>https://music.apple.com/us/album/like-a-virgin/6768157748</v>
       </c>
       <c r="L116" t="str">
-        <v>Ms. Tundra - Ne-Yo</v>
+        <v>Like A Virgin - fakemink</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>TARENTINO</v>
+        <v>24 Hours</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/tarentino/6769927265</v>
+        <v>https://music.apple.com/us/song/24-hours/6771060076</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-23</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>TARENTINO - Single</v>
+        <v>24 Hours - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:23</v>
+        <v>3:17</v>
       </c>
       <c r="H117" t="str">
-        <v>Labrinth</v>
+        <v>Stormzy</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/stormzy/394865154</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/tarentino/6769927262</v>
+        <v>https://music.apple.com/us/album/24-hours/6771060073</v>
       </c>
       <c r="L117" t="str">
-        <v>TARENTINO - Labrinth</v>
+        <v>24 Hours - Stormzy</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Daydreamin’</v>
+        <v>HOES (From Scary Movie)</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
+        <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-23</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>KONNAKOL (Deluxe)</v>
+        <v>HOES (From Scary Movie) - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:58</v>
+        <v>2:09</v>
       </c>
       <c r="H118" t="str">
-        <v>ZAYN</v>
+        <v>Lizzo</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/daydreamin/6769559345</v>
+        <v>https://music.apple.com/us/album/hoes-from-scary-movie/6770661290</v>
       </c>
       <c r="L118" t="str">
-        <v>Daydreamin’ - ZAYN</v>
+        <v>HOES (From Scary Movie) - Lizzo</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>End of an Era</v>
+        <v>Ms. Tundra</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
+        <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-23</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Dinner Party</v>
+        <v>Highway 79</v>
       </c>
       <c r="G119" t="str">
-        <v>3:38</v>
+        <v>3:12</v>
       </c>
       <c r="H119" t="str">
-        <v>Niall Horan</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/end-of-an-era/1884418567</v>
+        <v>https://music.apple.com/us/album/ms-tundra/6770614875</v>
       </c>
       <c r="L119" t="str">
-        <v>End of an Era - Niall Horan</v>
+        <v>Ms. Tundra - Ne-Yo</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Questions</v>
+        <v>TARENTINO</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/questions/1871502847</v>
+        <v>https://music.apple.com/us/song/tarentino/6769927265</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-23</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Florescence</v>
+        <v>TARENTINO - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:07</v>
+        <v>2:23</v>
       </c>
       <c r="H120" t="str">
-        <v>Maisie Peters</v>
+        <v>Labrinth</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/questions/1871502372</v>
+        <v>https://music.apple.com/us/album/tarentino/6769927262</v>
       </c>
       <c r="L120" t="str">
-        <v>Questions - Maisie Peters</v>
+        <v>TARENTINO - Labrinth</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Heart Has To Work So Hard</v>
+        <v>Daydreamin’</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
+        <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-23</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Heart Has To Work So Hard - Single</v>
+        <v>KONNAKOL (Deluxe)</v>
       </c>
       <c r="G121" t="str">
-        <v>3:12</v>
+        <v>2:58</v>
       </c>
       <c r="H121" t="str">
-        <v>Blondshell</v>
+        <v>ZAYN</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/blondshell/1624592688</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/heart-has-to-work-so-hard/1895982147</v>
+        <v>https://music.apple.com/us/album/daydreamin/6769559345</v>
       </c>
       <c r="L121" t="str">
-        <v>Heart Has To Work So Hard - Blondshell</v>
+        <v>Daydreamin’ - ZAYN</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski)</v>
+        <v>End of an Era</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
+        <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-23</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski) - Single</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G122" t="str">
-        <v>3:44</v>
+        <v>3:38</v>
       </c>
       <c r="H122" t="str">
-        <v>Kygo</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-your-mind-feat-dan-tyminski/6769007431</v>
+        <v>https://music.apple.com/us/album/end-of-an-era/1884418567</v>
       </c>
       <c r="L122" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski) - Kygo</v>
+        <v>End of an Era - Niall Horan</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>PERDISTE EL EMMY.</v>
+        <v>Questions</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
+        <v>https://music.apple.com/us/song/questions/1871502847</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-23</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>OMAKASE</v>
+        <v>Florescence</v>
       </c>
       <c r="G123" t="str">
-        <v>4:03</v>
+        <v>3:07</v>
       </c>
       <c r="H123" t="str">
-        <v>Álvaro Díaz</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/perdiste-el-emmy/6771082594</v>
+        <v>https://music.apple.com/us/album/questions/1871502372</v>
       </c>
       <c r="L123" t="str">
-        <v>PERDISTE EL EMMY. - Álvaro Díaz</v>
+        <v>Questions - Maisie Peters</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Dosis</v>
+        <v>Heart Has To Work So Hard</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/dosis/6762929729</v>
+        <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-23</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>DOSIS</v>
+        <v>Heart Has To Work So Hard - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:00</v>
+        <v>3:12</v>
       </c>
       <c r="H124" t="str">
-        <v>Xavi</v>
+        <v>Blondshell</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/blondshell/1624592688</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/dosis/1895081885</v>
+        <v>https://music.apple.com/us/album/heart-has-to-work-so-hard/1895982147</v>
       </c>
       <c r="L124" t="str">
-        <v>Dosis - Xavi</v>
+        <v>Heart Has To Work So Hard - Blondshell</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Would U Still Love Me</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
+        <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-23</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Whitcomb vs. Flores - Single</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski) - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:36</v>
+        <v>3:44</v>
       </c>
       <c r="H125" t="str">
-        <v>Diplo</v>
+        <v>Kygo</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/would-u-still-love-me/6769907832</v>
+        <v>https://music.apple.com/us/album/heaven-on-your-mind-feat-dan-tyminski/6769007431</v>
       </c>
       <c r="L125" t="str">
-        <v>Would U Still Love Me - Diplo</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski) - Kygo</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Saving This Bottle</v>
+        <v>PERDISTE EL EMMY.</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
+        <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-23</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Whitcomb vs. Flores - Single</v>
+        <v>OMAKASE</v>
       </c>
       <c r="G126" t="str">
-        <v>3:05</v>
+        <v>4:03</v>
       </c>
       <c r="H126" t="str">
-        <v>Diplo</v>
+        <v>Álvaro Díaz</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
+        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/saving-this-bottle/6769907832</v>
+        <v>https://music.apple.com/us/album/perdiste-el-emmy/6771082594</v>
       </c>
       <c r="L126" t="str">
-        <v>Saving This Bottle - Diplo</v>
+        <v>PERDISTE EL EMMY. - Álvaro Díaz</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>The Climb</v>
+        <v>Dosis</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/the-climb/6769546149</v>
+        <v>https://music.apple.com/us/song/dosis/6762929729</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-23</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>The Climb - Single</v>
+        <v>DOSIS</v>
       </c>
       <c r="G127" t="str">
-        <v>3:50</v>
+        <v>3:00</v>
       </c>
       <c r="H127" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Xavi</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/the-climb/6769546147</v>
+        <v>https://music.apple.com/us/album/dosis/1895081885</v>
       </c>
       <c r="L127" t="str">
-        <v>The Climb - Bailey Zimmerman</v>
+        <v>Dosis - Xavi</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>everything tatted</v>
+        <v>Would U Still Love Me</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
+        <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-23</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>everything tatted - Single</v>
+        <v>Whitcomb vs. Flores - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:25</v>
+        <v>2:36</v>
       </c>
       <c r="H128" t="str">
-        <v>mgk</v>
+        <v>Diplo</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/everything-tatted/6770773606</v>
+        <v>https://music.apple.com/us/album/would-u-still-love-me/6769907832</v>
       </c>
       <c r="L128" t="str">
-        <v>everything tatted - mgk</v>
+        <v>Would U Still Love Me - Diplo</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>BOOMPALA</v>
+        <v>Saving This Bottle</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/boompala/1894802726</v>
+        <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-23</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>'PUREFLOW', Pt. 1</v>
+        <v>Whitcomb vs. Flores - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:56</v>
+        <v>3:05</v>
       </c>
       <c r="H129" t="str">
-        <v>LE SSERAFIM</v>
+        <v>Diplo</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
+        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/boompala/1894802719</v>
+        <v>https://music.apple.com/us/album/saving-this-bottle/6769907832</v>
       </c>
       <c r="L129" t="str">
-        <v>BOOMPALA - LE SSERAFIM</v>
+        <v>Saving This Bottle - Diplo</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Let Me Be In Your Arms</v>
+        <v>The Climb</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
+        <v>https://music.apple.com/us/song/the-climb/6769546149</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-23</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>can we do it all again?</v>
+        <v>The Climb - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:13</v>
+        <v>3:50</v>
       </c>
       <c r="H130" t="str">
-        <v>Sonny Fodera</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/let-me-be-in-your-arms/1881610862</v>
+        <v>https://music.apple.com/us/album/the-climb/6769546147</v>
       </c>
       <c r="L130" t="str">
-        <v>Let Me Be In Your Arms - Sonny Fodera</v>
+        <v>The Climb - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Eat, Work, Pray</v>
+        <v>everything tatted</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
+        <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-23</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Eat, Work, Pray - Single</v>
+        <v>everything tatted - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:28</v>
+        <v>3:25</v>
       </c>
       <c r="H131" t="str">
-        <v>Sheff G</v>
+        <v>mgk</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/eat-work-pray/6769134493</v>
+        <v>https://music.apple.com/us/album/everything-tatted/6770773606</v>
       </c>
       <c r="L131" t="str">
-        <v>Eat, Work, Pray - Sheff G</v>
+        <v>everything tatted - mgk</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>touch myself</v>
+        <v>BOOMPALA</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
+        <v>https://music.apple.com/us/song/boompala/1894802726</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-23</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>and all pride aside</v>
+        <v>'PUREFLOW', Pt. 1</v>
       </c>
       <c r="G132" t="str">
-        <v>4:09</v>
+        <v>2:56</v>
       </c>
       <c r="H132" t="str">
-        <v>kwn</v>
+        <v>LE SSERAFIM</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/touch-myself/6769880663</v>
+        <v>https://music.apple.com/us/album/boompala/1894802719</v>
       </c>
       <c r="L132" t="str">
-        <v>touch myself - kwn</v>
+        <v>BOOMPALA - LE SSERAFIM</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Comes and Goes</v>
+        <v>Let Me Be In Your Arms</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
+        <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-23</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Comes and Goes - Single</v>
+        <v>can we do it all again?</v>
       </c>
       <c r="G133" t="str">
-        <v>4:22</v>
+        <v>3:13</v>
       </c>
       <c r="H133" t="str">
-        <v>KETTAMA</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/kettama/1425703970</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/comes-and-goes/6766618930</v>
+        <v>https://music.apple.com/us/album/let-me-be-in-your-arms/1881610862</v>
       </c>
       <c r="L133" t="str">
-        <v>Comes and Goes - KETTAMA</v>
+        <v>Let Me Be In Your Arms - Sonny Fodera</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Dear God</v>
+        <v>Eat, Work, Pray</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/dear-god/1878237813</v>
+        <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-23</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Dear God</v>
+        <v>Eat, Work, Pray - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>6:08</v>
+        <v>2:28</v>
       </c>
       <c r="H134" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Sheff G</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/dear-god/1878237662</v>
+        <v>https://music.apple.com/us/album/eat-work-pray/6769134493</v>
       </c>
       <c r="L134" t="str">
-        <v>Dear God - The Pretty Reckless</v>
+        <v>Eat, Work, Pray - Sheff G</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Hexagons</v>
+        <v>touch myself</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/hexagons/1885607736</v>
+        <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-23</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>The Wow! Signal</v>
+        <v>and all pride aside</v>
       </c>
       <c r="G135" t="str">
-        <v>5:26</v>
+        <v>4:09</v>
       </c>
       <c r="H135" t="str">
-        <v>Muse</v>
+        <v>kwn</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/hexagons/1885607338</v>
+        <v>https://music.apple.com/us/album/touch-myself/6769880663</v>
       </c>
       <c r="L135" t="str">
-        <v>Hexagons - Muse</v>
+        <v>touch myself - kwn</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Facile-Batiste</v>
+        <v>Comes and Goes</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
+        <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-23</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Black Mozart</v>
+        <v>Comes and Goes - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>4:55</v>
+        <v>4:22</v>
       </c>
       <c r="H136" t="str">
-        <v>Jon Batiste</v>
+        <v>KETTAMA</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/kettama/1425703970</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/facile-batiste/1895866355</v>
+        <v>https://music.apple.com/us/album/comes-and-goes/6766618930</v>
       </c>
       <c r="L136" t="str">
-        <v>Facile-Batiste - Jon Batiste</v>
+        <v>Comes and Goes - KETTAMA</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Pop Pop</v>
+        <v>Dear God</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
+        <v>https://music.apple.com/us/song/dear-god/1878237813</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-23</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Pop Pop - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G137" t="str">
-        <v>2:57</v>
+        <v>6:08</v>
       </c>
       <c r="H137" t="str">
-        <v>Channel Tres</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/pop-pop/1896269430</v>
+        <v>https://music.apple.com/us/album/dear-god/1878237662</v>
       </c>
       <c r="L137" t="str">
-        <v>Pop Pop - Channel Tres</v>
+        <v>Dear God - The Pretty Reckless</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>One Of Us</v>
+        <v>Hexagons</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
+        <v>https://music.apple.com/us/song/hexagons/1885607736</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-23</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>One Of Us - Single</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G138" t="str">
-        <v>3:35</v>
+        <v>5:26</v>
       </c>
       <c r="H138" t="str">
-        <v>Chris Young</v>
+        <v>Muse</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/chris-young/4779205</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/one-of-us/1895402922</v>
+        <v>https://music.apple.com/us/album/hexagons/1885607338</v>
       </c>
       <c r="L138" t="str">
-        <v>One Of Us - Chris Young</v>
+        <v>Hexagons - Muse</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Sins of the Father</v>
+        <v>Facile-Batiste</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
+        <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-23</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Is God Is (Original Motion Picture Soundtrack)</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G139" t="str">
-        <v>3:20</v>
+        <v>4:55</v>
       </c>
       <c r="H139" t="str">
-        <v>Moses Sumney</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/moses-sumney/843536848</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/sins-of-the-father/6771012707</v>
+        <v>https://music.apple.com/us/album/facile-batiste/1895866355</v>
       </c>
       <c r="L139" t="str">
-        <v>Sins of the Father - Moses Sumney</v>
+        <v>Facile-Batiste - Jon Batiste</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Life On The Run</v>
+        <v>Pop Pop</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
+        <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-23</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Life On The Run - Single</v>
+        <v>Pop Pop - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:49</v>
+        <v>2:57</v>
       </c>
       <c r="H140" t="str">
-        <v>Brandi Carlile</v>
+        <v>Channel Tres</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/brandi-carlile/64387579</v>
+        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/life-on-the-run/6766761019</v>
+        <v>https://music.apple.com/us/album/pop-pop/1896269430</v>
       </c>
       <c r="L140" t="str">
-        <v>Life On The Run - Brandi Carlile</v>
+        <v>Pop Pop - Channel Tres</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>New York Confident</v>
+        <v>One Of Us</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
+        <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-23</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>New York Confident - Single</v>
+        <v>One Of Us - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:27</v>
+        <v>3:35</v>
       </c>
       <c r="H141" t="str">
-        <v>Mark Ambor</v>
+        <v>Chris Young</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/mark-ambor/1459754985</v>
+        <v>https://music.apple.com/us/artist/chris-young/4779205</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/new-york-confident/6765558036</v>
+        <v>https://music.apple.com/us/album/one-of-us/1895402922</v>
       </c>
       <c r="L141" t="str">
-        <v>New York Confident - Mark Ambor</v>
+        <v>One Of Us - Chris Young</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>pequeñita!</v>
+        <v>Sins of the Father</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
+        <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-23</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>pequeñita! - Single</v>
+        <v>Is God Is (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G142" t="str">
-        <v>2:39</v>
+        <v>3:20</v>
       </c>
       <c r="H142" t="str">
-        <v>Judeline</v>
+        <v>Moses Sumney</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/judeline/1487503245</v>
+        <v>https://music.apple.com/us/artist/moses-sumney/843536848</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/peque%C3%B1ita/6769827604</v>
+        <v>https://music.apple.com/us/album/sins-of-the-father/6771012707</v>
       </c>
       <c r="L142" t="str">
-        <v>pequeñita! - Judeline</v>
+        <v>Sins of the Father - Moses Sumney</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Opaline</v>
+        <v>Life On The Run</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/opaline/1886737060</v>
+        <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-23</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>Life On The Run - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:17</v>
+        <v>3:49</v>
       </c>
       <c r="H143" t="str">
-        <v>Stephan Moccio</v>
+        <v>Brandi Carlile</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/brandi-carlile/64387579</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/opaline/1886736650</v>
+        <v>https://music.apple.com/us/album/life-on-the-run/6766761019</v>
       </c>
       <c r="L143" t="str">
-        <v>Opaline - Stephan Moccio</v>
+        <v>Life On The Run - Brandi Carlile</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Pretty Little Things</v>
+        <v>New York Confident</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
+        <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-23</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Pretty Little Things - Single</v>
+        <v>New York Confident - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:51</v>
+        <v>2:27</v>
       </c>
       <c r="H144" t="str">
-        <v>Lauv</v>
+        <v>Mark Ambor</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/mark-ambor/1459754985</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/pretty-little-things/6767353963</v>
+        <v>https://music.apple.com/us/album/new-york-confident/6765558036</v>
       </c>
       <c r="L144" t="str">
-        <v>Pretty Little Things - Lauv</v>
+        <v>New York Confident - Mark Ambor</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>COLORADO</v>
+        <v>pequeñita!</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/colorado/6769065232</v>
+        <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-23</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>COLORADO - Single</v>
+        <v>pequeñita! - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>1:54</v>
+        <v>2:39</v>
       </c>
       <c r="H145" t="str">
-        <v>Loud Luxury</v>
+        <v>Judeline</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
+        <v>https://music.apple.com/us/artist/judeline/1487503245</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/colorado/6769064981</v>
+        <v>https://music.apple.com/us/album/peque%C3%B1ita/6769827604</v>
       </c>
       <c r="L145" t="str">
-        <v>COLORADO - Loud Luxury</v>
+        <v>pequeñita! - Judeline</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Infidelidad</v>
+        <v>Opaline</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
+        <v>https://music.apple.com/us/song/opaline/1886737060</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-23</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>El Disco de Salsa</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G146" t="str">
-        <v>3:29</v>
+        <v>3:17</v>
       </c>
       <c r="H146" t="str">
-        <v>Neutro Shorty</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/neutro-shorty/1066850977</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/infidelidad/6768853655</v>
+        <v>https://music.apple.com/us/album/opaline/1886736650</v>
       </c>
       <c r="L146" t="str">
-        <v>Infidelidad - Neutro Shorty</v>
+        <v>Opaline - Stephan Moccio</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Wrong Place, Wrong time</v>
+        <v>Pretty Little Things</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
+        <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-23</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Y'all Won</v>
+        <v>Pretty Little Things - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:57</v>
+        <v>2:51</v>
       </c>
       <c r="H147" t="str">
-        <v>Veeze</v>
+        <v>Lauv</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/wrong-place-wrong-time/6771553812</v>
+        <v>https://music.apple.com/us/album/pretty-little-things/6767353963</v>
       </c>
       <c r="L147" t="str">
-        <v>Wrong Place, Wrong time - Veeze</v>
+        <v>Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>La Semana</v>
+        <v>COLORADO</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/la-semana/6769913466</v>
+        <v>https://music.apple.com/us/song/colorado/6769065232</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-23</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>No Quiero Que Se Acabe Este Bendito Verano - EP</v>
+        <v>COLORADO - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:30</v>
+        <v>1:54</v>
       </c>
       <c r="H148" t="str">
-        <v>ELENA ROSE</v>
+        <v>Loud Luxury</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/la-semana/6769913464</v>
+        <v>https://music.apple.com/us/album/colorado/6769064981</v>
       </c>
       <c r="L148" t="str">
-        <v>La Semana - ELENA ROSE</v>
+        <v>COLORADO - Loud Luxury</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Una Mujer Como la Suya</v>
+        <v>Infidelidad</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
+        <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-23</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Bandera Blanca</v>
+        <v>El Disco de Salsa</v>
       </c>
       <c r="G149" t="str">
-        <v>3:34</v>
+        <v>3:29</v>
       </c>
       <c r="H149" t="str">
-        <v>Christian Nodal</v>
+        <v>Neutro Shorty</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/neutro-shorty/1066850977</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/una-mujer-como-la-suya/1895154946</v>
+        <v>https://music.apple.com/us/album/infidelidad/6768853655</v>
       </c>
       <c r="L149" t="str">
-        <v>Una Mujer Como la Suya - Christian Nodal</v>
+        <v>Infidelidad - Neutro Shorty</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Cold</v>
+        <v>Wrong Place, Wrong time</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/cold/6763763802</v>
+        <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-23</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Cold - Single</v>
+        <v>Y'all Won</v>
       </c>
       <c r="G150" t="str">
-        <v>2:52</v>
+        <v>2:57</v>
       </c>
       <c r="H150" t="str">
-        <v>Majid Jordan</v>
+        <v>Veeze</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/majid-jordan/684530590</v>
+        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/cold/1895478371</v>
+        <v>https://music.apple.com/us/album/wrong-place-wrong-time/6771553812</v>
       </c>
       <c r="L150" t="str">
-        <v>Cold - Majid Jordan</v>
+        <v>Wrong Place, Wrong time - Veeze</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>VERTICAL WORLDS</v>
+        <v>La Semana</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
+        <v>https://music.apple.com/us/song/la-semana/6769913466</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-23</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
+        <v>No Quiero Que Se Acabe Este Bendito Verano - EP</v>
       </c>
       <c r="G151" t="str">
-        <v>3:15</v>
+        <v>3:30</v>
       </c>
       <c r="H151" t="str">
-        <v>Ecca Vandal</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/vertical-worlds/1886485694</v>
+        <v>https://music.apple.com/us/album/la-semana/6769913464</v>
       </c>
       <c r="L151" t="str">
-        <v>VERTICAL WORLDS - Ecca Vandal</v>
+        <v>La Semana - ELENA ROSE</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Child of Divorce</v>
+        <v>Una Mujer Como la Suya</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
+        <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-23</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>soft pop</v>
+        <v>Bandera Blanca</v>
       </c>
       <c r="G152" t="str">
-        <v>3:24</v>
+        <v>3:34</v>
       </c>
       <c r="H152" t="str">
-        <v>Amy Shark</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/child-of-divorce/1880496743</v>
+        <v>https://music.apple.com/us/album/una-mujer-como-la-suya/1895154946</v>
       </c>
       <c r="L152" t="str">
-        <v>Child of Divorce - Amy Shark</v>
+        <v>Una Mujer Como la Suya - Christian Nodal</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Taboo</v>
+        <v>Cold</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/taboo/6762838716</v>
+        <v>https://music.apple.com/us/song/cold/6763763802</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-23</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Taboo - Single</v>
+        <v>Cold - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:38</v>
+        <v>2:52</v>
       </c>
       <c r="H153" t="str">
-        <v>Jensen McRae</v>
+        <v>Majid Jordan</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/jensen-mcrae/591974463</v>
+        <v>https://music.apple.com/us/artist/majid-jordan/684530590</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/taboo/1895036934</v>
+        <v>https://music.apple.com/us/album/cold/1895478371</v>
       </c>
       <c r="L153" t="str">
-        <v>Taboo - Jensen McRae</v>
+        <v>Cold - Majid Jordan</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>I'M OK</v>
+        <v>VERTICAL WORLDS</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/im-ok/1893392647</v>
+        <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-23</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>A Rii Set</v>
+        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
       </c>
       <c r="G154" t="str">
-        <v>2:37</v>
+        <v>3:15</v>
       </c>
       <c r="H154" t="str">
-        <v>Pheelz</v>
+        <v>Ecca Vandal</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
+        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/im-ok/1893392643</v>
+        <v>https://music.apple.com/us/album/vertical-worlds/1886485694</v>
       </c>
       <c r="L154" t="str">
-        <v>I'M OK - Pheelz</v>
+        <v>VERTICAL WORLDS - Ecca Vandal</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Butterfly Feelings</v>
+        <v>Child of Divorce</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
+        <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-23</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Ritual</v>
+        <v>soft pop</v>
       </c>
       <c r="G155" t="str">
-        <v>2:35</v>
+        <v>3:24</v>
       </c>
       <c r="H155" t="str">
-        <v>Icona Pop</v>
+        <v>Amy Shark</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/butterfly-feelings/1892426976</v>
+        <v>https://music.apple.com/us/album/child-of-divorce/1880496743</v>
       </c>
       <c r="L155" t="str">
-        <v>Butterfly Feelings - Icona Pop</v>
+        <v>Child of Divorce - Amy Shark</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>F**k the DJ</v>
+        <v>Taboo</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
+        <v>https://music.apple.com/us/song/taboo/6762838716</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-23</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Stage Girl (Not A Dream Anymore)</v>
+        <v>Taboo - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:57</v>
+        <v>3:38</v>
       </c>
       <c r="H156" t="str">
-        <v>Eli</v>
+        <v>Jensen McRae</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/jensen-mcrae/591974463</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/f-k-the-dj/6769903867</v>
+        <v>https://music.apple.com/us/album/taboo/1895036934</v>
       </c>
       <c r="L156" t="str">
-        <v>F**k the DJ - Eli</v>
+        <v>Taboo - Jensen McRae</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Grateful</v>
+        <v>I'M OK</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/grateful/1887166624</v>
+        <v>https://music.apple.com/us/song/im-ok/1893392647</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-23</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>24</v>
+        <v>A Rii Set</v>
       </c>
       <c r="G157" t="str">
-        <v>2:18</v>
+        <v>2:37</v>
       </c>
       <c r="H157" t="str">
-        <v>Alexis Ffrench</v>
+        <v>Pheelz</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/grateful/1887166427</v>
+        <v>https://music.apple.com/us/album/im-ok/1893392643</v>
       </c>
       <c r="L157" t="str">
-        <v>Grateful - Alexis Ffrench</v>
+        <v>I'M OK - Pheelz</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Second Chance</v>
+        <v>Butterfly Feelings</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/second-chance/6766778687</v>
+        <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-23</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Second Chance - Single</v>
+        <v>Ritual</v>
       </c>
       <c r="G158" t="str">
-        <v>3:06</v>
+        <v>2:35</v>
       </c>
       <c r="H158" t="str">
-        <v>Lukas Graham</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/lukas-graham/473219952</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/second-chance/6766778682</v>
+        <v>https://music.apple.com/us/album/butterfly-feelings/1892426976</v>
       </c>
       <c r="L158" t="str">
-        <v>Second Chance - Lukas Graham</v>
+        <v>Butterfly Feelings - Icona Pop</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Stupid World (feat. Chad Tepper) [Bonus Track]</v>
+        <v>F**k the DJ</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
+        <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-23</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Tommyland Rides Again</v>
+        <v>Stage Girl (Not A Dream Anymore)</v>
       </c>
       <c r="G159" t="str">
-        <v>3:49</v>
+        <v>2:57</v>
       </c>
       <c r="H159" t="str">
-        <v>Tommy Lee</v>
+        <v>Eli</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/tommy-lee/68696</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/stupid-world-feat-chad-tepper-bonus-track/1893473875</v>
+        <v>https://music.apple.com/us/album/f-k-the-dj/6769903867</v>
       </c>
       <c r="L159" t="str">
-        <v>Stupid World (feat. Chad Tepper) [Bonus Track] - Tommy Lee</v>
+        <v>F**k the DJ - Eli</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>DOOM LOOP</v>
+        <v>Grateful</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
+        <v>https://music.apple.com/us/song/grateful/1887166624</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-23</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Blood Of Your Empire</v>
+        <v>24</v>
       </c>
       <c r="G160" t="str">
-        <v>4:00</v>
+        <v>2:18</v>
       </c>
       <c r="H160" t="str">
-        <v>PRESIDENT</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/doom-loop/6769905842</v>
+        <v>https://music.apple.com/us/album/grateful/1887166427</v>
       </c>
       <c r="L160" t="str">
-        <v>DOOM LOOP - PRESIDENT</v>
+        <v>Grateful - Alexis Ffrench</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>New York City</v>
+        <v>Second Chance</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
+        <v>https://music.apple.com/us/song/second-chance/6766778687</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-23</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>New York City - Single</v>
+        <v>Second Chance - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:30</v>
+        <v>3:06</v>
       </c>
       <c r="H161" t="str">
-        <v>Anthony Ramos</v>
+        <v>Lukas Graham</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/anthony-ramos/1313064678</v>
+        <v>https://music.apple.com/us/artist/lukas-graham/473219952</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/new-york-city/6770624324</v>
+        <v>https://music.apple.com/us/album/second-chance/6766778682</v>
       </c>
       <c r="L161" t="str">
-        <v>New York City - Anthony Ramos</v>
+        <v>Second Chance - Lukas Graham</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>I Found You</v>
+        <v>Stupid World (feat. Chad Tepper) [Bonus Track]</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
+        <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-23</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>I Found You - Single</v>
+        <v>Tommyland Rides Again</v>
       </c>
       <c r="G162" t="str">
-        <v>3:18</v>
+        <v>3:49</v>
       </c>
       <c r="H162" t="str">
-        <v>TA Thomas</v>
+        <v>Tommy Lee</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/ta-thomas/1232189106</v>
+        <v>https://music.apple.com/us/artist/tommy-lee/68696</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/i-found-you/1894024530</v>
+        <v>https://music.apple.com/us/album/stupid-world-feat-chad-tepper-bonus-track/1893473875</v>
       </c>
       <c r="L162" t="str">
-        <v>I Found You - TA Thomas</v>
+        <v>Stupid World (feat. Chad Tepper) [Bonus Track] - Tommy Lee</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Just My Type</v>
+        <v>DOOM LOOP</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
+        <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-23</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Labor Of Love</v>
+        <v>Blood Of Your Empire</v>
       </c>
       <c r="G163" t="str">
-        <v>2:40</v>
+        <v>4:00</v>
       </c>
       <c r="H163" t="str">
-        <v>Blxst</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/just-my-type/1895199881</v>
+        <v>https://music.apple.com/us/album/doom-loop/6769905842</v>
       </c>
       <c r="L163" t="str">
-        <v>Just My Type - Blxst</v>
+        <v>DOOM LOOP - PRESIDENT</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>teenage drama</v>
+        <v>New York City</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
+        <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-23</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>teenage drama - Single</v>
+        <v>New York City - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:06</v>
+        <v>3:30</v>
       </c>
       <c r="H164" t="str">
-        <v>paris jackson</v>
+        <v>Anthony Ramos</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/anthony-ramos/1313064678</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/teenage-drama/6768447515</v>
+        <v>https://music.apple.com/us/album/new-york-city/6770624324</v>
       </c>
       <c r="L164" t="str">
-        <v>teenage drama - paris jackson</v>
+        <v>New York City - Anthony Ramos</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>does it still mean something?</v>
+        <v>I Found You</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
+        <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-23</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>only if it matters</v>
+        <v>I Found You - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:48</v>
+        <v>3:18</v>
       </c>
       <c r="H165" t="str">
-        <v>Kevian Kraemer</v>
+        <v>TA Thomas</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/ta-thomas/1232189106</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/does-it-still-mean-something/6768446154</v>
+        <v>https://music.apple.com/us/album/i-found-you/1894024530</v>
       </c>
       <c r="L165" t="str">
-        <v>does it still mean something? - Kevian Kraemer</v>
+        <v>I Found You - TA Thomas</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Debbie Don't Cry</v>
+        <v>Just My Type</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
+        <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-23</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Debbie Don't Cry - Single</v>
+        <v>Labor Of Love</v>
       </c>
       <c r="G166" t="str">
-        <v>3:00</v>
+        <v>2:40</v>
       </c>
       <c r="H166" t="str">
-        <v>Ruel</v>
+        <v>Blxst</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
+        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/debbie-dont-cry/6768206616</v>
+        <v>https://music.apple.com/us/album/just-my-type/1895199881</v>
       </c>
       <c r="L166" t="str">
-        <v>Debbie Don't Cry - Ruel</v>
+        <v>Just My Type - Blxst</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>YEAH YEAH YEAH</v>
+        <v>teenage drama</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
+        <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-23</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>YEAH YEAH YEAH - Single</v>
+        <v>teenage drama - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:25</v>
+        <v>3:06</v>
       </c>
       <c r="H167" t="str">
-        <v>Cruz Beckham</v>
+        <v>paris jackson</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/yeah-yeah-yeah/6767515610</v>
+        <v>https://music.apple.com/us/album/teenage-drama/6768447515</v>
       </c>
       <c r="L167" t="str">
-        <v>YEAH YEAH YEAH - Cruz Beckham</v>
+        <v>teenage drama - paris jackson</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Cotton Flower</v>
+        <v>does it still mean something?</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
+        <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-23</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>only if it matters</v>
       </c>
       <c r="G168" t="str">
-        <v>3:53</v>
+        <v>3:48</v>
       </c>
       <c r="H168" t="str">
-        <v>Future Islands</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/cotton-flower/1883045480</v>
+        <v>https://music.apple.com/us/album/does-it-still-mean-something/6768446154</v>
       </c>
       <c r="L168" t="str">
-        <v>Cotton Flower - Future Islands</v>
+        <v>does it still mean something? - Kevian Kraemer</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>WAHALA RIDDIM</v>
+        <v>Debbie Don't Cry</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
+        <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-23</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>WAHALA RIDDIM - Single</v>
+        <v>Debbie Don't Cry - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:22</v>
+        <v>3:00</v>
       </c>
       <c r="H169" t="str">
-        <v>THEHONESTGUY</v>
+        <v>Ruel</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
+        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/wahala-riddim/1895810537</v>
+        <v>https://music.apple.com/us/album/debbie-dont-cry/6768206616</v>
       </c>
       <c r="L169" t="str">
-        <v>WAHALA RIDDIM - THEHONESTGUY</v>
+        <v>Debbie Don't Cry - Ruel</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Comfort</v>
+        <v>YEAH YEAH YEAH</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/comfort/1876521401</v>
+        <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-23</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>So Help Me God</v>
+        <v>YEAH YEAH YEAH - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>5:35</v>
+        <v>2:25</v>
       </c>
       <c r="H170" t="str">
-        <v>Kelsey Lu</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/comfort/1876521144</v>
+        <v>https://music.apple.com/us/album/yeah-yeah-yeah/6767515610</v>
       </c>
       <c r="L170" t="str">
-        <v>Comfort - Kelsey Lu</v>
+        <v>YEAH YEAH YEAH - Cruz Beckham</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Skin</v>
+        <v>Cotton Flower</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/skin/6764651585</v>
+        <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-23</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Skin - Single</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G171" t="str">
-        <v>3:00</v>
+        <v>3:53</v>
       </c>
       <c r="H171" t="str">
-        <v>Alessi Rose</v>
+        <v>Future Islands</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/alessi-rose/1628689028</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/skin/1895865252</v>
+        <v>https://music.apple.com/us/album/cotton-flower/1883045480</v>
       </c>
       <c r="L171" t="str">
-        <v>Skin - Alessi Rose</v>
+        <v>Cotton Flower - Future Islands</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>IDGAF</v>
+        <v>WAHALA RIDDIM</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/idgaf/6764422210</v>
+        <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-23</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>IDGAF - Single</v>
+        <v>WAHALA RIDDIM - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:55</v>
+        <v>3:22</v>
       </c>
       <c r="H172" t="str">
-        <v>Katelyn Tarver</v>
+        <v>THEHONESTGUY</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/idgaf/1895773358</v>
+        <v>https://music.apple.com/us/album/wahala-riddim/1895810537</v>
       </c>
       <c r="L172" t="str">
-        <v>IDGAF - Katelyn Tarver</v>
+        <v>WAHALA RIDDIM - THEHONESTGUY</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Run Rabbit</v>
+        <v>Comfort</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
+        <v>https://music.apple.com/us/song/comfort/1876521401</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-23</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Run Rabbit - Single</v>
+        <v>So Help Me God</v>
       </c>
       <c r="G173" t="str">
-        <v>3:09</v>
+        <v>5:35</v>
       </c>
       <c r="H173" t="str">
-        <v>Mollie Elizabeth</v>
+        <v>Kelsey Lu</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/mollie-elizabeth/1780515318</v>
+        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/run-rabbit/6767354664</v>
+        <v>https://music.apple.com/us/album/comfort/1876521144</v>
       </c>
       <c r="L173" t="str">
-        <v>Run Rabbit - Mollie Elizabeth</v>
+        <v>Comfort - Kelsey Lu</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>So Good (feat. Kuuda)</v>
+        <v>Skin</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
+        <v>https://music.apple.com/us/song/skin/6764651585</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-23</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>So Good (feat. Kuuda) - Single</v>
+        <v>Skin - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:03</v>
+        <v>3:00</v>
       </c>
       <c r="H174" t="str">
-        <v>CamelPhat</v>
+        <v>Alessi Rose</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/camelphat/385810888</v>
+        <v>https://music.apple.com/us/artist/alessi-rose/1628689028</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/so-good-feat-kuuda/6766655768</v>
+        <v>https://music.apple.com/us/album/skin/1895865252</v>
       </c>
       <c r="L174" t="str">
-        <v>So Good (feat. Kuuda) - CamelPhat</v>
+        <v>Skin - Alessi Rose</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Empty Theatre, Pretty Picture</v>
+        <v>IDGAF</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
+        <v>https://music.apple.com/us/song/idgaf/6764422210</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-23</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Empty Theatre, Pretty Picture</v>
+        <v>IDGAF - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>5:01</v>
+        <v>2:55</v>
       </c>
       <c r="H175" t="str">
-        <v>Lane 8</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/empty-theatre-pretty-picture/1895395993</v>
+        <v>https://music.apple.com/us/album/idgaf/1895773358</v>
       </c>
       <c r="L175" t="str">
-        <v>Empty Theatre, Pretty Picture - Lane 8</v>
+        <v>IDGAF - Katelyn Tarver</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>regalametutiempo</v>
+        <v>Run Rabbit</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
+        <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-23</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>PROYECTANDO</v>
+        <v>Run Rabbit - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:01</v>
+        <v>3:09</v>
       </c>
       <c r="H176" t="str">
-        <v>Julio Caesar</v>
+        <v>Mollie Elizabeth</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/mollie-elizabeth/1780515318</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/regalametutiempo/6769922866</v>
+        <v>https://music.apple.com/us/album/run-rabbit/6767354664</v>
       </c>
       <c r="L176" t="str">
-        <v>regalametutiempo - Julio Caesar</v>
+        <v>Run Rabbit - Mollie Elizabeth</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>On Sight</v>
+        <v>So Good (feat. Kuuda)</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/on-sight/6763971220</v>
+        <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-23</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Left on RED</v>
+        <v>So Good (feat. Kuuda) - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:25</v>
+        <v>3:03</v>
       </c>
       <c r="H177" t="str">
-        <v>REMI</v>
+        <v>CamelPhat</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/remi/1716510008</v>
+        <v>https://music.apple.com/us/artist/camelphat/385810888</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/on-sight/1895580736</v>
+        <v>https://music.apple.com/us/album/so-good-feat-kuuda/6766655768</v>
       </c>
       <c r="L177" t="str">
-        <v>On Sight - REMI</v>
+        <v>So Good (feat. Kuuda) - CamelPhat</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Masks Off</v>
+        <v>Empty Theatre, Pretty Picture</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/masks-off/6764077133</v>
+        <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-23</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Masks Off - Single</v>
+        <v>Empty Theatre, Pretty Picture</v>
       </c>
       <c r="G178" t="str">
-        <v>3:24</v>
+        <v>5:01</v>
       </c>
       <c r="H178" t="str">
-        <v>Jesse Welles</v>
+        <v>Lane 8</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/jesse-welles/1737507146</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/masks-off/1895628310</v>
+        <v>https://music.apple.com/us/album/empty-theatre-pretty-picture/1895395993</v>
       </c>
       <c r="L178" t="str">
-        <v>Masks Off - Jesse Welles</v>
+        <v>Empty Theatre, Pretty Picture - Lane 8</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>I'm Just A Girl</v>
+        <v>regalametutiempo</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
+        <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-23</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Di Hotel Malibu</v>
+        <v>PROYECTANDO</v>
       </c>
       <c r="G179" t="str">
-        <v>2:49</v>
+        <v>3:01</v>
       </c>
       <c r="H179" t="str">
-        <v>Thee Marloes</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/thee-marloes/1541376632</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/im-just-a-girl/1878399768</v>
+        <v>https://music.apple.com/us/album/regalametutiempo/6769922866</v>
       </c>
       <c r="L179" t="str">
-        <v>I'm Just A Girl - Thee Marloes</v>
+        <v>regalametutiempo - Julio Caesar</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Soleil (feat. Isabella Lovestory)</v>
+        <v>On Sight</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
+        <v>https://music.apple.com/us/song/on-sight/6763971220</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-23</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>EXIT 2B</v>
+        <v>Left on RED</v>
       </c>
       <c r="G180" t="str">
-        <v>2:11</v>
+        <v>2:25</v>
       </c>
       <c r="H180" t="str">
-        <v>B0YG1RL</v>
+        <v>REMI</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/b0yg1rl/1847766665</v>
+        <v>https://music.apple.com/us/artist/remi/1716510008</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/soleil-feat-isabella-lovestory/6769526101</v>
+        <v>https://music.apple.com/us/album/on-sight/1895580736</v>
       </c>
       <c r="L180" t="str">
-        <v>Soleil (feat. Isabella Lovestory) - B0YG1RL</v>
+        <v>On Sight - REMI</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Money Tree</v>
+        <v>Masks Off</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/money-tree/6763211637</v>
+        <v>https://music.apple.com/us/song/masks-off/6764077133</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-23</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Money Tree - Single</v>
+        <v>Masks Off - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:39</v>
+        <v>3:24</v>
       </c>
       <c r="H181" t="str">
-        <v>Olympia Vitalis</v>
+        <v>Jesse Welles</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/jesse-welles/1737507146</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/money-tree/1895216986</v>
+        <v>https://music.apple.com/us/album/masks-off/1895628310</v>
       </c>
       <c r="L181" t="str">
-        <v>Money Tree - Olympia Vitalis</v>
+        <v>Masks Off - Jesse Welles</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Homerunner</v>
+        <v>I'm Just A Girl</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/homerunner/6770682178</v>
+        <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-23</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Homerunner - Single</v>
+        <v>Di Hotel Malibu</v>
       </c>
       <c r="G182" t="str">
-        <v>2:36</v>
+        <v>2:49</v>
       </c>
       <c r="H182" t="str">
-        <v>slayr</v>
+        <v>Thee Marloes</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/thee-marloes/1541376632</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/homerunner/6770682177</v>
+        <v>https://music.apple.com/us/album/im-just-a-girl/1878399768</v>
       </c>
       <c r="L182" t="str">
-        <v>Homerunner - slayr</v>
+        <v>I'm Just A Girl - Thee Marloes</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Mail</v>
+        <v>Soleil (feat. Isabella Lovestory)</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/mail/6769190635</v>
+        <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-23</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Mail - Single</v>
+        <v>EXIT 2B</v>
       </c>
       <c r="G183" t="str">
-        <v>2:14</v>
+        <v>2:11</v>
       </c>
       <c r="H183" t="str">
-        <v>MexikoDro</v>
+        <v>B0YG1RL</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/b0yg1rl/1847766665</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/mail/6769190634</v>
+        <v>https://music.apple.com/us/album/soleil-feat-isabella-lovestory/6769526101</v>
       </c>
       <c r="L183" t="str">
-        <v>Mail - MexikoDro</v>
+        <v>Soleil (feat. Isabella Lovestory) - B0YG1RL</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Waste Your Heart</v>
+        <v>Money Tree</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
+        <v>https://music.apple.com/us/song/money-tree/6763211637</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-23</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Waste Your Heart - Single</v>
+        <v>Money Tree - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:31</v>
+        <v>2:39</v>
       </c>
       <c r="H184" t="str">
-        <v>Magnus Ferrell</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/waste-your-heart/6769241913</v>
+        <v>https://music.apple.com/us/album/money-tree/1895216986</v>
       </c>
       <c r="L184" t="str">
-        <v>Waste Your Heart - Magnus Ferrell</v>
+        <v>Money Tree - Olympia Vitalis</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Sleeping Pills</v>
+        <v>Homerunner</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
+        <v>https://music.apple.com/us/song/homerunner/6770682178</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-23</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Sleeping Pills - Single</v>
+        <v>Homerunner - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:03</v>
+        <v>2:36</v>
       </c>
       <c r="H185" t="str">
-        <v>Dolder</v>
+        <v>slayr</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/sleeping-pills/1896452689</v>
+        <v>https://music.apple.com/us/album/homerunner/6770682177</v>
       </c>
       <c r="L185" t="str">
-        <v>Sleeping Pills - Dolder</v>
+        <v>Homerunner - slayr</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>KODACHROMATIC</v>
+        <v>Mail</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
+        <v>https://music.apple.com/us/song/mail/6769190635</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-23</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>KODACHROMATIC - Single</v>
+        <v>Mail - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:53</v>
+        <v>2:14</v>
       </c>
       <c r="H186" t="str">
-        <v>Tiger La Flor</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/tiger-la-flor/1613113982</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/kodachromatic/6770724719</v>
+        <v>https://music.apple.com/us/album/mail/6769190634</v>
       </c>
       <c r="L186" t="str">
-        <v>KODACHROMATIC - Tiger La Flor</v>
+        <v>Mail - MexikoDro</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>FOMO</v>
+        <v>Waste Your Heart</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/fomo/1890190631</v>
+        <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-23</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Map Of Her Shadow</v>
+        <v>Waste Your Heart - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:01</v>
+        <v>2:31</v>
       </c>
       <c r="H187" t="str">
-        <v>Anais Cardot</v>
+        <v>Magnus Ferrell</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/fomo/1890190623</v>
+        <v>https://music.apple.com/us/album/waste-your-heart/6769241913</v>
       </c>
       <c r="L187" t="str">
-        <v>FOMO - Anais Cardot</v>
+        <v>Waste Your Heart - Magnus Ferrell</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Black Fire</v>
+        <v>Sleeping Pills</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/black-fire/6770696877</v>
+        <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-23</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Sulfur Surfer</v>
+        <v>Sleeping Pills - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:37</v>
+        <v>3:03</v>
       </c>
       <c r="H188" t="str">
-        <v>Bladee</v>
+        <v>Dolder</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/bladee/861359576</v>
+        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/black-fire/6770696743</v>
+        <v>https://music.apple.com/us/album/sleeping-pills/1896452689</v>
       </c>
       <c r="L188" t="str">
-        <v>Black Fire - Bladee</v>
+        <v>Sleeping Pills - Dolder</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>As Seen in the Unseen</v>
+        <v>KODACHROMATIC</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
+        <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-23</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Grand Serpent Rising</v>
+        <v>KODACHROMATIC - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>6:59</v>
+        <v>2:53</v>
       </c>
       <c r="H189" t="str">
-        <v>Dimmu Borgir</v>
+        <v>Tiger La Flor</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+        <v>https://music.apple.com/us/artist/tiger-la-flor/1613113982</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/as-seen-in-the-unseen/1883121436</v>
+        <v>https://music.apple.com/us/album/kodachromatic/6770724719</v>
       </c>
       <c r="L189" t="str">
-        <v>As Seen in the Unseen - Dimmu Borgir</v>
+        <v>KODACHROMATIC - Tiger La Flor</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Every Man-Any Man</v>
+        <v>FOMO</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
+        <v>https://music.apple.com/us/song/fomo/1890190631</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-23</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Emotion Factory Reset</v>
+        <v>Map Of Her Shadow</v>
       </c>
       <c r="G190" t="str">
-        <v>4:20</v>
+        <v>3:01</v>
       </c>
       <c r="H190" t="str">
-        <v>Armored Saint</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/every-man-any-man/1872193859</v>
+        <v>https://music.apple.com/us/album/fomo/1890190623</v>
       </c>
       <c r="L190" t="str">
-        <v>Every Man-Any Man - Armored Saint</v>
+        <v>FOMO - Anais Cardot</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>No Arms</v>
+        <v>Black Fire</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/no-arms/6765776563</v>
+        <v>https://music.apple.com/us/song/black-fire/6770696877</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-23</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>From A Distance</v>
+        <v>Sulfur Surfer</v>
       </c>
       <c r="G191" t="str">
-        <v>3:43</v>
+        <v>3:37</v>
       </c>
       <c r="H191" t="str">
-        <v>156/Silence</v>
+        <v>Bladee</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/156-silence/1071395282</v>
+        <v>https://music.apple.com/us/artist/bladee/861359576</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/no-arms/1896069437</v>
+        <v>https://music.apple.com/us/album/black-fire/6770696743</v>
       </c>
       <c r="L191" t="str">
-        <v>No Arms - 156/Silence</v>
+        <v>Black Fire - Bladee</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>It's Neverending</v>
+        <v>As Seen in the Unseen</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
+        <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-23</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Neverending</v>
+        <v>Grand Serpent Rising</v>
       </c>
       <c r="G192" t="str">
-        <v>8:35</v>
+        <v>6:59</v>
       </c>
       <c r="H192" t="str">
-        <v>Monolord</v>
+        <v>Dimmu Borgir</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/its-neverending/1871211801</v>
+        <v>https://music.apple.com/us/album/as-seen-in-the-unseen/1883121436</v>
       </c>
       <c r="L192" t="str">
-        <v>It's Neverending - Monolord</v>
+        <v>As Seen in the Unseen - Dimmu Borgir</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>The Kids Will Kill Us</v>
+        <v>Every Man-Any Man</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
+        <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-23</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>The Kids Will Kill Us - Single</v>
+        <v>Emotion Factory Reset</v>
       </c>
       <c r="G193" t="str">
-        <v>3:45</v>
+        <v>4:20</v>
       </c>
       <c r="H193" t="str">
-        <v>Witch Club Satan</v>
+        <v>Armored Saint</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/witch-club-satan/1626477576</v>
+        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/the-kids-will-kill-us/6766343272</v>
+        <v>https://music.apple.com/us/album/every-man-any-man/1872193859</v>
       </c>
       <c r="L193" t="str">
-        <v>The Kids Will Kill Us - Witch Club Satan</v>
+        <v>Every Man-Any Man - Armored Saint</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe")</v>
+        <v>No Arms</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
+        <v>https://music.apple.com/us/song/no-arms/6765776563</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-23</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe") - Single</v>
+        <v>From A Distance</v>
       </c>
       <c r="G194" t="str">
-        <v>3:20</v>
+        <v>3:43</v>
       </c>
       <c r="H194" t="str">
-        <v>The Darkness</v>
+        <v>156/Silence</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/the-darkness/2417388</v>
+        <v>https://music.apple.com/us/artist/156-silence/1071395282</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/masters-of-the-universe-from-masters-of-the-universe/6769065779</v>
+        <v>https://music.apple.com/us/album/no-arms/1896069437</v>
       </c>
       <c r="L194" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe") - The Darkness</v>
+        <v>No Arms - 156/Silence</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>All Day</v>
+        <v>It's Neverending</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/all-day/1880746584</v>
+        <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-23</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Feet On Fire</v>
+        <v>Neverending</v>
       </c>
       <c r="G195" t="str">
-        <v>2:29</v>
+        <v>8:35</v>
       </c>
       <c r="H195" t="str">
-        <v>Ben Chapman</v>
+        <v>Monolord</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/ben-chapman/1581192612</v>
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/all-day/1880746349</v>
+        <v>https://music.apple.com/us/album/its-neverending/1871211801</v>
       </c>
       <c r="L195" t="str">
-        <v>All Day - Ben Chapman</v>
+        <v>It's Neverending - Monolord</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Sigui</v>
+        <v>The Kids Will Kill Us</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/sigui/1890241955</v>
+        <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-23</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Massa</v>
+        <v>The Kids Will Kill Us - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:17</v>
+        <v>3:45</v>
       </c>
       <c r="H196" t="str">
-        <v>Fatoumata Diawara</v>
+        <v>Witch Club Satan</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/fatoumata-diawara/466213610</v>
+        <v>https://music.apple.com/us/artist/witch-club-satan/1626477576</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/sigui/1890241617</v>
+        <v>https://music.apple.com/us/album/the-kids-will-kill-us/6766343272</v>
       </c>
       <c r="L196" t="str">
-        <v>Sigui - Fatoumata Diawara</v>
+        <v>The Kids Will Kill Us - Witch Club Satan</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>High Tail</v>
+        <v>Masters of the Universe (from "Masters of the Universe")</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/high-tail/1870432994</v>
+        <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-23</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Where the South Winds Wail</v>
+        <v>Masters of the Universe (from "Masters of the Universe") - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:31</v>
+        <v>3:20</v>
       </c>
       <c r="H197" t="str">
-        <v>Gitkin</v>
+        <v>The Darkness</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/gitkin/1345281815</v>
+        <v>https://music.apple.com/us/artist/the-darkness/2417388</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/high-tail/1870432670</v>
+        <v>https://music.apple.com/us/album/masters-of-the-universe-from-masters-of-the-universe/6769065779</v>
       </c>
       <c r="L197" t="str">
-        <v>High Tail - Gitkin</v>
+        <v>Masters of the Universe (from "Masters of the Universe") - The Darkness</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Mice Protection</v>
+        <v>All Day</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
+        <v>https://music.apple.com/us/song/all-day/1880746584</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-23</v>
@@ -7899,68 +7899,182 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Ugly Duckling Union</v>
+        <v>Feet On Fire</v>
       </c>
       <c r="G198" t="str">
-        <v>3:34</v>
+        <v>2:29</v>
       </c>
       <c r="H198" t="str">
-        <v>Lowertown</v>
+        <v>Ben Chapman</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/lowertown/1448207323</v>
+        <v>https://music.apple.com/us/artist/ben-chapman/1581192612</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/mice-protection/1872171971</v>
+        <v>https://music.apple.com/us/album/all-day/1880746349</v>
       </c>
       <c r="L198" t="str">
-        <v>Mice Protection - Lowertown</v>
+        <v>All Day - Ben Chapman</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
+        <v>Sigui</v>
+      </c>
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
+        <v>https://music.apple.com/us/song/sigui/1890241955</v>
+      </c>
+      <c r="D199" t="str">
+        <v>2026-05-23</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v>Massa</v>
+      </c>
+      <c r="G199" t="str">
+        <v>3:17</v>
+      </c>
+      <c r="H199" t="str">
+        <v>Fatoumata Diawara</v>
+      </c>
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
+        <v>https://music.apple.com/us/artist/fatoumata-diawara/466213610</v>
+      </c>
+      <c r="K199" t="str">
+        <v>https://music.apple.com/us/album/sigui/1890241617</v>
+      </c>
+      <c r="L199" t="str">
+        <v>Sigui - Fatoumata Diawara</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>High Tail</v>
+      </c>
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
+        <v>https://music.apple.com/us/song/high-tail/1870432994</v>
+      </c>
+      <c r="D200" t="str">
+        <v>2026-05-23</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
+        <v>Where the South Winds Wail</v>
+      </c>
+      <c r="G200" t="str">
+        <v>2:31</v>
+      </c>
+      <c r="H200" t="str">
+        <v>Gitkin</v>
+      </c>
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
+        <v>https://music.apple.com/us/artist/gitkin/1345281815</v>
+      </c>
+      <c r="K200" t="str">
+        <v>https://music.apple.com/us/album/high-tail/1870432670</v>
+      </c>
+      <c r="L200" t="str">
+        <v>High Tail - Gitkin</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>Mice Protection</v>
+      </c>
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
+        <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-05-23</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v>Ugly Duckling Union</v>
+      </c>
+      <c r="G201" t="str">
+        <v>3:34</v>
+      </c>
+      <c r="H201" t="str">
+        <v>Lowertown</v>
+      </c>
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
+        <v>https://music.apple.com/us/artist/lowertown/1448207323</v>
+      </c>
+      <c r="K201" t="str">
+        <v>https://music.apple.com/us/album/mice-protection/1872171971</v>
+      </c>
+      <c r="L201" t="str">
+        <v>Mice Protection - Lowertown</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
         <v>Tóxica</v>
       </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
         <v>https://music.apple.com/us/song/t%C3%B3xica/6763056240</v>
       </c>
-      <c r="D199" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
+      <c r="D202" t="str">
+        <v>2026-05-23</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
         <v>Caribenya</v>
       </c>
-      <c r="G199" t="str">
+      <c r="G202" t="str">
         <v>3:48</v>
       </c>
-      <c r="H199" t="str">
+      <c r="H202" t="str">
         <v>Lido Pimienta</v>
       </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
         <v>https://music.apple.com/us/artist/lido-pimienta/389475023</v>
       </c>
-      <c r="K199" t="str">
+      <c r="K202" t="str">
         <v>https://music.apple.com/us/album/t%C3%B3xica/1895141218</v>
       </c>
-      <c r="L199" t="str">
+      <c r="L202" t="str">
         <v>Tóxica - Lido Pimienta</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week04/titles.xlsx
+++ b/data/global/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L202"/>
+  <dimension ref="A1:L199"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון בניטה - אכאב בשקט קאבר</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-23</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410989&amp;sid=343b179fe8bb09f870415378e128ebb7</v>
+        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-23</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>23 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Duran Duran</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון בניטה - אכאב בשקט קאבר</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רונן לוגסי - אבא יקר קאבר</v>
+        <v>Nico Santos - Optimist</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-23</v>
+        <v>3 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410988&amp;sid=343b179fe8bb09f870415378e128ebb7</v>
+        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-23</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>3 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Nico Santos</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רונן לוגסי - אבא יקר קאבר</v>
+        <v>Nico Santos - Optimist - Nico Santos</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>קורל אמויאל - עכשיו אתה חוזר בחזרה קאבר</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-23</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410987&amp;sid=343b179fe8bb09f870415378e128ebb7</v>
+        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-23</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>7 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>קורל אמויאל - עכשיו אתה חוזר בחזרה קאבר</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B5" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
+        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-23</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Duran Duran</v>
+        <v>Will Linley</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Nico Santos - Optimist</v>
+        <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
+        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-23</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Nico Santos</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Nico Santos - Optimist - Nico Santos</v>
+        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>4 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
+        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-23</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>4 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
+        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-23</v>
@@ -685,7 +685,7 @@
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Will Linley</v>
+        <v>The Offspring</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video)</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
+        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-23</v>
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Kylie Minogue</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B10" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
+        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-23</v>
@@ -761,7 +761,7 @@
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Billy Raffoul</v>
+        <v>Scorpions</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B11" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
+        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-23</v>
@@ -799,7 +799,7 @@
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>The Offspring</v>
+        <v>Brandon Lake</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
+        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-23</v>
@@ -837,7 +837,7 @@
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>David Gilmour</v>
+        <v>Kygo and Dan Tyminski</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
+        <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B13" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
+        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-23</v>
@@ -875,7 +875,7 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Scorpions</v>
+        <v>The Warning</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
+        <v>The Warning - Ego (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
+        <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B14" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
+        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-23</v>
@@ -913,7 +913,7 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Brandon Lake</v>
+        <v>paris jackson</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake</v>
+        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B15" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
+        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-23</v>
@@ -951,7 +951,7 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Kygo and Dan Tyminski</v>
+        <v>Minelli</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>The Warning - Ego (Official Video)</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B16" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
+        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-23</v>
@@ -989,7 +989,7 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>The Warning</v>
+        <v>Maggie Rose</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>The Warning - Ego (Official Video) - The Warning</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>paris jackson - teenage drama (official lyric video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B17" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
+        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-23</v>
@@ -1027,7 +1027,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>paris jackson</v>
+        <v>David Guetta</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B18" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
+        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-23</v>
@@ -1065,7 +1065,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Minelli</v>
+        <v>Chris Young and Shaylen</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
+        <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B19" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
+        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-23</v>
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Maggie Rose</v>
+        <v>Lauv</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
+        <v>Lauv - Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B20" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
+        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-23</v>
@@ -1141,7 +1141,7 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>David Guetta</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
+        <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B21" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
+        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-23</v>
@@ -1179,7 +1179,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Chris Young and Shaylen</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
+        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Lauv - Pretty Little Things</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B22" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-23</v>
@@ -1217,7 +1217,7 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Lauv</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Lauv - Pretty Little Things - Lauv</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B23" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-23</v>
@@ -1255,7 +1255,7 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Icona Pop</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Will Swinton - Only One (Official Video)</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B24" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-23</v>
@@ -1293,7 +1293,7 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Will Swinton</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B25" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-23</v>
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Dean Lewis</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-23</v>
@@ -1369,7 +1369,7 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>RUEL</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B27" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-23</v>
@@ -1407,7 +1407,7 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Niall Horan</v>
+        <v>TINI</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B28" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-23</v>
@@ -1445,7 +1445,7 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B29" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-23</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>RUEL</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-23</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>TINI</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B31" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-23</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Charli xcx</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-23</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Dua Lipa</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-23</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Matilda Mann</v>
+        <v>kesha</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-23</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Ella Langley</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B35" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-23</v>
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B36" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-23</v>
@@ -1749,7 +1749,7 @@
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>kesha</v>
+        <v>The Analogues</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B37" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-23</v>
@@ -1787,7 +1787,7 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Holly Humberstone</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B38" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-23</v>
@@ -1825,7 +1825,7 @@
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Foo Fighters</v>
+        <v>Blue October</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B39" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-23</v>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>The Analogues</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B40" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-23</v>
@@ -1901,7 +1901,7 @@
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Rod Stewart</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>Kenia Os - Love Bombing - Kenia Os</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B41" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
+        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-23</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Blue October</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Far Caspian - hum (Official Video)</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B42" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-23</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Far Caspian</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Kenia Os - Love Bombing</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B43" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-23</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Kenia Os</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Kenia Os - Love Bombing - Kenia Os</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B44" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-23</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B45" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-23</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B46" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-23</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B47" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-23</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-23</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Evanescence</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>6 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-23</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>6 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B50" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-23</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-23</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Evanescence</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-23</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-23</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Armin van Buuren</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-23</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Madison Cunningham</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B55" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-23</v>
@@ -2471,7 +2471,7 @@
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Johnny Orlando</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B56" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-23</v>
@@ -2509,7 +2509,7 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Carver Jones</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B57" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-23</v>
@@ -2547,7 +2547,7 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Jazmin bean</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B58" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-23</v>
@@ -2585,7 +2585,7 @@
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Baby Queen</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-23</v>
@@ -2623,7 +2623,7 @@
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Switchfoot</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B60" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-23</v>
@@ -2661,7 +2661,7 @@
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Grace Potter</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-23</v>
@@ -2699,7 +2699,7 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B62" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-23</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>The All-American Rejects</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B63" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-23</v>
@@ -2775,7 +2775,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Henry Moodie</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B64" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-23</v>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Spacey Jane</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B65" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-23</v>
@@ -2851,7 +2851,7 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Megan Moroney</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B66" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-23</v>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Matt Hansen</v>
+        <v>VALÉ</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
+        <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B67" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
+        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-23</v>
@@ -2927,7 +2927,7 @@
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Matt Hansen</v>
+        <v>Mackenzie Carpenter</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
+        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Keith Urban - Steal Away (Visualizer)</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
+        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-23</v>
@@ -2965,7 +2965,7 @@
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Keith Urban</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>VALÉ - Mugshot (Official Video)</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B69" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
+        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-23</v>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>VALÉ</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio)</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
+        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-23</v>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Mackenzie Carpenter</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
+        <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B71" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
+        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-23</v>
@@ -3079,7 +3079,7 @@
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Towa Bird</v>
+        <v>Becky G</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
+        <v>Becky G - EPA (Official Video) - Becky G</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
+        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-23</v>
@@ -3117,7 +3117,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Sabrina Sterling</v>
+        <v>Daisy the Great</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
+        <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
+        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-23</v>
@@ -3155,7 +3155,7 @@
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Little Big Town</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
+        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Becky G - EPA (Official Video)</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B74" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
+        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-23</v>
@@ -3193,7 +3193,7 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Becky G</v>
+        <v>Madonna</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Becky G - EPA (Official Video) - Becky G</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
+        <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B75" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
+        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-23</v>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Daisy the Great</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
+        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Towa Bird - Dog (Official Music Video)</v>
+        <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B76" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
+        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-23</v>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Towa Bird</v>
+        <v>Bella White</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
+        <v>Bella White - Better - Official Music Video - Bella White</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B77" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
+        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-23</v>
@@ -3307,7 +3307,7 @@
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Madonna</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video)</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B78" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
+        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-23</v>
@@ -3345,7 +3345,7 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Ally Salort</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Bella White - Better - Official Music Video</v>
+        <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B79" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
+        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-23</v>
@@ -3383,7 +3383,7 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Bella White</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Bella White - Better - Official Music Video - Bella White</v>
+        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B80" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
+        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-23</v>
@@ -3421,7 +3421,7 @@
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
+        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-23</v>
@@ -3459,7 +3459,7 @@
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Towa Bird</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer)</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B82" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
+        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-23</v>
@@ -3497,7 +3497,7 @@
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Miranda Lambert</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B83" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
+        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-23</v>
@@ -3535,7 +3535,7 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Lady Gaga</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
+        <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B84" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
+        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-23</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Gracie Abrams</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
+        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
+        <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
+        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-23</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>The Last Dinner Party</v>
+        <v>LP</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
+        <v>LP - Shelly (Official Music Video) - LP</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B86" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
+        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-23</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Martin Garrix</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Jorja Smith - What's Done Is Done</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B87" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
+        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-23</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Jorja Smith</v>
+        <v>Oasis</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>LP - Shelly (Official Music Video)</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B88" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
+        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-23</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>LP</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>LP - Shelly (Official Music Video) - LP</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B89" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
+        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-23</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>The Rolling Stones</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B90" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
+        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-23</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Oasis</v>
+        <v>Linkin Park</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
+        <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
+        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-23</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Breaking Benjamin</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
+        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
+        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-23</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>VictorBiliac</v>
+        <v>Eagles</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B93" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
+        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-23</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Linkin Park</v>
+        <v>Nora Fatehi</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Harry Styles - Dance No More (Official Video)</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
+        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-23</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Harry Styles</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
+        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-23</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Eagles</v>
+        <v>Eurovision Song Contest and Alis</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
+        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-23</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Nora Fatehi</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
+        <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
+        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-23</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>The Head And The Heart</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B98" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
+        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-23</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Eurovision Song Contest and Alis</v>
+        <v>Simply Red</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
+        <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 months ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
+        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-23</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 months ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Talking Heads</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video)</v>
+        <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
+        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-23</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>The Head And The Heart</v>
+        <v>Ellise</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
+        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
+        <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
+        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-23</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Simply Red</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
+        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video)</v>
+        <v>From Down Here</v>
       </c>
       <c r="B102" t="str">
-        <v>13 days ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
+        <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-23</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>13 days ago</v>
+        <v>From Down Here - Single</v>
       </c>
       <c r="G102" t="str">
-        <v/>
+        <v>4:01</v>
       </c>
       <c r="H102" t="str">
-        <v>Talking Heads</v>
+        <v>Lola Young</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/lola-young/452271760</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/from-down-here/6768357139</v>
       </c>
       <c r="L102" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
+        <v>From Down Here - Lola Young</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Ellise - Liplock (Official Music Video)</v>
+        <v>the cure</v>
       </c>
       <c r="B103" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
+        <v>https://music.apple.com/us/song/the-cure/1889992123</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-23</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>2 weeks ago</v>
+        <v>you seem pretty sad for a girl so in love</v>
       </c>
       <c r="G103" t="str">
-        <v/>
+        <v>4:57</v>
       </c>
       <c r="H103" t="str">
-        <v>Ellise</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/the-cure/1889992111</v>
       </c>
       <c r="L103" t="str">
-        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
+        <v>the cure - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Tori Kelly - Dive (Official Music Video)</v>
+        <v>SS26</v>
       </c>
       <c r="B104" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
+        <v>https://music.apple.com/us/song/ss26/6771061782</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-23</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>2 weeks ago</v>
+        <v>SS26 - Single</v>
       </c>
       <c r="G104" t="str">
-        <v/>
+        <v>2:47</v>
       </c>
       <c r="H104" t="str">
-        <v>Tori Kelly</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/ss26/6771061771</v>
       </c>
       <c r="L104" t="str">
-        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
+        <v>SS26 - Charli xcx</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>From Down Here</v>
+        <v>White Flag</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
+        <v>https://music.apple.com/us/song/white-flag/1887627840</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-23</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>From Down Here - Single</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G105" t="str">
-        <v>4:01</v>
+        <v>2:34</v>
       </c>
       <c r="H105" t="str">
-        <v>Lola Young</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/lola-young/452271760</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/from-down-here/6768357139</v>
+        <v>https://music.apple.com/us/album/white-flag/1887627836</v>
       </c>
       <c r="L105" t="str">
-        <v>From Down Here - Lola Young</v>
+        <v>White Flag - Vince Staples</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>the cure</v>
+        <v>Knew Better Part Two</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/the-cure/1889992123</v>
+        <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-23</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>you seem pretty sad for a girl so in love</v>
+        <v>Dangerous Woman (Tenth Anniversary Edition)</v>
       </c>
       <c r="G106" t="str">
-        <v>4:57</v>
+        <v>2:44</v>
       </c>
       <c r="H106" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/the-cure/1889992111</v>
+        <v>https://music.apple.com/us/album/knew-better-part-two/6770600996</v>
       </c>
       <c r="L106" t="str">
-        <v>the cure - Olivia Rodrigo</v>
+        <v>Knew Better Part Two - Ariana Grande</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>SS26</v>
+        <v>Goals</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/ss26/6771061782</v>
+        <v>https://music.apple.com/us/song/goals/6769251838</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-23</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>SS26 - Single</v>
+        <v>Goals (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>2:47</v>
+        <v>3:00</v>
       </c>
       <c r="H107" t="str">
-        <v>Charli xcx</v>
+        <v>LISA</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v>https://music.apple.com/us/artist/lisa/1583908668</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/ss26/6771061771</v>
+        <v>https://music.apple.com/us/album/goals/6769251829</v>
       </c>
       <c r="L107" t="str">
-        <v>SS26 - Charli xcx</v>
+        <v>Goals - LISA</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>White Flag</v>
+        <v>we should talk</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/white-flag/1887627840</v>
+        <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-23</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Cry Baby</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G108" t="str">
-        <v>2:34</v>
+        <v>3:04</v>
       </c>
       <c r="H108" t="str">
-        <v>Vince Staples</v>
+        <v>Bleachers</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/white-flag/1887627836</v>
+        <v>https://music.apple.com/us/album/we-should-talk/1872842313</v>
       </c>
       <c r="L108" t="str">
-        <v>White Flag - Vince Staples</v>
+        <v>we should talk - Bleachers</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Knew Better Part Two</v>
+        <v>Do What You Gotta Do</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
+        <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-23</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Dangerous Woman (Tenth Anniversary Edition)</v>
+        <v>NeverAlways (Vol. 2)</v>
       </c>
       <c r="G109" t="str">
-        <v>2:44</v>
+        <v>3:26</v>
       </c>
       <c r="H109" t="str">
-        <v>Ariana Grande</v>
+        <v>The Band CAMINO</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/knew-better-part-two/6770600996</v>
+        <v>https://music.apple.com/us/album/do-what-you-gotta-do/1887616173</v>
       </c>
       <c r="L109" t="str">
-        <v>Knew Better Part Two - Ariana Grande</v>
+        <v>Do What You Gotta Do - The Band CAMINO</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Goals</v>
+        <v>Ego</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/goals/6769251838</v>
+        <v>https://music.apple.com/us/song/ego/6769207667</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-23</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Goals (FIFA World Cup 2026™) - Single</v>
+        <v>Ego - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:00</v>
+        <v>2:53</v>
       </c>
       <c r="H110" t="str">
-        <v>LISA</v>
+        <v>The Warning</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/lisa/1583908668</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/goals/6769251829</v>
+        <v>https://music.apple.com/us/album/ego/6769207665</v>
       </c>
       <c r="L110" t="str">
-        <v>Goals - LISA</v>
+        <v>Ego - The Warning</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>we should talk</v>
+        <v>Light up (From the Netflix Documentary 'kylie')</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
+        <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-23</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Light up (From the Netflix Documentary 'Kylie') - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:04</v>
+        <v>3:17</v>
       </c>
       <c r="H111" t="str">
-        <v>Bleachers</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/kylie-minogue/465031</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/we-should-talk/1872842313</v>
+        <v>https://music.apple.com/us/album/light-up-from-the-netflix-documentary-kylie/6768013505</v>
       </c>
       <c r="L111" t="str">
-        <v>we should talk - Bleachers</v>
+        <v>Light up (From the Netflix Documentary 'kylie') - Kylie Minogue</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Do What You Gotta Do</v>
+        <v>All That Matters</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
+        <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-23</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>NeverAlways (Vol. 2)</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G112" t="str">
-        <v>3:26</v>
+        <v>3:43</v>
       </c>
       <c r="H112" t="str">
-        <v>The Band CAMINO</v>
+        <v>6LACK</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/do-what-you-gotta-do/1887616173</v>
+        <v>https://music.apple.com/us/album/all-that-matters/1884792154</v>
       </c>
       <c r="L112" t="str">
-        <v>Do What You Gotta Do - The Band CAMINO</v>
+        <v>All That Matters - 6LACK</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Ego</v>
+        <v>Like A Virgin</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/ego/6769207667</v>
+        <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-23</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Ego - Single</v>
+        <v>Terrified .</v>
       </c>
       <c r="G113" t="str">
-        <v>2:53</v>
+        <v>2:34</v>
       </c>
       <c r="H113" t="str">
-        <v>The Warning</v>
+        <v>fakemink</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/ego/6769207665</v>
+        <v>https://music.apple.com/us/album/like-a-virgin/6768157748</v>
       </c>
       <c r="L113" t="str">
-        <v>Ego - The Warning</v>
+        <v>Like A Virgin - fakemink</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Light up (From the Netflix Documentary 'kylie')</v>
+        <v>24 Hours</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
+        <v>https://music.apple.com/us/song/24-hours/6771060076</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-23</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Light up (From the Netflix Documentary 'Kylie') - Single</v>
+        <v>24 Hours - Single</v>
       </c>
       <c r="G114" t="str">
         <v>3:17</v>
       </c>
       <c r="H114" t="str">
-        <v>Kylie Minogue</v>
+        <v>Stormzy</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/kylie-minogue/465031</v>
+        <v>https://music.apple.com/us/artist/stormzy/394865154</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/light-up-from-the-netflix-documentary-kylie/6768013505</v>
+        <v>https://music.apple.com/us/album/24-hours/6771060073</v>
       </c>
       <c r="L114" t="str">
-        <v>Light up (From the Netflix Documentary 'kylie') - Kylie Minogue</v>
+        <v>24 Hours - Stormzy</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>All That Matters</v>
+        <v>HOES (From Scary Movie)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
+        <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-23</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>HOES (From Scary Movie) - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:43</v>
+        <v>2:09</v>
       </c>
       <c r="H115" t="str">
-        <v>6LACK</v>
+        <v>Lizzo</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/all-that-matters/1884792154</v>
+        <v>https://music.apple.com/us/album/hoes-from-scary-movie/6770661290</v>
       </c>
       <c r="L115" t="str">
-        <v>All That Matters - 6LACK</v>
+        <v>HOES (From Scary Movie) - Lizzo</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Like A Virgin</v>
+        <v>Ms. Tundra</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
+        <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-23</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Terrified .</v>
+        <v>Highway 79</v>
       </c>
       <c r="G116" t="str">
-        <v>2:34</v>
+        <v>3:12</v>
       </c>
       <c r="H116" t="str">
-        <v>fakemink</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/like-a-virgin/6768157748</v>
+        <v>https://music.apple.com/us/album/ms-tundra/6770614875</v>
       </c>
       <c r="L116" t="str">
-        <v>Like A Virgin - fakemink</v>
+        <v>Ms. Tundra - Ne-Yo</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>24 Hours</v>
+        <v>TARENTINO</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/24-hours/6771060076</v>
+        <v>https://music.apple.com/us/song/tarentino/6769927265</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-23</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>24 Hours - Single</v>
+        <v>TARENTINO - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:17</v>
+        <v>2:23</v>
       </c>
       <c r="H117" t="str">
-        <v>Stormzy</v>
+        <v>Labrinth</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/stormzy/394865154</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/24-hours/6771060073</v>
+        <v>https://music.apple.com/us/album/tarentino/6769927262</v>
       </c>
       <c r="L117" t="str">
-        <v>24 Hours - Stormzy</v>
+        <v>TARENTINO - Labrinth</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>HOES (From Scary Movie)</v>
+        <v>Daydreamin’</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
+        <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-23</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>HOES (From Scary Movie) - Single</v>
+        <v>KONNAKOL (Deluxe)</v>
       </c>
       <c r="G118" t="str">
-        <v>2:09</v>
+        <v>2:58</v>
       </c>
       <c r="H118" t="str">
-        <v>Lizzo</v>
+        <v>ZAYN</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/hoes-from-scary-movie/6770661290</v>
+        <v>https://music.apple.com/us/album/daydreamin/6769559345</v>
       </c>
       <c r="L118" t="str">
-        <v>HOES (From Scary Movie) - Lizzo</v>
+        <v>Daydreamin’ - ZAYN</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Ms. Tundra</v>
+        <v>End of an Era</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
+        <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-23</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Highway 79</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G119" t="str">
-        <v>3:12</v>
+        <v>3:38</v>
       </c>
       <c r="H119" t="str">
-        <v>Ne-Yo</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/ms-tundra/6770614875</v>
+        <v>https://music.apple.com/us/album/end-of-an-era/1884418567</v>
       </c>
       <c r="L119" t="str">
-        <v>Ms. Tundra - Ne-Yo</v>
+        <v>End of an Era - Niall Horan</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>TARENTINO</v>
+        <v>Questions</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/tarentino/6769927265</v>
+        <v>https://music.apple.com/us/song/questions/1871502847</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-23</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>TARENTINO - Single</v>
+        <v>Florescence</v>
       </c>
       <c r="G120" t="str">
-        <v>2:23</v>
+        <v>3:07</v>
       </c>
       <c r="H120" t="str">
-        <v>Labrinth</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/tarentino/6769927262</v>
+        <v>https://music.apple.com/us/album/questions/1871502372</v>
       </c>
       <c r="L120" t="str">
-        <v>TARENTINO - Labrinth</v>
+        <v>Questions - Maisie Peters</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Daydreamin’</v>
+        <v>Heart Has To Work So Hard</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
+        <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-23</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>KONNAKOL (Deluxe)</v>
+        <v>Heart Has To Work So Hard - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:58</v>
+        <v>3:12</v>
       </c>
       <c r="H121" t="str">
-        <v>ZAYN</v>
+        <v>Blondshell</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/blondshell/1624592688</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/daydreamin/6769559345</v>
+        <v>https://music.apple.com/us/album/heart-has-to-work-so-hard/1895982147</v>
       </c>
       <c r="L121" t="str">
-        <v>Daydreamin’ - ZAYN</v>
+        <v>Heart Has To Work So Hard - Blondshell</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>End of an Era</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
+        <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-23</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Dinner Party</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski) - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:38</v>
+        <v>3:44</v>
       </c>
       <c r="H122" t="str">
-        <v>Niall Horan</v>
+        <v>Kygo</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/end-of-an-era/1884418567</v>
+        <v>https://music.apple.com/us/album/heaven-on-your-mind-feat-dan-tyminski/6769007431</v>
       </c>
       <c r="L122" t="str">
-        <v>End of an Era - Niall Horan</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski) - Kygo</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Questions</v>
+        <v>PERDISTE EL EMMY.</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/questions/1871502847</v>
+        <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-23</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Florescence</v>
+        <v>OMAKASE</v>
       </c>
       <c r="G123" t="str">
-        <v>3:07</v>
+        <v>4:03</v>
       </c>
       <c r="H123" t="str">
-        <v>Maisie Peters</v>
+        <v>Álvaro Díaz</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/questions/1871502372</v>
+        <v>https://music.apple.com/us/album/perdiste-el-emmy/6771082594</v>
       </c>
       <c r="L123" t="str">
-        <v>Questions - Maisie Peters</v>
+        <v>PERDISTE EL EMMY. - Álvaro Díaz</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Heart Has To Work So Hard</v>
+        <v>Dosis</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
+        <v>https://music.apple.com/us/song/dosis/6762929729</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-23</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Heart Has To Work So Hard - Single</v>
+        <v>DOSIS</v>
       </c>
       <c r="G124" t="str">
-        <v>3:12</v>
+        <v>3:00</v>
       </c>
       <c r="H124" t="str">
-        <v>Blondshell</v>
+        <v>Xavi</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/blondshell/1624592688</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/heart-has-to-work-so-hard/1895982147</v>
+        <v>https://music.apple.com/us/album/dosis/1895081885</v>
       </c>
       <c r="L124" t="str">
-        <v>Heart Has To Work So Hard - Blondshell</v>
+        <v>Dosis - Xavi</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski)</v>
+        <v>Would U Still Love Me</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
+        <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-23</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski) - Single</v>
+        <v>Whitcomb vs. Flores - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:44</v>
+        <v>2:36</v>
       </c>
       <c r="H125" t="str">
-        <v>Kygo</v>
+        <v>Diplo</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-your-mind-feat-dan-tyminski/6769007431</v>
+        <v>https://music.apple.com/us/album/would-u-still-love-me/6769907832</v>
       </c>
       <c r="L125" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski) - Kygo</v>
+        <v>Would U Still Love Me - Diplo</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>PERDISTE EL EMMY.</v>
+        <v>Saving This Bottle</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
+        <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-23</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>OMAKASE</v>
+        <v>Whitcomb vs. Flores - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>4:03</v>
+        <v>3:05</v>
       </c>
       <c r="H126" t="str">
-        <v>Álvaro Díaz</v>
+        <v>Diplo</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
+        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/perdiste-el-emmy/6771082594</v>
+        <v>https://music.apple.com/us/album/saving-this-bottle/6769907832</v>
       </c>
       <c r="L126" t="str">
-        <v>PERDISTE EL EMMY. - Álvaro Díaz</v>
+        <v>Saving This Bottle - Diplo</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Dosis</v>
+        <v>The Climb</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/dosis/6762929729</v>
+        <v>https://music.apple.com/us/song/the-climb/6769546149</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-23</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>DOSIS</v>
+        <v>The Climb - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:00</v>
+        <v>3:50</v>
       </c>
       <c r="H127" t="str">
-        <v>Xavi</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/dosis/1895081885</v>
+        <v>https://music.apple.com/us/album/the-climb/6769546147</v>
       </c>
       <c r="L127" t="str">
-        <v>Dosis - Xavi</v>
+        <v>The Climb - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Would U Still Love Me</v>
+        <v>everything tatted</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
+        <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-23</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Whitcomb vs. Flores - Single</v>
+        <v>everything tatted - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:36</v>
+        <v>3:25</v>
       </c>
       <c r="H128" t="str">
-        <v>Diplo</v>
+        <v>mgk</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/would-u-still-love-me/6769907832</v>
+        <v>https://music.apple.com/us/album/everything-tatted/6770773606</v>
       </c>
       <c r="L128" t="str">
-        <v>Would U Still Love Me - Diplo</v>
+        <v>everything tatted - mgk</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Saving This Bottle</v>
+        <v>BOOMPALA</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
+        <v>https://music.apple.com/us/song/boompala/1894802726</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-23</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Whitcomb vs. Flores - Single</v>
+        <v>'PUREFLOW', Pt. 1</v>
       </c>
       <c r="G129" t="str">
-        <v>3:05</v>
+        <v>2:56</v>
       </c>
       <c r="H129" t="str">
-        <v>Diplo</v>
+        <v>LE SSERAFIM</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
+        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/saving-this-bottle/6769907832</v>
+        <v>https://music.apple.com/us/album/boompala/1894802719</v>
       </c>
       <c r="L129" t="str">
-        <v>Saving This Bottle - Diplo</v>
+        <v>BOOMPALA - LE SSERAFIM</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>The Climb</v>
+        <v>Let Me Be In Your Arms</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/the-climb/6769546149</v>
+        <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-23</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>The Climb - Single</v>
+        <v>can we do it all again?</v>
       </c>
       <c r="G130" t="str">
-        <v>3:50</v>
+        <v>3:13</v>
       </c>
       <c r="H130" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/the-climb/6769546147</v>
+        <v>https://music.apple.com/us/album/let-me-be-in-your-arms/1881610862</v>
       </c>
       <c r="L130" t="str">
-        <v>The Climb - Bailey Zimmerman</v>
+        <v>Let Me Be In Your Arms - Sonny Fodera</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>everything tatted</v>
+        <v>Eat, Work, Pray</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
+        <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-23</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>everything tatted - Single</v>
+        <v>Eat, Work, Pray - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:25</v>
+        <v>2:28</v>
       </c>
       <c r="H131" t="str">
-        <v>mgk</v>
+        <v>Sheff G</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/everything-tatted/6770773606</v>
+        <v>https://music.apple.com/us/album/eat-work-pray/6769134493</v>
       </c>
       <c r="L131" t="str">
-        <v>everything tatted - mgk</v>
+        <v>Eat, Work, Pray - Sheff G</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>BOOMPALA</v>
+        <v>touch myself</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/boompala/1894802726</v>
+        <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-23</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>'PUREFLOW', Pt. 1</v>
+        <v>and all pride aside</v>
       </c>
       <c r="G132" t="str">
-        <v>2:56</v>
+        <v>4:09</v>
       </c>
       <c r="H132" t="str">
-        <v>LE SSERAFIM</v>
+        <v>kwn</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/boompala/1894802719</v>
+        <v>https://music.apple.com/us/album/touch-myself/6769880663</v>
       </c>
       <c r="L132" t="str">
-        <v>BOOMPALA - LE SSERAFIM</v>
+        <v>touch myself - kwn</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Let Me Be In Your Arms</v>
+        <v>Comes and Goes</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
+        <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-23</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>can we do it all again?</v>
+        <v>Comes and Goes - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:13</v>
+        <v>4:22</v>
       </c>
       <c r="H133" t="str">
-        <v>Sonny Fodera</v>
+        <v>KETTAMA</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/kettama/1425703970</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/let-me-be-in-your-arms/1881610862</v>
+        <v>https://music.apple.com/us/album/comes-and-goes/6766618930</v>
       </c>
       <c r="L133" t="str">
-        <v>Let Me Be In Your Arms - Sonny Fodera</v>
+        <v>Comes and Goes - KETTAMA</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Eat, Work, Pray</v>
+        <v>Dear God</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
+        <v>https://music.apple.com/us/song/dear-god/1878237813</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-23</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Eat, Work, Pray - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G134" t="str">
-        <v>2:28</v>
+        <v>6:08</v>
       </c>
       <c r="H134" t="str">
-        <v>Sheff G</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/eat-work-pray/6769134493</v>
+        <v>https://music.apple.com/us/album/dear-god/1878237662</v>
       </c>
       <c r="L134" t="str">
-        <v>Eat, Work, Pray - Sheff G</v>
+        <v>Dear God - The Pretty Reckless</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>touch myself</v>
+        <v>Hexagons</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
+        <v>https://music.apple.com/us/song/hexagons/1885607736</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-23</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>and all pride aside</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G135" t="str">
-        <v>4:09</v>
+        <v>5:26</v>
       </c>
       <c r="H135" t="str">
-        <v>kwn</v>
+        <v>Muse</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/touch-myself/6769880663</v>
+        <v>https://music.apple.com/us/album/hexagons/1885607338</v>
       </c>
       <c r="L135" t="str">
-        <v>touch myself - kwn</v>
+        <v>Hexagons - Muse</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Comes and Goes</v>
+        <v>Facile-Batiste</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
+        <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-23</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Comes and Goes - Single</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G136" t="str">
-        <v>4:22</v>
+        <v>4:55</v>
       </c>
       <c r="H136" t="str">
-        <v>KETTAMA</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/kettama/1425703970</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/comes-and-goes/6766618930</v>
+        <v>https://music.apple.com/us/album/facile-batiste/1895866355</v>
       </c>
       <c r="L136" t="str">
-        <v>Comes and Goes - KETTAMA</v>
+        <v>Facile-Batiste - Jon Batiste</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Dear God</v>
+        <v>Pop Pop</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/dear-god/1878237813</v>
+        <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-23</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Dear God</v>
+        <v>Pop Pop - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>6:08</v>
+        <v>2:57</v>
       </c>
       <c r="H137" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Channel Tres</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/dear-god/1878237662</v>
+        <v>https://music.apple.com/us/album/pop-pop/1896269430</v>
       </c>
       <c r="L137" t="str">
-        <v>Dear God - The Pretty Reckless</v>
+        <v>Pop Pop - Channel Tres</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Hexagons</v>
+        <v>One Of Us</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/hexagons/1885607736</v>
+        <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-23</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>The Wow! Signal</v>
+        <v>One Of Us - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>5:26</v>
+        <v>3:35</v>
       </c>
       <c r="H138" t="str">
-        <v>Muse</v>
+        <v>Chris Young</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/chris-young/4779205</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/hexagons/1885607338</v>
+        <v>https://music.apple.com/us/album/one-of-us/1895402922</v>
       </c>
       <c r="L138" t="str">
-        <v>Hexagons - Muse</v>
+        <v>One Of Us - Chris Young</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Facile-Batiste</v>
+        <v>Sins of the Father</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
+        <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-23</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Black Mozart</v>
+        <v>Is God Is (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G139" t="str">
-        <v>4:55</v>
+        <v>3:20</v>
       </c>
       <c r="H139" t="str">
-        <v>Jon Batiste</v>
+        <v>Moses Sumney</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/moses-sumney/843536848</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/facile-batiste/1895866355</v>
+        <v>https://music.apple.com/us/album/sins-of-the-father/6771012707</v>
       </c>
       <c r="L139" t="str">
-        <v>Facile-Batiste - Jon Batiste</v>
+        <v>Sins of the Father - Moses Sumney</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Pop Pop</v>
+        <v>Life On The Run</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
+        <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-23</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Pop Pop - Single</v>
+        <v>Life On The Run - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:57</v>
+        <v>3:49</v>
       </c>
       <c r="H140" t="str">
-        <v>Channel Tres</v>
+        <v>Brandi Carlile</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
+        <v>https://music.apple.com/us/artist/brandi-carlile/64387579</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/pop-pop/1896269430</v>
+        <v>https://music.apple.com/us/album/life-on-the-run/6766761019</v>
       </c>
       <c r="L140" t="str">
-        <v>Pop Pop - Channel Tres</v>
+        <v>Life On The Run - Brandi Carlile</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>One Of Us</v>
+        <v>New York Confident</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
+        <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-23</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>One Of Us - Single</v>
+        <v>New York Confident - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:35</v>
+        <v>2:27</v>
       </c>
       <c r="H141" t="str">
-        <v>Chris Young</v>
+        <v>Mark Ambor</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/chris-young/4779205</v>
+        <v>https://music.apple.com/us/artist/mark-ambor/1459754985</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/one-of-us/1895402922</v>
+        <v>https://music.apple.com/us/album/new-york-confident/6765558036</v>
       </c>
       <c r="L141" t="str">
-        <v>One Of Us - Chris Young</v>
+        <v>New York Confident - Mark Ambor</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Sins of the Father</v>
+        <v>pequeñita!</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
+        <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-23</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Is God Is (Original Motion Picture Soundtrack)</v>
+        <v>pequeñita! - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:20</v>
+        <v>2:39</v>
       </c>
       <c r="H142" t="str">
-        <v>Moses Sumney</v>
+        <v>Judeline</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/moses-sumney/843536848</v>
+        <v>https://music.apple.com/us/artist/judeline/1487503245</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/sins-of-the-father/6771012707</v>
+        <v>https://music.apple.com/us/album/peque%C3%B1ita/6769827604</v>
       </c>
       <c r="L142" t="str">
-        <v>Sins of the Father - Moses Sumney</v>
+        <v>pequeñita! - Judeline</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Life On The Run</v>
+        <v>Opaline</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
+        <v>https://music.apple.com/us/song/opaline/1886737060</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-23</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Life On The Run - Single</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G143" t="str">
-        <v>3:49</v>
+        <v>3:17</v>
       </c>
       <c r="H143" t="str">
-        <v>Brandi Carlile</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/brandi-carlile/64387579</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/life-on-the-run/6766761019</v>
+        <v>https://music.apple.com/us/album/opaline/1886736650</v>
       </c>
       <c r="L143" t="str">
-        <v>Life On The Run - Brandi Carlile</v>
+        <v>Opaline - Stephan Moccio</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>New York Confident</v>
+        <v>Pretty Little Things</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
+        <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-23</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>New York Confident - Single</v>
+        <v>Pretty Little Things - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:27</v>
+        <v>2:51</v>
       </c>
       <c r="H144" t="str">
-        <v>Mark Ambor</v>
+        <v>Lauv</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/mark-ambor/1459754985</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/new-york-confident/6765558036</v>
+        <v>https://music.apple.com/us/album/pretty-little-things/6767353963</v>
       </c>
       <c r="L144" t="str">
-        <v>New York Confident - Mark Ambor</v>
+        <v>Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>pequeñita!</v>
+        <v>COLORADO</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
+        <v>https://music.apple.com/us/song/colorado/6769065232</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-23</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>pequeñita! - Single</v>
+        <v>COLORADO - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:39</v>
+        <v>1:54</v>
       </c>
       <c r="H145" t="str">
-        <v>Judeline</v>
+        <v>Loud Luxury</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/judeline/1487503245</v>
+        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/peque%C3%B1ita/6769827604</v>
+        <v>https://music.apple.com/us/album/colorado/6769064981</v>
       </c>
       <c r="L145" t="str">
-        <v>pequeñita! - Judeline</v>
+        <v>COLORADO - Loud Luxury</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Opaline</v>
+        <v>Infidelidad</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/opaline/1886737060</v>
+        <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-23</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>El Disco de Salsa</v>
       </c>
       <c r="G146" t="str">
-        <v>3:17</v>
+        <v>3:29</v>
       </c>
       <c r="H146" t="str">
-        <v>Stephan Moccio</v>
+        <v>Neutro Shorty</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/neutro-shorty/1066850977</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/opaline/1886736650</v>
+        <v>https://music.apple.com/us/album/infidelidad/6768853655</v>
       </c>
       <c r="L146" t="str">
-        <v>Opaline - Stephan Moccio</v>
+        <v>Infidelidad - Neutro Shorty</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Pretty Little Things</v>
+        <v>Wrong Place, Wrong time</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
+        <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-23</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Pretty Little Things - Single</v>
+        <v>Y'all Won</v>
       </c>
       <c r="G147" t="str">
-        <v>2:51</v>
+        <v>2:57</v>
       </c>
       <c r="H147" t="str">
-        <v>Lauv</v>
+        <v>Veeze</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/pretty-little-things/6767353963</v>
+        <v>https://music.apple.com/us/album/wrong-place-wrong-time/6771553812</v>
       </c>
       <c r="L147" t="str">
-        <v>Pretty Little Things - Lauv</v>
+        <v>Wrong Place, Wrong time - Veeze</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>COLORADO</v>
+        <v>La Semana</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/colorado/6769065232</v>
+        <v>https://music.apple.com/us/song/la-semana/6769913466</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-23</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>COLORADO - Single</v>
+        <v>No Quiero Que Se Acabe Este Bendito Verano - EP</v>
       </c>
       <c r="G148" t="str">
-        <v>1:54</v>
+        <v>3:30</v>
       </c>
       <c r="H148" t="str">
-        <v>Loud Luxury</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/colorado/6769064981</v>
+        <v>https://music.apple.com/us/album/la-semana/6769913464</v>
       </c>
       <c r="L148" t="str">
-        <v>COLORADO - Loud Luxury</v>
+        <v>La Semana - ELENA ROSE</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Infidelidad</v>
+        <v>Una Mujer Como la Suya</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
+        <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-23</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>El Disco de Salsa</v>
+        <v>Bandera Blanca</v>
       </c>
       <c r="G149" t="str">
-        <v>3:29</v>
+        <v>3:34</v>
       </c>
       <c r="H149" t="str">
-        <v>Neutro Shorty</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/neutro-shorty/1066850977</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/infidelidad/6768853655</v>
+        <v>https://music.apple.com/us/album/una-mujer-como-la-suya/1895154946</v>
       </c>
       <c r="L149" t="str">
-        <v>Infidelidad - Neutro Shorty</v>
+        <v>Una Mujer Como la Suya - Christian Nodal</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Wrong Place, Wrong time</v>
+        <v>Cold</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
+        <v>https://music.apple.com/us/song/cold/6763763802</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-23</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Y'all Won</v>
+        <v>Cold - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:57</v>
+        <v>2:52</v>
       </c>
       <c r="H150" t="str">
-        <v>Veeze</v>
+        <v>Majid Jordan</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
+        <v>https://music.apple.com/us/artist/majid-jordan/684530590</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/wrong-place-wrong-time/6771553812</v>
+        <v>https://music.apple.com/us/album/cold/1895478371</v>
       </c>
       <c r="L150" t="str">
-        <v>Wrong Place, Wrong time - Veeze</v>
+        <v>Cold - Majid Jordan</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>La Semana</v>
+        <v>VERTICAL WORLDS</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/la-semana/6769913466</v>
+        <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-23</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>No Quiero Que Se Acabe Este Bendito Verano - EP</v>
+        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
       </c>
       <c r="G151" t="str">
-        <v>3:30</v>
+        <v>3:15</v>
       </c>
       <c r="H151" t="str">
-        <v>ELENA ROSE</v>
+        <v>Ecca Vandal</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/la-semana/6769913464</v>
+        <v>https://music.apple.com/us/album/vertical-worlds/1886485694</v>
       </c>
       <c r="L151" t="str">
-        <v>La Semana - ELENA ROSE</v>
+        <v>VERTICAL WORLDS - Ecca Vandal</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Una Mujer Como la Suya</v>
+        <v>Child of Divorce</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
+        <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-23</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Bandera Blanca</v>
+        <v>soft pop</v>
       </c>
       <c r="G152" t="str">
-        <v>3:34</v>
+        <v>3:24</v>
       </c>
       <c r="H152" t="str">
-        <v>Christian Nodal</v>
+        <v>Amy Shark</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/una-mujer-como-la-suya/1895154946</v>
+        <v>https://music.apple.com/us/album/child-of-divorce/1880496743</v>
       </c>
       <c r="L152" t="str">
-        <v>Una Mujer Como la Suya - Christian Nodal</v>
+        <v>Child of Divorce - Amy Shark</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Cold</v>
+        <v>Taboo</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/cold/6763763802</v>
+        <v>https://music.apple.com/us/song/taboo/6762838716</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-23</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Cold - Single</v>
+        <v>Taboo - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:52</v>
+        <v>3:38</v>
       </c>
       <c r="H153" t="str">
-        <v>Majid Jordan</v>
+        <v>Jensen McRae</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/majid-jordan/684530590</v>
+        <v>https://music.apple.com/us/artist/jensen-mcrae/591974463</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/cold/1895478371</v>
+        <v>https://music.apple.com/us/album/taboo/1895036934</v>
       </c>
       <c r="L153" t="str">
-        <v>Cold - Majid Jordan</v>
+        <v>Taboo - Jensen McRae</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>VERTICAL WORLDS</v>
+        <v>I'M OK</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
+        <v>https://music.apple.com/us/song/im-ok/1893392647</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-23</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
+        <v>A Rii Set</v>
       </c>
       <c r="G154" t="str">
-        <v>3:15</v>
+        <v>2:37</v>
       </c>
       <c r="H154" t="str">
-        <v>Ecca Vandal</v>
+        <v>Pheelz</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
+        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/vertical-worlds/1886485694</v>
+        <v>https://music.apple.com/us/album/im-ok/1893392643</v>
       </c>
       <c r="L154" t="str">
-        <v>VERTICAL WORLDS - Ecca Vandal</v>
+        <v>I'M OK - Pheelz</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Child of Divorce</v>
+        <v>Butterfly Feelings</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
+        <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-23</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>soft pop</v>
+        <v>Ritual</v>
       </c>
       <c r="G155" t="str">
-        <v>3:24</v>
+        <v>2:35</v>
       </c>
       <c r="H155" t="str">
-        <v>Amy Shark</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/child-of-divorce/1880496743</v>
+        <v>https://music.apple.com/us/album/butterfly-feelings/1892426976</v>
       </c>
       <c r="L155" t="str">
-        <v>Child of Divorce - Amy Shark</v>
+        <v>Butterfly Feelings - Icona Pop</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Taboo</v>
+        <v>F**k the DJ</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/taboo/6762838716</v>
+        <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-23</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Taboo - Single</v>
+        <v>Stage Girl (Not A Dream Anymore)</v>
       </c>
       <c r="G156" t="str">
-        <v>3:38</v>
+        <v>2:57</v>
       </c>
       <c r="H156" t="str">
-        <v>Jensen McRae</v>
+        <v>Eli</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/jensen-mcrae/591974463</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/taboo/1895036934</v>
+        <v>https://music.apple.com/us/album/f-k-the-dj/6769903867</v>
       </c>
       <c r="L156" t="str">
-        <v>Taboo - Jensen McRae</v>
+        <v>F**k the DJ - Eli</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>I'M OK</v>
+        <v>Grateful</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/im-ok/1893392647</v>
+        <v>https://music.apple.com/us/song/grateful/1887166624</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-23</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>A Rii Set</v>
+        <v>24</v>
       </c>
       <c r="G157" t="str">
-        <v>2:37</v>
+        <v>2:18</v>
       </c>
       <c r="H157" t="str">
-        <v>Pheelz</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/im-ok/1893392643</v>
+        <v>https://music.apple.com/us/album/grateful/1887166427</v>
       </c>
       <c r="L157" t="str">
-        <v>I'M OK - Pheelz</v>
+        <v>Grateful - Alexis Ffrench</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Butterfly Feelings</v>
+        <v>Second Chance</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
+        <v>https://music.apple.com/us/song/second-chance/6766778687</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-23</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Ritual</v>
+        <v>Second Chance - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:35</v>
+        <v>3:06</v>
       </c>
       <c r="H158" t="str">
-        <v>Icona Pop</v>
+        <v>Lukas Graham</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/lukas-graham/473219952</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/butterfly-feelings/1892426976</v>
+        <v>https://music.apple.com/us/album/second-chance/6766778682</v>
       </c>
       <c r="L158" t="str">
-        <v>Butterfly Feelings - Icona Pop</v>
+        <v>Second Chance - Lukas Graham</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>F**k the DJ</v>
+        <v>Stupid World (feat. Chad Tepper) [Bonus Track]</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
+        <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-23</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Stage Girl (Not A Dream Anymore)</v>
+        <v>Tommyland Rides Again</v>
       </c>
       <c r="G159" t="str">
-        <v>2:57</v>
+        <v>3:49</v>
       </c>
       <c r="H159" t="str">
-        <v>Eli</v>
+        <v>Tommy Lee</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/tommy-lee/68696</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/f-k-the-dj/6769903867</v>
+        <v>https://music.apple.com/us/album/stupid-world-feat-chad-tepper-bonus-track/1893473875</v>
       </c>
       <c r="L159" t="str">
-        <v>F**k the DJ - Eli</v>
+        <v>Stupid World (feat. Chad Tepper) [Bonus Track] - Tommy Lee</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Grateful</v>
+        <v>DOOM LOOP</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/grateful/1887166624</v>
+        <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-23</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>24</v>
+        <v>Blood Of Your Empire</v>
       </c>
       <c r="G160" t="str">
-        <v>2:18</v>
+        <v>4:00</v>
       </c>
       <c r="H160" t="str">
-        <v>Alexis Ffrench</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/grateful/1887166427</v>
+        <v>https://music.apple.com/us/album/doom-loop/6769905842</v>
       </c>
       <c r="L160" t="str">
-        <v>Grateful - Alexis Ffrench</v>
+        <v>DOOM LOOP - PRESIDENT</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Second Chance</v>
+        <v>New York City</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/second-chance/6766778687</v>
+        <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-23</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Second Chance - Single</v>
+        <v>New York City - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:06</v>
+        <v>3:30</v>
       </c>
       <c r="H161" t="str">
-        <v>Lukas Graham</v>
+        <v>Anthony Ramos</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/lukas-graham/473219952</v>
+        <v>https://music.apple.com/us/artist/anthony-ramos/1313064678</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/second-chance/6766778682</v>
+        <v>https://music.apple.com/us/album/new-york-city/6770624324</v>
       </c>
       <c r="L161" t="str">
-        <v>Second Chance - Lukas Graham</v>
+        <v>New York City - Anthony Ramos</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Stupid World (feat. Chad Tepper) [Bonus Track]</v>
+        <v>I Found You</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
+        <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-23</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Tommyland Rides Again</v>
+        <v>I Found You - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:49</v>
+        <v>3:18</v>
       </c>
       <c r="H162" t="str">
-        <v>Tommy Lee</v>
+        <v>TA Thomas</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/tommy-lee/68696</v>
+        <v>https://music.apple.com/us/artist/ta-thomas/1232189106</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/stupid-world-feat-chad-tepper-bonus-track/1893473875</v>
+        <v>https://music.apple.com/us/album/i-found-you/1894024530</v>
       </c>
       <c r="L162" t="str">
-        <v>Stupid World (feat. Chad Tepper) [Bonus Track] - Tommy Lee</v>
+        <v>I Found You - TA Thomas</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>DOOM LOOP</v>
+        <v>Just My Type</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
+        <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-23</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Blood Of Your Empire</v>
+        <v>Labor Of Love</v>
       </c>
       <c r="G163" t="str">
-        <v>4:00</v>
+        <v>2:40</v>
       </c>
       <c r="H163" t="str">
-        <v>PRESIDENT</v>
+        <v>Blxst</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/doom-loop/6769905842</v>
+        <v>https://music.apple.com/us/album/just-my-type/1895199881</v>
       </c>
       <c r="L163" t="str">
-        <v>DOOM LOOP - PRESIDENT</v>
+        <v>Just My Type - Blxst</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>New York City</v>
+        <v>teenage drama</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
+        <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-23</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>New York City - Single</v>
+        <v>teenage drama - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:30</v>
+        <v>3:06</v>
       </c>
       <c r="H164" t="str">
-        <v>Anthony Ramos</v>
+        <v>paris jackson</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/anthony-ramos/1313064678</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/new-york-city/6770624324</v>
+        <v>https://music.apple.com/us/album/teenage-drama/6768447515</v>
       </c>
       <c r="L164" t="str">
-        <v>New York City - Anthony Ramos</v>
+        <v>teenage drama - paris jackson</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>I Found You</v>
+        <v>does it still mean something?</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
+        <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-23</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>I Found You - Single</v>
+        <v>only if it matters</v>
       </c>
       <c r="G165" t="str">
-        <v>3:18</v>
+        <v>3:48</v>
       </c>
       <c r="H165" t="str">
-        <v>TA Thomas</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/ta-thomas/1232189106</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/i-found-you/1894024530</v>
+        <v>https://music.apple.com/us/album/does-it-still-mean-something/6768446154</v>
       </c>
       <c r="L165" t="str">
-        <v>I Found You - TA Thomas</v>
+        <v>does it still mean something? - Kevian Kraemer</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Just My Type</v>
+        <v>Debbie Don't Cry</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
+        <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-23</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Labor Of Love</v>
+        <v>Debbie Don't Cry - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:40</v>
+        <v>3:00</v>
       </c>
       <c r="H166" t="str">
-        <v>Blxst</v>
+        <v>Ruel</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
+        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/just-my-type/1895199881</v>
+        <v>https://music.apple.com/us/album/debbie-dont-cry/6768206616</v>
       </c>
       <c r="L166" t="str">
-        <v>Just My Type - Blxst</v>
+        <v>Debbie Don't Cry - Ruel</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>teenage drama</v>
+        <v>YEAH YEAH YEAH</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
+        <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-23</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>teenage drama - Single</v>
+        <v>YEAH YEAH YEAH - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:06</v>
+        <v>2:25</v>
       </c>
       <c r="H167" t="str">
-        <v>paris jackson</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/teenage-drama/6768447515</v>
+        <v>https://music.apple.com/us/album/yeah-yeah-yeah/6767515610</v>
       </c>
       <c r="L167" t="str">
-        <v>teenage drama - paris jackson</v>
+        <v>YEAH YEAH YEAH - Cruz Beckham</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>does it still mean something?</v>
+        <v>Cotton Flower</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
+        <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-23</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>only if it matters</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G168" t="str">
-        <v>3:48</v>
+        <v>3:53</v>
       </c>
       <c r="H168" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Future Islands</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/does-it-still-mean-something/6768446154</v>
+        <v>https://music.apple.com/us/album/cotton-flower/1883045480</v>
       </c>
       <c r="L168" t="str">
-        <v>does it still mean something? - Kevian Kraemer</v>
+        <v>Cotton Flower - Future Islands</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Debbie Don't Cry</v>
+        <v>WAHALA RIDDIM</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
+        <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-23</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Debbie Don't Cry - Single</v>
+        <v>WAHALA RIDDIM - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:00</v>
+        <v>3:22</v>
       </c>
       <c r="H169" t="str">
-        <v>Ruel</v>
+        <v>THEHONESTGUY</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
+        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/debbie-dont-cry/6768206616</v>
+        <v>https://music.apple.com/us/album/wahala-riddim/1895810537</v>
       </c>
       <c r="L169" t="str">
-        <v>Debbie Don't Cry - Ruel</v>
+        <v>WAHALA RIDDIM - THEHONESTGUY</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>YEAH YEAH YEAH</v>
+        <v>Comfort</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
+        <v>https://music.apple.com/us/song/comfort/1876521401</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-23</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>YEAH YEAH YEAH - Single</v>
+        <v>So Help Me God</v>
       </c>
       <c r="G170" t="str">
-        <v>2:25</v>
+        <v>5:35</v>
       </c>
       <c r="H170" t="str">
-        <v>Cruz Beckham</v>
+        <v>Kelsey Lu</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/yeah-yeah-yeah/6767515610</v>
+        <v>https://music.apple.com/us/album/comfort/1876521144</v>
       </c>
       <c r="L170" t="str">
-        <v>YEAH YEAH YEAH - Cruz Beckham</v>
+        <v>Comfort - Kelsey Lu</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Cotton Flower</v>
+        <v>Skin</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
+        <v>https://music.apple.com/us/song/skin/6764651585</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-23</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>Skin - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:53</v>
+        <v>3:00</v>
       </c>
       <c r="H171" t="str">
-        <v>Future Islands</v>
+        <v>Alessi Rose</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/alessi-rose/1628689028</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/cotton-flower/1883045480</v>
+        <v>https://music.apple.com/us/album/skin/1895865252</v>
       </c>
       <c r="L171" t="str">
-        <v>Cotton Flower - Future Islands</v>
+        <v>Skin - Alessi Rose</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>WAHALA RIDDIM</v>
+        <v>IDGAF</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
+        <v>https://music.apple.com/us/song/idgaf/6764422210</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-23</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>WAHALA RIDDIM - Single</v>
+        <v>IDGAF - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:22</v>
+        <v>2:55</v>
       </c>
       <c r="H172" t="str">
-        <v>THEHONESTGUY</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/wahala-riddim/1895810537</v>
+        <v>https://music.apple.com/us/album/idgaf/1895773358</v>
       </c>
       <c r="L172" t="str">
-        <v>WAHALA RIDDIM - THEHONESTGUY</v>
+        <v>IDGAF - Katelyn Tarver</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Comfort</v>
+        <v>Run Rabbit</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/comfort/1876521401</v>
+        <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-23</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>So Help Me God</v>
+        <v>Run Rabbit - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>5:35</v>
+        <v>3:09</v>
       </c>
       <c r="H173" t="str">
-        <v>Kelsey Lu</v>
+        <v>Mollie Elizabeth</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
+        <v>https://music.apple.com/us/artist/mollie-elizabeth/1780515318</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/comfort/1876521144</v>
+        <v>https://music.apple.com/us/album/run-rabbit/6767354664</v>
       </c>
       <c r="L173" t="str">
-        <v>Comfort - Kelsey Lu</v>
+        <v>Run Rabbit - Mollie Elizabeth</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Skin</v>
+        <v>So Good (feat. Kuuda)</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/skin/6764651585</v>
+        <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-23</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Skin - Single</v>
+        <v>So Good (feat. Kuuda) - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:00</v>
+        <v>3:03</v>
       </c>
       <c r="H174" t="str">
-        <v>Alessi Rose</v>
+        <v>CamelPhat</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/alessi-rose/1628689028</v>
+        <v>https://music.apple.com/us/artist/camelphat/385810888</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/skin/1895865252</v>
+        <v>https://music.apple.com/us/album/so-good-feat-kuuda/6766655768</v>
       </c>
       <c r="L174" t="str">
-        <v>Skin - Alessi Rose</v>
+        <v>So Good (feat. Kuuda) - CamelPhat</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>IDGAF</v>
+        <v>Empty Theatre, Pretty Picture</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/idgaf/6764422210</v>
+        <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-23</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>IDGAF - Single</v>
+        <v>Empty Theatre, Pretty Picture</v>
       </c>
       <c r="G175" t="str">
-        <v>2:55</v>
+        <v>5:01</v>
       </c>
       <c r="H175" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Lane 8</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/idgaf/1895773358</v>
+        <v>https://music.apple.com/us/album/empty-theatre-pretty-picture/1895395993</v>
       </c>
       <c r="L175" t="str">
-        <v>IDGAF - Katelyn Tarver</v>
+        <v>Empty Theatre, Pretty Picture - Lane 8</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Run Rabbit</v>
+        <v>regalametutiempo</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
+        <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-23</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Run Rabbit - Single</v>
+        <v>PROYECTANDO</v>
       </c>
       <c r="G176" t="str">
-        <v>3:09</v>
+        <v>3:01</v>
       </c>
       <c r="H176" t="str">
-        <v>Mollie Elizabeth</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/mollie-elizabeth/1780515318</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/run-rabbit/6767354664</v>
+        <v>https://music.apple.com/us/album/regalametutiempo/6769922866</v>
       </c>
       <c r="L176" t="str">
-        <v>Run Rabbit - Mollie Elizabeth</v>
+        <v>regalametutiempo - Julio Caesar</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>So Good (feat. Kuuda)</v>
+        <v>On Sight</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
+        <v>https://music.apple.com/us/song/on-sight/6763971220</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-23</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>So Good (feat. Kuuda) - Single</v>
+        <v>Left on RED</v>
       </c>
       <c r="G177" t="str">
-        <v>3:03</v>
+        <v>2:25</v>
       </c>
       <c r="H177" t="str">
-        <v>CamelPhat</v>
+        <v>REMI</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/camelphat/385810888</v>
+        <v>https://music.apple.com/us/artist/remi/1716510008</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/so-good-feat-kuuda/6766655768</v>
+        <v>https://music.apple.com/us/album/on-sight/1895580736</v>
       </c>
       <c r="L177" t="str">
-        <v>So Good (feat. Kuuda) - CamelPhat</v>
+        <v>On Sight - REMI</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Empty Theatre, Pretty Picture</v>
+        <v>Masks Off</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
+        <v>https://music.apple.com/us/song/masks-off/6764077133</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-23</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Empty Theatre, Pretty Picture</v>
+        <v>Masks Off - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>5:01</v>
+        <v>3:24</v>
       </c>
       <c r="H178" t="str">
-        <v>Lane 8</v>
+        <v>Jesse Welles</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/jesse-welles/1737507146</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/empty-theatre-pretty-picture/1895395993</v>
+        <v>https://music.apple.com/us/album/masks-off/1895628310</v>
       </c>
       <c r="L178" t="str">
-        <v>Empty Theatre, Pretty Picture - Lane 8</v>
+        <v>Masks Off - Jesse Welles</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>regalametutiempo</v>
+        <v>I'm Just A Girl</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
+        <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-23</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>PROYECTANDO</v>
+        <v>Di Hotel Malibu</v>
       </c>
       <c r="G179" t="str">
-        <v>3:01</v>
+        <v>2:49</v>
       </c>
       <c r="H179" t="str">
-        <v>Julio Caesar</v>
+        <v>Thee Marloes</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/thee-marloes/1541376632</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/regalametutiempo/6769922866</v>
+        <v>https://music.apple.com/us/album/im-just-a-girl/1878399768</v>
       </c>
       <c r="L179" t="str">
-        <v>regalametutiempo - Julio Caesar</v>
+        <v>I'm Just A Girl - Thee Marloes</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>On Sight</v>
+        <v>Soleil (feat. Isabella Lovestory)</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/on-sight/6763971220</v>
+        <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-23</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Left on RED</v>
+        <v>EXIT 2B</v>
       </c>
       <c r="G180" t="str">
-        <v>2:25</v>
+        <v>2:11</v>
       </c>
       <c r="H180" t="str">
-        <v>REMI</v>
+        <v>B0YG1RL</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/remi/1716510008</v>
+        <v>https://music.apple.com/us/artist/b0yg1rl/1847766665</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/on-sight/1895580736</v>
+        <v>https://music.apple.com/us/album/soleil-feat-isabella-lovestory/6769526101</v>
       </c>
       <c r="L180" t="str">
-        <v>On Sight - REMI</v>
+        <v>Soleil (feat. Isabella Lovestory) - B0YG1RL</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Masks Off</v>
+        <v>Money Tree</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/masks-off/6764077133</v>
+        <v>https://music.apple.com/us/song/money-tree/6763211637</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-23</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Masks Off - Single</v>
+        <v>Money Tree - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:24</v>
+        <v>2:39</v>
       </c>
       <c r="H181" t="str">
-        <v>Jesse Welles</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/jesse-welles/1737507146</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/masks-off/1895628310</v>
+        <v>https://music.apple.com/us/album/money-tree/1895216986</v>
       </c>
       <c r="L181" t="str">
-        <v>Masks Off - Jesse Welles</v>
+        <v>Money Tree - Olympia Vitalis</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>I'm Just A Girl</v>
+        <v>Homerunner</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
+        <v>https://music.apple.com/us/song/homerunner/6770682178</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-23</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Di Hotel Malibu</v>
+        <v>Homerunner - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:49</v>
+        <v>2:36</v>
       </c>
       <c r="H182" t="str">
-        <v>Thee Marloes</v>
+        <v>slayr</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/thee-marloes/1541376632</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/im-just-a-girl/1878399768</v>
+        <v>https://music.apple.com/us/album/homerunner/6770682177</v>
       </c>
       <c r="L182" t="str">
-        <v>I'm Just A Girl - Thee Marloes</v>
+        <v>Homerunner - slayr</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Soleil (feat. Isabella Lovestory)</v>
+        <v>Mail</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
+        <v>https://music.apple.com/us/song/mail/6769190635</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-23</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>EXIT 2B</v>
+        <v>Mail - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:11</v>
+        <v>2:14</v>
       </c>
       <c r="H183" t="str">
-        <v>B0YG1RL</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/b0yg1rl/1847766665</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/soleil-feat-isabella-lovestory/6769526101</v>
+        <v>https://music.apple.com/us/album/mail/6769190634</v>
       </c>
       <c r="L183" t="str">
-        <v>Soleil (feat. Isabella Lovestory) - B0YG1RL</v>
+        <v>Mail - MexikoDro</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Money Tree</v>
+        <v>Waste Your Heart</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/money-tree/6763211637</v>
+        <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-23</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Money Tree - Single</v>
+        <v>Waste Your Heart - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:39</v>
+        <v>2:31</v>
       </c>
       <c r="H184" t="str">
-        <v>Olympia Vitalis</v>
+        <v>Magnus Ferrell</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/money-tree/1895216986</v>
+        <v>https://music.apple.com/us/album/waste-your-heart/6769241913</v>
       </c>
       <c r="L184" t="str">
-        <v>Money Tree - Olympia Vitalis</v>
+        <v>Waste Your Heart - Magnus Ferrell</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Homerunner</v>
+        <v>Sleeping Pills</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/homerunner/6770682178</v>
+        <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-23</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Homerunner - Single</v>
+        <v>Sleeping Pills - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:36</v>
+        <v>3:03</v>
       </c>
       <c r="H185" t="str">
-        <v>slayr</v>
+        <v>Dolder</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/homerunner/6770682177</v>
+        <v>https://music.apple.com/us/album/sleeping-pills/1896452689</v>
       </c>
       <c r="L185" t="str">
-        <v>Homerunner - slayr</v>
+        <v>Sleeping Pills - Dolder</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Mail</v>
+        <v>KODACHROMATIC</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/mail/6769190635</v>
+        <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-23</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Mail - Single</v>
+        <v>KODACHROMATIC - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:14</v>
+        <v>2:53</v>
       </c>
       <c r="H186" t="str">
-        <v>MexikoDro</v>
+        <v>Tiger La Flor</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/tiger-la-flor/1613113982</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/mail/6769190634</v>
+        <v>https://music.apple.com/us/album/kodachromatic/6770724719</v>
       </c>
       <c r="L186" t="str">
-        <v>Mail - MexikoDro</v>
+        <v>KODACHROMATIC - Tiger La Flor</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Waste Your Heart</v>
+        <v>FOMO</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
+        <v>https://music.apple.com/us/song/fomo/1890190631</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-23</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Waste Your Heart - Single</v>
+        <v>Map Of Her Shadow</v>
       </c>
       <c r="G187" t="str">
-        <v>2:31</v>
+        <v>3:01</v>
       </c>
       <c r="H187" t="str">
-        <v>Magnus Ferrell</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/waste-your-heart/6769241913</v>
+        <v>https://music.apple.com/us/album/fomo/1890190623</v>
       </c>
       <c r="L187" t="str">
-        <v>Waste Your Heart - Magnus Ferrell</v>
+        <v>FOMO - Anais Cardot</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Sleeping Pills</v>
+        <v>Black Fire</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
+        <v>https://music.apple.com/us/song/black-fire/6770696877</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-23</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Sleeping Pills - Single</v>
+        <v>Sulfur Surfer</v>
       </c>
       <c r="G188" t="str">
-        <v>3:03</v>
+        <v>3:37</v>
       </c>
       <c r="H188" t="str">
-        <v>Dolder</v>
+        <v>Bladee</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
+        <v>https://music.apple.com/us/artist/bladee/861359576</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/sleeping-pills/1896452689</v>
+        <v>https://music.apple.com/us/album/black-fire/6770696743</v>
       </c>
       <c r="L188" t="str">
-        <v>Sleeping Pills - Dolder</v>
+        <v>Black Fire - Bladee</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>KODACHROMATIC</v>
+        <v>As Seen in the Unseen</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
+        <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-23</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>KODACHROMATIC - Single</v>
+        <v>Grand Serpent Rising</v>
       </c>
       <c r="G189" t="str">
-        <v>2:53</v>
+        <v>6:59</v>
       </c>
       <c r="H189" t="str">
-        <v>Tiger La Flor</v>
+        <v>Dimmu Borgir</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/tiger-la-flor/1613113982</v>
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/kodachromatic/6770724719</v>
+        <v>https://music.apple.com/us/album/as-seen-in-the-unseen/1883121436</v>
       </c>
       <c r="L189" t="str">
-        <v>KODACHROMATIC - Tiger La Flor</v>
+        <v>As Seen in the Unseen - Dimmu Borgir</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>FOMO</v>
+        <v>Every Man-Any Man</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/fomo/1890190631</v>
+        <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-23</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Map Of Her Shadow</v>
+        <v>Emotion Factory Reset</v>
       </c>
       <c r="G190" t="str">
-        <v>3:01</v>
+        <v>4:20</v>
       </c>
       <c r="H190" t="str">
-        <v>Anais Cardot</v>
+        <v>Armored Saint</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/fomo/1890190623</v>
+        <v>https://music.apple.com/us/album/every-man-any-man/1872193859</v>
       </c>
       <c r="L190" t="str">
-        <v>FOMO - Anais Cardot</v>
+        <v>Every Man-Any Man - Armored Saint</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Black Fire</v>
+        <v>No Arms</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/black-fire/6770696877</v>
+        <v>https://music.apple.com/us/song/no-arms/6765776563</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-23</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Sulfur Surfer</v>
+        <v>From A Distance</v>
       </c>
       <c r="G191" t="str">
-        <v>3:37</v>
+        <v>3:43</v>
       </c>
       <c r="H191" t="str">
-        <v>Bladee</v>
+        <v>156/Silence</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/bladee/861359576</v>
+        <v>https://music.apple.com/us/artist/156-silence/1071395282</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/black-fire/6770696743</v>
+        <v>https://music.apple.com/us/album/no-arms/1896069437</v>
       </c>
       <c r="L191" t="str">
-        <v>Black Fire - Bladee</v>
+        <v>No Arms - 156/Silence</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>As Seen in the Unseen</v>
+        <v>It's Neverending</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
+        <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-23</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Grand Serpent Rising</v>
+        <v>Neverending</v>
       </c>
       <c r="G192" t="str">
-        <v>6:59</v>
+        <v>8:35</v>
       </c>
       <c r="H192" t="str">
-        <v>Dimmu Borgir</v>
+        <v>Monolord</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/as-seen-in-the-unseen/1883121436</v>
+        <v>https://music.apple.com/us/album/its-neverending/1871211801</v>
       </c>
       <c r="L192" t="str">
-        <v>As Seen in the Unseen - Dimmu Borgir</v>
+        <v>It's Neverending - Monolord</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Every Man-Any Man</v>
+        <v>The Kids Will Kill Us</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
+        <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-23</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Emotion Factory Reset</v>
+        <v>The Kids Will Kill Us - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>4:20</v>
+        <v>3:45</v>
       </c>
       <c r="H193" t="str">
-        <v>Armored Saint</v>
+        <v>Witch Club Satan</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
+        <v>https://music.apple.com/us/artist/witch-club-satan/1626477576</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/every-man-any-man/1872193859</v>
+        <v>https://music.apple.com/us/album/the-kids-will-kill-us/6766343272</v>
       </c>
       <c r="L193" t="str">
-        <v>Every Man-Any Man - Armored Saint</v>
+        <v>The Kids Will Kill Us - Witch Club Satan</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>No Arms</v>
+        <v>Masters of the Universe (from "Masters of the Universe")</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/no-arms/6765776563</v>
+        <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-23</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>From A Distance</v>
+        <v>Masters of the Universe (from "Masters of the Universe") - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:43</v>
+        <v>3:20</v>
       </c>
       <c r="H194" t="str">
-        <v>156/Silence</v>
+        <v>The Darkness</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/156-silence/1071395282</v>
+        <v>https://music.apple.com/us/artist/the-darkness/2417388</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/no-arms/1896069437</v>
+        <v>https://music.apple.com/us/album/masters-of-the-universe-from-masters-of-the-universe/6769065779</v>
       </c>
       <c r="L194" t="str">
-        <v>No Arms - 156/Silence</v>
+        <v>Masters of the Universe (from "Masters of the Universe") - The Darkness</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>It's Neverending</v>
+        <v>All Day</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
+        <v>https://music.apple.com/us/song/all-day/1880746584</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-23</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Neverending</v>
+        <v>Feet On Fire</v>
       </c>
       <c r="G195" t="str">
-        <v>8:35</v>
+        <v>2:29</v>
       </c>
       <c r="H195" t="str">
-        <v>Monolord</v>
+        <v>Ben Chapman</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+        <v>https://music.apple.com/us/artist/ben-chapman/1581192612</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/its-neverending/1871211801</v>
+        <v>https://music.apple.com/us/album/all-day/1880746349</v>
       </c>
       <c r="L195" t="str">
-        <v>It's Neverending - Monolord</v>
+        <v>All Day - Ben Chapman</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>The Kids Will Kill Us</v>
+        <v>Sigui</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
+        <v>https://music.apple.com/us/song/sigui/1890241955</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-23</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>The Kids Will Kill Us - Single</v>
+        <v>Massa</v>
       </c>
       <c r="G196" t="str">
-        <v>3:45</v>
+        <v>3:17</v>
       </c>
       <c r="H196" t="str">
-        <v>Witch Club Satan</v>
+        <v>Fatoumata Diawara</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/witch-club-satan/1626477576</v>
+        <v>https://music.apple.com/us/artist/fatoumata-diawara/466213610</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/the-kids-will-kill-us/6766343272</v>
+        <v>https://music.apple.com/us/album/sigui/1890241617</v>
       </c>
       <c r="L196" t="str">
-        <v>The Kids Will Kill Us - Witch Club Satan</v>
+        <v>Sigui - Fatoumata Diawara</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe")</v>
+        <v>High Tail</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
+        <v>https://music.apple.com/us/song/high-tail/1870432994</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-23</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe") - Single</v>
+        <v>Where the South Winds Wail</v>
       </c>
       <c r="G197" t="str">
-        <v>3:20</v>
+        <v>2:31</v>
       </c>
       <c r="H197" t="str">
-        <v>The Darkness</v>
+        <v>Gitkin</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/the-darkness/2417388</v>
+        <v>https://music.apple.com/us/artist/gitkin/1345281815</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/masters-of-the-universe-from-masters-of-the-universe/6769065779</v>
+        <v>https://music.apple.com/us/album/high-tail/1870432670</v>
       </c>
       <c r="L197" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe") - The Darkness</v>
+        <v>High Tail - Gitkin</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>All Day</v>
+        <v>Mice Protection</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/all-day/1880746584</v>
+        <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-23</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Feet On Fire</v>
+        <v>Ugly Duckling Union</v>
       </c>
       <c r="G198" t="str">
-        <v>2:29</v>
+        <v>3:34</v>
       </c>
       <c r="H198" t="str">
-        <v>Ben Chapman</v>
+        <v>Lowertown</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/ben-chapman/1581192612</v>
+        <v>https://music.apple.com/us/artist/lowertown/1448207323</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/all-day/1880746349</v>
+        <v>https://music.apple.com/us/album/mice-protection/1872171971</v>
       </c>
       <c r="L198" t="str">
-        <v>All Day - Ben Chapman</v>
+        <v>Mice Protection - Lowertown</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Sigui</v>
+        <v>Tóxica</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/sigui/1890241955</v>
+        <v>https://music.apple.com/us/song/t%C3%B3xica/6763056240</v>
       </c>
       <c r="D199" t="str">
         <v>2026-05-23</v>
@@ -7937,144 +7937,30 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Massa</v>
+        <v>Caribenya</v>
       </c>
       <c r="G199" t="str">
-        <v>3:17</v>
+        <v>3:48</v>
       </c>
       <c r="H199" t="str">
-        <v>Fatoumata Diawara</v>
+        <v>Lido Pimienta</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/fatoumata-diawara/466213610</v>
+        <v>https://music.apple.com/us/artist/lido-pimienta/389475023</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/sigui/1890241617</v>
+        <v>https://music.apple.com/us/album/t%C3%B3xica/1895141218</v>
       </c>
       <c r="L199" t="str">
-        <v>Sigui - Fatoumata Diawara</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>High Tail</v>
-      </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/high-tail/1870432994</v>
-      </c>
-      <c r="D200" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
-        <v>Where the South Winds Wail</v>
-      </c>
-      <c r="G200" t="str">
-        <v>2:31</v>
-      </c>
-      <c r="H200" t="str">
-        <v>Gitkin</v>
-      </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/gitkin/1345281815</v>
-      </c>
-      <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/high-tail/1870432670</v>
-      </c>
-      <c r="L200" t="str">
-        <v>High Tail - Gitkin</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>Mice Protection</v>
-      </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
-      </c>
-      <c r="D201" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
-        <v>Ugly Duckling Union</v>
-      </c>
-      <c r="G201" t="str">
-        <v>3:34</v>
-      </c>
-      <c r="H201" t="str">
-        <v>Lowertown</v>
-      </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/lowertown/1448207323</v>
-      </c>
-      <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/mice-protection/1872171971</v>
-      </c>
-      <c r="L201" t="str">
-        <v>Mice Protection - Lowertown</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>Tóxica</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/t%C3%B3xica/6763056240</v>
-      </c>
-      <c r="D202" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
-        <v>Caribenya</v>
-      </c>
-      <c r="G202" t="str">
-        <v>3:48</v>
-      </c>
-      <c r="H202" t="str">
-        <v>Lido Pimienta</v>
-      </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/lido-pimienta/389475023</v>
-      </c>
-      <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/t%C3%B3xica/1895141218</v>
-      </c>
-      <c r="L202" t="str">
         <v>Tóxica - Lido Pimienta</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week04/titles.xlsx
+++ b/data/global/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L209"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
+        <v>יובל קונסטנטיני - שירי אהבה</v>
       </c>
       <c r="B2" t="str">
-        <v>23 hours ago</v>
+        <v>2026-05-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410999&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-23</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>23 hours ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Duran Duran</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
+        <v>יובל קונסטנטיני - שירי אהבה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Nico Santos - Optimist</v>
+        <v>יובל גולד &amp; שירה זלוף - מחר יבוא מחר</v>
       </c>
       <c r="B3" t="str">
-        <v>3 days ago</v>
+        <v>2026-05-23</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410998&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-23</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Nico Santos</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Nico Santos - Optimist - Nico Santos</v>
+        <v>יובל גולד &amp; שירה זלוף - מחר יבוא מחר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
+        <v>טלי רבקה סימן טוב - יוצאת לדרך</v>
       </c>
       <c r="B4" t="str">
-        <v>7 hours ago</v>
+        <v>2026-05-23</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410997&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-23</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>7 hours ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>DEF LEPPARD</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
+        <v>טלי רבקה סימן טוב - יוצאת לדרך</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
+        <v>טודיאל - לא ממלא לי ת'נשמה</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2026-05-23</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410996&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-23</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Will Linley</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
+        <v>טודיאל - לא ממלא לי ת'נשמה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video)</v>
+        <v>זיו גבאי - מין נהאר לי נפטר</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2026-05-23</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410995&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-23</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Kylie Minogue</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
+        <v>זיו גבאי - מין נהאר לי נפטר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
+        <v>דקלה תפילין - צלקת שלך על הלב</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2026-05-23</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410994&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-23</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Billy Raffoul</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
+        <v>דקלה תפילין - צלקת שלך על הלב</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
+        <v>בני קראוס - ממשיך לחיות</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>2026-05-23</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410993&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-23</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>The Offspring</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
+        <v>בני קראוס - ממשיך לחיות</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
+        <v>אליאור נונה - מחרוזת מאמי שלי 2026</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2026-05-23</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410992&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-23</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>David Gilmour</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
+        <v>אליאור נונה - מחרוזת מאמי שלי 2026</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
+        <v>איציק שריקי - בָּבָּא לִּיווִי</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2026-05-23</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410991&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-23</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Scorpions</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
+        <v>איציק שריקי - בָּבָּא לִּיווִי</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
+        <v>אביחי טהיא - אל נבקש קאבר</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2026-05-23</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410990&amp;sid=ffec9639250a4b1c014231eebf5db17d</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-23</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Brandon Lake</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake</v>
+        <v>אביחי טהיא - אל נבקש קאבר</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B12" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
+        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-23</v>
@@ -837,7 +837,7 @@
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Kygo and Dan Tyminski</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>The Warning - Ego (Official Video)</v>
+        <v>Nico Santos - Optimist</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
+        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-23</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>The Warning</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>The Warning - Ego (Official Video) - The Warning</v>
+        <v>Nico Santos - Optimist - Nico Santos</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>paris jackson - teenage drama (official lyric video)</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
+        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-23</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>paris jackson</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B15" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
+        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-23</v>
@@ -951,7 +951,7 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Minelli</v>
+        <v>Will Linley</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
+        <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
+        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-23</v>
@@ -989,7 +989,7 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Maggie Rose</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
+        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B17" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
+        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-23</v>
@@ -1027,7 +1027,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>David Guetta</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B18" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
+        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-23</v>
@@ -1065,7 +1065,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Chris Young and Shaylen</v>
+        <v>The Offspring</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Lauv - Pretty Little Things</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B19" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
+        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-23</v>
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Lauv</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Lauv - Pretty Little Things - Lauv</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B20" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
+        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-23</v>
@@ -1141,7 +1141,7 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Icona Pop</v>
+        <v>Scorpions</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Will Swinton - Only One (Official Video)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B21" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
+        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-23</v>
@@ -1179,7 +1179,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Will Swinton</v>
+        <v>Brandon Lake</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-23</v>
@@ -1217,7 +1217,7 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Dean Lewis</v>
+        <v>Kygo and Dan Tyminski</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B23" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-23</v>
@@ -1255,7 +1255,7 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>The Warning</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>The Warning - Ego (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B24" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-23</v>
@@ -1293,7 +1293,7 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Niall Horan</v>
+        <v>paris jackson</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B25" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-23</v>
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Minelli</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B26" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-23</v>
@@ -1369,7 +1369,7 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>RUEL</v>
+        <v>Maggie Rose</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B27" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-23</v>
@@ -1407,7 +1407,7 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>TINI</v>
+        <v>David Guetta</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-23</v>
@@ -1445,7 +1445,7 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Charli xcx</v>
+        <v>Chris Young and Shaylen</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-23</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Dua Lipa</v>
+        <v>Lauv</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>Lauv - Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-23</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Matilda Mann</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-23</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Ella Langley</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-23</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B33" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-23</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>kesha</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-23</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Holly Humberstone</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-23</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Foo Fighters</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-23</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>The Analogues</v>
+        <v>RUEL</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B37" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-23</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Rod Stewart</v>
+        <v>TINI</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-23</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Blue October</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Far Caspian - hum (Official Video)</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B39" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-23</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Far Caspian</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Kenia Os - Love Bombing</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-23</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Kenia Os</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Kenia Os - Love Bombing - Kenia Os</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B41" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-23</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B42" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-23</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B43" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-23</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>kesha</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B44" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-23</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-23</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B46" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-23</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>The Analogues</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B47" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-23</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-23</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Evanescence</v>
+        <v>Blue October</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>11 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-23</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>11 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-23</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Armin van Buuren</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Kenia Os - Love Bombing - Kenia Os</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-23</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Madison Cunningham</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-23</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Johnny Orlando</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-23</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Carver Jones</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-23</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Jazmin bean</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-23</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Baby Queen</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-23</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Switchfoot</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-23</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Grace Potter</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B58" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-23</v>
@@ -2585,7 +2585,7 @@
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Evanescence</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>8 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-23</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>The All-American Rejects</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B60" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-23</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Henry Moodie</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B61" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-23</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Spacey Jane</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B62" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-23</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Megan Moroney</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B63" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-23</v>
@@ -2775,7 +2775,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Matt Hansen</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-23</v>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Matt Hansen</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Keith Urban - Steal Away (Visualizer)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B65" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-23</v>
@@ -2851,7 +2851,7 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Keith Urban</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>VALÉ - Mugshot (Official Video)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B66" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-23</v>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>VALÉ</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio)</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B67" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-23</v>
@@ -2927,7 +2927,7 @@
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Mackenzie Carpenter</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B68" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-23</v>
@@ -2965,7 +2965,7 @@
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Towa Bird</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B69" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-23</v>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Sabrina Sterling</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B70" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-23</v>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Little Big Town</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Becky G - EPA (Official Video)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-23</v>
@@ -3079,7 +3079,7 @@
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Becky G</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Becky G - EPA (Official Video) - Becky G</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-23</v>
@@ -3117,7 +3117,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Daisy the Great</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Towa Bird - Dog (Official Music Video)</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B73" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-23</v>
@@ -3155,7 +3155,7 @@
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Towa Bird</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B74" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
+        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-23</v>
@@ -3193,7 +3193,7 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Madonna</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video)</v>
+        <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B75" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
+        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-23</v>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Ally Salort</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
+        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Bella White - Better - Official Music Video</v>
+        <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
+        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-23</v>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Bella White</v>
+        <v>VALÉ</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Bella White - Better - Official Music Video - Bella White</v>
+        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
+        <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B77" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
+        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-23</v>
@@ -3307,7 +3307,7 @@
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Mackenzie Carpenter</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
+        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B78" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
+        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-23</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer)</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B79" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
+        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-23</v>
@@ -3383,7 +3383,7 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Miranda Lambert</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
+        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-23</v>
@@ -3421,7 +3421,7 @@
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Lady Gaga</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
+        <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B81" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
+        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-23</v>
@@ -3459,7 +3459,7 @@
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Gracie Abrams</v>
+        <v>Becky G</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
+        <v>Becky G - EPA (Official Video) - Becky G</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B82" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
+        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-23</v>
@@ -3497,7 +3497,7 @@
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Daisy the Great</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
+        <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
+        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-23</v>
@@ -3535,7 +3535,7 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Martin Garrix</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
+        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Jorja Smith - What's Done Is Done</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B84" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
+        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-23</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Jorja Smith</v>
+        <v>Madonna</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>LP - Shelly (Official Music Video)</v>
+        <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
+        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-23</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>LP</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>LP - Shelly (Official Music Video) - LP</v>
+        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
+        <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B86" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
+        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-23</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>The Rolling Stones</v>
+        <v>Bella White</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
+        <v>Bella White - Better - Official Music Video - Bella White</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
+        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-23</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Oasis</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B88" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
+        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-23</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Breaking Benjamin</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
+        <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B89" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
+        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-23</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>VictorBiliac</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
+        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B90" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
+        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-23</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Linkin Park</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Harry Styles - Dance No More (Official Video)</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
+        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-23</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Harry Styles</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
+        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-23</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Eagles</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
+        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-23</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Nora Fatehi</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
+        <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B94" t="str">
-        <v>2 months ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
+        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-23</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 months ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
+        <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 months ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
+        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-23</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 months ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Eurovision Song Contest and Alis</v>
+        <v>LP</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
+        <v>LP - Shelly (Official Music Video) - LP</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B96" t="str">
-        <v>2 months ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
+        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-23</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 months ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video)</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
+        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-23</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>The Head And The Heart</v>
+        <v>Oasis</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
+        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-23</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Simply Red</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video)</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B99" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
+        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-23</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Talking Heads</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Ellise - Liplock (Official Music Video)</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
+        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-23</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Ellise</v>
+        <v>Linkin Park</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Tori Kelly - Dive (Official Music Video)</v>
+        <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
+        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-23</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Tori Kelly</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
+        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>From Down Here</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
+        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-23</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>From Down Here - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>4:01</v>
+        <v/>
       </c>
       <c r="H102" t="str">
-        <v>Lola Young</v>
+        <v>Eagles</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/lola-young/452271760</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/from-down-here/6768357139</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>From Down Here - Lola Young</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>the cure</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/the-cure/1889992123</v>
+        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-23</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>you seem pretty sad for a girl so in love</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>4:57</v>
+        <v/>
       </c>
       <c r="H103" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Nora Fatehi</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/the-cure/1889992111</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>the cure - Olivia Rodrigo</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>SS26</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>2 months ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/ss26/6771061782</v>
+        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-23</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>SS26 - Single</v>
+        <v>2 months ago</v>
       </c>
       <c r="G104" t="str">
-        <v>2:47</v>
+        <v/>
       </c>
       <c r="H104" t="str">
-        <v>Charli xcx</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/ss26/6771061771</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>SS26 - Charli xcx</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>White Flag</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>2 months ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/white-flag/1887627840</v>
+        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-23</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Cry Baby</v>
+        <v>2 months ago</v>
       </c>
       <c r="G105" t="str">
-        <v>2:34</v>
+        <v/>
       </c>
       <c r="H105" t="str">
-        <v>Vince Staples</v>
+        <v>Eurovision Song Contest and Alis</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/white-flag/1887627836</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>White Flag - Vince Staples</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Knew Better Part Two</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>2 months ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
+        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-23</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Dangerous Woman (Tenth Anniversary Edition)</v>
+        <v>2 months ago</v>
       </c>
       <c r="G106" t="str">
-        <v>2:44</v>
+        <v/>
       </c>
       <c r="H106" t="str">
-        <v>Ariana Grande</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/knew-better-part-two/6770600996</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>Knew Better Part Two - Ariana Grande</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Goals</v>
+        <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/goals/6769251838</v>
+        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-23</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Goals (FIFA World Cup 2026™) - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G107" t="str">
-        <v>3:00</v>
+        <v/>
       </c>
       <c r="H107" t="str">
-        <v>LISA</v>
+        <v>The Head And The Heart</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/lisa/1583908668</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/goals/6769251829</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>Goals - LISA</v>
+        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>we should talk</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
+        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-23</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>everyone for ten minutes</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G108" t="str">
-        <v>3:04</v>
+        <v/>
       </c>
       <c r="H108" t="str">
-        <v>Bleachers</v>
+        <v>Simply Red</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/we-should-talk/1872842313</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>we should talk - Bleachers</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Do What You Gotta Do</v>
+        <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>13 days ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
+        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-23</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>NeverAlways (Vol. 2)</v>
+        <v>13 days ago</v>
       </c>
       <c r="G109" t="str">
-        <v>3:26</v>
+        <v/>
       </c>
       <c r="H109" t="str">
-        <v>The Band CAMINO</v>
+        <v>Talking Heads</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/do-what-you-gotta-do/1887616173</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>Do What You Gotta Do - The Band CAMINO</v>
+        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Ego</v>
+        <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/ego/6769207667</v>
+        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-23</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Ego - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G110" t="str">
-        <v>2:53</v>
+        <v/>
       </c>
       <c r="H110" t="str">
-        <v>The Warning</v>
+        <v>Ellise</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/ego/6769207665</v>
+        <v/>
       </c>
       <c r="L110" t="str">
-        <v>Ego - The Warning</v>
+        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Light up (From the Netflix Documentary 'kylie')</v>
+        <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
+        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-23</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Light up (From the Netflix Documentary 'Kylie') - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G111" t="str">
-        <v>3:17</v>
+        <v/>
       </c>
       <c r="H111" t="str">
-        <v>Kylie Minogue</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/kylie-minogue/465031</v>
+        <v/>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/light-up-from-the-netflix-documentary-kylie/6768013505</v>
+        <v/>
       </c>
       <c r="L111" t="str">
-        <v>Light up (From the Netflix Documentary 'kylie') - Kylie Minogue</v>
+        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>All That Matters</v>
+        <v>From Down Here</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
+        <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-23</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>From Down Here - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:43</v>
+        <v>4:01</v>
       </c>
       <c r="H112" t="str">
-        <v>6LACK</v>
+        <v>Lola Young</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/lola-young/452271760</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/all-that-matters/1884792154</v>
+        <v>https://music.apple.com/us/album/from-down-here/6768357139</v>
       </c>
       <c r="L112" t="str">
-        <v>All That Matters - 6LACK</v>
+        <v>From Down Here - Lola Young</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Like A Virgin</v>
+        <v>the cure</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
+        <v>https://music.apple.com/us/song/the-cure/1889992123</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-23</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Terrified .</v>
+        <v>you seem pretty sad for a girl so in love</v>
       </c>
       <c r="G113" t="str">
-        <v>2:34</v>
+        <v>4:57</v>
       </c>
       <c r="H113" t="str">
-        <v>fakemink</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/like-a-virgin/6768157748</v>
+        <v>https://music.apple.com/us/album/the-cure/1889992111</v>
       </c>
       <c r="L113" t="str">
-        <v>Like A Virgin - fakemink</v>
+        <v>the cure - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>24 Hours</v>
+        <v>SS26</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/24-hours/6771060076</v>
+        <v>https://music.apple.com/us/song/ss26/6771061782</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-23</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>24 Hours - Single</v>
+        <v>SS26 - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:17</v>
+        <v>2:47</v>
       </c>
       <c r="H114" t="str">
-        <v>Stormzy</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/stormzy/394865154</v>
+        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/24-hours/6771060073</v>
+        <v>https://music.apple.com/us/album/ss26/6771061771</v>
       </c>
       <c r="L114" t="str">
-        <v>24 Hours - Stormzy</v>
+        <v>SS26 - Charli xcx</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>HOES (From Scary Movie)</v>
+        <v>White Flag</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
+        <v>https://music.apple.com/us/song/white-flag/1887627840</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-23</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>HOES (From Scary Movie) - Single</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G115" t="str">
-        <v>2:09</v>
+        <v>2:34</v>
       </c>
       <c r="H115" t="str">
-        <v>Lizzo</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/hoes-from-scary-movie/6770661290</v>
+        <v>https://music.apple.com/us/album/white-flag/1887627836</v>
       </c>
       <c r="L115" t="str">
-        <v>HOES (From Scary Movie) - Lizzo</v>
+        <v>White Flag - Vince Staples</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Ms. Tundra</v>
+        <v>Knew Better Part Two</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
+        <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-23</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Highway 79</v>
+        <v>Dangerous Woman (Tenth Anniversary Edition)</v>
       </c>
       <c r="G116" t="str">
-        <v>3:12</v>
+        <v>2:44</v>
       </c>
       <c r="H116" t="str">
-        <v>Ne-Yo</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/ms-tundra/6770614875</v>
+        <v>https://music.apple.com/us/album/knew-better-part-two/6770600996</v>
       </c>
       <c r="L116" t="str">
-        <v>Ms. Tundra - Ne-Yo</v>
+        <v>Knew Better Part Two - Ariana Grande</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>TARENTINO</v>
+        <v>Goals</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/tarentino/6769927265</v>
+        <v>https://music.apple.com/us/song/goals/6769251838</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-23</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>TARENTINO - Single</v>
+        <v>Goals (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:23</v>
+        <v>3:00</v>
       </c>
       <c r="H117" t="str">
-        <v>Labrinth</v>
+        <v>LISA</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/lisa/1583908668</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/tarentino/6769927262</v>
+        <v>https://music.apple.com/us/album/goals/6769251829</v>
       </c>
       <c r="L117" t="str">
-        <v>TARENTINO - Labrinth</v>
+        <v>Goals - LISA</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Daydreamin’</v>
+        <v>we should talk</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
+        <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-23</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>KONNAKOL (Deluxe)</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G118" t="str">
-        <v>2:58</v>
+        <v>3:04</v>
       </c>
       <c r="H118" t="str">
-        <v>ZAYN</v>
+        <v>Bleachers</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/daydreamin/6769559345</v>
+        <v>https://music.apple.com/us/album/we-should-talk/1872842313</v>
       </c>
       <c r="L118" t="str">
-        <v>Daydreamin’ - ZAYN</v>
+        <v>we should talk - Bleachers</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>End of an Era</v>
+        <v>Do What You Gotta Do</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
+        <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-23</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Dinner Party</v>
+        <v>NeverAlways (Vol. 2)</v>
       </c>
       <c r="G119" t="str">
-        <v>3:38</v>
+        <v>3:26</v>
       </c>
       <c r="H119" t="str">
-        <v>Niall Horan</v>
+        <v>The Band CAMINO</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/end-of-an-era/1884418567</v>
+        <v>https://music.apple.com/us/album/do-what-you-gotta-do/1887616173</v>
       </c>
       <c r="L119" t="str">
-        <v>End of an Era - Niall Horan</v>
+        <v>Do What You Gotta Do - The Band CAMINO</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Questions</v>
+        <v>Ego</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/questions/1871502847</v>
+        <v>https://music.apple.com/us/song/ego/6769207667</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-23</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Florescence</v>
+        <v>Ego - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:07</v>
+        <v>2:53</v>
       </c>
       <c r="H120" t="str">
-        <v>Maisie Peters</v>
+        <v>The Warning</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/questions/1871502372</v>
+        <v>https://music.apple.com/us/album/ego/6769207665</v>
       </c>
       <c r="L120" t="str">
-        <v>Questions - Maisie Peters</v>
+        <v>Ego - The Warning</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Heart Has To Work So Hard</v>
+        <v>Light up (From the Netflix Documentary 'kylie')</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
+        <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-23</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Heart Has To Work So Hard - Single</v>
+        <v>Light up (From the Netflix Documentary 'Kylie') - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:12</v>
+        <v>3:17</v>
       </c>
       <c r="H121" t="str">
-        <v>Blondshell</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/blondshell/1624592688</v>
+        <v>https://music.apple.com/us/artist/kylie-minogue/465031</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/heart-has-to-work-so-hard/1895982147</v>
+        <v>https://music.apple.com/us/album/light-up-from-the-netflix-documentary-kylie/6768013505</v>
       </c>
       <c r="L121" t="str">
-        <v>Heart Has To Work So Hard - Blondshell</v>
+        <v>Light up (From the Netflix Documentary 'kylie') - Kylie Minogue</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski)</v>
+        <v>All That Matters</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
+        <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-23</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski) - Single</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G122" t="str">
-        <v>3:44</v>
+        <v>3:43</v>
       </c>
       <c r="H122" t="str">
-        <v>Kygo</v>
+        <v>6LACK</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-your-mind-feat-dan-tyminski/6769007431</v>
+        <v>https://music.apple.com/us/album/all-that-matters/1884792154</v>
       </c>
       <c r="L122" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski) - Kygo</v>
+        <v>All That Matters - 6LACK</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>PERDISTE EL EMMY.</v>
+        <v>Like A Virgin</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
+        <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-23</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>OMAKASE</v>
+        <v>Terrified .</v>
       </c>
       <c r="G123" t="str">
-        <v>4:03</v>
+        <v>2:34</v>
       </c>
       <c r="H123" t="str">
-        <v>Álvaro Díaz</v>
+        <v>fakemink</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/perdiste-el-emmy/6771082594</v>
+        <v>https://music.apple.com/us/album/like-a-virgin/6768157748</v>
       </c>
       <c r="L123" t="str">
-        <v>PERDISTE EL EMMY. - Álvaro Díaz</v>
+        <v>Like A Virgin - fakemink</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Dosis</v>
+        <v>24 Hours</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/dosis/6762929729</v>
+        <v>https://music.apple.com/us/song/24-hours/6771060076</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-23</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>DOSIS</v>
+        <v>24 Hours - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:00</v>
+        <v>3:17</v>
       </c>
       <c r="H124" t="str">
-        <v>Xavi</v>
+        <v>Stormzy</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/stormzy/394865154</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/dosis/1895081885</v>
+        <v>https://music.apple.com/us/album/24-hours/6771060073</v>
       </c>
       <c r="L124" t="str">
-        <v>Dosis - Xavi</v>
+        <v>24 Hours - Stormzy</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Would U Still Love Me</v>
+        <v>HOES (From Scary Movie)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
+        <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-23</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Whitcomb vs. Flores - Single</v>
+        <v>HOES (From Scary Movie) - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:36</v>
+        <v>2:09</v>
       </c>
       <c r="H125" t="str">
-        <v>Diplo</v>
+        <v>Lizzo</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/would-u-still-love-me/6769907832</v>
+        <v>https://music.apple.com/us/album/hoes-from-scary-movie/6770661290</v>
       </c>
       <c r="L125" t="str">
-        <v>Would U Still Love Me - Diplo</v>
+        <v>HOES (From Scary Movie) - Lizzo</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Saving This Bottle</v>
+        <v>Ms. Tundra</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
+        <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-23</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Whitcomb vs. Flores - Single</v>
+        <v>Highway 79</v>
       </c>
       <c r="G126" t="str">
-        <v>3:05</v>
+        <v>3:12</v>
       </c>
       <c r="H126" t="str">
-        <v>Diplo</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/saving-this-bottle/6769907832</v>
+        <v>https://music.apple.com/us/album/ms-tundra/6770614875</v>
       </c>
       <c r="L126" t="str">
-        <v>Saving This Bottle - Diplo</v>
+        <v>Ms. Tundra - Ne-Yo</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>The Climb</v>
+        <v>TARENTINO</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/the-climb/6769546149</v>
+        <v>https://music.apple.com/us/song/tarentino/6769927265</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-23</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>The Climb - Single</v>
+        <v>TARENTINO - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:50</v>
+        <v>2:23</v>
       </c>
       <c r="H127" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Labrinth</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/the-climb/6769546147</v>
+        <v>https://music.apple.com/us/album/tarentino/6769927262</v>
       </c>
       <c r="L127" t="str">
-        <v>The Climb - Bailey Zimmerman</v>
+        <v>TARENTINO - Labrinth</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>everything tatted</v>
+        <v>Daydreamin’</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
+        <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-23</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>everything tatted - Single</v>
+        <v>KONNAKOL (Deluxe)</v>
       </c>
       <c r="G128" t="str">
-        <v>3:25</v>
+        <v>2:58</v>
       </c>
       <c r="H128" t="str">
-        <v>mgk</v>
+        <v>ZAYN</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/everything-tatted/6770773606</v>
+        <v>https://music.apple.com/us/album/daydreamin/6769559345</v>
       </c>
       <c r="L128" t="str">
-        <v>everything tatted - mgk</v>
+        <v>Daydreamin’ - ZAYN</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>BOOMPALA</v>
+        <v>End of an Era</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/boompala/1894802726</v>
+        <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-23</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>'PUREFLOW', Pt. 1</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G129" t="str">
-        <v>2:56</v>
+        <v>3:38</v>
       </c>
       <c r="H129" t="str">
-        <v>LE SSERAFIM</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/boompala/1894802719</v>
+        <v>https://music.apple.com/us/album/end-of-an-era/1884418567</v>
       </c>
       <c r="L129" t="str">
-        <v>BOOMPALA - LE SSERAFIM</v>
+        <v>End of an Era - Niall Horan</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Let Me Be In Your Arms</v>
+        <v>Questions</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
+        <v>https://music.apple.com/us/song/questions/1871502847</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-23</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>can we do it all again?</v>
+        <v>Florescence</v>
       </c>
       <c r="G130" t="str">
-        <v>3:13</v>
+        <v>3:07</v>
       </c>
       <c r="H130" t="str">
-        <v>Sonny Fodera</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/let-me-be-in-your-arms/1881610862</v>
+        <v>https://music.apple.com/us/album/questions/1871502372</v>
       </c>
       <c r="L130" t="str">
-        <v>Let Me Be In Your Arms - Sonny Fodera</v>
+        <v>Questions - Maisie Peters</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Eat, Work, Pray</v>
+        <v>Heart Has To Work So Hard</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
+        <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-23</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Eat, Work, Pray - Single</v>
+        <v>Heart Has To Work So Hard - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:28</v>
+        <v>3:12</v>
       </c>
       <c r="H131" t="str">
-     